--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -471,1928 +471,2555 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
+          <t>SAR evakuasi penumpang KM Mutiara Santosa 2 yang terbakar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
+          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
+          <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan telah mengevakuasi sebanyak 236 penumpang KM Mutiara Santosa 2 yang terbakar di perairan sebelah utara Pulau Madura, Minggu malam (2/8). Lima korban di antaranya meninggal dunia.(Hanif Nasrullah/Denno Ramdha Asmara/I Gusti Agung Ayu N)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
+          <t>https://www.antaranews.com/berita/5676992/sar-evakuasi-penumpang-km-mutiara-santosa-2-yang-terbakar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SAR-EVAKUASI-PENUMPANG-KM-MUTIARA-SANTOSA-2-YANG-TERBAKAR.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
+          <t>John Herdman tunggu hasil pemeriksaan Marselino jelang jamu Vietnam</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
+          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
+          <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu,(2/8), mengatakan kondisi kesehatan dan status gelandang Marselino Ferdinan dalam turnamen baru akan ditentukan setelah mendapat laporan lengkap dari tim medis. Hal itu disampaikan Herdman, usai Marselino kembali absen dalam latihan jelang laga Grup A Piala AFF 2026 melawan Timnas Vietnam pada Senin (2/8). (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
+          <t>https://www.antaranews.com/berita/5676945/john-herdman-tunggu-hasil-pemeriksaan-marselino-jelang-jamu-vietnam</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-TUNGGU-HASIL-PEMERIKSAAN-MARSELINO-JELANG-JAMU-VIETNAM.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
+          <t>John Herdman sebut laga RI Vs Vietnam ujian sangat berat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
+          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
+          <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu(2/8), mengaku pertandingan melawan Timnas Vietnam akan menjadi ujian sangat berat bagi skuad Garuda di Grup A Piala AFF 2026 (ASEAN Championship 2026). Menurut Herdman. laga tersebut juga merupakan peluang untuk mengambil alih kendali grup dan memastikan langkah ke babak berikutnya. (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
+          <t>https://www.antaranews.com/berita/5676944/john-herdman-sebut-laga-ri-vs-vietnam-ujian-sangat-berat</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-SEBUT-LAGA-RI-VS-VIETNAM-UJIAN-SANGAT-BERAT.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
+          <t>BI targetkan bawa wastra Sulsel ke pasar global</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
+          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
+          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Sulawesi Selatan bersama Pemerintah Provinsi Sulsel menyasar penguatan pasar produk kain tradisional (wastra) di tingkat nasional hingga mancanegara melalui "Wastra Heritage Market 2026". Hal itu dikemukakan Kepala Kantor Perwakilan BI Sulsel Rizki Ernadi Wimanda di Makassar, Minggu (2/8). (Suriani Mappong/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
+          <t>https://www.antaranews.com/berita/5676935/bi-targetkan-bawa-wastra-sulsel-ke-pasar-global</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BI-TARGETKAN-BAWA-WASTRA-SULSEL-KE-PASAR-GLOBAL.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
+          <t>Tong Tong Night Market masuk KEN, angkat UMKM dan budaya lokal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
+          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
+          <t>ANTARA - ‎Memasuki satu dekade penyelenggaraan, Tong Tong Night Market kembali meramaikan Kota Malang. Festival budaya dan kuliner yang masuk dalam Karisma Event Nusantara (KEN) itu tak hanya menghadirkan nuansa tempo dulu, tetapi juga menjadi ajang promosi puluhan UMKM sekaligus upaya melestarikan budaya lokal. (Achmad Saif Hajarani/Sandy Arizona/Gracia Simanjuntak)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
+          <t>https://www.antaranews.com/berita/5676927/tong-tong-night-market-masuk-ken-angkat-umkm-dan-budaya-lokal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_TONG-TONG-NIGHT-MARKET-MASUK-KEN-ANGKAT-UMKM-DAN-BUDAYA-LOKAL_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
+          <t>Perputaran ekonomi Piala Presiden 2026 tembus Rp70 miliar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
+          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
+          <t>ANTARA - Ketua Steering Committee Piala Presiden 2026 Maruarar Sirait menyebut perputaran ekonomi selama babak penyisihan turnamen di Surabaya dan Bandung telah mencapai lebih dari Rp70 miliar. Dampak ekonomi tersebut turut dirasakan pelaku usaha mikro, kecil, dan menengah (UMKM) serta dimanfaatkan untuk menyubsidi harga tiket pertandingan.
+(Hanif Nasrullah/Sandy Arizona/I Gusti Agung Ayu N)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
+          <t>https://www.antaranews.com/berita/5676895/perputaran-ekonomi-piala-presiden-2026-tembus-rp70-miliar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PERPUTARAN-EKONOMI-PIALA-PRESIDEN-2026-TEMBUS-RP70-MILIAR.jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
+          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
+          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
+          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
+          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
+          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
+          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>John Herdman akui Vietnam unggul secara taktik</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
 (Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
         <is>
           <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
         <is>
           <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
 (Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
         <is>
           <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
 (Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
         <is>
           <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
 (Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
         <is>
           <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
         <is>
           <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
         <is>
           <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
         <is>
           <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
         <is>
           <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
         <is>
           <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
 (Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
         <is>
           <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
         <is>
           <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
         <is>
           <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
         <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
         <is>
           <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
         <is>
           <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
         <is>
           <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
         <is>
           <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
         <is>
           <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
         <is>
           <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
         <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
         <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan hingga Senin (3/8), telah mengevakuasi 234 penumpang KMP Mutiara Sentosa 2 yang sebelumnya terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Sebanyak 113 korban di antaranya, kini telah tiba di Pelabuhan Tanjung Perak Surabaya setelah diangkut menggunakan kapal kargo Meratus Pematang Siantar.  (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677085/lebih-dari-100-korban-kmp-mutiara-sentosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>SAR evakuasi penumpang KM Mutiara Santosa 2 yang terbakar</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan telah mengevakuasi sebanyak 236 penumpang KM Mutiara Santosa 2 yang terbakar di perairan sebelah utara Pulau Madura, Minggu malam (2/8). Lima korban di antaranya meninggal dunia.(Hanif Nasrullah/Denno Ramdha Asmara/I Gusti Agung Ayu N)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676992/sar-evakuasi-penumpang-km-mutiara-santosa-2-yang-terbakar</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SAR-EVAKUASI-PENUMPANG-KM-MUTIARA-SANTOSA-2-YANG-TERBAKAR.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>John Herdman tunggu hasil pemeriksaan Marselino jelang jamu Vietnam</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu,(2/8), mengatakan kondisi kesehatan dan status gelandang Marselino Ferdinan dalam turnamen baru akan ditentukan setelah mendapat laporan lengkap dari tim medis. Hal itu disampaikan Herdman, usai Marselino kembali absen dalam latihan jelang laga Grup A Piala AFF 2026 melawan Timnas Vietnam pada Senin (2/8). (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676945/john-herdman-tunggu-hasil-pemeriksaan-marselino-jelang-jamu-vietnam</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-TUNGGU-HASIL-PEMERIKSAAN-MARSELINO-JELANG-JAMU-VIETNAM.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>John Herdman sebut laga RI Vs Vietnam ujian sangat berat</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>ANTARA - Pelatih Timnas Indonesia John Herdman di Jakarta, Minggu(2/8), mengaku pertandingan melawan Timnas Vietnam akan menjadi ujian sangat berat bagi skuad Garuda di Grup A Piala AFF 2026 (ASEAN Championship 2026). Menurut Herdman. laga tersebut juga merupakan peluang untuk mengambil alih kendali grup dan memastikan langkah ke babak berikutnya. (Anggah/Sandy Arizona/Gracia Simanjuntak)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676944/john-herdman-sebut-laga-ri-vs-vietnam-ujian-sangat-berat</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-SEBUT-LAGA-RI-VS-VIETNAM-UJIAN-SANGAT-BERAT.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>BI targetkan bawa wastra Sulsel ke pasar global</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Sulawesi Selatan bersama Pemerintah Provinsi Sulsel menyasar penguatan pasar produk kain tradisional (wastra) di tingkat nasional hingga mancanegara melalui "Wastra Heritage Market 2026". Hal itu dikemukakan Kepala Kantor Perwakilan BI Sulsel Rizki Ernadi Wimanda di Makassar, Minggu (2/8). (Suriani Mappong/Sandy Arizona/Gracia Simanjuntak)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676935/bi-targetkan-bawa-wastra-sulsel-ke-pasar-global</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BI-TARGETKAN-BAWA-WASTRA-SULSEL-KE-PASAR-GLOBAL.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Tong Tong Night Market masuk KEN, angkat UMKM dan budaya lokal</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ANTARA - ‎Memasuki satu dekade penyelenggaraan, Tong Tong Night Market kembali meramaikan Kota Malang. Festival budaya dan kuliner yang masuk dalam Karisma Event Nusantara (KEN) itu tak hanya menghadirkan nuansa tempo dulu, tetapi juga menjadi ajang promosi puluhan UMKM sekaligus upaya melestarikan budaya lokal. (Achmad Saif Hajarani/Sandy Arizona/Gracia Simanjuntak)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676927/tong-tong-night-market-masuk-ken-angkat-umkm-dan-budaya-lokal</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_TONG-TONG-NIGHT-MARKET-MASUK-KEN-ANGKAT-UMKM-DAN-BUDAYA-LOKAL_1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Perputaran ekonomi Piala Presiden 2026 tembus Rp70 miliar</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:45:01 +0700</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ANTARA - Ketua Steering Committee Piala Presiden 2026 Maruarar Sirait menyebut perputaran ekonomi selama babak penyisihan turnamen di Surabaya dan Bandung telah mencapai lebih dari Rp70 miliar. Dampak ekonomi tersebut turut dirasakan pelaku usaha mikro, kecil, dan menengah (UMKM) serta dimanfaatkan untuk menyubsidi harga tiket pertandingan.
-(Hanif Nasrullah/Sandy Arizona/I Gusti Agung Ayu N)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5676895/perputaran-ekonomi-piala-presiden-2026-tembus-rp70-miliar</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PERPUTARAN-EKONOMI-PIALA-PRESIDEN-2026-TEMBUS-RP70-MILIAR.jpg</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G59"/>
+  <autoFilter ref="A1:G78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -670,132 +670,132 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
+          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
+          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
+          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
+          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
+          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
+          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
+          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
+          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
+          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
         </is>
       </c>
     </row>
@@ -807,61 +807,61 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
+          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
         </is>
       </c>
     </row>
@@ -873,28 +873,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
+          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
+          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
         </is>
       </c>
     </row>
@@ -906,28 +906,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
+          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
         </is>
       </c>
     </row>
@@ -939,28 +939,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
+          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
@@ -972,28 +972,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>John Herdman akui Vietnam unggul secara taktik</t>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
+          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
+          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
         </is>
       </c>
     </row>
@@ -1005,28 +1005,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
+          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
+          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,28 +1038,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>John Herdman akui Vietnam unggul secara taktik</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
+          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
         </is>
       </c>
     </row>
@@ -1071,28 +1071,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
+          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
+          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
+          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
+          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
         </is>
       </c>
     </row>
@@ -1104,28 +1104,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
+          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
+          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
+          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
+          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
+          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
+          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
         </is>
       </c>
     </row>
@@ -1170,28 +1170,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
+          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
+          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
+          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
         </is>
       </c>
     </row>
@@ -1203,28 +1203,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
+          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
+          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
+          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
+          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
         </is>
       </c>
     </row>
@@ -1236,28 +1236,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
+          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
+          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
+          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
         </is>
       </c>
     </row>
@@ -1269,28 +1269,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
+          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
+          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
+          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
+          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
@@ -1302,127 +1302,127 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
+          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
+          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
+          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
+          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
+          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
+          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
         </is>
       </c>
     </row>
@@ -1434,28 +1434,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
         </is>
       </c>
     </row>
@@ -1467,28 +1467,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
         </is>
       </c>
     </row>
@@ -1500,28 +1500,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
         </is>
       </c>
     </row>
@@ -1533,28 +1533,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
         </is>
       </c>
     </row>
@@ -1566,95 +1566,95 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
 (Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
     </row>
@@ -1666,95 +1666,95 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
 (Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
     </row>
@@ -1766,162 +1766,162 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
+          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
+          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
 (Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
         <is>
           <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
 (Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
@@ -1933,28 +1933,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
+          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
@@ -1966,28 +1966,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
+          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
@@ -1999,28 +1999,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
+          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
+          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
     </row>
@@ -2032,28 +2032,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
+          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
+          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
         </is>
       </c>
     </row>
@@ -2065,28 +2065,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
+          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
+          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
+          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
         </is>
       </c>
     </row>
@@ -2098,28 +2098,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
+          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
+          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
+          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
         </is>
       </c>
     </row>
@@ -2131,28 +2131,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
+          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
+          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
         </is>
       </c>
     </row>
@@ -2164,28 +2164,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
+          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
         </is>
       </c>
     </row>
@@ -2197,28 +2197,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
         </is>
       </c>
     </row>
@@ -2263,95 +2263,95 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
+          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
 (Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
@@ -2363,28 +2363,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
+          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
+          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
+          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
@@ -2396,28 +2396,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
+          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
+          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
@@ -2429,28 +2429,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
+          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
+          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
@@ -2462,28 +2462,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
+          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
+          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
         </is>
       </c>
     </row>
@@ -2495,28 +2495,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
+          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
+          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
+          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
         </is>
       </c>
     </row>
@@ -2528,28 +2528,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
+          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
+          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
         </is>
       </c>
     </row>
@@ -2561,28 +2561,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
         </is>
       </c>
     </row>
@@ -2594,28 +2594,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
         </is>
       </c>
     </row>
@@ -2627,95 +2627,95 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
+          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
@@ -2727,28 +2727,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
+          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
@@ -2760,28 +2760,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
@@ -2793,28 +2793,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
@@ -2826,28 +2826,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
@@ -2859,129 +2859,129 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
@@ -2993,33 +2993,99 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
+          <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
+          <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan hingga Senin (3/8), telah mengevakuasi 234 penumpang KMP Mutiara Sentosa 2 yang sebelumnya terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Sebanyak 113 korban di antaranya, kini telah tiba di Pelabuhan Tanjung Perak Surabaya setelah diangkut menggunakan kapal kargo Meratus Pematang Siantar.  (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677085/lebih-dari-100-korban-kmp-mutiara-sentosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G78"/>
+  <autoFilter ref="A1:G80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -670,99 +670,99 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
+          <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
+          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
+          <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan hingga Senin (3/8), telah mengevakuasi 234 penumpang KMP Mutiara Sentosa 2 yang sebelumnya terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Sebanyak 113 korban di antaranya, kini telah tiba di Pelabuhan Tanjung Perak Surabaya setelah diangkut menggunakan kapal kargo Meratus Pematang Siantar.  (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
+          <t>https://www.antaranews.com/berita/5677085/lebih-dari-100-korban-kmp-mutiara-sentosa-2-tiba-di-tanjung-perak</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
+          <t>Wali kota tawarkan Makassar jadi hub investasi Indonesia Timur</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
+          <t>Tue, 04 Aug 2026 04:46:09 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
+          <t>Wali Kota Makassar Munafri Arifuddin menawarkan kota itu sebagai hub investasi di kawasan Indonesia Timur (Intim) pada ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
+          <t>https://www.antaranews.com/berita/5678604/wali-kota-tawarkan-makassar-jadi-hub-investasi-indonesia-timur</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
+          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
+          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
+          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
         </is>
       </c>
     </row>
@@ -774,28 +774,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
+          <t>John Herdman pastikan Marselino absen hingga akhir Piala AFF 2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
+          <t>Tue, 04 Aug 2026 04:14:04 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
+          <t>Pelatih tim nasional Indonesia John Herdman memastikan gelandang Marselino Ferdinan bakal absen hingga akhir turnamen ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
+          <t>https://www.antaranews.com/berita/5678600/john-herdman-pastikan-marselino-absen-hingga-akhir-piala-aff-2026</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
         </is>
       </c>
     </row>
@@ -807,127 +807,127 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
+          <t>Tue, 04 Aug 2026 04:02:18 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
+          <t>https://www.antaranews.com/video/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
+          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
+          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
+          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
         </is>
       </c>
     </row>
@@ -939,28 +939,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
+          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
+          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
+          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
+          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
         </is>
       </c>
     </row>
@@ -972,61 +972,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
+          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,28 +1038,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>John Herdman akui Vietnam unggul secara taktik</t>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
+          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
+          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
         </is>
       </c>
     </row>
@@ -1071,28 +1071,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
+          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
+          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
         </is>
       </c>
     </row>
@@ -1104,28 +1104,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
+          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
+          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
+          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
         </is>
       </c>
     </row>
@@ -1170,28 +1170,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
+          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
+          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
         </is>
       </c>
     </row>
@@ -1203,28 +1203,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
+          <t>John Herdman akui Vietnam unggul secara taktik</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
+          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
+          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
         </is>
       </c>
     </row>
@@ -1236,28 +1236,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
+          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
+          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
+          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
         </is>
       </c>
     </row>
@@ -1269,28 +1269,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
+          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
+          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
         </is>
       </c>
     </row>
@@ -1302,28 +1302,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
+          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
+          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
+          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
+          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
         </is>
       </c>
     </row>
@@ -1335,28 +1335,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
+          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
+          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
+          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
+          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
         </is>
       </c>
     </row>
@@ -1368,226 +1368,226 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
+          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
+          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
+          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
+          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
+          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
+          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
         </is>
       </c>
     </row>
@@ -1599,28 +1599,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
         </is>
       </c>
     </row>
@@ -1632,494 +1632,494 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
 (Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
         <is>
           <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
         <is>
           <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
 (Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
         <is>
           <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
 (Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
         <is>
           <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
 (Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
         </is>
       </c>
     </row>
@@ -2131,28 +2131,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
+          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
@@ -2164,28 +2164,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
+          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
@@ -2197,28 +2197,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
+          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
+          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
     </row>
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
+          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
         </is>
       </c>
     </row>
@@ -2263,28 +2263,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
         </is>
       </c>
     </row>
@@ -2296,28 +2296,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
         </is>
       </c>
     </row>
@@ -2329,227 +2329,227 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
+          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
 (Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
         </is>
       </c>
     </row>
@@ -2561,28 +2561,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
+          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
+          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
+          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
@@ -2594,28 +2594,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
+          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
+          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
@@ -2627,28 +2627,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
@@ -2660,28 +2660,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
         </is>
       </c>
     </row>
@@ -2693,227 +2693,227 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
+          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
     </row>
@@ -2925,167 +2925,332 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Lebih dari 100 korban KMP Mutiara Sentosa 2 tiba di Tanjung Perak</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 03:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>ANTARA - Tim pencarian dan pertolongan (SAR) gabungan hingga Senin (3/8), telah mengevakuasi 234 penumpang KMP Mutiara Sentosa 2 yang sebelumnya terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Sebanyak 113 korban di antaranya, kini telah tiba di Pelabuhan Tanjung Perak Surabaya setelah diangkut menggunakan kapal kargo Meratus Pematang Siantar.  (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677085/lebih-dari-100-korban-kmp-mutiara-sentosa-2-tiba-di-tanjung-perak</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G80"/>
+  <autoFilter ref="A1:G85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -708,28 +708,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wali kota tawarkan Makassar jadi hub investasi Indonesia Timur</t>
+          <t>Fulham resmi rampungkan transfer Gonzalo Garcia dari Real Madrid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:46:09 +0700</t>
+          <t>Tue, 04 Aug 2026 05:48:40 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wali Kota Makassar Munafri Arifuddin menawarkan kota itu sebagai hub investasi di kawasan Indonesia Timur (Intim) pada ...</t>
+          <t>Fulham resmi merampungkan transfer penyerang muda Gonzalo Garcia dari Real Madrid pada musim panas 2026
+"Dengan ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678604/wali-kota-tawarkan-makassar-jadi-hub-investasi-indonesia-timur</t>
+          <t>https://www.antaranews.com/berita/5678609/fulham-resmi-rampungkan-transfer-gonzalo-garcia-dari-real-madrid</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000042507.jpg</t>
         </is>
       </c>
     </row>
@@ -741,28 +742,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
+          <t>Pengamat nilai cara Seskab rawat jaringan perlu dicontoh politisi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
+          <t>Tue, 04 Aug 2026 05:44:45 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
+          <t>Pengamat politik Hendri Satrio alias Hensa menilai cara-cara Sekretaris Kabinet (Seskab) Teddy Indra Wijaya dalam ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
+          <t>https://www.antaranews.com/berita/5678608/pengamat-nilai-cara-seskab-rawat-jaringan-perlu-dicontoh-politisi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/11/20/Zulkieflimansyah.jpg</t>
         </is>
       </c>
     </row>
@@ -774,28 +775,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>John Herdman pastikan Marselino absen hingga akhir Piala AFF 2026</t>
+          <t>GMR buka peluang perluas investasi di bandara lain Indonesia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:14:04 +0700</t>
+          <t>Tue, 04 Aug 2026 05:00:12 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional Indonesia John Herdman memastikan gelandang Marselino Ferdinan bakal absen hingga akhir turnamen ...</t>
+          <t>GMR Airports Limited (GMR Airports), perusahaan operator bandara asal India, membuka peluang untuk memperluas ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678600/john-herdman-pastikan-marselino-absen-hingga-akhir-piala-aff-2026</t>
+          <t>https://www.antaranews.com/berita/5678607/gmr-buka-peluang-perluas-investasi-di-bandara-lain-indonesia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/09a99626-b25f-41b2-8db2-de5355d06e86.jpeg</t>
         </is>
       </c>
     </row>
@@ -807,28 +808,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+          <t>Wali kota tawarkan Makassar jadi hub investasi Indonesia Timur</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:02:18 +0700</t>
+          <t>Tue, 04 Aug 2026 04:46:09 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A ...</t>
+          <t>Wali Kota Makassar Munafri Arifuddin menawarkan kota itu sebagai hub investasi di kawasan Indonesia Timur (Intim) pada ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+          <t>https://www.antaranews.com/berita/5678604/wali-kota-tawarkan-makassar-jadi-hub-investasi-indonesia-timur</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
         </is>
       </c>
     </row>
@@ -840,94 +841,94 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
+          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
+          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
+          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
+          <t>John Herdman pastikan Marselino absen hingga akhir Piala AFF 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
+          <t>Tue, 04 Aug 2026 04:14:04 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
+          <t>Pelatih tim nasional Indonesia John Herdman memastikan gelandang Marselino Ferdinan bakal absen hingga akhir turnamen ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
+          <t>https://www.antaranews.com/berita/5678600/john-herdman-pastikan-marselino-absen-hingga-akhir-piala-aff-2026</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
+          <t>Tue, 04 Aug 2026 04:02:18 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
+          <t>https://www.antaranews.com/video/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
         </is>
       </c>
     </row>
@@ -939,61 +940,61 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
+          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
+          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
+          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
+          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
+          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1005,28 +1006,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,28 +1039,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
+          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
+          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
         </is>
       </c>
     </row>
@@ -1071,61 +1072,61 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
+          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1138,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
+          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
         </is>
       </c>
     </row>
@@ -1170,28 +1171,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
+          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
         </is>
       </c>
     </row>
@@ -1203,28 +1204,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>John Herdman akui Vietnam unggul secara taktik</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
+          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
+          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
@@ -1236,28 +1237,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
+          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
+          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
         </is>
       </c>
     </row>
@@ -1269,28 +1270,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
+          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
         </is>
       </c>
     </row>
@@ -1302,28 +1303,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
+          <t>John Herdman akui Vietnam unggul secara taktik</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
+          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
+          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
         </is>
       </c>
     </row>
@@ -1335,28 +1336,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
+          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
+          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
+          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
+          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
         </is>
       </c>
     </row>
@@ -1368,28 +1369,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
+          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
+          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
         </is>
       </c>
     </row>
@@ -1401,28 +1402,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
+          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
+          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
+          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
         </is>
       </c>
     </row>
@@ -1434,28 +1435,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
+          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
+          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
+          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
+          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
         </is>
       </c>
     </row>
@@ -1467,28 +1468,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
+          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
+          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
+          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
+          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
         </is>
       </c>
     </row>
@@ -1500,28 +1501,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
+          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
+          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
+          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
         </is>
       </c>
     </row>
@@ -1533,160 +1534,160 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
+          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
+          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
+          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
+          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
+          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
+          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
         </is>
       </c>
     </row>
@@ -1698,28 +1699,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
         </is>
       </c>
     </row>
@@ -1731,28 +1732,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
         </is>
       </c>
     </row>
@@ -1764,28 +1765,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
         </is>
       </c>
     </row>
@@ -1797,28 +1798,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
         </is>
       </c>
     </row>
@@ -1830,395 +1831,395 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
 (Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
         <is>
           <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
         <is>
           <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
 (Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
         <is>
           <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
 (Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
         <is>
           <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
 (Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
     </row>
@@ -2230,28 +2231,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
+          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
@@ -2263,28 +2264,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
+          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
@@ -2296,28 +2297,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
+          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
+          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
     </row>
@@ -2329,28 +2330,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
+          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
+          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
+          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
         </is>
       </c>
     </row>
@@ -2362,28 +2363,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
+          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
+          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
+          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
         </is>
       </c>
     </row>
@@ -2395,28 +2396,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
+          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
+          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
         </is>
       </c>
     </row>
@@ -2428,28 +2429,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
+          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
         </is>
       </c>
     </row>
@@ -2461,28 +2462,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
         </is>
       </c>
     </row>
@@ -2494,28 +2495,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
         </is>
       </c>
     </row>
@@ -2527,128 +2528,128 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
 (Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
@@ -2660,28 +2661,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
+          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
+          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
@@ -2693,28 +2694,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
+          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
+          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
@@ -2726,28 +2727,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
+          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
+          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
@@ -2759,28 +2760,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
+          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
+          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
         </is>
       </c>
     </row>
@@ -2792,28 +2793,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
+          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
+          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
         </is>
       </c>
     </row>
@@ -2825,28 +2826,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
         </is>
       </c>
     </row>
@@ -2858,28 +2859,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
         </is>
       </c>
     </row>
@@ -2891,128 +2892,128 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
+          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
@@ -3024,28 +3025,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
@@ -3057,28 +3058,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
@@ -3090,28 +3091,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
@@ -3123,134 +3124,233 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:55:02 +0700</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G85"/>
+  <autoFilter ref="A1:G88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -708,326 +708,326 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fulham resmi rampungkan transfer Gonzalo Garcia dari Real Madrid</t>
+          <t>Jalan pulang para srikandi jalanan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:48:40 +0700</t>
+          <t>Tue, 04 Aug 2026 06:53:36 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Di tengah lalu lintas Kota Surabaya yang nyaris tak pernah berhenti, semakin banyak perempuan mengenakan jaket ojek ...</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678627/jalan-pulang-para-srikandi-jalanan</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/dok.Pelatihan-sablon-Ojol-perempuan-Surabaya-4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DKI kemarin, inflasi tahunan Jakarta hingga potensi aksi demonstrasi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:41:11 +0700</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sejumlah berita seputar DKI Jakarta yang terjadi pada Senin (3/8) kemarin, mulai dari inflasi tahunan Jakarta hingga ...</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678625/dki-kemarin-inflasi-tahunan-jakarta-hingga-potensi-aksi-demonstrasi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000313673.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Eksotis bahari Maratua, warisan laut bagi Nusantara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:37:43 +0700</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Meresapi keanggunan laut Nusantara serasa merenungi betapa agung karya Sang Pencipta yang terpancar melalui warisan ...</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678621/eksotis-bahari-maratuawarisan-laut-bagi-nusantara</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001881799.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kriminal kemarin, hoaks ajakan demonstrasi hingga lansia disekap</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:36:29 +0700</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sejumlah peristiwa berkaitan dengan tindak kriminal dan keamanan menghiasi Jakarta yang terjadi pada Senin (3/8) ...</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678620/kriminal-kemarin-hoaks-ajakan-demonstrasi-hingga-lansia-disekap</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_192143033.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>photo, terkini</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, ...</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Menembus tembok stigma, memulihkan luka anak</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:11:55 +0700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Tidak ada anak yang lahir dengan pilihan peta nasib di genggamannya. Sebagian beruntung tumbuh dalam rumah yang penuh ...</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678616/menembus-tembok-stigma-memulihkan-luka-anak</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-07-27-at-12.27.07.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kontingen Indonesia di Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HRTA kantongi laba Rp700,01 M pada semester I 2026, naik 100,86 persen</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:54:06 +0700</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PT Hartadinata Abadi Tbk (HRTA) membukukan laba bersih sebesar Rp700,01 miliar pada semester I 2026, meningkat 100,86 ...</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678611/hrta-kantongi-laba-rp70001-m-pada-semester-i-2026-naik-10086-persen</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-13.37.37.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fulham resmi rampungkan transfer Gonzalo Garcia dari Real Madrid</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:48:40 +0700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Fulham resmi merampungkan transfer penyerang muda Gonzalo Garcia dari Real Madrid pada musim panas 2026
 "Dengan ...</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678609/fulham-resmi-rampungkan-transfer-gonzalo-garcia-dari-real-madrid</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000042507.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Pengamat nilai cara Seskab rawat jaringan perlu dicontoh politisi</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:44:45 +0700</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Pengamat politik Hendri Satrio alias Hensa menilai cara-cara Sekretaris Kabinet (Seskab) Teddy Indra Wijaya dalam ...</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678608/pengamat-nilai-cara-seskab-rawat-jaringan-perlu-dicontoh-politisi</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/11/20/Zulkieflimansyah.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>GMR buka peluang perluas investasi di bandara lain Indonesia</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:00:12 +0700</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>GMR Airports Limited (GMR Airports), perusahaan operator bandara asal India, membuka peluang untuk memperluas ...</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678607/gmr-buka-peluang-perluas-investasi-di-bandara-lain-indonesia</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/09a99626-b25f-41b2-8db2-de5355d06e86.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Wali kota tawarkan Makassar jadi hub investasi Indonesia Timur</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:46:09 +0700</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Wali Kota Makassar Munafri Arifuddin menawarkan kota itu sebagai hub investasi di kawasan Indonesia Timur (Intim) pada ...</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678604/wali-kota-tawarkan-makassar-jadi-hub-investasi-indonesia-timur</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>John Herdman pastikan Marselino absen hingga akhir Piala AFF 2026</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:14:04 +0700</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Pelatih tim nasional Indonesia John Herdman memastikan gelandang Marselino Ferdinan bakal absen hingga akhir turnamen ...</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678600/john-herdman-pastikan-marselino-absen-hingga-akhir-piala-aff-2026</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:02:18 +0700</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A ...</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/video/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis, terkini</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
+          <t>Pengamat nilai cara Seskab rawat jaringan perlu dicontoh politisi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
+          <t>Tue, 04 Aug 2026 05:44:45 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
+          <t>Pengamat politik Hendri Satrio alias Hensa menilai cara-cara Sekretaris Kabinet (Seskab) Teddy Indra Wijaya dalam ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
+          <t>https://www.antaranews.com/berita/5678608/pengamat-nilai-cara-seskab-rawat-jaringan-perlu-dicontoh-politisi</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/11/20/Zulkieflimansyah.jpg</t>
         </is>
       </c>
     </row>
@@ -1039,28 +1039,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
+          <t>GMR buka peluang perluas investasi di bandara lain Indonesia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
+          <t>Tue, 04 Aug 2026 05:00:12 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
+          <t>GMR Airports Limited (GMR Airports), perusahaan operator bandara asal India, membuka peluang untuk memperluas ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
+          <t>https://www.antaranews.com/berita/5678607/gmr-buka-peluang-perluas-investasi-di-bandara-lain-indonesia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/09a99626-b25f-41b2-8db2-de5355d06e86.jpeg</t>
         </is>
       </c>
     </row>
@@ -1072,61 +1072,61 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
+          <t>Wali kota tawarkan Makassar jadi hub investasi Indonesia Timur</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
+          <t>Tue, 04 Aug 2026 04:46:09 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
+          <t>Wali Kota Makassar Munafri Arifuddin menawarkan kota itu sebagai hub investasi di kawasan Indonesia Timur (Intim) pada ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678604/wali-kota-tawarkan-makassar-jadi-hub-investasi-indonesia-timur</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini, top-news</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
         </is>
       </c>
     </row>
@@ -1138,28 +1138,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>John Herdman pastikan Marselino absen hingga akhir Piala AFF 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
+          <t>Tue, 04 Aug 2026 04:14:04 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
+          <t>Pelatih tim nasional Indonesia John Herdman memastikan gelandang Marselino Ferdinan bakal absen hingga akhir turnamen ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678600/john-herdman-pastikan-marselino-absen-hingga-akhir-piala-aff-2026</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
         </is>
       </c>
     </row>
@@ -1171,28 +1171,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
+          <t>Tue, 04 Aug 2026 04:02:18 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/video/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
         </is>
       </c>
     </row>
@@ -1204,94 +1204,94 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
+          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
+          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
+          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
+          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
+          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
+          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
         </is>
       </c>
     </row>
@@ -1303,28 +1303,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>John Herdman akui Vietnam unggul secara taktik</t>
+          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
+          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
+          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
+          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
         </is>
       </c>
     </row>
@@ -1336,61 +1336,61 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
+          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
+          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
         </is>
       </c>
     </row>
@@ -1402,28 +1402,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
+          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
+          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
         </is>
       </c>
     </row>
@@ -1435,28 +1435,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
+          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
+          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
         </is>
       </c>
     </row>
@@ -1468,28 +1468,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
+          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
+          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
@@ -1501,28 +1501,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
+          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
+          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
         </is>
       </c>
     </row>
@@ -1534,28 +1534,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
+          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
+          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
         </is>
       </c>
     </row>
@@ -1567,28 +1567,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
+          <t>John Herdman akui Vietnam unggul secara taktik</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
+          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
+          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
         </is>
       </c>
     </row>
@@ -1600,28 +1600,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
+          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
+          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
+          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
+          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
         </is>
       </c>
     </row>
@@ -1633,857 +1633,857 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
+          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
+          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
+          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
+          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
+          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
 (Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
         <is>
           <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
         <is>
           <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
 (Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
         <is>
           <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
 (Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
         <is>
           <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
 (Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
         </is>
       </c>
     </row>
@@ -2495,28 +2495,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
+          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
@@ -2528,28 +2528,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
@@ -2561,28 +2561,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
     </row>
@@ -2594,28 +2594,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
         </is>
       </c>
     </row>
@@ -2627,293 +2627,293 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
+          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
 (Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
         </is>
       </c>
     </row>
@@ -2925,28 +2925,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
@@ -2958,28 +2958,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
@@ -2991,366 +2991,630 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
         <is>
           <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
         <is>
           <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
         <is>
           <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
         <is>
           <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
         <is>
           <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
         <is>
           <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
         <is>
           <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
         <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:50:01 +0700</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G88"/>
+  <autoFilter ref="A1:G96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -708,28 +708,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jalan pulang para srikandi jalanan</t>
+          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:53:36 +0700</t>
+          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Di tengah lalu lintas Kota Surabaya yang nyaris tak pernah berhenti, semakin banyak perempuan mengenakan jaket ojek ...</t>
+          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678627/jalan-pulang-para-srikandi-jalanan</t>
+          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/dok.Pelatihan-sablon-Ojol-perempuan-Surabaya-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
@@ -741,61 +741,61 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DKI kemarin, inflasi tahunan Jakarta hingga potensi aksi demonstrasi</t>
+          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:41:11 +0700</t>
+          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sejumlah berita seputar DKI Jakarta yang terjadi pada Senin (3/8) kemarin, mulai dari inflasi tahunan Jakarta hingga ...</t>
+          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678625/dki-kemarin-inflasi-tahunan-jakarta-hingga-potensi-aksi-demonstrasi</t>
+          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000313673.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eksotis bahari Maratua, warisan laut bagi Nusantara</t>
+          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:37:43 +0700</t>
+          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Meresapi keanggunan laut Nusantara serasa merenungi betapa agung karya Sang Pencipta yang terpancar melalui warisan ...</t>
+          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678621/eksotis-bahari-maratuawarisan-laut-bagi-nusantara</t>
+          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001881799.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
         </is>
       </c>
     </row>
@@ -807,61 +807,61 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kriminal kemarin, hoaks ajakan demonstrasi hingga lansia disekap</t>
+          <t>Kemarin, manfaat timun untuk tubuh hingga rencana Ariana Grande rehat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:36:29 +0700</t>
+          <t>Tue, 04 Aug 2026 08:42:04 +0700</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sejumlah peristiwa berkaitan dengan tindak kriminal dan keamanan menghiasi Jakarta yang terjadi pada Senin (3/8) ...</t>
+          <t>Sejumlah berita menarik ditayangkan di kanal hiburan, gaya hidup, otomotif, dan teknologi, pada Senin (3/8) seperti ...</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678620/kriminal-kemarin-hoaks-ajakan-demonstrasi-hingga-lansia-disekap</t>
+          <t>https://www.antaranews.com/berita/5678661/kemarin-manfaat-timun-untuk-tubuh-hingga-rencana-ariana-grande-rehat</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_192143033.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/01/IMG_0569.jpeg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+          <t>Satgas Yonif 511/DY evakuasi dua orang selamat dari serangan KKB di Tolikara</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+          <t>Tue, 04 Aug 2026 08:36:02 +0700</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, ...</t>
+          <t>Satuan Tugas Pengamanan Perbatasan Yonif 511/DY berhasil mengevakuasi dua orang yang selamat dari serangan ...</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+          <t>https://www.antaranews.com/berita/5678660/satgas-yonif-511-dy-evakuasi-dua-orang-selamat-dari-serangan-kkb-di-tolikara</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-09.25.32.jpeg</t>
         </is>
       </c>
     </row>
@@ -873,755 +873,755 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Menembus tembok stigma, memulihkan luka anak</t>
+          <t>Janice kandas di WTA 1000 Toronto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:11:55 +0700</t>
+          <t>Tue, 04 Aug 2026 08:33:11 +0700</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tidak ada anak yang lahir dengan pilihan peta nasib di genggamannya. Sebagian beruntung tumbuh dalam rumah yang penuh ...</t>
+          <t>Petenis Indonesia Janice Tjen memberikan perlawanan sengit sebelum dikalahkan Liudmila Samsonova pada babak pertama WTA ...</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678616/menembus-tembok-stigma-memulihkan-luka-anak</t>
+          <t>https://www.antaranews.com/berita/5678659/janice-kandas-di-wta-1000-toronto</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-07-27-at-12.27.07.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/22/Janice.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kontingen Indonesia di Asian Games 2026</t>
+          <t>Kemnaker ajak masyarakat pacu kompetensi di Pelatihan Vokasi Nasional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
+          <t>Tue, 04 Aug 2026 08:15:02 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengajak masyarakat untuk meningkatkan kompetensi melalui Pelatihan Vokasi ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
+          <t>https://www.antaranews.com/berita/5678657/kemnaker-ajak-masyarakat-pacu-kompetensi-di-pelatihan-vokasi-nasional</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/kesiapan-tenaga-kerja-di-balai-pelatihan-kerja-semarang-2828648.jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HRTA kantongi laba Rp700,01 M pada semester I 2026, naik 100,86 persen</t>
+          <t>Humaniora kemarin, status keracunan MBG hingga 1 tahun Sekolah Rakyat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:54:06 +0700</t>
+          <t>Tue, 04 Aug 2026 08:14:30 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PT Hartadinata Abadi Tbk (HRTA) membukukan laba bersih sebesar Rp700,01 miliar pada semester I 2026, meningkat 100,86 ...</t>
+          <t>Sejumlah berita humaniora pada Senin yang mendapat perhatian pembaca dan masih menarik untuk disimak pagi ini, mulai ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678611/hrta-kantongi-laba-rp70001-m-pada-semester-i-2026-naik-10086-persen</t>
+          <t>https://www.antaranews.com/berita/5678655/humaniora-kemarin-status-keracunan-mbg-hingga-1-tahun-sekolah-rakyat</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-13.37.37.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/menteri-sosial-tinjau-mpls-di-srt-i-sukoharjo-2831859.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fulham resmi rampungkan transfer Gonzalo Garcia dari Real Madrid</t>
+          <t>ICPI soroti tantangan sektor pariwisata RI hadapi dinamika global</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:48:40 +0700</t>
+          <t>Tue, 04 Aug 2026 08:07:43 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Ikatan Cendikiawan Pariwisata Indonesia (ICPI) menyoroti sejumlah tantangan pariwisata Indonesia dalam menghadapi ...</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678652/icpi-soroti-tantangan-sektor-pariwisata-ri-hadapi-dinamika-global</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/26/kunjungan-turis-asing-ke-ntb-tumbuh-106-persen-1jdoh-dom.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial, terkini</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CORE: Penilaian kredit alternatif dapat perluas pembiayaan UMKM</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:58:42 +0700</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai pemanfaatan penilaian kredit ...</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678651/core-penilaian-kredit-alternatif-dapat-perluas-pembiayaan-umkm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/realisasi-penyaluran-kur-umkm-2832719.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cuaca di kota-kota besar diperkirakan cerah berawan hingga berawan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:57:38 +0700</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan kondisi cuaca di kota-kota besar di Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678648/cuaca-di-kota-kota-besar-diperkirakan-cerah-berawan-hingga-berawan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/09/22/Cuaca-Jakarta-290812-DDS-2.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Selasa, layanan Samsat Keliling tersedia di 14 wilayah Jadetabek</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:52:34 +0700</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menyediakan layanan Sistem Administrasi Manunggal Satu Atap (Samsat) Keliling untuk membantu para ...</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678647/selasa-layanan-samsat-keliling-tersedia-di-14-wilayah-jadetabek</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/SAMSAT-Keliling-04082026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Selasa, layanan SIM keliling tersedia di lima lokasi Jakarta</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:51:07 +0700</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Direktorat Lalu Lintas Polda Metro Jaya membuka layanan Surat Izin Mengemudi (SIM) Keliling bagi masyarakat yang ...</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678645/selasa-layanan-sim-keliling-tersedia-di-lima-lokasi-jakarta</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/SIM-Keliling-04082026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pelanggan KA Makassar--Parepare Naik 13,62 Persen, KAI Perluas Konektivitas dan Kesempatan Masyarakat Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:40:47 +0700</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) mencatat pertumbuhan positif layanan KA Makassar–Parepare sepanjang ...</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678641/pelanggan-ka-makassar-parepare-naik-1362-persen-kai-perluas-konektivitas-dan-kesempatan-masyarakat-sulawesi-selatan</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001085218.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Angkutan Petikemas KAI Naik 20,28 Persen, Perkuat Konektivitas Rel–Pelabuhan bagi Logistik Nasional</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:35:21 +0700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat layanan angkutan petikemas sebagai bagian dari sistem logistik ...</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678640/angkutan-petikemas-kai-naik-2028-persen-perkuat-konektivitas-rel-pelabuhan-bagi-logistik-nasional</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001085217.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BMKG prakirakan Jaksel dan Jaktim hujan ringan pada Selasa malam</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:20:02 +0700</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan wilayah Jakarta Selatan dan Jakarta Timur diguyur ...</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678639/bmkg-prakirakan-jaksel-dan-jaktim-hujan-ringan-pada-selasa-malam</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CuacaJakarta160710.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ekonomi kemarin, harga bensin turun hingga kredit perbankan tumbuh</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:19:27 +0700</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Berbagai peristiwa ekonomi diberitakan Kantor Berita ANTARA pada Senin (3/8), mulai dari penurunan harga bensin pada ...</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678637/ekonomi-kemarin-harga-bensin-turun-hingga-kredit-perbankan-tumbuh</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2016/01/20160105492.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Praktisi: Material bangunan berkarakter visual kian diminati konsumen</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:07:17 +0700</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Praktisi industri bangunan, Jali Wijaya, mengatakan seiring berkembangnya tren hunian yang semakin personal, material ...</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678635/praktisi-material-bangunan-berkarakter-visual-kian-diminati-konsumen</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/pearlescent-effect.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BPS sebut El Nino ubah pola harga pangan di Nabire</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:00:42 +0700</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) Kabupaten Nabire menyebut fenomena El Nino mengubah pola harga pangan di daerah itu ...</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678631/bps-sebut-el-nino-ubah-pola-harga-pangan-di-nabire</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-06-15-at-15.40.12.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Jalan pulang para srikandi jalanan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:53:36 +0700</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Di tengah lalu lintas Kota Surabaya yang nyaris tak pernah berhenti, semakin banyak perempuan mengenakan jaket ojek ...</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678627/jalan-pulang-para-srikandi-jalanan</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/dok.Pelatihan-sablon-Ojol-perempuan-Surabaya-4.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DKI kemarin, inflasi tahunan Jakarta hingga potensi aksi demonstrasi</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:41:11 +0700</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sejumlah berita seputar DKI Jakarta yang terjadi pada Senin (3/8) kemarin, mulai dari inflasi tahunan Jakarta hingga ...</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678625/dki-kemarin-inflasi-tahunan-jakarta-hingga-potensi-aksi-demonstrasi</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000313673.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Eksotis bahari Maratua,warisan laut bagi Nusantara</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:37:43 +0700</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Meresapi keanggunan laut Nusantara serasa merenungi betapa agung karya Sang Pencipta yang terpancar melalui warisan ...</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678621/eksotis-bahari-maratuawarisan-laut-bagi-nusantara</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001881799.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kriminal kemarin, hoaks ajakan demonstrasi hingga lansia disekap</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:36:29 +0700</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sejumlah peristiwa berkaitan dengan tindak kriminal dan keamanan menghiasi Jakarta yang terjadi pada Senin (3/8) ...</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678620/kriminal-kemarin-hoaks-ajakan-demonstrasi-hingga-lansia-disekap</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_192143033.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>photo, terkini</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, ...</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Menembus tembok stigma, memulihkan luka anak</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:11:55 +0700</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Tidak ada anak yang lahir dengan pilihan peta nasib di genggamannya. Sebagian beruntung tumbuh dalam rumah yang penuh ...</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678616/menembus-tembok-stigma-memulihkan-luka-anak</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-07-27-at-12.27.07.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>terkini, top-news</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kontingen Indonesia di Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HRTA kantongi laba Rp700,01 M pada semester I 2026, naik 100,86 persen</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:54:06 +0700</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PT Hartadinata Abadi Tbk (HRTA) membukukan laba bersih sebesar Rp700,01 miliar pada semester I 2026, meningkat 100,86 ...</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678611/hrta-kantongi-laba-rp70001-m-pada-semester-i-2026-naik-10086-persen</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-13.37.37.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fulham resmi rampungkan transfer Gonzalo Garcia dari Real Madrid</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 05:48:40 +0700</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Fulham resmi merampungkan transfer penyerang muda Gonzalo Garcia dari Real Madrid pada musim panas 2026
 "Dengan ...</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678609/fulham-resmi-rampungkan-transfer-gonzalo-garcia-dari-real-madrid</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000042507.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Pengamat nilai cara Seskab rawat jaringan perlu dicontoh politisi</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:44:45 +0700</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Pengamat politik Hendri Satrio alias Hensa menilai cara-cara Sekretaris Kabinet (Seskab) Teddy Indra Wijaya dalam ...</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678608/pengamat-nilai-cara-seskab-rawat-jaringan-perlu-dicontoh-politisi</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/11/20/Zulkieflimansyah.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>GMR buka peluang perluas investasi di bandara lain Indonesia</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 05:00:12 +0700</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>GMR Airports Limited (GMR Airports), perusahaan operator bandara asal India, membuka peluang untuk memperluas ...</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678607/gmr-buka-peluang-perluas-investasi-di-bandara-lain-indonesia</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/09a99626-b25f-41b2-8db2-de5355d06e86.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Wali kota tawarkan Makassar jadi hub investasi Indonesia Timur</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:46:09 +0700</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Wali Kota Makassar Munafri Arifuddin menawarkan kota itu sebagai hub investasi di kawasan Indonesia Timur (Intim) pada ...</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678604/wali-kota-tawarkan-makassar-jadi-hub-investasi-indonesia-timur</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>terkini, top-news</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>John Herdman pastikan Marselino absen hingga akhir Piala AFF 2026</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:14:04 +0700</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Pelatih tim nasional Indonesia John Herdman memastikan gelandang Marselino Ferdinan bakal absen hingga akhir turnamen ...</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678600/john-herdman-pastikan-marselino-absen-hingga-akhir-piala-aff-2026</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 04:02:18 +0700</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A ...</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/video/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis, terkini</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis, terkini</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ekonomi-bisnis, terkini</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>John Herdman akui Vietnam unggul secara taktik</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>terkini</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
         </is>
       </c>
     </row>
@@ -1633,28 +1633,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Pengamat nilai cara Seskab rawat jaringan perlu dicontoh politisi</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
+          <t>Tue, 04 Aug 2026 05:44:45 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
+          <t>Pengamat politik Hendri Satrio alias Hensa menilai cara-cara Sekretaris Kabinet (Seskab) Teddy Indra Wijaya dalam ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5678608/pengamat-nilai-cara-seskab-rawat-jaringan-perlu-dicontoh-politisi</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/11/20/Zulkieflimansyah.jpg</t>
         </is>
       </c>
     </row>
@@ -1666,28 +1666,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
+          <t>GMR buka peluang perluas investasi di bandara lain Indonesia</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
+          <t>Tue, 04 Aug 2026 05:00:12 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
+          <t>GMR Airports Limited (GMR Airports), perusahaan operator bandara asal India, membuka peluang untuk memperluas ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
+          <t>https://www.antaranews.com/berita/5678607/gmr-buka-peluang-perluas-investasi-di-bandara-lain-indonesia</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/09a99626-b25f-41b2-8db2-de5355d06e86.jpeg</t>
         </is>
       </c>
     </row>
@@ -1699,61 +1699,61 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
+          <t>Wali kota tawarkan Makassar jadi hub investasi Indonesia Timur</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
+          <t>Tue, 04 Aug 2026 04:46:09 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
+          <t>Wali Kota Makassar Munafri Arifuddin menawarkan kota itu sebagai hub investasi di kawasan Indonesia Timur (Intim) pada ...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
+          <t>https://www.antaranews.com/berita/5678604/wali-kota-tawarkan-makassar-jadi-hub-investasi-indonesia-timur</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>terkini, top-news</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
+          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
+          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
+          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
         </is>
       </c>
     </row>
@@ -1765,28 +1765,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
+          <t>John Herdman pastikan Marselino absen hingga akhir Piala AFF 2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
+          <t>Tue, 04 Aug 2026 04:14:04 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
+          <t>Pelatih tim nasional Indonesia John Herdman memastikan gelandang Marselino Ferdinan bakal absen hingga akhir turnamen ...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678600/john-herdman-pastikan-marselino-absen-hingga-akhir-piala-aff-2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
         </is>
       </c>
     </row>
@@ -1798,28 +1798,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
+          <t>Tue, 04 Aug 2026 04:02:18 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A ...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
+          <t>https://www.antaranews.com/video/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
         </is>
       </c>
     </row>
@@ -1831,1790 +1831,2318 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Peneliti di Australia kembangkan sensor optik untuk jantung &amp; otak</t>
+          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:09:59 +0700</t>
+          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Para insinyur biomedis di Australia telah mengembangkan sebuah sensor cahaya yang sepenuhnya fleksibel dan mampu ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678555/peneliti-di-australia-kembangkan-sensor-optik-untuk-jantung-otak</t>
+          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alibaba luncurkan model AI terbaru Qwen3.8-Max</t>
+          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:08:15 +0700</t>
+          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Perusahaan teknologi China Alibaba pada Senin (3/8) meluncurkan model bahasa besar terbarunya, Qwen3.8-Max, yang ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678552/alibaba-luncurkan-model-ai-terbaru-qwen38-max</t>
+          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Garuda TV menandai babak baru dengan "Mahayuga"</t>
+          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:05:27 +0700</t>
+          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dalam rangkaian perayaan ulang tahun ketiganya, Garuda TV akan menggelar "Mahayuga" untuk menandai babak baru ...</t>
+          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678551/garuda-tv-menandai-babak-baru-dengan-mahayuga</t>
+          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
+          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
+          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini, top-news</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>John Herdman akui Vietnam unggul secara taktik</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
+          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
+          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
 (Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
         <is>
           <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
         <is>
           <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
         <is>
           <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
 (Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
         <is>
           <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
 (Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
         <is>
           <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
 (Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
         <is>
           <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
         <is>
           <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
         <is>
           <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
         <is>
           <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
         <is>
           <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
         <is>
           <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
         <is>
           <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
         <is>
           <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
         <is>
           <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
         <is>
           <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
         <is>
           <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
         <is>
           <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
 (Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
         <is>
           <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
         <is>
           <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
         <is>
           <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
         <is>
           <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
         <is>
           <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
         <is>
           <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
         <is>
           <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
         <is>
           <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
         <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
         <is>
           <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
         <is>
           <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
         <is>
           <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
         <is>
           <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
         <is>
           <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
         <is>
           <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
         <is>
           <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
         <is>
           <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
         <is>
           <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
         <is>
           <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
         <is>
           <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
         <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
         <is>
           <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 06:55:01 +0700</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
         <is>
           <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G96"/>
+  <autoFilter ref="A1:G112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -901,33 +901,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kemnaker ajak masyarakat pacu kompetensi di Pelatihan Vokasi Nasional</t>
+          <t>Humaniora kemarin, status keracunan MBG hingga 1 tahun Sekolah Rakyat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 08:14:30 +0700</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengajak masyarakat untuk meningkatkan kompetensi melalui Pelatihan Vokasi ...</t>
+          <t>Sejumlah berita humaniora pada Senin yang mendapat perhatian pembaca dan masih menarik untuk disimak pagi ini, mulai ...</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678657/kemnaker-ajak-masyarakat-pacu-kompetensi-di-pelatihan-vokasi-nasional</t>
+          <t>https://www.antaranews.com/berita/5678655/humaniora-kemarin-status-keracunan-mbg-hingga-1-tahun-sekolah-rakyat</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/kesiapan-tenaga-kerja-di-balai-pelatihan-kerja-semarang-2828648.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/menteri-sosial-tinjau-mpls-di-srt-i-sukoharjo-2831859.jpg</t>
         </is>
       </c>
     </row>
@@ -939,94 +939,94 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Humaniora kemarin, status keracunan MBG hingga 1 tahun Sekolah Rakyat</t>
+          <t>Cuaca di kota-kota besar diperkirakan cerah berawan hingga berawan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:14:30 +0700</t>
+          <t>Tue, 04 Aug 2026 07:57:38 +0700</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sejumlah berita humaniora pada Senin yang mendapat perhatian pembaca dan masih menarik untuk disimak pagi ini, mulai ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan kondisi cuaca di kota-kota besar di Indonesia ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678655/humaniora-kemarin-status-keracunan-mbg-hingga-1-tahun-sekolah-rakyat</t>
+          <t>https://www.antaranews.com/berita/5678648/cuaca-di-kota-kota-besar-diperkirakan-cerah-berawan-hingga-berawan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/menteri-sosial-tinjau-mpls-di-srt-i-sukoharjo-2831859.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/09/22/Cuaca-Jakarta-290812-DDS-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICPI soroti tantangan sektor pariwisata RI hadapi dinamika global</t>
+          <t>Selasa, layanan Samsat Keliling tersedia di 14 wilayah Jadetabek</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:07:43 +0700</t>
+          <t>Tue, 04 Aug 2026 07:52:34 +0700</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ikatan Cendikiawan Pariwisata Indonesia (ICPI) menyoroti sejumlah tantangan pariwisata Indonesia dalam menghadapi ...</t>
+          <t>Polda Metro Jaya menyediakan layanan Sistem Administrasi Manunggal Satu Atap (Samsat) Keliling untuk membantu para ...</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678652/icpi-soroti-tantangan-sektor-pariwisata-ri-hadapi-dinamika-global</t>
+          <t>https://www.antaranews.com/berita/5678647/selasa-layanan-samsat-keliling-tersedia-di-14-wilayah-jadetabek</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/11/26/kunjungan-turis-asing-ke-ntb-tumbuh-106-persen-1jdoh-dom.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/SAMSAT-Keliling-04082026.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CORE: Penilaian kredit alternatif dapat perluas pembiayaan UMKM</t>
+          <t>Selasa, layanan SIM keliling tersedia di lima lokasi Jakarta</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:58:42 +0700</t>
+          <t>Tue, 04 Aug 2026 07:51:07 +0700</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai pemanfaatan penilaian kredit ...</t>
+          <t>Direktorat Lalu Lintas Polda Metro Jaya membuka layanan Surat Izin Mengemudi (SIM) Keliling bagi masyarakat yang ...</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678651/core-penilaian-kredit-alternatif-dapat-perluas-pembiayaan-umkm</t>
+          <t>https://www.antaranews.com/berita/5678645/selasa-layanan-sim-keliling-tersedia-di-lima-lokasi-jakarta</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/realisasi-penyaluran-kur-umkm-2832719.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/SIM-Keliling-04082026.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,28 +1038,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cuaca di kota-kota besar diperkirakan cerah berawan hingga berawan</t>
+          <t>Pelanggan KA Makassar--Parepare Naik 13,62 Persen, KAI Perluas Konektivitas dan Kesempatan Masyarakat Sulawesi Selatan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:57:38 +0700</t>
+          <t>Tue, 04 Aug 2026 07:40:47 +0700</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan kondisi cuaca di kota-kota besar di Indonesia ...</t>
+          <t>PT Kereta Api Indonesia (Persero) mencatat pertumbuhan positif layanan KA Makassar–Parepare sepanjang ...</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678648/cuaca-di-kota-kota-besar-diperkirakan-cerah-berawan-hingga-berawan</t>
+          <t>https://www.antaranews.com/berita/5678641/pelanggan-ka-makassar-parepare-naik-1362-persen-kai-perluas-konektivitas-dan-kesempatan-masyarakat-sulawesi-selatan</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/09/22/Cuaca-Jakarta-290812-DDS-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001085218.jpg</t>
         </is>
       </c>
     </row>
@@ -1071,28 +1071,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Selasa, layanan Samsat Keliling tersedia di 14 wilayah Jadetabek</t>
+          <t>Angkutan Petikemas KAI Naik 20,28 Persen, Perkuat Konektivitas Rel–Pelabuhan bagi Logistik Nasional</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:52:34 +0700</t>
+          <t>Tue, 04 Aug 2026 07:35:21 +0700</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Polda Metro Jaya menyediakan layanan Sistem Administrasi Manunggal Satu Atap (Samsat) Keliling untuk membantu para ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat layanan angkutan petikemas sebagai bagian dari sistem logistik ...</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678647/selasa-layanan-samsat-keliling-tersedia-di-14-wilayah-jadetabek</t>
+          <t>https://www.antaranews.com/berita/5678640/angkutan-petikemas-kai-naik-2028-persen-perkuat-konektivitas-rel-pelabuhan-bagi-logistik-nasional</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/SAMSAT-Keliling-04082026.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001085217.jpg</t>
         </is>
       </c>
     </row>
@@ -1104,28 +1104,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Selasa, layanan SIM keliling tersedia di lima lokasi Jakarta</t>
+          <t>BMKG prakirakan Jaksel dan Jaktim hujan ringan pada Selasa malam</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:51:07 +0700</t>
+          <t>Tue, 04 Aug 2026 07:20:02 +0700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Direktorat Lalu Lintas Polda Metro Jaya membuka layanan Surat Izin Mengemudi (SIM) Keliling bagi masyarakat yang ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan wilayah Jakarta Selatan dan Jakarta Timur diguyur ...</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678645/selasa-layanan-sim-keliling-tersedia-di-lima-lokasi-jakarta</t>
+          <t>https://www.antaranews.com/berita/5678639/bmkg-prakirakan-jaksel-dan-jaktim-hujan-ringan-pada-selasa-malam</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/SIM-Keliling-04082026.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CuacaJakarta160710.jpg</t>
         </is>
       </c>
     </row>
@@ -1137,94 +1137,94 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pelanggan KA Makassar--Parepare Naik 13,62 Persen, KAI Perluas Konektivitas dan Kesempatan Masyarakat Sulawesi Selatan</t>
+          <t>Ekonomi kemarin, harga bensin turun hingga kredit perbankan tumbuh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:40:47 +0700</t>
+          <t>Tue, 04 Aug 2026 07:19:27 +0700</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) mencatat pertumbuhan positif layanan KA Makassar–Parepare sepanjang ...</t>
+          <t>Berbagai peristiwa ekonomi diberitakan Kantor Berita ANTARA pada Senin (3/8), mulai dari penurunan harga bensin pada ...</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678641/pelanggan-ka-makassar-parepare-naik-1362-persen-kai-perluas-konektivitas-dan-kesempatan-masyarakat-sulawesi-selatan</t>
+          <t>https://www.antaranews.com/berita/5678637/ekonomi-kemarin-harga-bensin-turun-hingga-kredit-perbankan-tumbuh</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001085218.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2016/01/20160105492.jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Angkutan Petikemas KAI Naik 20,28 Persen, Perkuat Konektivitas Rel–Pelabuhan bagi Logistik Nasional</t>
+          <t>Praktisi: Material bangunan berkarakter visual kian diminati konsumen</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:35:21 +0700</t>
+          <t>Tue, 04 Aug 2026 07:07:17 +0700</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) terus memperkuat layanan angkutan petikemas sebagai bagian dari sistem logistik ...</t>
+          <t>Praktisi industri bangunan, Jali Wijaya, mengatakan seiring berkembangnya tren hunian yang semakin personal, material ...</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678640/angkutan-petikemas-kai-naik-2028-persen-perkuat-konektivitas-rel-pelabuhan-bagi-logistik-nasional</t>
+          <t>https://www.antaranews.com/berita/5678635/praktisi-material-bangunan-berkarakter-visual-kian-diminati-konsumen</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001085217.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/pearlescent-effect.jpeg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BMKG prakirakan Jaksel dan Jaktim hujan ringan pada Selasa malam</t>
+          <t>BPS sebut El Nino ubah pola harga pangan di Nabire</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:20:02 +0700</t>
+          <t>Tue, 04 Aug 2026 07:00:42 +0700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan wilayah Jakarta Selatan dan Jakarta Timur diguyur ...</t>
+          <t>Badan Pusat Statistik (BPS) Kabupaten Nabire menyebut fenomena El Nino mengubah pola harga pangan di daerah itu ...</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678639/bmkg-prakirakan-jaksel-dan-jaktim-hujan-ringan-pada-selasa-malam</t>
+          <t>https://www.antaranews.com/berita/5678631/bps-sebut-el-nino-ubah-pola-harga-pangan-di-nabire</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CuacaJakarta160710.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-06-15-at-15.40.12.jpeg</t>
         </is>
       </c>
     </row>
@@ -1236,61 +1236,61 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ekonomi kemarin, harga bensin turun hingga kredit perbankan tumbuh</t>
+          <t>Jalan pulang para srikandi jalanan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:19:27 +0700</t>
+          <t>Tue, 04 Aug 2026 06:53:36 +0700</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Berbagai peristiwa ekonomi diberitakan Kantor Berita ANTARA pada Senin (3/8), mulai dari penurunan harga bensin pada ...</t>
+          <t>Di tengah lalu lintas Kota Surabaya yang nyaris tak pernah berhenti, semakin banyak perempuan mengenakan jaket ojek ...</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678637/ekonomi-kemarin-harga-bensin-turun-hingga-kredit-perbankan-tumbuh</t>
+          <t>https://www.antaranews.com/berita/5678627/jalan-pulang-para-srikandi-jalanan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2016/01/20160105492.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/dok.Pelatihan-sablon-Ojol-perempuan-Surabaya-4.jpg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Praktisi: Material bangunan berkarakter visual kian diminati konsumen</t>
+          <t>DKI kemarin, inflasi tahunan Jakarta hingga potensi aksi demonstrasi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:07:17 +0700</t>
+          <t>Tue, 04 Aug 2026 06:41:11 +0700</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Praktisi industri bangunan, Jali Wijaya, mengatakan seiring berkembangnya tren hunian yang semakin personal, material ...</t>
+          <t>Sejumlah berita seputar DKI Jakarta yang terjadi pada Senin (3/8) kemarin, mulai dari inflasi tahunan Jakarta hingga ...</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678635/praktisi-material-bangunan-berkarakter-visual-kian-diminati-konsumen</t>
+          <t>https://www.antaranews.com/berita/5678625/dki-kemarin-inflasi-tahunan-jakarta-hingga-potensi-aksi-demonstrasi</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/pearlescent-effect.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000313673.jpg</t>
         </is>
       </c>
     </row>
@@ -1302,28 +1302,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BPS sebut El Nino ubah pola harga pangan di Nabire</t>
+          <t>Eksotis bahari Maratua,warisan laut bagi Nusantara</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:00:42 +0700</t>
+          <t>Tue, 04 Aug 2026 06:37:43 +0700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Kabupaten Nabire menyebut fenomena El Nino mengubah pola harga pangan di daerah itu ...</t>
+          <t>Meresapi keanggunan laut Nusantara serasa merenungi betapa agung karya Sang Pencipta yang terpancar melalui warisan ...</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678631/bps-sebut-el-nino-ubah-pola-harga-pangan-di-nabire</t>
+          <t>https://www.antaranews.com/berita/5678621/eksotis-bahari-maratuawarisan-laut-bagi-nusantara</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-06-15-at-15.40.12.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001881799.jpg</t>
         </is>
       </c>
     </row>
@@ -1335,28 +1335,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jalan pulang para srikandi jalanan</t>
+          <t>Kriminal kemarin, hoaks ajakan demonstrasi hingga lansia disekap</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:53:36 +0700</t>
+          <t>Tue, 04 Aug 2026 06:36:29 +0700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Di tengah lalu lintas Kota Surabaya yang nyaris tak pernah berhenti, semakin banyak perempuan mengenakan jaket ojek ...</t>
+          <t>Sejumlah peristiwa berkaitan dengan tindak kriminal dan keamanan menghiasi Jakarta yang terjadi pada Senin (3/8) ...</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678627/jalan-pulang-para-srikandi-jalanan</t>
+          <t>https://www.antaranews.com/berita/5678620/kriminal-kemarin-hoaks-ajakan-demonstrasi-hingga-lansia-disekap</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/dok.Pelatihan-sablon-Ojol-perempuan-Surabaya-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_192143033.jpg</t>
         </is>
       </c>
     </row>
@@ -1368,28 +1368,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DKI kemarin, inflasi tahunan Jakarta hingga potensi aksi demonstrasi</t>
+          <t>Menembus tembok stigma, memulihkan luka anak</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:41:11 +0700</t>
+          <t>Tue, 04 Aug 2026 06:11:55 +0700</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sejumlah berita seputar DKI Jakarta yang terjadi pada Senin (3/8) kemarin, mulai dari inflasi tahunan Jakarta hingga ...</t>
+          <t>Tidak ada anak yang lahir dengan pilihan peta nasib di genggamannya. Sebagian beruntung tumbuh dalam rumah yang penuh ...</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678625/dki-kemarin-inflasi-tahunan-jakarta-hingga-potensi-aksi-demonstrasi</t>
+          <t>https://www.antaranews.com/berita/5678616/menembus-tembok-stigma-memulihkan-luka-anak</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000313673.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-07-27-at-12.27.07.jpeg</t>
         </is>
       </c>
     </row>
@@ -1401,28 +1401,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eksotis bahari Maratua,warisan laut bagi Nusantara</t>
+          <t>HRTA kantongi laba Rp700,01 M pada semester I 2026, naik 100,86 persen</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:37:43 +0700</t>
+          <t>Tue, 04 Aug 2026 05:54:06 +0700</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Meresapi keanggunan laut Nusantara serasa merenungi betapa agung karya Sang Pencipta yang terpancar melalui warisan ...</t>
+          <t>PT Hartadinata Abadi Tbk (HRTA) membukukan laba bersih sebesar Rp700,01 miliar pada semester I 2026, meningkat 100,86 ...</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678621/eksotis-bahari-maratuawarisan-laut-bagi-nusantara</t>
+          <t>https://www.antaranews.com/berita/5678611/hrta-kantongi-laba-rp70001-m-pada-semester-i-2026-naik-10086-persen</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001881799.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-13.37.37.jpeg</t>
         </is>
       </c>
     </row>
@@ -1434,61 +1434,62 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kriminal kemarin, hoaks ajakan demonstrasi hingga lansia disekap</t>
+          <t>Fulham resmi rampungkan transfer Gonzalo Garcia dari Real Madrid</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:36:29 +0700</t>
+          <t>Tue, 04 Aug 2026 05:48:40 +0700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sejumlah peristiwa berkaitan dengan tindak kriminal dan keamanan menghiasi Jakarta yang terjadi pada Senin (3/8) ...</t>
+          <t>Fulham resmi merampungkan transfer penyerang muda Gonzalo Garcia dari Real Madrid pada musim panas 2026
+"Dengan ...</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678620/kriminal-kemarin-hoaks-ajakan-demonstrasi-hingga-lansia-disekap</t>
+          <t>https://www.antaranews.com/berita/5678609/fulham-resmi-rampungkan-transfer-gonzalo-garcia-dari-real-madrid</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_192143033.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000042507.jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+          <t>Pengamat nilai cara Seskab rawat jaringan perlu dicontoh politisi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+          <t>Tue, 04 Aug 2026 05:44:45 +0700</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, ...</t>
+          <t>Pengamat politik Hendri Satrio alias Hensa menilai cara-cara Sekretaris Kabinet (Seskab) Teddy Indra Wijaya dalam ...</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+          <t>https://www.antaranews.com/berita/5678608/pengamat-nilai-cara-seskab-rawat-jaringan-perlu-dicontoh-politisi</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/11/20/Zulkieflimansyah.jpg</t>
         </is>
       </c>
     </row>
@@ -1500,94 +1501,94 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Menembus tembok stigma, memulihkan luka anak</t>
+          <t>GMR buka peluang perluas investasi di bandara lain Indonesia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:11:55 +0700</t>
+          <t>Tue, 04 Aug 2026 05:00:12 +0700</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tidak ada anak yang lahir dengan pilihan peta nasib di genggamannya. Sebagian beruntung tumbuh dalam rumah yang penuh ...</t>
+          <t>GMR Airports Limited (GMR Airports), perusahaan operator bandara asal India, membuka peluang untuk memperluas ...</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678616/menembus-tembok-stigma-memulihkan-luka-anak</t>
+          <t>https://www.antaranews.com/berita/5678607/gmr-buka-peluang-perluas-investasi-di-bandara-lain-indonesia</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-07-27-at-12.27.07.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/09a99626-b25f-41b2-8db2-de5355d06e86.jpeg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kontingen Indonesia di Asian Games 2026</t>
+          <t>Wali kota tawarkan Makassar jadi hub investasi Indonesia Timur</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
+          <t>Tue, 04 Aug 2026 04:46:09 +0700</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
+          <t>Wali Kota Makassar Munafri Arifuddin menawarkan kota itu sebagai hub investasi di kawasan Indonesia Timur (Intim) pada ...</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
+          <t>https://www.antaranews.com/berita/5678604/wali-kota-tawarkan-makassar-jadi-hub-investasi-indonesia-timur</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HRTA kantongi laba Rp700,01 M pada semester I 2026, naik 100,86 persen</t>
+          <t>John Herdman pastikan Marselino absen hingga akhir Piala AFF 2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:54:06 +0700</t>
+          <t>Tue, 04 Aug 2026 04:14:04 +0700</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PT Hartadinata Abadi Tbk (HRTA) membukukan laba bersih sebesar Rp700,01 miliar pada semester I 2026, meningkat 100,86 ...</t>
+          <t>Pelatih tim nasional Indonesia John Herdman memastikan gelandang Marselino Ferdinan bakal absen hingga akhir turnamen ...</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678611/hrta-kantongi-laba-rp70001-m-pada-semester-i-2026-naik-10086-persen</t>
+          <t>https://www.antaranews.com/berita/5678600/john-herdman-pastikan-marselino-absen-hingga-akhir-piala-aff-2026</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-13.37.37.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
         </is>
       </c>
     </row>
@@ -1599,29 +1600,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fulham resmi rampungkan transfer Gonzalo Garcia dari Real Madrid</t>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:48:40 +0700</t>
+          <t>Tue, 04 Aug 2026 04:02:18 +0700</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fulham resmi merampungkan transfer penyerang muda Gonzalo Garcia dari Real Madrid pada musim panas 2026
-"Dengan ...</t>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A ...</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678609/fulham-resmi-rampungkan-transfer-gonzalo-garcia-dari-real-madrid</t>
+          <t>https://www.antaranews.com/video/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000042507.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
         </is>
       </c>
     </row>
@@ -1633,127 +1633,127 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pengamat nilai cara Seskab rawat jaringan perlu dicontoh politisi</t>
+          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:44:45 +0700</t>
+          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pengamat politik Hendri Satrio alias Hensa menilai cara-cara Sekretaris Kabinet (Seskab) Teddy Indra Wijaya dalam ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678608/pengamat-nilai-cara-seskab-rawat-jaringan-perlu-dicontoh-politisi</t>
+          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/11/20/Zulkieflimansyah.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GMR buka peluang perluas investasi di bandara lain Indonesia</t>
+          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 05:00:12 +0700</t>
+          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GMR Airports Limited (GMR Airports), perusahaan operator bandara asal India, membuka peluang untuk memperluas ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678607/gmr-buka-peluang-perluas-investasi-di-bandara-lain-indonesia</t>
+          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/09a99626-b25f-41b2-8db2-de5355d06e86.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wali kota tawarkan Makassar jadi hub investasi Indonesia Timur</t>
+          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:46:09 +0700</t>
+          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wali Kota Makassar Munafri Arifuddin menawarkan kota itu sebagai hub investasi di kawasan Indonesia Timur (Intim) pada ...</t>
+          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678604/wali-kota-tawarkan-makassar-jadi-hub-investasi-indonesia-timur</t>
+          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
+          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
+          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
+          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
+          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
         </is>
       </c>
     </row>
@@ -1765,28 +1765,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>John Herdman pastikan Marselino absen hingga akhir Piala AFF 2026</t>
+          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:14:04 +0700</t>
+          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional Indonesia John Herdman memastikan gelandang Marselino Ferdinan bakal absen hingga akhir turnamen ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678600/john-herdman-pastikan-marselino-absen-hingga-akhir-piala-aff-2026</t>
+          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
         </is>
       </c>
     </row>
@@ -1798,28 +1798,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:02:18 +0700</t>
+          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A ...</t>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
         </is>
       </c>
     </row>
@@ -1831,94 +1831,94 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>John Herdman sebut kerapatan formasi timnas harus diperbaiki</t>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:23:09 +0700</t>
+          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional sepak bola Indonesia John Herdman menyebutkan kerapatan formasi tim asuhannya harus ...</t>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678597/john-herdman-sebut-kerapatan-formasi-timnas-harus-diperbaiki</t>
+          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bahlil sebut peresmian tahap I PLTS 100 GW akan dilakukan di Bali</t>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:21:27 +0700</t>
+          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan peresmian tahap pertama program pembangkit ...</t>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678596/bahlil-sebut-peresmian-tahap-i-plts-100-gw-akan-dilakukan-di-bali</t>
+          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BP BUMN dan Danantara terus persiapkan strategi transformasi 5 tahun</t>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 02:02:28 +0700</t>
+          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BP BUMN bersama Danantara terus mematangkan arah transformasi BUMN melalui penyusunan peta strategi lima tahun sebagai ...</t>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678593/bp-bumn-dan-danantara-terus-persiapkan-strategi-transformasi-5-tahun</t>
+          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
         </is>
       </c>
     </row>
@@ -1930,28 +1930,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola AS perpanjang kontrak Pochettino hingga 2030</t>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:43:15 +0700</t>
+          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Federasi Sepak Bola Amerika Serikat (U.S. Soccer) resmi memperpanjang kontrak Mauricio Pochettino sebagai pelatih tim ...</t>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678587/federasi-sepak-bola-as-perpanjang-kontrak-pochettino-hingga-2030</t>
+          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
         </is>
       </c>
     </row>
@@ -1963,61 +1963,61 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rizky Ridho akui lakukan kesalahan fatal saat hadapi Vietnam</t>
+          <t>John Herdman akui Vietnam unggul secara taktik</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:38:31 +0700</t>
+          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho mengakui melakukan kesalahan fatal yang berakibat gol saat ...</t>
+          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678585/rizky-ridho-akui-lakukan-kesalahan-fatal-saat-hadapi-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini, top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
         </is>
       </c>
     </row>
@@ -2029,28 +2029,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:30:00 +0700</t>
+          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin ...</t>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
         </is>
       </c>
     </row>
@@ -2062,28 +2062,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:25:12 +0700</t>
+          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special ...</t>
+          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
         </is>
       </c>
     </row>
@@ -2095,28 +2095,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
+          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:14:03 +0700</t>
+          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan ...</t>
+          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
+          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
         </is>
       </c>
     </row>
@@ -2128,28 +2128,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:12:16 +0700</t>
+          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan ...</t>
+          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
         </is>
       </c>
     </row>
@@ -2161,28 +2161,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:10:23 +0700</t>
+          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh ...</t>
+          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
         </is>
       </c>
     </row>
@@ -2194,127 +2194,127 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>John Herdman akui Vietnam unggul secara taktik</t>
+          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:58:24 +0700</t>
+          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pelatih tim nasional sepak bola Indonesia, John Herdman, mengakui Vietnam unggul secara taktik saat melawan tim ...</t>
+          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678580/john-herdman-akui-vietnam-unggul-secara-taktik</t>
+          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jordi Amat minta dukungan suporter tak surut usai kalah dari Vietnam</t>
+          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:52:18 +0700</t>
+          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bek Timnas Indonesia Jordi Amat meminta suporter tetap memberikan dukungan kepada skuad Garuda meski baru menelan ...</t>
+          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678576/jordi-amat-minta-dukungan-suporter-tak-surut-usai-kalah-dari-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:48:34 +0700</t>
+          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) ...</t>
+          <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Baker: Peluang Indonesia masih terbuka jika kalahkan Singapura</t>
+          <t>Pakar: Harga minyak dunia turun jadi kesempatan menata aturan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:47:05 +0700</t>
+          <t>Tue, 04 Aug 2026 11:49:32 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Penyerang Timnas Indonesia Mitchell Baker menegaskan peluang Garuda untuk lolos ke semifinal Piala AFF 2026 masih ...</t>
+          <t>Peneliti sekaligus dosen Fakultas Ekonomi dan Bisnis Universitas Padjadjaran Yayan Satyakti menilai turunnya harga ...</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678573/baker-peluang-indonesia-masih-terbuka-jika-kalahkan-singapura</t>
+          <t>https://www.antaranews.com/berita/5678851/pakar-harga-minyak-dunia-turun-jadi-kesempatan-menata-aturan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
         </is>
       </c>
     </row>
@@ -2326,28 +2326,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pemain Vietnam kagum dukungan suporter Indonesia di Pakansari</t>
+          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:39:56 +0700</t>
+          <t>Tue, 04 Aug 2026 11:47:59 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pemain tim nasional Vietnam Do Hoang Hen mengaku terkesan dengan dukungan suporter Indonesia saat timnya meraih ...</t>
+          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi ...</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678569/pemain-vietnam-kagum-dukungan-suporter-indonesia-di-pakansari</t>
+          <t>https://www.antaranews.com/video/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
         </is>
       </c>
     </row>
@@ -2359,28 +2359,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Reno Salampessy memilih bertahan bersama Persipura</t>
+          <t>BPKH salurkan Rp2,06 triliun nilai manfaat ke 5,7 juta calon haji</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:37:37 +0700</t>
+          <t>Tue, 04 Aug 2026 11:47:58 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pemain muda Persipura Jayapura Reno Salampessy memilih untuk bertahan bersama Mutiara Hitam, meski timnya masih akan ...</t>
+          <t>Badan Pengelola Keuangan Haji (BPKH) menyalurkan Nilai Manfaat Tahap I Tahun 2026 lebih dari Rp2,06 triliun kepada ...</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678568/reno-salampessy-memilih-bertahan-bersama-persipura</t>
+          <t>https://www.antaranews.com/berita/5678849/bpkh-salurkan-rp206-triliun-nilai-manfaat-ke-57-juta-calon-haji</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176506.jpg</t>
         </is>
       </c>
     </row>
@@ -2392,28 +2392,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PSSI percaya Garuda bisa bangkit setelah kekalahan dari Vietnam</t>
+          <t>Fiorentina pinjam Joao Mario dari Juventus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:33:39 +0700</t>
+          <t>Tue, 04 Aug 2026 11:46:34 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir mengatakan dirinya tetap percaya tim nasional ...</t>
+          <t>Fiorentina mendatangkan bek sayap Joao Mario dari  Juventus dalamd status pinjaman dari Juvantus disertai opsi ...</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678564/pssi-percaya-garuda-bisa-bangkit-setelah-kekalahan-dari-vietnam</t>
+          <t>https://www.antaranews.com/berita/5678847/fiorentina-pinjam-joao-mario-dari-juventus</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_7595.jpg</t>
         </is>
       </c>
     </row>
@@ -2425,1724 +2425,3639 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AI perluas peluang kerja sama pendidikan China-ASEAN</t>
+          <t>Mendes bantah Kopdes Merah Putih matikan toko kelontong di daerah</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:11:40 +0700</t>
+          <t>Tue, 04 Aug 2026 11:44:03 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bagi Worawit Boonkate, seorang pemuda asal Thailand kelahiran tahun 1990-an, tiga tahun pelatihan akademis di China ...</t>
+          <t>Menteri Desa dan Pembangunan Daerah Tertinggal (Mendes PDT) Yandri Susanto secara tegas membantah kehadiran Koperasi ...</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678559/ai-perluas-peluang-kerja-sama-pendidikan-china-asean</t>
+          <t>https://www.antaranews.com/berita/5678845/mendes-bantah-kopdes-merah-putih-matikan-toko-kelontong-di-daerah</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002904686.jpg</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BPS: Ekspor di Kalsel tembus Rp98,20 triliun selama semester I 2026</t>
+          <t>China luncurkan seleksi perdana pemimpin efisiensi karbon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 00:03:27 +0700</t>
+          <t>Tue, 04 Aug 2026 11:39:58 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Badan Pusat Statistik (BPS) Kalimantan Selatan mencatat nilai ekspor di provinsi itu tembus sekitar Rp98,20 triliun ...</t>
+          <t>Pemberitahuan yang diterbitkan bersama oleh Kementerian Perindustrian dan Teknologi Informasi China serta dua lembaga ...</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678549/bps-ekspor-di-kalsel-tembus-rp9820-triliun-selama-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678841/china-luncurkan-seleksi-perdana-pemimpin-efisiensi-karbon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000003_20260804_CBMFN0A001.jpg</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+          <t>Wuling sediakan "test drive" mobil-mobil terbaru di GIIAS 2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+          <t>Pabrikan otomotif asal China Wuling Motors menyediakan aneka mobil keluaran terbaru mereka untuk diuji coba ...</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+          <t>https://otomotif.antaranews.com/berita/5678837/wuling-sediakan-test-drive-mobil-mobil-terbaru-di-giias-2026</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pada-area-test-drive-Wuling-menyediakan-beragam-lini-kendaraan-sehingga-pengunjung-dapat-merasakan-secara-langsung-performa-kenyamanan-serta-teknologi-yang-dihadirkan.jpeg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Aldila jadi petenis Indonesia yang pertama juarai DC Open</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+          <t>Petenis Indonesia Aldila Sutjiadi mencatatkan sejarah setelah menjuarai nomor ganda putri turnamen Mubadala DC Open ...</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5678836/aldila-jadi-petenis-indonesia-yang-pertama-juarai-dc-open</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/IMG_4155.jpeg</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>Kementan siapkan Juknis penyerapan telur bagi SPPG Rp26.500/kg</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 11:26:36 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+          <t>Kementerian Pertanian (Kementan) menyiapkan petunjuk teknis (Juknis) penyerapan telur oleh seluruh Satuan Pelayanan ...</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/berita/5678831/kementan-siapkan-juknis-penyerapan-telur-bagi-sppg-rp26500-kg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/4FB30E01-205C-4253-9C88-5373F761A9FB.jpeg</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial, terkini</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Panda Bond dan sinyal kepercayaan investasi global</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 11:26:35 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Di tengah ketidakpastian ekonomi global yang semakin kompleks, pemerintah Indonesia perlu memastikan bahwa ...</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678827/panda-bond-dan-sinyal-kepercayaan-investasi-global</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/permintaan-pembelian-obligasi-global-capai-46-miliar-dolar-as-2806089.jpg</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Kejagung ungkap empat perusahaan digeledah Tim 9 milik Don Ritto</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 11:24:51 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Kejaksaan Agung mengungkapkan bahwa empat perusahaan yang digeledah tim penyidik (Tim 9) pada Senin (3/8) merupakan ...</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5678825/kejagung-ungkap-empat-perusahaan-digeledah-tim-9-milik-don-ritto</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087161.jpg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Polda Kalsel tangkap jaringan Fredy Pratama selundupkan 32 kg sabu</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 11:24:07 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>Direktorat Reserse Narkoba Polda Kalimantan Selatan menangkap dua anggota jaringan narkotika internasional Fredy ...</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678824/polda-kalsel-tangkap-jaringan-fredy-pratama-selundupkan-32-kg-sabu</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_114833.jpg</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Ekonom proyeksikan pangsa NEV capai 31,7 persen penjualan mobil 2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 11:22:55 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+          <t>Ekonom PT Bank Danamon Indonesia Tbk memproyeksikan pangsa kendaraan energi baru (new energy vehicle/NEV) mencapai 31,7 ...</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5678821/ekonom-proyeksikan-pangsa-nev-capai-317-persen-penjualan-mobil-2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penjualan-kendaraan-di-semester-1-2026-meningkat-2831868.jpg</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Michigan catat dua kematian akibat wabah siklosporiasis</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
+          <t>Tue, 04 Aug 2026 11:22:00 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
+          <t>Dua orang meninggal akibat siklosporiasis di Michigan di tengah wabah yang melanda sejumlah negara bagian Amerika ...</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678820/michigan-catat-dua-kematian-akibat-wabah-siklosporiasis</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Fulham datangkan Cesar Palacios dari Real Madrid</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:19:58 +0700</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Fulham mendaratkan gelandang serang Cesar Palacios dari Real Madrid dalak kontrak tujuh tahun dan menggunakan nomor ...</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678819/fulham-datangkan-cesar-palacios-dari-real-madrid</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/image-35.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, photo, terkini</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BPS proyeksikan produksi beras nasional capai 28,71 Juta ton hingga September 2026, stok dipastikan tetap aman</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Pekerja menata karung berisi cadangan beras pemerintah di gudang Perum Bulog Cabang Meulaboh, Aceh Barat, Aceh, Selasa ...</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678815/bps-proyeksikan-produksi-beras-nasional-capai-2871-juta-ton-hingga-september-2026-stok-dipastikan-tetap-aman</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Prediksi-produksi-beras-nasional-040826-Syf-3.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kemnaker: Magang Nasional 2026 perkuat link and match dengan industri</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:17:05 +0700</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan penyelenggaraan Magang Nasional (MagangHub) 2026 akan fokus pada ...</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678811/kemnaker-magang-nasional-2026-perkuat-link-and-match-dengan-industri</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/26/1000096004.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial, terkini</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Rupiah Selasa melemah dipicu kenaikan harga minyak global</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:15:57 +0700</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah pada Selasa pagi bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per dolar AS ...</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678808/rupiah-selasa-melemah-dipicu-kenaikan-harga-minyak-global</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/nilai-tukar-rupiah-melemah-44-poin-2821215.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BRIN dukung riset panel surya generasi baru untuk kemandirian energi</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:15:31 +0700</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) mengkaji peluang industri manufaktur panel surya generasi baru berteknologi ...</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678807/brin-dukung-riset-panel-surya-generasi-baru-untuk-kemandirian-energi</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/21/plts-terpadu-di-pulau-labengki-kecil-2795679.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hotel di Bangkok manfaatkan bangunan bersejarah bekas kantor pabean</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:15:06 +0700</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Hotel yang memanfaatkan bangunan bersejarah custom house (kantor pabean) di Bangkok, Thailand, ...</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678804/hotel-di-bangkok-manfaatkan-bangunan-bersejarah-bekas-kantor-pabean</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000697011.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Politisi Finlandia desak Uni Eropa setop bantuan militer ke Ukraina</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:12:11 +0700</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Politisi Finlandia dari Partai Freedom Alliance, Armando Mema, mendesak Uni Eropa menghentikan bantuan militer kepada ...</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678801/politisi-finlandia-desak-uni-eropa-setop-bantuan-militer-ke-ukraina</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/04/14/reuters_finnishflag.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bidik Pasar "Aftermarket" Otomotif, ZF Aftermarket Gandeng MKN sebagai Distributor Tunggal TRW di Indonesia</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:11:29 +0700</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Juli 25, ZF Aftermarket, produsen komponen otomotif global, terus memperkuat kiprahnya di pasar otomotif ...</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678800/bidik-pasar-aftermarket-otomotif-zf-aftermarket-gandeng-mkn-sebagai-distributor-tunggal-trw-di-indonesia</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Aftermarket-Otomotif.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Jawab tantangan ketenagakerjaan, Wamendikti dorong transformasi vokasi</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:04:45 +0700</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Pendidikan Tinggi, Sains, dan Teknologi (Wamendiktisaintek) Fauzan menegaskan penguatan karakter dan ...</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678797/jawab-tantangan-ketenagakerjaan-wamendikti-dorong-transformasi-vokasi</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-14.08.44.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BMKG: El Nino 2026 berpotensi menjadi sangat kuat</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:59:51 +0700</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyatakan El Nino 2026 telah mencapai kategori kuat dan masih ...</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678791/bmkg-el-nino-2026-berpotensi-menjadi-sangat-kuat</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bmkg-sampaikan-prospek-musim-kemarau-2026-1oo3c-dom.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Hankook catat pertumbuhan penjualan 130 persen pada semester I-2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:54:12 +0700</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PT Hankook Tire Sales Indonesia mencatat pertumbuhan penjualan sebesar 130 persen pada segmen passenger car radial ...</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5678789/hankook-catat-pertumbuhan-penjualan-130-persen-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Picture_3_-_Strategi_The_Right_Tire_for_The_Right_Vehicle_Antar_Hankook_Tire_Sales_Indonesia_Tumbuh_130_pada_Semester_Pertama_2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Kementan-industri pakan tunda kenaikan harga lindungi peternak ayam</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:54:11 +0700</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian (Kementan) bersama industri pakan menyepakati penundaan kenaikan harga pakan ayam sebagai langkah ...</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678788/kementan-industri-pakan-tunda-kenaikan-harga-lindungi-peternak-ayam</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/6884F332-B2BC-4196-90E6-BB4ACC0370D3.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Bareskrim gagalkan peredaran 86,3 kg sabu jaringan Riau-Sumsel</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:53:40 +0700</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Direktorat Tindak Pidana Narkoba (Dittipidnarkoba) Bareskrim Polri menggagalkan peredaran 86,3 kilogram sabu dan 5.171 ...</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678784/bareskrim-gagalkan-peredaran-863-kg-sabu-jaringan-riau-sumsel</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087157.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NOL World Luncurkan Platform Pemesanan Akomodasi bagi Penggemar K-Pop yang Berkunjung ke Korea Selatan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:49:24 +0700</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NOL World, platform perjalanan internasional (inbound travel) yang dikelola NOL Universe di bawah kepemimpinan ...</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678781/nol-world-luncurkan-platform-pemesanan-akomodasi-bagi-penggemar-k-pop-yang-berkunjung-ke-korea-selatan</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/NOL-World.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>China-ASEAN Alliance for Lifelong Learning Resmi Diluncurkan</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:43:50 +0700</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Artikel berita dari CNS: 
+China-ASEAN Alliance for Lifelong Learning resmi diluncurkan dalam edisi ...</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678780/china-asean-alliance-for-lifelong-learning-resmi-diluncurkan</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/China-ASEAN-Alliance-CAECW.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Polres Tangerang Selatan musnahkan 46 juta butir obat keras daftar G</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:40:26 +0700</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Polres Tangerang Selatan memusnahkan 46 juta butir obat keras ilegal daftar G yang merupakan hasil pengungkapan kasus ...</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678777/polres-tangerang-selatan-musnahkan-46-juta-butir-obat-keras-daftar-g</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ac70ac48-dc1d-439b-9c43-7f76e1b5159d.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Cathay United Bank dan Indovina Bank Dorong Penguatan Daya Tahan Bisnis di Tengah Kondisi Dunia yang Tidak Menentu</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:37:40 +0700</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Kantor Cabang Cathay United Bank di Ho Chi Minh City (CUBHCM) bersama Indovina Bank Ltd. (IVB) menggelar seminar ...</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678775/cathay-united-bank-dan-indovina-bank-dorong-penguatan-daya-tahan-bisnis-di-tengah-kondisi-dunia-yang-tidak-menentu</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Cathay-United-Bank-x-Indovina-Bank.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Utusan perdamaian AS desak Israel hentikan serangan di Gaza</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:34:11 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Utusan khusus Dewan Perdamaian (Board of Peace) pimpinan Amerika Serikat untuk Gaza, Nickolay Mladenov, dan penasihat ...</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678773/utusan-perdamaian-as-desak-israel-hentikan-serangan-di-gaza</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/thumbs_b_c_c8afe6335c568927cfc257757ed34ecc.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Qatar serukan koordinasi Teluk jalankan kesepakatan AS-Iran</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:31:50 +0700</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Qatar menyerukan koordinasi yang lebih erat di antara negara-negara Teluk untuk melaksanakan nota kesepahaman antara ...</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678772/qatar-serukan-koordinasi-teluk-jalankan-kesepakatan-as-iran</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/23/Menlu-Qatar.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Trump: bukan Iran, tetapi AS yang akan pungut biaya di Hormuz</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:27:04 +0700</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump mengatakan Washington tidak akan membiarkan Iran mengenakan biaya terhadap ...</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678768/trump-bukan-iran-tetapi-as-yang-akan-pungut-biaya-di-hormuz</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/AA-20260802-42124703-42124695-TRUMPTARGETING_BANNER_DISPLAYED_IN_TEHRANS_AZADI_SQUARE.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Selasa ini harga emas Antam kembali turun menjadi Rp2,603 juta/gr</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:26:38 +0700</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Harga emas Antam, yang dipantau dari laman Logam Mulia, di Jakarta, Selasa pukul 10.14 WIB turun Rp7.000 menjadi ...</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678767/selasa-ini-harga-emas-antam-kembali-turun-menjadi-rp2603-juta-gr</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/harga-emas-antam-turun-2829987.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Trump beri Iran peluang terakhir untuk capai kesepakatan damai</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:23:40 +0700</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump mengatakan bahwa Washington masih memberikan kesempatan kepada Iran untuk ...</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678765/trump-beri-iran-peluang-terakhir-untuk-capai-kesepakatan-damai</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1001014481.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PTPP bangun SMA Unggul Garuda Konawe Selatan senilai Rp234,28 miliar</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:18:53 +0700</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>BUMN bidang konstruksi dan investasi PT PP (Persero) Tbk (PTPP) membangun fasilitas SMA Unggul Garuda Konawe Selatan, ...</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678763/ptpp-bangun-sma-unggul-garuda-konawe-selatan-senilai-rp23428-miliar</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176733.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Pemerintah diminta buka kembali penempatan pekerja migran di Timteng</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:17:52 +0700</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Sejumlah organisasi kemasyarakatan, asosiasi pejuang dan pemerhati hak pekerja migran Indonesia meminta pemerintah bisa ...</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678759/pemerintah-diminta-buka-kembali-penempatan-pekerja-migran-di-timteng</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469679.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>XTransfer Tercantum dalam Daftar "World's Top Fintech Companies 2026" versi CNBC</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:14:24 +0700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>XTransfer, platform pembayaran perdagangan lintasnegara untuk segmen B2B terbesar di dunia, untuk pertama kalinya ...</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678757/xtransfer-tercantum-dalam-daftar-worlds-top-fintech-companies-2026-versi-cnbc</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CNBC-s-World-s-Top-Fintech.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>China tetapkan standar akurasi indikator kesehatan baterai EV</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:13:45 +0700</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>China mengungkap rincian persyaratan implementasi standar nasional yang direkomendasikan GB/T 46991.1-2025, yang ...</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5678753/china-tetapkan-standar-akurasi-indikator-kesehatan-baterai-ev</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/10/cdde688d-ce12-408e-9408-3ca6363285a5.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Konflik Rusia-Ukraina meningkat di dekat Laut Hitam</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:12:18 +0700</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Konflik antara Rusia dan Ukraina telah meningkat di wilayah Laut Hitam dan kawasan pesisirnya, menurut keterangan pihak ...</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678751/konflik-rusia-ukraina-meningkat-di-dekat-laut-hitam</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/12/19/Xinhua-News-Agency.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa, terkini</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>IHSG menguat ditopang kinerja keuangan emiten periode kuartal II</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:12:17 +0700</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa bergerak menguat ditopang oleh laporan ...</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678748/ihsg-menguat-ditopang-kinerja-keuangan-emiten-periode-kuartal-ii</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/30/BEI-catatkan-14-perusahaan-baru-pada-2025-260625-fzn-3.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Menhub pastikan hak korban dan keluarga KMP Mutiara Sentosa terpenuhi</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:11:14 +0700</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan (Menhub) Dudy Purwagandhi memastikan pemerintah mengawal pemenuhan seluruh hak korban dan keluarga ...</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678744/menhub-pastikan-hak-korban-dan-keluarga-kmp-mutiara-sentosa-terpenuhi</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/FAC78DF1-7644-4B13-80B9-6D4721546F42.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Perwakilan ICRC untuk Myanmar temui Aung San Suu Kyi</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:04:02 +0700</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Perwakilan Tetap Komite Palang Merah Internasional (International Committee of the Red Cross/ICRC) untuk Myanmar, ...</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678741/perwakilan-icrc-untuk-myanmar-temui-aung-san-suu-kyi</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000029_20260803_CBMFN0A001_2.v1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mempertemukan Malin Kundang dan kecerdasan artifisial</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:02:51 +0700</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>"Pak, buat apa belajar Malin Kundang? Kan kita semua sudah tahu ceritanya." Kalimat itu meluncur ringan dari ...</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678737/mempertemukan-malin-kundang-dan-kecerdasan-artifisial</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ilustrasi_ai_malinkundang.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PT Insight Investments hadapi sidang tuntutan kasus investasi fiktif</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:01:03 +0700</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PT Insight Investments Management (IIM) menghadapi sidang pembacaan tuntutan dalam perkara dugaan investasi fiktif PT ...</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678736/pt-insight-investments-hadapi-sidang-tuntutan-kasus-investasi-fiktif</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/22/1000155321.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial, terkini</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DJPb catat pembelanjaan di 75 KDKMP Sultra capai 1.055 kali transaksi</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:00:21 +0700</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Kantor Wilayah (Kanwil) Direktorat Jenderal Perbendaharaan (DJPb) Provinsi Sulawesi Tenggara (Sultra), mencatat ...</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678732/djpb-catat-pembelanjaan-di-75-kdkmp-sultra-capai-1055-kali-transaksi</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/2798be53-c5ca-4be6-bcf8-a2e9eb6c7488.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Dewan Pakar BPIP nilai Indonesia dapat jadi mediator Thailand-Kamboja</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:55:43 +0700</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Dewan Pakar Badan Pembinaan Ideologi Pancasila (BPIP) Bidang Strategi Hubungan Luar Negeri Darmansjah Djumala menilai ...</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678728/dewan-pakar-bpip-nilai-indonesia-dapat-jadi-mediator-thailand-kamboja</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/03/WhatsApp-Image-2025-06-14-at-22.18.20-1_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Eala petenis Filipina pertama juarai WTA 500</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:52:01 +0700</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Petenis muda Filipina Alexandra Eala mencatat sejarah dengan menjadi atlet pertama dari negaranya yang menjuarai ...</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678724/eala-petenis-filipina-pertama-juarai-wta-500</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_0142.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Envision Energy Raih Kontrak Proyek PLTB dengan Lokasi di Dekat Pantai Berkapasitas 200 MW di Vietnam</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:48:05 +0700</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Envision Energy, pemimpin teknologi hijau di pasar global, berhasil meraih kontrak proyek pembangkit listrik tenaga ...</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678723/envision-energy-raih-kontrak-proyek-pltb-dengan-lokasi-di-dekat-pantai-berkapasitas-200-mw-di-vietnam</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Envision-Energy-Vietnam.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Kontingen Indonesia di Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Rupiah pada Selasa pagi melemah jadi Rp18.029 per dolar AS</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:16:27 +0700</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar AS pada Selasa pagi, bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per ...</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678685/rupiah-pada-selasa-pagi-melemah-jadi-rp18029-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CORE: Penilaian kredit alternatif dapat perluas pembiayaan UMKM</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:58:42 +0700</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai pemanfaatan penilaian kredit ...</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678651/core-penilaian-kredit-alternatif-dapat-perluas-pembiayaan-umkm</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/realisasi-penyaluran-kur-umkm-2832719.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Indonesia-Uni Eropa bahas kesiapan regulasi Wajib Halal 2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:44:09 +0700</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Indonesia dan Uni Eropa membahas perkembangan regulasi serta kesiapan implementasi mandatori sertifikasi halal (Wajib ...</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678721/indonesia-uni-eropa-bahas-kesiapan-regulasi-wajib-halal-2026</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_0808.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Tapera: Pertumbuhan keluarga muda pendorong permintaan rumah subsidi</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:40:03 +0700</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Tabungan Perumahan Rakyat (BP Tapera) mengungkapkan pertumbuhan keluarga muda menjadi pendorong utama ...</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678716/tapera-pertumbuhan-keluarga-muda-pendorong-permintaan-rumah-subsidi</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1031.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Kemenko Pangan perkuat kerja sama kelautan dukung ketahanan pangan RI</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:37:19 +0700</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Kementerian Koordinator (Kemenko) Bidang Pangan memperkuat pengelolaan sumber daya maritim melalui penandatanganan lima ...</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678715/kemenko-pangan-perkuat-kerja-sama-kelautan-dukung-ketahanan-pangan-ri</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176713.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>LLV-NMAI jalin kerja sama kembangkan bisnis di Indonesia dan Jepang</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:31:29 +0700</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Living Lab Ventures (LLV) menjalin kemitraan dengan PT Nihon M&amp;A Center Indonesia (NMAI) terkait dukungan kedua ...</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678713/llv-nmai-jalin-kerja-sama-kembangkan-bisnis-di-indonesia-dan-jepang</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Foto-1-Living-Lab-Ventures-Bermitra-dengan-Nihon-M-A-Center-untuk-Memperkuat-Konektivitas-Investasi-IndonesianJepang-1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PIHPS: Harga cabai rawit Rp61.450/kg, telur ayam Rp31.800/kg</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:18:01 +0700</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Pusat Informasi Harga Pangan Strategis (PIHPS) Nasional yang dikelola Bank Indonesia, mencatat harga komoditas ...</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678693/pihps-harga-cabai-rawit-rp61450-kg-telur-ayam-rp31800-kg</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/8A4AD925-2D85-4C88-89BC-229C828F159D.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Kemnaker ajak masyarakat pacu kompetensi di Pelatihan Vokasi Nasional</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:15:02 +0700</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengajak masyarakat untuk meningkatkan kompetensi melalui Pelatihan Vokasi ...</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678657/kemnaker-ajak-masyarakat-pacu-kompetensi-di-pelatihan-vokasi-nasional</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/kesiapan-tenaga-kerja-di-balai-pelatihan-kerja-semarang-2828648.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ICPI soroti tantangan sektor pariwisata RI hadapi dinamika global</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 08:07:43 +0700</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Ikatan Cendikiawan Pariwisata Indonesia (ICPI) menyoroti sejumlah tantangan pariwisata Indonesia dalam menghadapi ...</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678652/icpi-soroti-tantangan-sektor-pariwisata-ri-hadapi-dinamika-global</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/26/kunjungan-turis-asing-ke-ntb-tumbuh-106-persen-1jdoh-dom.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IHSG Selasa dibuka menguat 20,28 poin ke posisi 6.254</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:06:02 +0700</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa pagi, dibuka menguat 20,28 poin atau 0,33 ...</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678675/ihsg-selasa-dibuka-menguat-2028-poin-ke-posisi-6254</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/Pembukaan-IHSG-usai-libur-Lebaran.jpg250326-Ada-3.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, Pemulutan Barat, Ogan Ilir (OI), Sumatera Selatan, Senin (3/8/2026). Petugas dibantu warga masih berupaya memadamkan kebakaran lahan di daerah tersebut. ANTARA FOTO/Nova Wahyudi/agr</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi melalui penerapan sistem verifikasi berbasis Quick Response (QR) berlapis. Wali Kota Palu Harianto Rasyid pada Senin (3/8), mengatakan, bahwa QR tersebut menjadi verifikasi tambahan guna melengkapi sistem QR Subsidi tepat milik Pertamina, sehingga setiap kendaraan yang nantinya memperoleh solar bersubsidi wajib lebih dahulu terdaftar pada Pemerintah Kota Palu. (Farah Khadija/M. Izfaldi/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
 (Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
         <is>
           <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
         <is>
           <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
 (Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
         <is>
           <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
 (Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G136" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
         <is>
           <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
 (Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
         <is>
           <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
         <is>
           <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
         <is>
           <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G142" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G143" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
         <is>
           <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
         <is>
           <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G145" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
         <is>
           <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
 (Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G150" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
         <is>
           <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G153" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
         <is>
           <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G157" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G158" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
         <is>
           <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G159" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
         <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
         <is>
           <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
         <is>
           <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
         <is>
           <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
         <is>
           <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B167" t="inlineStr">
         <is>
           <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
         <is>
           <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
         <is>
           <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
 (Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G168" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
 (Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B170" t="inlineStr">
         <is>
           <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Keluarga dengan dua balita selamat dari maut KMP Mutiara Sentosa 2</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 08:50:02 +0700</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>ANTARA - Pasangan suami istri muda, Karhap dan Krisnawati bersama dua anak balitanya sempat terpisah saat terjun ke laut menyelamatkan diri dari kapal penumpang KMP Mutiara Sentosa 2 yang terbakar di perairan sebelah utara Pulau Madura pada Minggu (2/8). Keluarga kecil asal Sidenreng Rappang, Sulawesi Selatan tersebut kembali berkumpul pada Senin (3/8) setelah dievakuasi oleh kapal kargo Meratus Pematang Siantar yang kebetulan melintas di lokasi musibah terjadi. (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677141/keluarga-dengan-dua-balita-selamat-dari-maut-kmp-mutiara-sentosa-2</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G112"/>
+  <autoFilter ref="A1:G170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Berita" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$G$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$234</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:H234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -429,6 +429,7 @@
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +468,11 @@
           <t>URL Gambar</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,6 +506,7 @@
           <t>https://img.antaranews.com/video/preview/2026/08/small/SAR-EVAKUASI-PENUMPANG-KM-MUTIARA-SANTOSA-2-YANG-TERBAKAR.jpg</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,6 +540,7 @@
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-TUNGGU-HASIL-PEMERIKSAAN-MARSELINO-JELANG-JAMU-VIETNAM.jpg</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -566,6 +574,7 @@
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_JOHN-HERDMAN-SEBUT-LAGA-RI-VS-VIETNAM-UJIAN-SANGAT-BERAT.jpg</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -599,6 +608,7 @@
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_BI-TARGETKAN-BAWA-WASTRA-SULSEL-KE-PASAR-GLOBAL.jpg</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -632,6 +642,7 @@
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_TONG-TONG-NIGHT-MARKET-MASUK-KEN-ANGKAT-UMKM-DAN-BUDAYA-LOKAL_1.jpg</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -666,6 +677,7 @@
           <t>https://img.antaranews.com/video/preview/2026/08/small/SANS_PERPUTARAN-EKONOMI-PIALA-PRESIDEN-2026-TEMBUS-RP70-MILIAR.jpg</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -699,6 +711,7 @@
           <t>https://img.antaranews.com/video/preview/2026/08/small/LEBIH-DARI-100-KORBAN-KMP-MUTIARA-SENTOSA-2-TIBA-DI-TANJUNG-PERAK.jpg</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -732,6 +745,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000035_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -765,6 +779,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000034_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -798,6 +813,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-22.21.21.jpeg</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -831,6 +847,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2025/01/01/IMG_0569.jpeg</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -864,6 +881,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-09.25.32.jpeg</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -897,6 +915,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/05/22/Janice.jpg</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -930,6 +949,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/menteri-sosial-tinjau-mpls-di-srt-i-sukoharjo-2831859.jpg</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -963,6 +983,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2024/09/22/Cuaca-Jakarta-290812-DDS-2.jpg</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -996,6 +1017,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/SAMSAT-Keliling-04082026.jpg</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1029,6 +1051,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/SIM-Keliling-04082026.jpg</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1062,6 +1085,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001085218.jpg</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1095,6 +1119,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001085217.jpg</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1128,6 +1153,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CuacaJakarta160710.jpg</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1161,6 +1187,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2016/01/20160105492.jpg</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1194,6 +1221,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/pearlescent-effect.jpeg</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1227,6 +1255,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-06-15-at-15.40.12.jpeg</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1260,6 +1289,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/dok.Pelatihan-sablon-Ojol-perempuan-Surabaya-4.jpg</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1293,6 +1323,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1000313673.jpg</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1326,6 +1357,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1001881799.jpg</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1359,6 +1391,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/InShot_20260803_192143033.jpg</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1392,6 +1425,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-07-27-at-12.27.07.jpeg</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1425,6 +1459,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/WhatsApp-Image-2026-08-03-at-13.37.37.jpeg</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1459,6 +1494,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000042507.jpg</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1492,6 +1528,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2024/11/20/Zulkieflimansyah.jpg</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1525,6 +1562,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/09a99626-b25f-41b2-8db2-de5355d06e86.jpeg</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1558,6 +1596,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002903990.jpg</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1591,6 +1630,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/06/09/Timnas-Indonesia-lawan-Mozambik-090626-MRH-07_1.jpg</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1624,6 +1664,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1657,6 +1698,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/Timnas-Indonesia-lawan-Vietnam-030826-Bay-11b.jpg</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1690,6 +1732,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/05/06/PLTS-100-gigawatt-sebagai-ketahanan-energi-nasional-060526-ANO-1.jpg</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1723,6 +1766,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/469463.jpg</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1756,6 +1800,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2025/06/16/thumbs_b_c_fa4ee57b38f4e1185b8b45a9cf369533.jpg</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1789,6 +1834,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/b7a68101-7bd7-4773-abde-ea464d4b03c8.jpeg</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1822,6 +1868,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1855,6 +1902,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1888,6 +1936,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1921,6 +1970,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1954,6 +2004,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1987,6 +2038,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ca5190e4-b594-4a68-9745-4223ef0c79fe.jpeg</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2020,6 +2072,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314092.jpg</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2053,6 +2106,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2086,6 +2140,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314079.jpg</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2119,6 +2174,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1003314068.jpg</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2152,6 +2208,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/06/04/piala-aff-u-19-indonesia-melawan-timor-leste-2800019.jpg</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2185,6 +2242,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pertandingan-timnas-indonesia-lawan-vietnam-2833611.jpg</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2218,6 +2276,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000030_20260803_CBMFN0A001.jpg</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2251,6 +2310,7 @@
           <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/IMG_1556.jpeg</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2284,39 +2344,41 @@
           <t>https://img.antaranews.com/video/preview/2026/08/small/KELUARGA-DENGAN-DUA-BALITA-SELAMAT-DARI-MAUT-KMP-MUTIARA-SENTOSA-2.jpg</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pakar: Harga minyak dunia turun jadi kesempatan menata aturan</t>
+          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:49:32 +0700</t>
+          <t>Tue, 04 Aug 2026 11:47:59 +0700</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Peneliti sekaligus dosen Fakultas Ekonomi dan Bisnis Universitas Padjadjaran Yayan Satyakti menilai turunnya harga ...</t>
+          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi ...</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678851/pakar-harga-minyak-dunia-turun-jadi-kesempatan-menata-aturan</t>
+          <t>https://www.antaranews.com/video/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2326,30 +2388,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
+          <t>Fiorentina pinjam Joao Mario dari Juventus</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:47:59 +0700</t>
+          <t>Tue, 04 Aug 2026 11:46:34 +0700</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi ...</t>
+          <t>Fiorentina mendatangkan bek sayap Joao Mario dari  Juventus dalamd status pinjaman dari Juvantus disertai opsi ...</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
+          <t>https://www.antaranews.com/berita/5678847/fiorentina-pinjam-joao-mario-dari-juventus</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_7595.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2359,30 +2422,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BPKH salurkan Rp2,06 triliun nilai manfaat ke 5,7 juta calon haji</t>
+          <t>Mendes bantah Kopdes Merah Putih matikan toko kelontong di daerah</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:47:58 +0700</t>
+          <t>Tue, 04 Aug 2026 11:44:03 +0700</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Badan Pengelola Keuangan Haji (BPKH) menyalurkan Nilai Manfaat Tahap I Tahun 2026 lebih dari Rp2,06 triliun kepada ...</t>
+          <t>Menteri Desa dan Pembangunan Daerah Tertinggal (Mendes PDT) Yandri Susanto secara tegas membantah kehadiran Koperasi ...</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678849/bpkh-salurkan-rp206-triliun-nilai-manfaat-ke-57-juta-calon-haji</t>
+          <t>https://www.antaranews.com/berita/5678845/mendes-bantah-kopdes-merah-putih-matikan-toko-kelontong-di-daerah</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176506.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002904686.jpg</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2392,30 +2456,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fiorentina pinjam Joao Mario dari Juventus</t>
+          <t>China luncurkan seleksi perdana pemimpin efisiensi karbon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:46:34 +0700</t>
+          <t>Tue, 04 Aug 2026 11:39:58 +0700</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fiorentina mendatangkan bek sayap Joao Mario dari  Juventus dalamd status pinjaman dari Juvantus disertai opsi ...</t>
+          <t>Pemberitahuan yang diterbitkan bersama oleh Kementerian Perindustrian dan Teknologi Informasi China serta dua lembaga ...</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678847/fiorentina-pinjam-joao-mario-dari-juventus</t>
+          <t>https://www.antaranews.com/berita/5678841/china-luncurkan-seleksi-perdana-pemimpin-efisiensi-karbon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_7595.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000003_20260804_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2425,30 +2490,31 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mendes bantah Kopdes Merah Putih matikan toko kelontong di daerah</t>
+          <t>Kejagung ungkap empat perusahaan digeledah Tim 9 milik Don Ritto</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:44:03 +0700</t>
+          <t>Tue, 04 Aug 2026 11:24:51 +0700</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Menteri Desa dan Pembangunan Daerah Tertinggal (Mendes PDT) Yandri Susanto secara tegas membantah kehadiran Koperasi ...</t>
+          <t>Kejaksaan Agung mengungkapkan bahwa empat perusahaan yang digeledah tim penyidik (Tim 9) pada Senin (3/8) merupakan ...</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678845/mendes-bantah-kopdes-merah-putih-matikan-toko-kelontong-di-daerah</t>
+          <t>https://www.antaranews.com/berita/5678825/kejagung-ungkap-empat-perusahaan-digeledah-tim-9-milik-don-ritto</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002904686.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087161.jpg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2458,63 +2524,65 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>China luncurkan seleksi perdana pemimpin efisiensi karbon</t>
+          <t>Polda Kalsel tangkap jaringan Fredy Pratama selundupkan 32 kg sabu</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:39:58 +0700</t>
+          <t>Tue, 04 Aug 2026 11:24:07 +0700</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pemberitahuan yang diterbitkan bersama oleh Kementerian Perindustrian dan Teknologi Informasi China serta dua lembaga ...</t>
+          <t>Direktorat Reserse Narkoba Polda Kalimantan Selatan menangkap dua anggota jaringan narkotika internasional Fredy ...</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678841/china-luncurkan-seleksi-perdana-pemimpin-efisiensi-karbon</t>
+          <t>https://www.antaranews.com/berita/5678824/polda-kalsel-tangkap-jaringan-fredy-pratama-selundupkan-32-kg-sabu</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000003_20260804_CBMFN0A001.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_114833.jpg</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wuling sediakan "test drive" mobil-mobil terbaru di GIIAS 2026</t>
+          <t>Michigan catat dua kematian akibat wabah siklosporiasis</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
+          <t>Tue, 04 Aug 2026 11:22:00 +0700</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pabrikan otomotif asal China Wuling Motors menyediakan aneka mobil keluaran terbaru mereka untuk diuji coba ...</t>
+          <t>Dua orang meninggal akibat siklosporiasis di Michigan di tengah wabah yang melanda sejumlah negara bagian Amerika ...</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678837/wuling-sediakan-test-drive-mobil-mobil-terbaru-di-giias-2026</t>
+          <t>https://www.antaranews.com/berita/5678820/michigan-catat-dua-kematian-akibat-wabah-siklosporiasis</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pada-area-test-drive-Wuling-menyediakan-beragam-lini-kendaraan-sehingga-pengunjung-dapat-merasakan-secara-langsung-performa-kenyamanan-serta-teknologi-yang-dihadirkan.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2524,30 +2592,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Aldila jadi petenis Indonesia yang pertama juarai DC Open</t>
+          <t>Fulham datangkan Cesar Palacios dari Real Madrid</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
+          <t>Tue, 04 Aug 2026 11:19:58 +0700</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Petenis Indonesia Aldila Sutjiadi mencatatkan sejarah setelah menjuarai nomor ganda putri turnamen Mubadala DC Open ...</t>
+          <t>Fulham mendaratkan gelandang serang Cesar Palacios dari Real Madrid dalak kontrak tujuh tahun dan menggunakan nomor ...</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678836/aldila-jadi-petenis-indonesia-yang-pertama-juarai-dc-open</t>
+          <t>https://www.antaranews.com/berita/5678819/fulham-datangkan-cesar-palacios-dari-real-madrid</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/IMG_4155.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/image-35.jpg</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2557,63 +2626,65 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kementan siapkan Juknis penyerapan telur bagi SPPG Rp26.500/kg</t>
+          <t>Kemnaker: Magang Nasional 2026 perkuat link and match dengan industri</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:26:36 +0700</t>
+          <t>Tue, 04 Aug 2026 11:17:05 +0700</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kementerian Pertanian (Kementan) menyiapkan petunjuk teknis (Juknis) penyerapan telur oleh seluruh Satuan Pelayanan ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan penyelenggaraan Magang Nasional (MagangHub) 2026 akan fokus pada ...</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678831/kementan-siapkan-juknis-penyerapan-telur-bagi-sppg-rp26500-kg</t>
+          <t>https://www.antaranews.com/berita/5678811/kemnaker-magang-nasional-2026-perkuat-link-and-match-dengan-industri</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/4FB30E01-205C-4253-9C88-5373F761A9FB.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/26/1000096004.jpg</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Panda Bond dan sinyal kepercayaan investasi global</t>
+          <t>BRIN dukung riset panel surya generasi baru untuk kemandirian energi</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:26:35 +0700</t>
+          <t>Tue, 04 Aug 2026 11:15:31 +0700</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Di tengah ketidakpastian ekonomi global yang semakin kompleks, pemerintah Indonesia perlu memastikan bahwa ...</t>
+          <t>Badan Riset dan Inovasi Nasional (BRIN) mengkaji peluang industri manufaktur panel surya generasi baru berteknologi ...</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678827/panda-bond-dan-sinyal-kepercayaan-investasi-global</t>
+          <t>https://www.antaranews.com/berita/5678807/brin-dukung-riset-panel-surya-generasi-baru-untuk-kemandirian-energi</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/permintaan-pembelian-obligasi-global-capai-46-miliar-dolar-as-2806089.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/21/plts-terpadu-di-pulau-labengki-kecil-2795679.jpg</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2623,30 +2694,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kejagung ungkap empat perusahaan digeledah Tim 9 milik Don Ritto</t>
+          <t>Hotel di Bangkok manfaatkan bangunan bersejarah bekas kantor pabean</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:24:51 +0700</t>
+          <t>Tue, 04 Aug 2026 11:15:06 +0700</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kejaksaan Agung mengungkapkan bahwa empat perusahaan yang digeledah tim penyidik (Tim 9) pada Senin (3/8) merupakan ...</t>
+          <t>Hotel yang memanfaatkan bangunan bersejarah custom house (kantor pabean) di Bangkok, Thailand, ...</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678825/kejagung-ungkap-empat-perusahaan-digeledah-tim-9-milik-don-ritto</t>
+          <t>https://www.antaranews.com/berita/5678804/hotel-di-bangkok-manfaatkan-bangunan-bersejarah-bekas-kantor-pabean</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087161.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000697011.jpg</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2656,63 +2728,65 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Polda Kalsel tangkap jaringan Fredy Pratama selundupkan 32 kg sabu</t>
+          <t>Politisi Finlandia desak Uni Eropa setop bantuan militer ke Ukraina</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:24:07 +0700</t>
+          <t>Tue, 04 Aug 2026 11:12:11 +0700</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Direktorat Reserse Narkoba Polda Kalimantan Selatan menangkap dua anggota jaringan narkotika internasional Fredy ...</t>
+          <t>Politisi Finlandia dari Partai Freedom Alliance, Armando Mema, mendesak Uni Eropa menghentikan bantuan militer kepada ...</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678824/polda-kalsel-tangkap-jaringan-fredy-pratama-selundupkan-32-kg-sabu</t>
+          <t>https://www.antaranews.com/berita/5678801/politisi-finlandia-desak-uni-eropa-setop-bantuan-militer-ke-ukraina</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_114833.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/04/14/reuters_finnishflag.jpg</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ekonom proyeksikan pangsa NEV capai 31,7 persen penjualan mobil 2026</t>
+          <t>Bidik Pasar "Aftermarket" Otomotif, ZF Aftermarket Gandeng MKN sebagai Distributor Tunggal TRW di Indonesia</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:22:55 +0700</t>
+          <t>Tue, 04 Aug 2026 11:11:29 +0700</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ekonom PT Bank Danamon Indonesia Tbk memproyeksikan pangsa kendaraan energi baru (new energy vehicle/NEV) mencapai 31,7 ...</t>
+          <t>Juli 25, ZF Aftermarket, produsen komponen otomotif global, terus memperkuat kiprahnya di pasar otomotif ...</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678821/ekonom-proyeksikan-pangsa-nev-capai-317-persen-penjualan-mobil-2026</t>
+          <t>https://www.antaranews.com/berita/5678800/bidik-pasar-aftermarket-otomotif-zf-aftermarket-gandeng-mkn-sebagai-distributor-tunggal-trw-di-indonesia</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penjualan-kendaraan-di-semester-1-2026-meningkat-2831868.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Aftermarket-Otomotif.jpg</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2722,96 +2796,99 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Michigan catat dua kematian akibat wabah siklosporiasis</t>
+          <t>Jawab tantangan ketenagakerjaan, Wamendikti dorong transformasi vokasi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:22:00 +0700</t>
+          <t>Tue, 04 Aug 2026 11:04:45 +0700</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dua orang meninggal akibat siklosporiasis di Michigan di tengah wabah yang melanda sejumlah negara bagian Amerika ...</t>
+          <t>Wakil Menteri Pendidikan Tinggi, Sains, dan Teknologi (Wamendiktisaintek) Fauzan menegaskan penguatan karakter dan ...</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678820/michigan-catat-dua-kematian-akibat-wabah-siklosporiasis</t>
+          <t>https://www.antaranews.com/berita/5678797/jawab-tantangan-ketenagakerjaan-wamendikti-dorong-transformasi-vokasi</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/AmerikaSerikatBenderaPixabay.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-14.08.44.jpeg</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fulham datangkan Cesar Palacios dari Real Madrid</t>
+          <t>BMKG: El Nino 2026 berpotensi menjadi sangat kuat</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:19:58 +0700</t>
+          <t>Tue, 04 Aug 2026 10:59:51 +0700</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fulham mendaratkan gelandang serang Cesar Palacios dari Real Madrid dalak kontrak tujuh tahun dan menggunakan nomor ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyatakan El Nino 2026 telah mencapai kategori kuat dan masih ...</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678819/fulham-datangkan-cesar-palacios-dari-real-madrid</t>
+          <t>https://www.antaranews.com/berita/5678791/bmkg-el-nino-2026-berpotensi-menjadi-sangat-kuat</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/image-35.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bmkg-sampaikan-prospek-musim-kemarau-2026-1oo3c-dom.jpg</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, photo, terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BPS proyeksikan produksi beras nasional capai 28,71 Juta ton hingga September 2026, stok dipastikan tetap aman</t>
+          <t>Hankook catat pertumbuhan penjualan 130 persen pada semester I-2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:19:05 +0700</t>
+          <t>Tue, 04 Aug 2026 10:54:12 +0700</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pekerja menata karung berisi cadangan beras pemerintah di gudang Perum Bulog Cabang Meulaboh, Aceh Barat, Aceh, Selasa ...</t>
+          <t>PT Hankook Tire Sales Indonesia mencatat pertumbuhan penjualan sebesar 130 persen pada segmen passenger car radial ...</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678815/bps-proyeksikan-produksi-beras-nasional-capai-2871-juta-ton-hingga-september-2026-stok-dipastikan-tetap-aman</t>
+          <t>https://otomotif.antaranews.com/berita/5678789/hankook-catat-pertumbuhan-penjualan-130-persen-pada-semester-i-2026</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Prediksi-produksi-beras-nasional-040826-Syf-3.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Picture_3_-_Strategi_The_Right_Tire_for_The_Right_Vehicle_Antar_Hankook_Tire_Sales_Indonesia_Tumbuh_130_pada_Semester_Pertama_2026.jpg</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2821,63 +2898,65 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kemnaker: Magang Nasional 2026 perkuat link and match dengan industri</t>
+          <t>Kementan-industri pakan tunda kenaikan harga lindungi peternak ayam</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:17:05 +0700</t>
+          <t>Tue, 04 Aug 2026 10:54:11 +0700</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengatakan penyelenggaraan Magang Nasional (MagangHub) 2026 akan fokus pada ...</t>
+          <t>Kementerian Pertanian (Kementan) bersama industri pakan menyepakati penundaan kenaikan harga pakan ayam sebagai langkah ...</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678811/kemnaker-magang-nasional-2026-perkuat-link-and-match-dengan-industri</t>
+          <t>https://www.antaranews.com/berita/5678788/kementan-industri-pakan-tunda-kenaikan-harga-lindungi-peternak-ayam</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/11/26/1000096004.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/6884F332-B2BC-4196-90E6-BB4ACC0370D3.jpeg</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rupiah Selasa melemah dipicu kenaikan harga minyak global</t>
+          <t>Bareskrim gagalkan peredaran 86,3 kg sabu jaringan Riau-Sumsel</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:15:57 +0700</t>
+          <t>Tue, 04 Aug 2026 10:53:40 +0700</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Selasa pagi bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per dolar AS ...</t>
+          <t>Direktorat Tindak Pidana Narkoba (Dittipidnarkoba) Bareskrim Polri menggagalkan peredaran 86,3 kilogram sabu dan 5.171 ...</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678808/rupiah-selasa-melemah-dipicu-kenaikan-harga-minyak-global</t>
+          <t>https://www.antaranews.com/berita/5678784/bareskrim-gagalkan-peredaran-863-kg-sabu-jaringan-riau-sumsel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/nilai-tukar-rupiah-melemah-44-poin-2821215.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087157.jpg</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2887,30 +2966,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BRIN dukung riset panel surya generasi baru untuk kemandirian energi</t>
+          <t>NOL World Luncurkan Platform Pemesanan Akomodasi bagi Penggemar K-Pop yang Berkunjung ke Korea Selatan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:15:31 +0700</t>
+          <t>Tue, 04 Aug 2026 10:49:24 +0700</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Badan Riset dan Inovasi Nasional (BRIN) mengkaji peluang industri manufaktur panel surya generasi baru berteknologi ...</t>
+          <t>NOL World, platform perjalanan internasional (inbound travel) yang dikelola NOL Universe di bawah kepemimpinan ...</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678807/brin-dukung-riset-panel-surya-generasi-baru-untuk-kemandirian-energi</t>
+          <t>https://www.antaranews.com/berita/5678781/nol-world-luncurkan-platform-pemesanan-akomodasi-bagi-penggemar-k-pop-yang-berkunjung-ke-korea-selatan</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/21/plts-terpadu-di-pulau-labengki-kecil-2795679.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/NOL-World.jpg</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2920,30 +3000,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hotel di Bangkok manfaatkan bangunan bersejarah bekas kantor pabean</t>
+          <t>China-ASEAN Alliance for Lifelong Learning Resmi Diluncurkan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:15:06 +0700</t>
+          <t>Tue, 04 Aug 2026 10:43:50 +0700</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hotel yang memanfaatkan bangunan bersejarah custom house (kantor pabean) di Bangkok, Thailand, ...</t>
+          <t>Artikel berita dari CNS: 
+China-ASEAN Alliance for Lifelong Learning resmi diluncurkan dalam edisi ...</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678804/hotel-di-bangkok-manfaatkan-bangunan-bersejarah-bekas-kantor-pabean</t>
+          <t>https://www.antaranews.com/berita/5678780/china-asean-alliance-for-lifelong-learning-resmi-diluncurkan</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000697011.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/China-ASEAN-Alliance-CAECW.jpg</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2953,30 +3035,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Politisi Finlandia desak Uni Eropa setop bantuan militer ke Ukraina</t>
+          <t>Polres Tangerang Selatan musnahkan 46 juta butir obat keras daftar G</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:12:11 +0700</t>
+          <t>Tue, 04 Aug 2026 10:40:26 +0700</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Politisi Finlandia dari Partai Freedom Alliance, Armando Mema, mendesak Uni Eropa menghentikan bantuan militer kepada ...</t>
+          <t>Polres Tangerang Selatan memusnahkan 46 juta butir obat keras ilegal daftar G yang merupakan hasil pengungkapan kasus ...</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678801/politisi-finlandia-desak-uni-eropa-setop-bantuan-militer-ke-ukraina</t>
+          <t>https://www.antaranews.com/berita/5678777/polres-tangerang-selatan-musnahkan-46-juta-butir-obat-keras-daftar-g</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/04/14/reuters_finnishflag.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ac70ac48-dc1d-439b-9c43-7f76e1b5159d.jpeg</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2986,30 +3069,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bidik Pasar "Aftermarket" Otomotif, ZF Aftermarket Gandeng MKN sebagai Distributor Tunggal TRW di Indonesia</t>
+          <t>Cathay United Bank dan Indovina Bank Dorong Penguatan Daya Tahan Bisnis di Tengah Kondisi Dunia yang Tidak Menentu</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:11:29 +0700</t>
+          <t>Tue, 04 Aug 2026 10:37:40 +0700</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Juli 25, ZF Aftermarket, produsen komponen otomotif global, terus memperkuat kiprahnya di pasar otomotif ...</t>
+          <t>Kantor Cabang Cathay United Bank di Ho Chi Minh City (CUBHCM) bersama Indovina Bank Ltd. (IVB) menggelar seminar ...</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678800/bidik-pasar-aftermarket-otomotif-zf-aftermarket-gandeng-mkn-sebagai-distributor-tunggal-trw-di-indonesia</t>
+          <t>https://www.antaranews.com/berita/5678775/cathay-united-bank-dan-indovina-bank-dorong-penguatan-daya-tahan-bisnis-di-tengah-kondisi-dunia-yang-tidak-menentu</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Aftermarket-Otomotif.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Cathay-United-Bank-x-Indovina-Bank.jpg</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3019,96 +3103,99 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jawab tantangan ketenagakerjaan, Wamendikti dorong transformasi vokasi</t>
+          <t>Utusan perdamaian AS desak Israel hentikan serangan di Gaza</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:04:45 +0700</t>
+          <t>Tue, 04 Aug 2026 10:34:11 +0700</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wakil Menteri Pendidikan Tinggi, Sains, dan Teknologi (Wamendiktisaintek) Fauzan menegaskan penguatan karakter dan ...</t>
+          <t>Utusan khusus Dewan Perdamaian (Board of Peace) pimpinan Amerika Serikat untuk Gaza, Nickolay Mladenov, dan penasihat ...</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678797/jawab-tantangan-ketenagakerjaan-wamendikti-dorong-transformasi-vokasi</t>
+          <t>https://www.antaranews.com/berita/5678773/utusan-perdamaian-as-desak-israel-hentikan-serangan-di-gaza</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-14.08.44.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/thumbs_b_c_c8afe6335c568927cfc257757ed34ecc.jpg</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BMKG: El Nino 2026 berpotensi menjadi sangat kuat</t>
+          <t>Qatar serukan koordinasi Teluk jalankan kesepakatan AS-Iran</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:59:51 +0700</t>
+          <t>Tue, 04 Aug 2026 10:31:50 +0700</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyatakan El Nino 2026 telah mencapai kategori kuat dan masih ...</t>
+          <t>Qatar menyerukan koordinasi yang lebih erat di antara negara-negara Teluk untuk melaksanakan nota kesepahaman antara ...</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678791/bmkg-el-nino-2026-berpotensi-menjadi-sangat-kuat</t>
+          <t>https://www.antaranews.com/berita/5678772/qatar-serukan-koordinasi-teluk-jalankan-kesepakatan-as-iran</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bmkg-sampaikan-prospek-musim-kemarau-2026-1oo3c-dom.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/23/Menlu-Qatar.jpg</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hankook catat pertumbuhan penjualan 130 persen pada semester I-2026</t>
+          <t>Trump: bukan Iran, tetapi AS yang akan pungut biaya di Hormuz</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:54:12 +0700</t>
+          <t>Tue, 04 Aug 2026 10:27:04 +0700</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PT Hankook Tire Sales Indonesia mencatat pertumbuhan penjualan sebesar 130 persen pada segmen passenger car radial ...</t>
+          <t>Presiden Amerika Serikat Donald Trump mengatakan Washington tidak akan membiarkan Iran mengenakan biaya terhadap ...</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678789/hankook-catat-pertumbuhan-penjualan-130-persen-pada-semester-i-2026</t>
+          <t>https://www.antaranews.com/berita/5678768/trump-bukan-iran-tetapi-as-yang-akan-pungut-biaya-di-hormuz</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Picture_3_-_Strategi_The_Right_Tire_for_The_Right_Vehicle_Antar_Hankook_Tire_Sales_Indonesia_Tumbuh_130_pada_Semester_Pertama_2026.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/AA-20260802-42124703-42124695-TRUMPTARGETING_BANNER_DISPLAYED_IN_TEHRANS_AZADI_SQUARE.jpg</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3118,30 +3205,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kementan-industri pakan tunda kenaikan harga lindungi peternak ayam</t>
+          <t>Selasa ini harga emas Antam kembali turun menjadi Rp2,603 juta/gr</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:54:11 +0700</t>
+          <t>Tue, 04 Aug 2026 10:26:38 +0700</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kementerian Pertanian (Kementan) bersama industri pakan menyepakati penundaan kenaikan harga pakan ayam sebagai langkah ...</t>
+          <t>Harga emas Antam, yang dipantau dari laman Logam Mulia, di Jakarta, Selasa pukul 10.14 WIB turun Rp7.000 menjadi ...</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678788/kementan-industri-pakan-tunda-kenaikan-harga-lindungi-peternak-ayam</t>
+          <t>https://www.antaranews.com/berita/5678767/selasa-ini-harga-emas-antam-kembali-turun-menjadi-rp2603-juta-gr</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/6884F332-B2BC-4196-90E6-BB4ACC0370D3.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/harga-emas-antam-turun-2829987.jpg</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3151,63 +3239,65 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bareskrim gagalkan peredaran 86,3 kg sabu jaringan Riau-Sumsel</t>
+          <t>Trump beri Iran peluang terakhir untuk capai kesepakatan damai</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:53:40 +0700</t>
+          <t>Tue, 04 Aug 2026 10:23:40 +0700</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Direktorat Tindak Pidana Narkoba (Dittipidnarkoba) Bareskrim Polri menggagalkan peredaran 86,3 kilogram sabu dan 5.171 ...</t>
+          <t>Presiden Amerika Serikat Donald Trump mengatakan bahwa Washington masih memberikan kesempatan kepada Iran untuk ...</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678784/bareskrim-gagalkan-peredaran-863-kg-sabu-jaringan-riau-sumsel</t>
+          <t>https://www.antaranews.com/berita/5678765/trump-beri-iran-peluang-terakhir-untuk-capai-kesepakatan-damai</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087157.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1001014481.jpg</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NOL World Luncurkan Platform Pemesanan Akomodasi bagi Penggemar K-Pop yang Berkunjung ke Korea Selatan</t>
+          <t>PTPP bangun SMA Unggul Garuda Konawe Selatan senilai Rp234,28 miliar</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:49:24 +0700</t>
+          <t>Tue, 04 Aug 2026 10:18:53 +0700</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NOL World, platform perjalanan internasional (inbound travel) yang dikelola NOL Universe di bawah kepemimpinan ...</t>
+          <t>BUMN bidang konstruksi dan investasi PT PP (Persero) Tbk (PTPP) membangun fasilitas SMA Unggul Garuda Konawe Selatan, ...</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678781/nol-world-luncurkan-platform-pemesanan-akomodasi-bagi-penggemar-k-pop-yang-berkunjung-ke-korea-selatan</t>
+          <t>https://www.antaranews.com/berita/5678763/ptpp-bangun-sma-unggul-garuda-konawe-selatan-senilai-rp23428-miliar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/NOL-World.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176733.jpg</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3217,31 +3307,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>China-ASEAN Alliance for Lifelong Learning Resmi Diluncurkan</t>
+          <t>Pemerintah diminta buka kembali penempatan pekerja migran di Timteng</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:43:50 +0700</t>
+          <t>Tue, 04 Aug 2026 10:17:52 +0700</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Artikel berita dari CNS: 
-China-ASEAN Alliance for Lifelong Learning resmi diluncurkan dalam edisi ...</t>
+          <t>Sejumlah organisasi kemasyarakatan, asosiasi pejuang dan pemerhati hak pekerja migran Indonesia meminta pemerintah bisa ...</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678780/china-asean-alliance-for-lifelong-learning-resmi-diluncurkan</t>
+          <t>https://www.antaranews.com/berita/5678759/pemerintah-diminta-buka-kembali-penempatan-pekerja-migran-di-timteng</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/China-ASEAN-Alliance-CAECW.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469679.jpg</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3251,63 +3341,65 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Polres Tangerang Selatan musnahkan 46 juta butir obat keras daftar G</t>
+          <t>XTransfer Tercantum dalam Daftar "World's Top Fintech Companies 2026" versi CNBC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:40:26 +0700</t>
+          <t>Tue, 04 Aug 2026 10:14:24 +0700</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Polres Tangerang Selatan memusnahkan 46 juta butir obat keras ilegal daftar G yang merupakan hasil pengungkapan kasus ...</t>
+          <t>XTransfer, platform pembayaran perdagangan lintasnegara untuk segmen B2B terbesar di dunia, untuk pertama kalinya ...</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678777/polres-tangerang-selatan-musnahkan-46-juta-butir-obat-keras-daftar-g</t>
+          <t>https://www.antaranews.com/berita/5678757/xtransfer-tercantum-dalam-daftar-worlds-top-fintech-companies-2026-versi-cnbc</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ac70ac48-dc1d-439b-9c43-7f76e1b5159d.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CNBC-s-World-s-Top-Fintech.jpg</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cathay United Bank dan Indovina Bank Dorong Penguatan Daya Tahan Bisnis di Tengah Kondisi Dunia yang Tidak Menentu</t>
+          <t>China tetapkan standar akurasi indikator kesehatan baterai EV</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:37:40 +0700</t>
+          <t>Tue, 04 Aug 2026 10:13:45 +0700</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kantor Cabang Cathay United Bank di Ho Chi Minh City (CUBHCM) bersama Indovina Bank Ltd. (IVB) menggelar seminar ...</t>
+          <t>China mengungkap rincian persyaratan implementasi standar nasional yang direkomendasikan GB/T 46991.1-2025, yang ...</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678775/cathay-united-bank-dan-indovina-bank-dorong-penguatan-daya-tahan-bisnis-di-tengah-kondisi-dunia-yang-tidak-menentu</t>
+          <t>https://otomotif.antaranews.com/berita/5678753/china-tetapkan-standar-akurasi-indikator-kesehatan-baterai-ev</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Cathay-United-Bank-x-Indovina-Bank.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/10/cdde688d-ce12-408e-9408-3ca6363285a5.jpeg</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3317,63 +3409,65 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Utusan perdamaian AS desak Israel hentikan serangan di Gaza</t>
+          <t>Konflik Rusia-Ukraina meningkat di dekat Laut Hitam</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:34:11 +0700</t>
+          <t>Tue, 04 Aug 2026 10:12:18 +0700</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Utusan khusus Dewan Perdamaian (Board of Peace) pimpinan Amerika Serikat untuk Gaza, Nickolay Mladenov, dan penasihat ...</t>
+          <t>Konflik antara Rusia dan Ukraina telah meningkat di wilayah Laut Hitam dan kawasan pesisirnya, menurut keterangan pihak ...</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678773/utusan-perdamaian-as-desak-israel-hentikan-serangan-di-gaza</t>
+          <t>https://www.antaranews.com/berita/5678751/konflik-rusia-ukraina-meningkat-di-dekat-laut-hitam</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/thumbs_b_c_c8afe6335c568927cfc257757ed34ecc.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/12/19/Xinhua-News-Agency.jpg</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Qatar serukan koordinasi Teluk jalankan kesepakatan AS-Iran</t>
+          <t>Menhub pastikan hak korban dan keluarga KMP Mutiara Sentosa terpenuhi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:31:50 +0700</t>
+          <t>Tue, 04 Aug 2026 10:11:14 +0700</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Qatar menyerukan koordinasi yang lebih erat di antara negara-negara Teluk untuk melaksanakan nota kesepahaman antara ...</t>
+          <t>Menteri Perhubungan (Menhub) Dudy Purwagandhi memastikan pemerintah mengawal pemenuhan seluruh hak korban dan keluarga ...</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678772/qatar-serukan-koordinasi-teluk-jalankan-kesepakatan-as-iran</t>
+          <t>https://www.antaranews.com/berita/5678744/menhub-pastikan-hak-korban-dan-keluarga-kmp-mutiara-sentosa-terpenuhi</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/23/Menlu-Qatar.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/FAC78DF1-7644-4B13-80B9-6D4721546F42.jpeg</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3383,63 +3477,65 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Trump: bukan Iran, tetapi AS yang akan pungut biaya di Hormuz</t>
+          <t>Perwakilan ICRC untuk Myanmar temui Aung San Suu Kyi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:27:04 +0700</t>
+          <t>Tue, 04 Aug 2026 10:04:02 +0700</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Presiden Amerika Serikat Donald Trump mengatakan Washington tidak akan membiarkan Iran mengenakan biaya terhadap ...</t>
+          <t>Perwakilan Tetap Komite Palang Merah Internasional (International Committee of the Red Cross/ICRC) untuk Myanmar, ...</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678768/trump-bukan-iran-tetapi-as-yang-akan-pungut-biaya-di-hormuz</t>
+          <t>https://www.antaranews.com/berita/5678741/perwakilan-icrc-untuk-myanmar-temui-aung-san-suu-kyi</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/AA-20260802-42124703-42124695-TRUMPTARGETING_BANNER_DISPLAYED_IN_TEHRANS_AZADI_SQUARE.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000029_20260803_CBMFN0A001_2.v1.jpg</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Selasa ini harga emas Antam kembali turun menjadi Rp2,603 juta/gr</t>
+          <t>Mempertemukan Malin Kundang dan kecerdasan artifisial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:26:38 +0700</t>
+          <t>Tue, 04 Aug 2026 10:02:51 +0700</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Harga emas Antam, yang dipantau dari laman Logam Mulia, di Jakarta, Selasa pukul 10.14 WIB turun Rp7.000 menjadi ...</t>
+          <t>"Pak, buat apa belajar Malin Kundang? Kan kita semua sudah tahu ceritanya." Kalimat itu meluncur ringan dari ...</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678767/selasa-ini-harga-emas-antam-kembali-turun-menjadi-rp2603-juta-gr</t>
+          <t>https://www.antaranews.com/berita/5678737/mempertemukan-malin-kundang-dan-kecerdasan-artifisial</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/harga-emas-antam-turun-2829987.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ilustrasi_ai_malinkundang.jpg</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3449,63 +3545,65 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Trump beri Iran peluang terakhir untuk capai kesepakatan damai</t>
+          <t>PT Insight Investments hadapi sidang tuntutan kasus investasi fiktif</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:23:40 +0700</t>
+          <t>Tue, 04 Aug 2026 10:01:03 +0700</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Presiden Amerika Serikat Donald Trump mengatakan bahwa Washington masih memberikan kesempatan kepada Iran untuk ...</t>
+          <t>PT Insight Investments Management (IIM) menghadapi sidang pembacaan tuntutan dalam perkara dugaan investasi fiktif PT ...</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678765/trump-beri-iran-peluang-terakhir-untuk-capai-kesepakatan-damai</t>
+          <t>https://www.antaranews.com/berita/5678736/pt-insight-investments-hadapi-sidang-tuntutan-kasus-investasi-fiktif</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1001014481.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/22/1000155321.jpg</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PTPP bangun SMA Unggul Garuda Konawe Selatan senilai Rp234,28 miliar</t>
+          <t>Dewan Pakar BPIP nilai Indonesia dapat jadi mediator Thailand-Kamboja</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:18:53 +0700</t>
+          <t>Tue, 04 Aug 2026 09:55:43 +0700</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BUMN bidang konstruksi dan investasi PT PP (Persero) Tbk (PTPP) membangun fasilitas SMA Unggul Garuda Konawe Selatan, ...</t>
+          <t>Dewan Pakar Badan Pembinaan Ideologi Pancasila (BPIP) Bidang Strategi Hubungan Luar Negeri Darmansjah Djumala menilai ...</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678763/ptpp-bangun-sma-unggul-garuda-konawe-selatan-senilai-rp23428-miliar</t>
+          <t>https://www.antaranews.com/berita/5678728/dewan-pakar-bpip-nilai-indonesia-dapat-jadi-mediator-thailand-kamboja</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176733.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/03/WhatsApp-Image-2025-06-14-at-22.18.20-1_1.jpeg</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3515,30 +3613,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pemerintah diminta buka kembali penempatan pekerja migran di Timteng</t>
+          <t>Eala petenis Filipina pertama juarai WTA 500</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:17:52 +0700</t>
+          <t>Tue, 04 Aug 2026 09:52:01 +0700</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sejumlah organisasi kemasyarakatan, asosiasi pejuang dan pemerhati hak pekerja migran Indonesia meminta pemerintah bisa ...</t>
+          <t>Petenis muda Filipina Alexandra Eala mencatat sejarah dengan menjadi atlet pertama dari negaranya yang menjuarai ...</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678759/pemerintah-diminta-buka-kembali-penempatan-pekerja-migran-di-timteng</t>
+          <t>https://www.antaranews.com/berita/5678724/eala-petenis-filipina-pertama-juarai-wta-500</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469679.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_0142.jpg</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3548,2516 +3647,5284 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>XTransfer Tercantum dalam Daftar "World's Top Fintech Companies 2026" versi CNBC</t>
+          <t>Envision Energy Raih Kontrak Proyek PLTB dengan Lokasi di Dekat Pantai Berkapasitas 200 MW di Vietnam</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:14:24 +0700</t>
+          <t>Tue, 04 Aug 2026 09:48:05 +0700</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>XTransfer, platform pembayaran perdagangan lintasnegara untuk segmen B2B terbesar di dunia, untuk pertama kalinya ...</t>
+          <t>Envision Energy, pemimpin teknologi hijau di pasar global, berhasil meraih kontrak proyek pembangkit listrik tenaga ...</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678757/xtransfer-tercantum-dalam-daftar-worlds-top-fintech-companies-2026-versi-cnbc</t>
+          <t>https://www.antaranews.com/berita/5678723/envision-energy-raih-kontrak-proyek-pltb-dengan-lokasi-di-dekat-pantai-berkapasitas-200-mw-di-vietnam</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CNBC-s-World-s-Top-Fintech.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Envision-Energy-Vietnam.jpg</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>China tetapkan standar akurasi indikator kesehatan baterai EV</t>
+          <t>Indonesia-Uni Eropa bahas kesiapan regulasi Wajib Halal 2026</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:13:45 +0700</t>
+          <t>Tue, 04 Aug 2026 09:44:09 +0700</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>China mengungkap rincian persyaratan implementasi standar nasional yang direkomendasikan GB/T 46991.1-2025, yang ...</t>
+          <t>Indonesia dan Uni Eropa membahas perkembangan regulasi serta kesiapan implementasi mandatori sertifikasi halal (Wajib ...</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678753/china-tetapkan-standar-akurasi-indikator-kesehatan-baterai-ev</t>
+          <t>https://www.antaranews.com/berita/5678721/indonesia-uni-eropa-bahas-kesiapan-regulasi-wajib-halal-2026</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/01/10/cdde688d-ce12-408e-9408-3ca6363285a5.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_0808.jpeg</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Konflik Rusia-Ukraina meningkat di dekat Laut Hitam</t>
+          <t>Tapera: Pertumbuhan keluarga muda pendorong permintaan rumah subsidi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:12:18 +0700</t>
+          <t>Tue, 04 Aug 2026 09:40:03 +0700</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Konflik antara Rusia dan Ukraina telah meningkat di wilayah Laut Hitam dan kawasan pesisirnya, menurut keterangan pihak ...</t>
+          <t>Badan Pengelola Tabungan Perumahan Rakyat (BP Tapera) mengungkapkan pertumbuhan keluarga muda menjadi pendorong utama ...</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678751/konflik-rusia-ukraina-meningkat-di-dekat-laut-hitam</t>
+          <t>https://www.antaranews.com/berita/5678716/tapera-pertumbuhan-keluarga-muda-pendorong-permintaan-rumah-subsidi</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2021/12/19/Xinhua-News-Agency.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1031.jpg</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ekonomi-bursa, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>IHSG menguat ditopang kinerja keuangan emiten periode kuartal II</t>
+          <t>Kemenko Pangan perkuat kerja sama kelautan dukung ketahanan pangan RI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:12:17 +0700</t>
+          <t>Tue, 04 Aug 2026 09:37:19 +0700</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa bergerak menguat ditopang oleh laporan ...</t>
+          <t>Kementerian Koordinator (Kemenko) Bidang Pangan memperkuat pengelolaan sumber daya maritim melalui penandatanganan lima ...</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678748/ihsg-menguat-ditopang-kinerja-keuangan-emiten-periode-kuartal-ii</t>
+          <t>https://www.antaranews.com/berita/5678715/kemenko-pangan-perkuat-kerja-sama-kelautan-dukung-ketahanan-pangan-ri</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/06/30/BEI-catatkan-14-perusahaan-baru-pada-2025-260625-fzn-3.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176713.jpg</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Menhub pastikan hak korban dan keluarga KMP Mutiara Sentosa terpenuhi</t>
+          <t>LLV-NMAI jalin kerja sama kembangkan bisnis di Indonesia dan Jepang</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:11:14 +0700</t>
+          <t>Tue, 04 Aug 2026 09:31:29 +0700</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Menteri Perhubungan (Menhub) Dudy Purwagandhi memastikan pemerintah mengawal pemenuhan seluruh hak korban dan keluarga ...</t>
+          <t>Living Lab Ventures (LLV) menjalin kemitraan dengan PT Nihon M&amp;A Center Indonesia (NMAI) terkait dukungan kedua ...</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678744/menhub-pastikan-hak-korban-dan-keluarga-kmp-mutiara-sentosa-terpenuhi</t>
+          <t>https://www.antaranews.com/berita/5678713/llv-nmai-jalin-kerja-sama-kembangkan-bisnis-di-indonesia-dan-jepang</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/FAC78DF1-7644-4B13-80B9-6D4721546F42.jpeg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Foto-1-Living-Lab-Ventures-Bermitra-dengan-Nihon-M-A-Center-untuk-Memperkuat-Konektivitas-Investasi-IndonesianJepang-1.jpeg</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Perwakilan ICRC untuk Myanmar temui Aung San Suu Kyi</t>
+          <t>PIHPS: Harga cabai rawit Rp61.450/kg, telur ayam Rp31.800/kg</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:04:02 +0700</t>
+          <t>Tue, 04 Aug 2026 09:18:01 +0700</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Perwakilan Tetap Komite Palang Merah Internasional (International Committee of the Red Cross/ICRC) untuk Myanmar, ...</t>
+          <t>Pusat Informasi Harga Pangan Strategis (PIHPS) Nasional yang dikelola Bank Indonesia, mencatat harga komoditas ...</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678741/perwakilan-icrc-untuk-myanmar-temui-aung-san-suu-kyi</t>
+          <t>https://www.antaranews.com/berita/5678693/pihps-harga-cabai-rawit-rp61450-kg-telur-ayam-rp31800-kg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/CjkinzN000029_20260803_CBMFN0A001_2.v1.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/8A4AD925-2D85-4C88-89BC-229C828F159D.jpeg</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mempertemukan Malin Kundang dan kecerdasan artifisial</t>
+          <t>Kemnaker ajak masyarakat pacu kompetensi di Pelatihan Vokasi Nasional</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:02:51 +0700</t>
+          <t>Tue, 04 Aug 2026 08:15:02 +0700</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>"Pak, buat apa belajar Malin Kundang? Kan kita semua sudah tahu ceritanya." Kalimat itu meluncur ringan dari ...</t>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) mengajak masyarakat untuk meningkatkan kompetensi melalui Pelatihan Vokasi ...</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678737/mempertemukan-malin-kundang-dan-kecerdasan-artifisial</t>
+          <t>https://www.antaranews.com/berita/5678657/kemnaker-ajak-masyarakat-pacu-kompetensi-di-pelatihan-vokasi-nasional</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/ilustrasi_ai_malinkundang.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/kesiapan-tenaga-kerja-di-balai-pelatihan-kerja-semarang-2828648.jpg</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PT Insight Investments hadapi sidang tuntutan kasus investasi fiktif</t>
+          <t>ICPI soroti tantangan sektor pariwisata RI hadapi dinamika global</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:01:03 +0700</t>
+          <t>Tue, 04 Aug 2026 08:07:43 +0700</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PT Insight Investments Management (IIM) menghadapi sidang pembacaan tuntutan dalam perkara dugaan investasi fiktif PT ...</t>
+          <t>Ikatan Cendikiawan Pariwisata Indonesia (ICPI) menyoroti sejumlah tantangan pariwisata Indonesia dalam menghadapi ...</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678736/pt-insight-investments-hadapi-sidang-tuntutan-kasus-investasi-fiktif</t>
+          <t>https://www.antaranews.com/berita/5678652/icpi-soroti-tantangan-sektor-pariwisata-ri-hadapi-dinamika-global</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/01/22/1000155321.jpg</t>
-        </is>
-      </c>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/26/kunjungan-turis-asing-ke-ntb-tumbuh-106-persen-1jdoh-dom.jpg</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DJPb catat pembelanjaan di 75 KDKMP Sultra capai 1.055 kali transaksi</t>
+          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:00:21 +0700</t>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kantor Wilayah (Kanwil) Direktorat Jenderal Perbendaharaan (DJPb) Provinsi Sulawesi Tenggara (Sultra), mencatat ...</t>
+          <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
+(Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678732/djpb-catat-pembelanjaan-di-75-kdkmp-sultra-capai-1055-kali-transaksi</t>
+          <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/2798be53-c5ca-4be6-bcf8-a2e9eb6c7488.jpeg</t>
-        </is>
-      </c>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dewan Pakar BPIP nilai Indonesia dapat jadi mediator Thailand-Kamboja</t>
+          <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:55:43 +0700</t>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dewan Pakar Badan Pembinaan Ideologi Pancasila (BPIP) Bidang Strategi Hubungan Luar Negeri Darmansjah Djumala menilai ...</t>
+          <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
+(Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678728/dewan-pakar-bpip-nilai-indonesia-dapat-jadi-mediator-thailand-kamboja</t>
+          <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/09/03/WhatsApp-Image-2025-06-14-at-22.18.20-1_1.jpeg</t>
-        </is>
-      </c>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Eala petenis Filipina pertama juarai WTA 500</t>
+          <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:52:01 +0700</t>
+          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Petenis muda Filipina Alexandra Eala mencatat sejarah dengan menjadi atlet pertama dari negaranya yang menjuarai ...</t>
+          <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678724/eala-petenis-filipina-pertama-juarai-wta-500</t>
+          <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_0142.jpg</t>
-        </is>
-      </c>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Envision Energy Raih Kontrak Proyek PLTB dengan Lokasi di Dekat Pantai Berkapasitas 200 MW di Vietnam</t>
+          <t>BMKG: Penyesuaian pola tanam penting cegah gagal panen saat El Nino</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:48:05 +0700</t>
+          <t>Tue, 04 Aug 2026 14:06:51 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Envision Energy, pemimpin teknologi hijau di pasar global, berhasil meraih kontrak proyek pembangkit listrik tenaga ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menekankan pentingnya penyesuaian pola tanam di wilayah terdampak ...</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678723/envision-energy-raih-kontrak-proyek-pltb-dengan-lokasi-di-dekat-pantai-berkapasitas-200-mw-di-vietnam</t>
+          <t>https://www.antaranews.com/berita/5679069/bmkg-penyesuaian-pola-tanam-penting-cegah-gagal-panen-saat-el-nino</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Envision-Energy-Vietnam.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/upaya-petani-beradaptasi-menghadapi-musim-kemarau-2830336.jpg</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>photo, terkini</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kontingen Indonesia di Asian Games 2026</t>
+          <t>Target besar 2029, TPST Bantargebang pasang geomembran sebagai kunci transformasi pengelolaan sampah</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
+          <t>Tue, 04 Aug 2026 14:00:03 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
+          <t>Petugas memasang patok pada geomembran sebagai media pelindung untuk menutup tumpukan sampah di Tempat Pengolahan ...</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
+          <t>https://www.antaranews.com/foto/5679067/target-besar-2029-tpst-bantargebang-pasang-geomembran-sebagai-kunci-transformasi-pengelolaan-sampah</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Dinas-DLH-DKI-pasang-Geomembrane-di-TPST-Bantargebang-040826-ryl-5.jpg</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
+          <t>Kemenkes ajak sekolah perkuat perlindungan kesehatan anak lewat BIAS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
+          <t>Tue, 04 Aug 2026 13:59:06 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
+          <t>Kementerian Kesehatan (Kemenkes) mengajak seluruh kementerian dan lembaga terkait serta satuan pendidikan untuk ...</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
+          <t>https://www.antaranews.com/berita/5679065/kemenkes-ajak-sekolah-perkuat-perlindungan-kesehatan-anak-lewat-bias</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/07/bulan-imunisasi-anak-sekolah-15082025-bal-10.jpg</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+          <t>KAI Perkuat Keamanan Data Pelanggan, Terapkan ISO 27001 dan Bentuk Tim Respons Siber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+          <t>Tue, 04 Aug 2026 13:57:28 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat keamanan dan kerahasiaan data pelanggan seiring semakin luasnya ...</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+          <t>https://www.antaranews.com/berita/5679063/kai-perkuat-keamanan-data-pelanggan-terapkan-iso-27001-dan-bentuk-tim-respons-siber</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/face-recognition.jpg</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Rupiah pada Selasa pagi melemah jadi Rp18.029 per dolar AS</t>
+          <t>Kementerian ESDM: Teknologi hemat energi dukung target penurunan emisi</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:16:27 +0700</t>
+          <t>Tue, 04 Aug 2026 13:56:13 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah terhadap dolar AS pada Selasa pagi, bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per ...</t>
+          <t>Direktur Konservasi Energi Direktorat Jenderal Energi Baru, Terbarukan, dan Konservasi Energi (EBTKE) Kementerian ...</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678685/rupiah-pada-selasa-pagi-melemah-jadi-rp18029-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5679060/kementerian-esdm-teknologi-hemat-energi-dukung-target-penurunan-emisi</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Proyek-SETI-EBTKE.jpeg</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CORE: Penilaian kredit alternatif dapat perluas pembiayaan UMKM</t>
+          <t>Kemenhub: Trans Sumatra Railway hadirkan transportasi terintegrasi</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:58:42 +0700</t>
+          <t>Tue, 04 Aug 2026 13:55:35 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai pemanfaatan penilaian kredit ...</t>
+          <t>Kementerian Perhubungan (Kemenhub) mengatakan pengembangan Trans Sumatra Railway atau jalur kereta Trans Sumatra dapat ...</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678651/core-penilaian-kredit-alternatif-dapat-perluas-pembiayaan-umkm</t>
+          <t>https://www.antaranews.com/berita/5679053/kemenhub-trans-sumatra-railway-hadirkan-transportasi-terintegrasi</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/realisasi-penyaluran-kur-umkm-2832719.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/0E2BC257-2126-4A9E-BCED-562A035F164A.jpeg</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Indonesia-Uni Eropa bahas kesiapan regulasi Wajib Halal 2026</t>
+          <t>Kemendagri minta pemdes libatkan kelompok rentan dalam pembangunan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:44:09 +0700</t>
+          <t>Tue, 04 Aug 2026 13:55:16 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Indonesia dan Uni Eropa membahas perkembangan regulasi serta kesiapan implementasi mandatori sertifikasi halal (Wajib ...</t>
+          <t>Kementerian Dalam Negeri (Kemendagri) meminta pemerintah desa melibatkan kelompok rentan dalam perencanaan pembangunan ...</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678721/indonesia-uni-eropa-bahas-kesiapan-regulasi-wajib-halal-2026</t>
+          <t>https://www.antaranews.com/berita/5679049/kemendagri-minta-pemdes-libatkan-kelompok-rentan-dalam-pembangunan</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_0808.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG-20260804-WA0011.jpg</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tapera: Pertumbuhan keluarga muda pendorong permintaan rumah subsidi</t>
+          <t>Angkutan Perkebunan KAI Naik 18 Persen menjadi 374.098 Ton, Perkuat Rantai Pasok Sawit Nasional</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:40:03 +0700</t>
+          <t>Tue, 04 Aug 2026 13:52:09 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Badan Pengelola Tabungan Perumahan Rakyat (BP Tapera) mengungkapkan pertumbuhan keluarga muda menjadi pendorong utama ...</t>
+          <t>PT Kereta Api Indonesia (Persero) melayani 374.098 ton angkutan perkebunan sepanjang 1 Januari–31 Juli 2026. ...</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678716/tapera-pertumbuhan-keluarga-muda-pendorong-permintaan-rumah-subsidi</t>
+          <t>https://www.antaranews.com/berita/5679045/angkutan-perkebunan-kai-naik-18-persen-menjadi-374098-ton-perkuat-rantai-pasok-sawit-nasional</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1031.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.18.37.jpeg</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kemenko Pangan perkuat kerja sama kelautan dukung ketahanan pangan RI</t>
+          <t>KSP: RUU Sistranas jadi perekat sistem transportasi massal nasional</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:37:19 +0700</t>
+          <t>Tue, 04 Aug 2026 13:48:52 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kementerian Koordinator (Kemenko) Bidang Pangan memperkuat pengelolaan sumber daya maritim melalui penandatanganan lima ...</t>
+          <t>Kantor Staf Presiden (KSP) mengungkapkan Rancangan Undang-Undang Sistem Transportasi Nasional (RUU Sistranas) menjadi ...</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678715/kemenko-pangan-perkuat-kerja-sama-kelautan-dukung-ketahanan-pangan-ri</t>
+          <t>https://www.antaranews.com/berita/5679041/ksp-ruu-sistranas-jadi-perekat-sistem-transportasi-massal-nasional</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176713.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1032.jpg</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LLV-NMAI jalin kerja sama kembangkan bisnis di Indonesia dan Jepang</t>
+          <t>Kemenhut kolaborasi perkuat tata kelola perhutanan sosial di ASEAN</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:31:29 +0700</t>
+          <t>Tue, 04 Aug 2026 13:47:42 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Living Lab Ventures (LLV) menjalin kemitraan dengan PT Nihon M&amp;A Center Indonesia (NMAI) terkait dukungan kedua ...</t>
+          <t>Kementerian Kehutanan (Kemenhut) RI mendukung penguatan tata kelola perhutanan sosial di negara-negara ASEAN untuk ...</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678713/llv-nmai-jalin-kerja-sama-kembangkan-bisnis-di-indonesia-dan-jepang</t>
+          <t>https://www.antaranews.com/berita/5679040/kemenhut-kolaborasi-perkuat-tata-kelola-perhutanan-sosial-di-asean</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Foto-1-Living-Lab-Ventures-Bermitra-dengan-Nihon-M-A-Center-untuk-Memperkuat-Konektivitas-Investasi-IndonesianJepang-1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_1306.jpg</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, photo, terkini</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PIHPS: Harga cabai rawit Rp61.450/kg, telur ayam Rp31.800/kg</t>
+          <t>Tambak modern udang vaname di kawasan industri Semarang bidik produksi 1,3 ton per siklus</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:18:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:47:21 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pusat Informasi Harga Pangan Strategis (PIHPS) Nasional yang dikelola Bank Indonesia, mencatat harga komoditas ...</t>
+          <t>Pekerja menunjukkan udang vaname hasil budidaya Loka Perbenihan dan Budi Daya Ikan (PBI) Tugu Dinas Kelautan dan ...</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678693/pihps-harga-cabai-rawit-rp61450-kg-telur-ayam-rp31800-kg</t>
+          <t>https://www.antaranews.com/foto/5679037/tambak-modern-udang-vaname-di-kawasan-industri-semarang-bidik-produksi-13-ton-per-siklus</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/8A4AD925-2D85-4C88-89BC-229C828F159D.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/panen-udang-vaname-budidaya-pemprov-jateng-040826-aaa-2.jpg</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Kemnaker ajak masyarakat pacu kompetensi di Pelatihan Vokasi Nasional</t>
+          <t>BBPMP Jateng siapkan sekolah transisi bagi siswa SNT Banyumas</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:15:02 +0700</t>
+          <t>Tue, 04 Aug 2026 13:45:59 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kementerian Ketenagakerjaan (Kemnaker) mengajak masyarakat untuk meningkatkan kompetensi melalui Pelatihan Vokasi ...</t>
+          <t>Balai Besar Penjaminan Mutu Pendidikan (BBPMP) Provinsi Jawa Tengah menyiapkan sekolah transisi bagi siswa Sekolah ...</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678657/kemnaker-ajak-masyarakat-pacu-kompetensi-di-pelatihan-vokasi-nasional</t>
+          <t>https://www.antaranews.com/berita/5679036/bbpmp-jateng-siapkan-sekolah-transisi-bagi-siswa-snt-banyumas</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/kesiapan-tenaga-kerja-di-balai-pelatihan-kerja-semarang-2828648.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001091712.jpg</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ICPI soroti tantangan sektor pariwisata RI hadapi dinamika global</t>
+          <t>Penjualan mobil naik, Menkeu yakin daya beli domestik tetap terjaga</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 08:07:43 +0700</t>
+          <t>Tue, 04 Aug 2026 13:45:23 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ikatan Cendikiawan Pariwisata Indonesia (ICPI) menyoroti sejumlah tantangan pariwisata Indonesia dalam menghadapi ...</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan pertumbuhan penjualan mobil menjadi salah satu indikator yang ...</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678652/icpi-soroti-tantangan-sektor-pariwisata-ri-hadapi-dinamika-global</t>
+          <t>https://www.antaranews.com/berita/5679033/penjualan-mobil-naik-menkeu-yakin-daya-beli-domestik-tetap-terjaga</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/11/26/kunjungan-turis-asing-ke-ntb-tumbuh-106-persen-1jdoh-dom.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.13.50.jpeg</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>IHSG Selasa dibuka menguat 20,28 poin ke posisi 6.254</t>
+          <t>Pedagang Taman Puring tagih janji Pemprov revitalisasi pascakebakaran</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:06:02 +0700</t>
+          <t>Tue, 04 Aug 2026 13:42:39 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa pagi, dibuka menguat 20,28 poin atau 0,33 ...</t>
+          <t>Koordinator pedagang di Taman Puring, Jakarta Selatan, menagih janji Pemerintah Provinsi DKI untuk segera ...</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678675/ihsg-selasa-dibuka-menguat-2028-poin-ke-posisi-6254</t>
+          <t>https://www.antaranews.com/berita/5679032/pedagang-taman-puring-tagih-janji-pemprov-revitalisasi-pascakebakaran</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/Pembukaan-IHSG-usai-libur-Lebaran.jpg250326-Ada-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001011610.jpg</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+          <t>Tim Preventive Strike Polda Metro harus utamakan pencegahan gangguan kamtibmas</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:28 +0700</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, Pemulutan Barat, Ogan Ilir (OI), Sumatera Selatan, Senin (3/8/2026). Petugas dibantu warga masih berupaya memadamkan kebakaran lahan di daerah tersebut. ANTARA FOTO/Nova Wahyudi/agr</t>
+          <t>Ketua Dewan Nasional SETARA Institute, Hendardi mengingatkan tim Preventive Strike yang dibentuk Polda Metro Jaya harus ...</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+          <t>https://www.antaranews.com/berita/5679029/tim-preventive-strike-polda-metro-harus-utamakan-pencegahan-gangguan-kamtibmas</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/12/Petisi-Untuk-Perdamaian-Indonesia-011116-agr-02.jpg</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
+          <t>Samsung larang aplikasi TV yang mengekspos koneksi internet pengguna</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:22 +0700</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi melalui penerapan sistem verifikasi berbasis Quick Response (QR) berlapis. Wali Kota Palu Harianto Rasyid pada Senin (3/8), mengatakan, bahwa QR tersebut menjadi verifikasi tambahan guna melengkapi sistem QR Subsidi tepat milik Pertamina, sehingga setiap kendaraan yang nantinya memperoleh solar bersubsidi wajib lebih dahulu terdaftar pada Pemerintah Kota Palu. (Farah Khadija/M. Izfaldi/Denno Ramdha Asmara/Winanto)</t>
+          <t>Samsung menyatakan bahwa perusahaan melarang aplikasi-aplikasi yang berpotensi mengekspos koneksi internet ...</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
+          <t>https://www.antaranews.com/berita/5679025/samsung-larang-aplikasi-tv-yang-mengekspos-koneksi-internet-pengguna</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/495339513_23879065098420444_7610565358307725dcCC188_n.jpg</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+          <t>Bappenas rumuskan arah respons dalam 4 kluster utama hadapi El-Nino</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:21 +0700</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+          <t>Pemerintah merumuskan arah respons empat kluster pembangunan utama dalam bentuk policy brief untuk menghadapi dan ...</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+          <t>https://www.antaranews.com/berita/5679024/bappenas-rumuskan-arah-respons-dalam-4-kluster-utama-hadapi-el-nino</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-12.43.09.jpeg</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Mendag sebut perjanjian dagang pacu minat investasi</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:38:49 +0700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso menyampaikan semakin banyaknya perjanjian perdagangan yang dimiliki ...</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5679017/mendag-sebut-perjanjian-dagang-pacu-minat-investasi</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Mendag.jpg</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>BMKG: Waspada gelombang setinggi 6 meter di perairan selatan Bali</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:36:42 +0700</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+          <t>Balai Besar Meteorologi Klimatologi dan Geofisika (BBMKG) Wilayah III Denpasar memprakirakan ketinggian gelombang laut ...</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/berita/5679015/bmkg-waspada-gelombang-setinggi-6-meter-di-perairan-selatan-bali</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_142653.jpg</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Pemkot Palu paparkan implementasi kota inklusif bagi disabilitas</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:35:28 +0700</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Pemerintah Kota (Pemkot) Palu, Sulawesi Tengah (Sulteng) memaparkan sejumlah kebijakan yang sudah dilakukan pemerintah ...</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5679012/pemkot-palu-paparkan-implementasi-kota-inklusif-bagi-disabilitas</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-20.58.47.jpeg</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Polda Metro Jaya panen 82 kg pakcoy untuk bahan baku MBG</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:34:09 +0700</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Polda Metro Jaya kembali memanen 82 kilogram sayur pakcoy pada Selasa untuk didistribusikan langsung sebagai ...</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5679011/polda-metro-jaya-panen-82-kg-pakcoy-untuk-bahan-baku-mbg</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/e5362e67-38db-4936-a5fa-c050f3c6eec9.jpeg</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>73 santri dan pengasuh ponpes lolos beasiswa Pemprov Jateng</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:33:28 +0700</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>Sebanyak 73 santri dan pengasuh pondok pesantren berhasil lolos dalam proses seleksi Beasiswa Santri dan Pengasuh ...</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5679007/73-santri-dan-pengasuh-ponpes-lolos-beasiswa-pemprov-jateng</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002077974.jpg</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Cegah banjir-longsor susulan, BNPB perbaiki tebing sungai di Sipange</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:30:48 +0700</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) memperbaiki sekaligus memperkuat struktur tebing Sungai Sigala-gala di ...</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5679003/cegah-banjir-longsor-susulan-bnpb-perbaiki-tebing-sungai-di-sipange</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/IMG_20251207_094949.jpg</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Program Taruna Bhakti dimulai di Sekolah Rakyat Gumas</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:29:40 +0700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
-(Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
+          <t>Program Taruna Bhakti 2026 resmi berjalan di Sekolah Rakyat Terintegrasi 54 Kabupaten Gunung Mas (Gumas), Kalimantan ...</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
+          <t>https://www.antaranews.com/berita/5679000/program-taruna-bhakti-dimulai-di-sekolah-rakyat-gumas</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Gumas-Sekolah-Rakyat-di-gunung-mas-Kabupaten-Gunung-Mas-Kalimantan-Tengah-gumas-kalteng.jpg</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
+          <t>BNPT sebut ormas agama mitra pemerintah perkuat ketahanan radikalisme</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:27:11 +0700</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
+          <t>Badan Nasional Penanggulangan Terorisme (BNPT) menyatakan organisasi kemasyarakatan keagamaan memiliki posisi strategis ...</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
+          <t>https://www.antaranews.com/berita/5678997/bnpt-sebut-ormas-agama-mitra-pemerintah-perkuat-ketahanan-radikalisme</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469936.jpg</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
+          <t>Jakpus percepat penyelesaian aset fasos hasil kewajiban pengembang</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:26:16 +0700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+          <t>Pemerintah Kota Jakarta Pusat mempercepat penyelesaian administrasi aset berupa fasilitas sosial dan fasilitas ...</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
+          <t>https://www.antaranews.com/berita/5678995/jakpus-percepat-penyelesaian-aset-fasos-hasil-kewajiban-pengembang</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Tamasya-Trotoar-Kita-271218-aaa-1.jpg</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+          <t>Dinkes Tanjungpinang: Program CKG anak sekolah sasar 49.343 siswa</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:20:20 +0700</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
-(Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
+          <t>Dinas Kesehatan, Pengendalian Penduduk, dan Keluarga Berencana (Dinkes PPKB) Kota Tanjungpinang, Kepulauan Riau (Kepri) ...</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
+          <t>https://www.antaranews.com/berita/5678991/dinkes-tanjungpinang-program-ckg-anak-sekolah-sasar-49343-siswa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_892E3D72-14C7-4D65-8D8A-54508D212D10.png</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
+          <t>Pertamina Hulu Indonesia catat produksi migas di atas target</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:19:27 +0700</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
+          <t>PT Pertamina Hulu Indonesia (PHI), bagian Subholding Upstream PT Pertamina (Persero), yang mengelola aset hulu migas di ...</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+          <t>https://www.antaranews.com/berita/5678988/pertamina-hulu-indonesia-catat-produksi-migas-di-atas-target</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260515_154910.jpg</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
+          <t>Trump desak perusahaan minyak AS segera turunkan harga ke konsumen</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:18:22 +0700</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
+          <t>Presiden Amerika Serikat Donald Trump mendesak perusahaan-perusahaan minyak di negaranya untuk segera menurunkan harga ...</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
+          <t>https://www.antaranews.com/berita/5678984/trump-desak-perusahaan-minyak-as-segera-turunkan-harga-ke-konsumen</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_ab5d296d556bf61eed768b8ca4900658.jpg</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
+          <t>Gubernur Kepri pastikan program strategis nasional berjalan baik</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:14:01 +0700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
-(Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
+          <t>Gubernur Kepulauan Riau Ansar Ahmad memastikan pelaksanaan berbagai program nasional di daerahnya berjalan baik hingga ...</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
+          <t>https://www.antaranews.com/berita/5678983/gubernur-kepri-pastikan-program-strategis-nasional-berjalan-baik</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_1BD7B733-6D15-464A-B72C-E9015EF50D0A.jpeg</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
+          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:11:01 +0700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
+          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, ...</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
+          <t>https://www.antaranews.com/video/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
+          <t>BNPT dan LAN sepakat tangkal pola baru terorisme di ruang digital</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:09:01 +0700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
-(Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
+          <t>Badan Nasional Penanggulangan Terorisme (BNPT) bersama Lembaga Administrasi Negara (LAN) sepakat untuk menangkal pola ...</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
+          <t>https://www.antaranews.com/berita/5678979/bnpt-dan-lan-sepakat-tangkal-pola-baru-terorisme-di-ruang-digital</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469877.jpg</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
+          <t>Bocoran kamera Galaxy S27 Pro dan Ultra terungkap, ini perbedaannya</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:07:58 +0700</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
+          <t>Bocoran spesifikasi kamera Galaxy S27 Pro dan Galaxy S27 Ultra mencuat setelah dokumen yang dibagikan Samsung kepada ...</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
+          <t>https://www.antaranews.com/berita/5678976/bocoran-kamera-galaxy-s27-pro-dan-ultra-terungkap-ini-perbedaannya</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/26/WhatsApp-Image-2026-02-26-at-16.18.01.jpeg</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
+          <t>Taruna AAL bekali siswa Sekolah Rakyat 32 Natuna pendidikan karakter</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:07:51 +0700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
+          <t>Taruna Akademi Angkatan Laut (AAL) membekali siswa Sekolah Rakyat (SR) Terintegrasi 32 Natuna, Provinsi Kepulauan Riau, ...</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
+          <t>https://www.antaranews.com/berita/5678973/taruna-aal-bekali-siswa-sekolah-rakyat-32-natuna-pendidikan-karakter</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000833131.jpg</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
+          <t>Transjakarta beri alasan turunkan seorang penumpang di Kampung Melayu</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:07:38 +0700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
+          <t>PT Transportasi Jakarta menyampaikan tindakan petugas menurunkan seorang penumpang dari bus di Halte Kampung Melayu, ...</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
+          <t>https://www.antaranews.com/berita/5678969/transjakarta-beri-alasan-turunkan-seorang-penumpang-di-kampung-melayu</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/jumlah-penumpang-angkutan-umum-di-jakarta-meningkat-2816319.jpg</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
+          <t>Sopir truk korban KMP Mutiara Sentosa asal Tulungagung dimakamkan</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:05:38 +0700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
+          <t>Jenazah Sari Sukoco (39), salah satu korban meninggal dunia dalam kebakaran KMP Mutiara Sentosa 2 di perairan Madura, ...</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
+          <t>https://www.antaranews.com/berita/5678967/sopir-truk-korban-kmp-mutiara-sentosa-asal-tulungagung-dimakamkan</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/454482.jpg</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
+          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:03:10 +0700</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi ...</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
+          <t>https://www.antaranews.com/video/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
+          <t>BNPB: 150 warga mengungsi akibat tanggul jebol picu banjir di Tapteng</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:59:51 +0700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) mencatat sebanyak 150 warga di Kabupaten Tapanuli Tengah (Tapteng), ...</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
+          <t>https://www.antaranews.com/berita/5678961/bnpb-150-warga-mengungsi-akibat-tanggul-jebol-picu-banjir-di-tapteng</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/81e7716a-5d0a-474c-a05f-b4b702088781.jpeg</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
+          <t>Pemkab Karo imbau masyarakat patuhi zona aman Gunung Sinabung</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:59:44 +0700</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
+          <t>Pemerintah Kabupaten (Pemkab) Karo mengimbau masyarakat mematuhi zona aman menyusul peningkatan status aktivitas ...</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
+          <t>https://www.antaranews.com/berita/5678957/pemkab-karo-imbau-masyarakat-patuhi-zona-aman-gunung-sinabung</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000497965.jpg</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
+          <t>DKPP pastikan cadangan beras Kab. Serang aman hingga setahun ke depan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:58:52 +0700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
+          <t>ANTARA - Dinas Ketahanan Pangan dan Pertanian (DKPP) Kabupaten Serang, Selasa (4/8), memastikan cadangan beras ...</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
+          <t>https://www.antaranews.com/video/5678939/dkpp-pastikan-cadangan-beras-kab-serang-aman-hingga-setahun-ke-depan</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DKPP-PASTIKAN-CADANGAN-BERAS-KAB.SERANG-AMAN-HINGGA-SETAHUN-KE-DEPAN.jpg</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
+          <t>Puan dorong penguatan keamanan transportasi laut pascakecelakaan kapal</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:58:46 +0700</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
+          <t>Ketua DPR RI Puan Maharani mendorong penguatan keamanan dan keselamatan transportasi laut menyusul sejumlah kecelakaan ...</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
+          <t>https://www.antaranews.com/berita/5678953/puan-dorong-penguatan-keamanan-transportasi-laut-pascakecelakaan-kapal</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/Tangkapan-Layar-2026-07-07-pukul-18.21.50.jpeg</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
+          <t>Maroon 5 dijadwalkan tampil di Jakarta pada Februari 2027</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:57:20 +0700</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+          <t>Grup musik pop-rock Maroon 5 dijadwalkan tampil di Jakarta pada 5 Februari 2027 dalam rangkaian tur pertunjukannya ...</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+          <t>https://www.antaranews.com/berita/5678949/maroon-5-dijadwalkan-tampil-di-jakarta-pada-februari-2027</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/02/02/Konser-Maroon5-Di-Jakarta-010225-IES-2.jpg</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial, terkini</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+          <t>LPEM FEB UI perkirakan ekonomi RI tumbuh 4,8 persen di kuartal II 2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:57:01 +0700</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+          <t>Lembaga Penyelidikan Ekonomi dan Masyarakat Fakultas Ekonomi dan Bisnis Universitas Indonesia (LPEM FEB UI) ...</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+          <t>https://www.antaranews.com/berita/5678945/lpem-feb-ui-perkirakan-ekonomi-ri-tumbuh-48-persen-di-kuartal-ii-2026</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/05/17/Screenshot_20220517-151559_YouTube.jpg</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+          <t>Polda Metro Jaya selidiki dugaan ekploitasi anak dalam promosi vape</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:56:55 +0700</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+          <t>Direktorat Perlindungan Perempuan dan Anak Pemberantasan Perdagangan Orang (PPA PPO) Polda Metro Jaya menyelidiki ...</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+          <t>https://www.antaranews.com/berita/5678944/polda-metro-jaya-selidiki-dugaan-ekploitasi-anak-dalam-promosi-vape</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4026.jpeg</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+          <t>Saat rantai pasok menjadi benteng inflasi</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:56:38 +0700</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
-(Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
+          <t>Di tengah ancaman El Nino dan tantangan logistik negara kepulauan, inflasi Indonesia pada Juli 2026 menunjukkan bahwa ...</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
+          <t>https://www.antaranews.com/berita/5678943/saat-rantai-pasok-menjadi-benteng-inflasi</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/12/05/1000001928.jpg</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
+          <t>Diskominfo: Waspada ada 12 hoaks terkait Papua pada Januari-Juli 2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:55:52 +0700</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
+          <t>Dinas Komunikasi dan Informatika (Diskominfo) Provinsi Papua mencatat sebanyak 12 hoaks yang berkaitan dengan Papua ...</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
+          <t>https://www.antaranews.com/berita/5678940/diskominfo-waspada-ada-12-hoaks-terkait-papua-pada-januari-juli-2026</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002059446.jpg</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
+          <t>BMKG: Juli 2026 menjadi Juli terkering sejak 1991</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:55:25 +0700</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyatakan Juli 2026 menjadi bulan Juli terkering di Indonesia ...</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
+          <t>https://www.antaranews.com/berita/5678936/bmkg-juli-2026-menjadi-juli-terkering-sejak-1991</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Prediksi-kemarau-di-Jawa-Barat-160726-adb-7.jpg</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
+          <t>NTB ubah paradigma cagar budaya jadi penggerak ekonomi</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:52:11 +0700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
+          <t>Gubernur Nusa Tenggara Barat (NTB) Lalu Muhamad Iqbal mengatakan paradigma cagar budaya perlu diubah agar warisan ...</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
+          <t>https://www.antaranews.com/berita/5678935/ntb-ubah-paradigma-cagar-budaya-jadi-penggerak-ekonomi</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001433707.jpg</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
+          <t>RSUD Dompu tambah lima dokter spesialis perkuat layanan kesehatan</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:48:05 +0700</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+          <t>Rumah Sakit Umum Daerah (RSUD) Kabupaten Dompu, Nusa Tenggara Barat, menambah lima dokter spesialis untuk memperkuat ...</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
+          <t>https://www.antaranews.com/berita/5678932/rsud-dompu-tambah-lima-dokter-spesialis-perkuat-layanan-kesehatan</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001778561.jpg</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
+          <t>Polda NTT gagalkan dugaan perekrutan 21 pekerja migran ilegal</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:47:34 +0700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
+          <t>Tim URC Burhan Satreskrim Polres Ende, Polda Nusa Tenggara Timur, menggagalkan dugaan perekrutan 21 calon pekerja ...</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
+          <t>https://www.antaranews.com/berita/5678929/polda-ntt-gagalkan-dugaan-perekrutan-21-pekerja-migran-ilegal</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/image_750x_6a6d44c0944c4.jpg</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
+          <t>Ada 2 bibit siklon tropis, BMKG: Waspada ombak setinggi 4 meter di RI</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:09:44 +0700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi kemunculan dua bibit siklon tropis sekaligus di wilayah ...</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
+          <t>https://www.antaranews.com/berita/5678879/ada-2-bibit-siklon-tropis-bmkg-waspada-ombak-setinggi-4-meter-di-ri</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20250609_135328.jpg</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
+          <t>Korban tewas gempa Venezuela terus bertambah jadi 6.100 orang</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:00:56 +0700</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
+          <t>Jumlah korban tewas akibat gempa kembar dahsyat yang mengguncang Venezuela pada 24 Juni 2026, terus bertambah ...</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
+          <t>https://www.antaranews.com/berita/5678865/korban-tewas-gempa-venezuela-terus-bertambah-jadi-6100-orang</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_d4a34a165f13a0667255577d3cfac46f.jpg</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
+          <t>BPKH salurkan Rp2,06 triliun nilai manfaat ke 5,7 juta calon haji</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 11:47:58 +0700</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
+          <t>Badan Pengelola Keuangan Haji (BPKH) menyalurkan Nilai Manfaat Tahap I Tahun 2026 lebih dari Rp2,06 triliun kepada ...</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
+          <t>https://www.antaranews.com/berita/5678849/bpkh-salurkan-rp206-triliun-nilai-manfaat-ke-57-juta-calon-haji</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176506_1.jpg</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+          <t>Aldila jadi petenis Indonesia yang pertama juarai DC Open</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+          <t>Petenis Indonesia Aldila Sutjiadi mencatatkan sejarah setelah menjuarai nomor ganda putri turnamen Mubadala DC Open ...</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+          <t>https://www.antaranews.com/berita/5678836/aldila-jadi-petenis-indonesia-yang-pertama-juarai-dc-open</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4155-copy.jpg</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+          <t>Indonesia raih 15 medali dari Kejuaraan MMAAsia</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 09:16:36 +0700</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+          <t>Tim mixed martial arts (MMA) amatir Indonesia meraih 15 medali dan menempati peringkat keempat pada GAMMA Asian ...</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+          <t>https://www.antaranews.com/berita/5678689/indonesia-raih-15-medali-dari-kejuaraan-mmaasia</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Delvi-Novia_Medal.jpg</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+          <t>Kontingen Indonesia di Asian Games 2026</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
-(XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
+          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
+          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
+          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
+          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
+          <t>BI siapkan Rp20 miliar ekspedisi rupiah berdaulat 2026 di 3T Papua</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:24:47 +0700</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
+          <t>Kantor Perwakilan Bank Indonesia (BI) Provinsi Papua menyiapkan uang layak edar senilai Rp20 miliar dalam pelaksanaan ...</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
+          <t>https://www.antaranews.com/berita/5678896/bi-siapkan-rp20-miliar-ekspedisi-rupiah-berdaulat-2026-di-3t-papua</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002062154.jpg</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+          <t>Panda Bond dan sinyal kepercayaan investasi global</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 11:26:35 +0700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+          <t>Di tengah ketidakpastian ekonomi global yang semakin kompleks, pemerintah Indonesia perlu memastikan bahwa ...</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+          <t>https://www.antaranews.com/berita/5678827/panda-bond-dan-sinyal-kepercayaan-investasi-global</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/permintaan-pembelian-obligasi-global-capai-46-miliar-dolar-as-2806089.jpg</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+          <t>Rupiah Selasa melemah dipicu kenaikan harga minyak global</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 11:15:57 +0700</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+          <t>Nilai tukar rupiah pada Selasa pagi bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per dolar AS ...</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+          <t>https://www.antaranews.com/berita/5678808/rupiah-selasa-melemah-dipicu-kenaikan-harga-minyak-global</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/nilai-tukar-rupiah-melemah-44-poin-2821215.jpg</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+          <t>DJPb catat pembelanjaan di 75 KDKMP Sultra capai 1.055 kali transaksi</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 10:00:21 +0700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+          <t>Kantor Wilayah (Kanwil) Direktorat Jenderal Perbendaharaan (DJPb) Provinsi Sulawesi Tenggara (Sultra), mencatat ...</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+          <t>https://www.antaranews.com/berita/5678732/djpb-catat-pembelanjaan-di-75-kdkmp-sultra-capai-1055-kali-transaksi</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/2798be53-c5ca-4be6-bcf8-a2e9eb6c7488.jpeg</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Resmi dibuka, Sekolah Rakyat Terintegrasi 2 Kendari tampung 339 siswa</t>
+          <t>Rupiah pada Selasa pagi melemah jadi Rp18.029 per dolar AS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 09:16:27 +0700</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ANTARA - Sekolah Rakyat Terintegrasi 2 Kota Kendari resmi dibuka pada Senin (3/8), yang ditandai dengan Masa Pengenalan Lingkungan Sekolah (MPLS). Sekolah tersebut menampung total sebanyak 339 siswa untuk tahun ajaran 2026/2027, yang terdiri dari jenjang SD, SMP dan SMA.
-(Saharudin/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
+          <t>Nilai tukar rupiah terhadap dolar AS pada Selasa pagi, bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per ...</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677373/resmi-dibuka-sekolah-rakyat-terintegrasi-2-kendari-tampung-339-siswa</t>
+          <t>https://www.antaranews.com/berita/5678685/rupiah-pada-selasa-pagi-melemah-jadi-rp18029-per-dolar-as</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/RESMI-DIBUKA-SEKOLAH-RAKYAT-TERINTEGRASI-2-KENDARI-TAMPUNG-339-SISWA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Dinkop UKM Cilegon targetkan 21 gerai baru KKMP beroperasi September</t>
+          <t>CORE: Penilaian kredit alternatif dapat perluas pembiayaan UMKM</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 07:58:42 +0700</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Koperasi Usaha Kecil dan Menengah (Dinkop UKM) Kota Cilegon menargetkan pembangunan  21 gedung gerai Koperasi Kelurahan Merah Putih (KKMP) di wilayah setempat dapat selesai dan beroperasi pada bulan September mendatang. Kepala Dinkop UKM Kota Cilegon, Suhendi pada Senin (3/8) mengatakan saat ini tercatat baru sebanyak 10 gedung yang telah selesai dibangun.
-(Susmiatun Hayati/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
+          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai pemanfaatan penilaian kredit ...</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677301/dinkop-ukm-cilegon-targetkan-21-gerai-baru-kkmp-beroperasi-september</t>
+          <t>https://www.antaranews.com/berita/5678651/core-penilaian-kredit-alternatif-dapat-perluas-pembiayaan-umkm</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DINKOP-UKM-CILEGON-TARGETKAN-21-GERAI-BARU-KKMP-BEROPERASI-SEPTEMBER.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/realisasi-penyaluran-kur-umkm-2832719.jpg</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Menhub sebut segera evaluasi operator KMP Mutiara Sentosa 2</t>
+          <t>Airbus A380-800 Emirates akan mendarat perdana di Bandara Soetta</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:50:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:47:25 +0700</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah akan segera mengevaluasi kinerja PT Atosim Lampung Pelayaran yang merupakan operator KMP Mutiara Sentosa II. Hal tersebut disampaikan Menteri Perhubungan Dudy Purwagandhi saat meninjau para korban kebakaran KMP Mutiara Sentosa II di Surabaya, Jawa Timur, Senin (3/8). (Hanif Nasrullah/Denno Ramdha Asmara/Ludmila Yusufin Diah Nastiti)</t>
+          <t>Pesawat jenis Airbus A380-800 milik maskapai Emirates yang melayani penerbangan EK358 rute Dubai (DXB)–Jakarta ...</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5677187/menhub-sebut-segera-evaluasi-operator-kmp-mutiara-sentosa-2</t>
+          <t>https://www.antaranews.com/berita/5678928/airbus-a380-800-emirates-akan-mendarat-perdana-di-bandara-soetta</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/MENHUB-SEBUT-SEGERA-EVALUASI-OPERATOR-KMP-MUTIARA-SENTOSA-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/06/02/A380-2_1.jpeg</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Pemerintah targetkan pembangunan 35.872 unit KDKMP rampung di Agustus</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:41:37 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Pemerintah menargetkan pembangunan gedung koperasi desa dan kelurahan merah putih (KDKMP) rampung sebanyak 35.872 ...</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678915/pemerintah-targetkan-pembangunan-35872-unit-kdkmp-rampung-di-agustus</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002905262.jpg</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, photo</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Kementan usulkan telur ayam masuk skema cadangan pangan pemerintah</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:30:53 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Pekerja memberikan pakan ayam di salah satu peternakan di Cihampelas, Kabupaten Bandung Barat, Jawa Barat, Selasa ...</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678903/kementan-usulkan-telur-ayam-masuk-skema-cadangan-pangan-pemerintah</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Kementan-Usulkan-Telur-Ayam-Masuk-Skema-CPP-040826-DAN-07.jpg</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Honda Super-One 2026 dijual di Australia, segini harganya</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:29:17 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Honda Super-One debut perdana di Gaikindo Indonesia International Auto Show (GIIAS) 2026, Indonesia, harganya masih ...</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5678901/honda-super-one-2026-dijual-di-australia-segini-harganya</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG_1401.jpg</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Kemenekraf perkuat KPT Ekraf jadi penggerak hilirisasi talenta kreatif</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:59:18 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Kementerian Ekonomi Kreatif/Badan Ekonomi Kreatif (Ekraf) memperkuat peran Konsorsium Perguruan Tinggi (KPT) Ekraf ...</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678861/kemenekraf-perkuat-kpt-ekraf-jadi-penggerak-hilirisasi-talenta-kreatif</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000453579.jpg</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Pakar: Harga minyak dunia turun jadi kesempatan menata aturan</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:49:32 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Peneliti sekaligus dosen Fakultas Ekonomi dan Bisnis Universitas Padjadjaran Yayan Satyakti menilai turunnya harga ...</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678851/pakar-harga-minyak-dunia-turun-jadi-kesempatan-menata-aturan</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Wuling sediakan "test drive" mobil-mobil terbaru di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Pabrikan otomotif asal China Wuling Motors menyediakan aneka mobil keluaran terbaru mereka untuk diuji coba ...</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5678837/wuling-sediakan-test-drive-mobil-mobil-terbaru-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pada-area-test-drive-Wuling-menyediakan-beragam-lini-kendaraan-sehingga-pengunjung-dapat-merasakan-secara-langsung-performa-kenyamanan-serta-teknologi-yang-dihadirkan.jpeg</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Kementan siapkan Juknis penyerapan telur bagi SPPG Rp26.500/kg</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:26:36 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian (Kementan) menyiapkan petunjuk teknis (Juknis) penyerapan telur oleh seluruh Satuan Pelayanan ...</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678831/kementan-siapkan-juknis-penyerapan-telur-bagi-sppg-rp26500-kg</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/4FB30E01-205C-4253-9C88-5373F761A9FB.jpeg</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Ekonom proyeksikan pangsa NEV capai 31,7 persen penjualan mobil 2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:22:55 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Ekonom PT Bank Danamon Indonesia Tbk memproyeksikan pangsa kendaraan energi baru (new energy vehicle/NEV) mencapai 31,7 ...</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678821/ekonom-proyeksikan-pangsa-nev-capai-317-persen-penjualan-mobil-2026</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penjualan-kendaraan-di-semester-1-2026-meningkat-2831868.jpg</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>IHSG menguat ditopang kinerja keuangan emiten periode kuartal II</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:12:17 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa bergerak menguat ditopang oleh laporan ...</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678748/ihsg-menguat-ditopang-kinerja-keuangan-emiten-periode-kuartal-ii</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/30/BEI-catatkan-14-perusahaan-baru-pada-2025-260625-fzn-3.jpg</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>IHSG Selasa dibuka menguat 20,28 poin ke posisi 6.254</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:06:02 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa pagi, dibuka menguat 20,28 poin atau 0,33 ...</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678675/ihsg-selasa-dibuka-menguat-2028-poin-ke-posisi-6254</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/Pembukaan-IHSG-usai-libur-Lebaran.jpg250326-Ada-3.jpg</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>252 siswa SMAN 28 Bandung belajar di Kompleks Sport Jabar, gedung sekolah baru rampung Desember 2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:12:31 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Siswa kelas X SMAN 28 Bandung mengikuti kegiatan belajar mengajar di ruang kelas Gedung Laga Satria Sport Jabar Arcamanik, Bandung, Jawa Barat, Selasa (4/8/2026). Sebanyak 252 siswa angkatan pertama SMAN 28 Bandung untuk sementara mengikuti kegiatan belajar mengajar di kompleks Sport Jabar Arcamanik karena gedung sekolah masih dalam tahap pembangunan dan ditargetkan selesai pada Desember 2026. ANTARA FOTO/Novrian Arbi/agr</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678884/252-siswa-sman-28-bandung-belajar-di-kompleks-sport-jabar-gedung-sekolah-baru-rampung-desember-2026</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Siswa-SMAN-28-Bandung-belajar-di-gedung-sementara-040826-NA-6.jpg</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan catat realisasi Belanja Pemerintah Pusat (BPP) capai Rp1.298,6 triliun atau tumbuh 29,4 persen</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:05:28 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Siswa berjalan membawa paket Makan Bergizi Gratis (MBG) di SDN Pejaten Barat 01, Pasar Minggu, Jakarta, Selasa (4/8/2026). Kementerian Keuangan mencatat realisasi Belanja Pemerintah Pusat (BPP) mencapai Rp1.298,6 triliun atau tumbuh 29,4 persen secara tahunan, yang antara lain didorong pelaksanaan program Makan Bergizi Gratis (MBG), penyaluran bantuan sosial, pembangunan infrastruktur, pembayaran tunjangan hari raya (THR) dan gaji ke-13, manfaat pensiun, subsidi dan kompensasi bahan bakar minyak (BBM) dan listrik. ANTARA FOTO/Angga Budhiyanto/agr</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678877/kementerian-keuangan-catat-realisasi-belanja-pemerintah-pusat-bpp-capai-rp12986-triliun-atau-tumbuh-294-persen</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Realisasi-Belanja-Pemerintah-Pusat-04082026-ab-6.jpg</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>BPS proyeksikan produksi beras nasional capai 28,71 Juta ton hingga September 2026, stok dipastikan tetap aman</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Pekerja menata karung berisi cadangan beras pemerintah di gudang Perum Bulog Cabang Meulaboh, Aceh Barat, Aceh, Selasa (4/8/2026). Badan Pusat Statistik (BPS) memproyeksi produksi beras nasional untuk konsumsi pangan sepanjang Januari - September 2026 mencapai 28,71 juta ton atau meningkat 0,01 persen dibandingkan periode yang sama tahun sebelumnya. ANTARA FOTO/Syifa Yulinnas/agr</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678815/bps-proyeksikan-produksi-beras-nasional-capai-2871-juta-ton-hingga-september-2026-stok-dipastikan-tetap-aman</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Prediksi-produksi-beras-nasional-040826-Syf-3.jpg</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, Pemulutan Barat, Ogan Ilir (OI), Sumatera Selatan, Senin (3/8/2026). Petugas dibantu warga masih berupaya memadamkan kebakaran lahan di daerah tersebut. ANTARA FOTO/Nova Wahyudi/agr</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, kota Ambon, Maluku, Selasa (4/8). Kegiatan digitalisasi bansos ini diwajibkan untuk seluruh Apartur Sipil Negara di lingkup Pemkot Ambon. (Alfian Sanusi/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>DKPP pastikan cadangan beras Kab. Serang aman hingga setahun ke depan</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Ketahanan Pangan dan Pertanian (DKPP) Kabupaten Serang, Selasa (4/8), memastikan cadangan beras Kabupaten Serang aman hingga satu tahun ke depan. Kepala Bidang Ketahanan Pangan DKPP Kabupaten Serang, Endra Nuryana, mengatakan, hingga per Agustus 2026, Kabupaten Serang tercatat masih memiliki sebanyak 334 ton beras cadangan, yang saat ini masih tersimpan di gudang Bulog Cabang Serang. (Susmiatun Hayati/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678939/dkpp-pastikan-cadangan-beras-kab-serang-aman-hingga-setahun-ke-depan</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DKPP-PASTIKAN-CADANGAN-BERAS-KAB.SERANG-AMAN-HINGGA-SETAHUN-KE-DEPAN.jpg</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi Rupiah Berdaulat (ERB) 2026  yang digelar di lima pulau  yang masuk dalam wilayah Terdepan, Terluar dan Terpencil (3T) di wilayah Papua, di Dermaga Satrol Kodaeral X Jayapura, Selasa (4/8). Kepala Perwakilan Bank Indonesia Provinsi Papua, Warsono, mengatakan pelepasan tim ERB mencakup kegiatan edukasi Cinta, Bangga, dan Paham (CBP) Rupiah bahwa kehadiran rupiah hingga ke pulau-pulau terluar merupakan bagian dari upaya menjaga kedaulatan ekonomi nasional. (Laksa Mahendra/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi melalui penerapan sistem verifikasi berbasis Quick Response (QR) berlapis. Wali Kota Palu Harianto Rasyid pada Senin (3/8), mengatakan, bahwa QR tersebut menjadi verifikasi tambahan guna melengkapi sistem QR Subsidi tepat milik Pertamina, sehingga setiap kendaraan yang nantinya memperoleh solar bersubsidi wajib lebih dahulu terdaftar pada Pemerintah Kota Palu. (Farah Khadija/M. Izfaldi/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
+(Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
+(Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
+(Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
+(Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (AFP/Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
+(Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
+(XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>antara</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G170"/>
+  <autoFilter ref="A1:H234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$248</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H234"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -4018,33 +4018,33 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BMKG: Penyesuaian pola tanam penting cegah gagal panen saat El Nino</t>
+          <t>BNPB: 150 warga mengungsi akibat tanggul jebol picu banjir di Tapteng</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:06:51 +0700</t>
+          <t>Tue, 04 Aug 2026 12:59:51 +0700</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menekankan pentingnya penyesuaian pola tanam di wilayah terdampak ...</t>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) mencatat sebanyak 150 warga di Kabupaten Tapanuli Tengah (Tapteng), ...</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679069/bmkg-penyesuaian-pola-tanam-penting-cegah-gagal-panen-saat-el-nino</t>
+          <t>https://www.antaranews.com/berita/5678961/bnpb-150-warga-mengungsi-akibat-tanggul-jebol-picu-banjir-di-tapteng</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/upaya-petani-beradaptasi-menghadapi-musim-kemarau-2830336.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/81e7716a-5d0a-474c-a05f-b4b702088781.jpeg</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4056,33 +4056,33 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Target besar 2029, TPST Bantargebang pasang geomembran sebagai kunci transformasi pengelolaan sampah</t>
+          <t>Pemkab Karo imbau masyarakat patuhi zona aman Gunung Sinabung</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:00:03 +0700</t>
+          <t>Tue, 04 Aug 2026 12:59:44 +0700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Petugas memasang patok pada geomembran sebagai media pelindung untuk menutup tumpukan sampah di Tempat Pengolahan ...</t>
+          <t>Pemerintah Kabupaten (Pemkab) Karo mengimbau masyarakat mematuhi zona aman menyusul peningkatan status aktivitas ...</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5679067/target-besar-2029-tpst-bantargebang-pasang-geomembran-sebagai-kunci-transformasi-pengelolaan-sampah</t>
+          <t>https://www.antaranews.com/berita/5678957/pemkab-karo-imbau-masyarakat-patuhi-zona-aman-gunung-sinabung</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Dinas-DLH-DKI-pasang-Geomembrane-di-TPST-Bantargebang-040826-ryl-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000497965.jpg</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4099,28 +4099,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kemenkes ajak sekolah perkuat perlindungan kesehatan anak lewat BIAS</t>
+          <t>DKPP pastikan cadangan beras Kab. Serang aman hingga setahun ke depan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:59:06 +0700</t>
+          <t>Tue, 04 Aug 2026 12:58:52 +0700</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kementerian Kesehatan (Kemenkes) mengajak seluruh kementerian dan lembaga terkait serta satuan pendidikan untuk ...</t>
+          <t>ANTARA - Dinas Ketahanan Pangan dan Pertanian (DKPP) Kabupaten Serang, Selasa (4/8), memastikan cadangan beras ...</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679065/kemenkes-ajak-sekolah-perkuat-perlindungan-kesehatan-anak-lewat-bias</t>
+          <t>https://www.antaranews.com/video/5678939/dkpp-pastikan-cadangan-beras-kab-serang-aman-hingga-setahun-ke-depan</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/07/bulan-imunisasi-anak-sekolah-15082025-bal-10.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DKPP-PASTIKAN-CADANGAN-BERAS-KAB.SERANG-AMAN-HINGGA-SETAHUN-KE-DEPAN.jpg</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4137,28 +4137,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KAI Perkuat Keamanan Data Pelanggan, Terapkan ISO 27001 dan Bentuk Tim Respons Siber</t>
+          <t>Puan dorong penguatan keamanan transportasi laut pascakecelakaan kapal</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:57:28 +0700</t>
+          <t>Tue, 04 Aug 2026 12:58:46 +0700</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) terus memperkuat keamanan dan kerahasiaan data pelanggan seiring semakin luasnya ...</t>
+          <t>Ketua DPR RI Puan Maharani mendorong penguatan keamanan dan keselamatan transportasi laut menyusul sejumlah kecelakaan ...</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679063/kai-perkuat-keamanan-data-pelanggan-terapkan-iso-27001-dan-bentuk-tim-respons-siber</t>
+          <t>https://www.antaranews.com/berita/5678953/puan-dorong-penguatan-keamanan-transportasi-laut-pascakecelakaan-kapal</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/face-recognition.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/Tangkapan-Layar-2026-07-07-pukul-18.21.50.jpeg</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4170,33 +4170,33 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kementerian ESDM: Teknologi hemat energi dukung target penurunan emisi</t>
+          <t>Maroon 5 dijadwalkan tampil di Jakarta pada Februari 2027</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:56:13 +0700</t>
+          <t>Tue, 04 Aug 2026 12:57:20 +0700</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Direktur Konservasi Energi Direktorat Jenderal Energi Baru, Terbarukan, dan Konservasi Energi (EBTKE) Kementerian ...</t>
+          <t>Grup musik pop-rock Maroon 5 dijadwalkan tampil di Jakarta pada 5 Februari 2027 dalam rangkaian tur pertunjukannya ...</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679060/kementerian-esdm-teknologi-hemat-energi-dukung-target-penurunan-emisi</t>
+          <t>https://www.antaranews.com/berita/5678949/maroon-5-dijadwalkan-tampil-di-jakarta-pada-februari-2027</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Proyek-SETI-EBTKE.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/02/02/Konser-Maroon5-Di-Jakarta-010225-IES-2.jpg</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4208,33 +4208,33 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kemenhub: Trans Sumatra Railway hadirkan transportasi terintegrasi</t>
+          <t>Polda Metro Jaya selidiki dugaan ekploitasi anak dalam promosi vape</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:55:35 +0700</t>
+          <t>Tue, 04 Aug 2026 12:56:55 +0700</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kementerian Perhubungan (Kemenhub) mengatakan pengembangan Trans Sumatra Railway atau jalur kereta Trans Sumatra dapat ...</t>
+          <t>Direktorat Perlindungan Perempuan dan Anak Pemberantasan Perdagangan Orang (PPA PPO) Polda Metro Jaya menyelidiki ...</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679053/kemenhub-trans-sumatra-railway-hadirkan-transportasi-terintegrasi</t>
+          <t>https://www.antaranews.com/berita/5678944/polda-metro-jaya-selidiki-dugaan-ekploitasi-anak-dalam-promosi-vape</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/0E2BC257-2126-4A9E-BCED-562A035F164A.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4026.jpeg</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4251,28 +4251,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kemendagri minta pemdes libatkan kelompok rentan dalam pembangunan</t>
+          <t>Diskominfo: Waspada ada 12 hoaks terkait Papua pada Januari-Juli 2026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:55:16 +0700</t>
+          <t>Tue, 04 Aug 2026 12:55:52 +0700</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kementerian Dalam Negeri (Kemendagri) meminta pemerintah desa melibatkan kelompok rentan dalam perencanaan pembangunan ...</t>
+          <t>Dinas Komunikasi dan Informatika (Diskominfo) Provinsi Papua mencatat sebanyak 12 hoaks yang berkaitan dengan Papua ...</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679049/kemendagri-minta-pemdes-libatkan-kelompok-rentan-dalam-pembangunan</t>
+          <t>https://www.antaranews.com/berita/5678940/diskominfo-waspada-ada-12-hoaks-terkait-papua-pada-januari-juli-2026</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG-20260804-WA0011.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002059446.jpg</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4289,28 +4289,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Angkutan Perkebunan KAI Naik 18 Persen menjadi 374.098 Ton, Perkuat Rantai Pasok Sawit Nasional</t>
+          <t>NTB ubah paradigma cagar budaya jadi penggerak ekonomi</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:52:09 +0700</t>
+          <t>Tue, 04 Aug 2026 12:52:11 +0700</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) melayani 374.098 ton angkutan perkebunan sepanjang 1 Januari–31 Juli 2026. ...</t>
+          <t>Gubernur Nusa Tenggara Barat (NTB) Lalu Muhamad Iqbal mengatakan paradigma cagar budaya perlu diubah agar warisan ...</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679045/angkutan-perkebunan-kai-naik-18-persen-menjadi-374098-ton-perkuat-rantai-pasok-sawit-nasional</t>
+          <t>https://www.antaranews.com/berita/5678935/ntb-ubah-paradigma-cagar-budaya-jadi-penggerak-ekonomi</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.18.37.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001433707.jpg</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4322,33 +4322,33 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KSP: RUU Sistranas jadi perekat sistem transportasi massal nasional</t>
+          <t>RSUD Dompu tambah lima dokter spesialis perkuat layanan kesehatan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:48:52 +0700</t>
+          <t>Tue, 04 Aug 2026 12:48:05 +0700</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kantor Staf Presiden (KSP) mengungkapkan Rancangan Undang-Undang Sistem Transportasi Nasional (RUU Sistranas) menjadi ...</t>
+          <t>Rumah Sakit Umum Daerah (RSUD) Kabupaten Dompu, Nusa Tenggara Barat, menambah lima dokter spesialis untuk memperkuat ...</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679041/ksp-ruu-sistranas-jadi-perekat-sistem-transportasi-massal-nasional</t>
+          <t>https://www.antaranews.com/berita/5678932/rsud-dompu-tambah-lima-dokter-spesialis-perkuat-layanan-kesehatan</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1032.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001778561.jpg</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4365,28 +4365,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kemenhut kolaborasi perkuat tata kelola perhutanan sosial di ASEAN</t>
+          <t>Polda NTT gagalkan dugaan perekrutan 21 pekerja migran ilegal</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:47:42 +0700</t>
+          <t>Tue, 04 Aug 2026 12:47:34 +0700</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kementerian Kehutanan (Kemenhut) RI mendukung penguatan tata kelola perhutanan sosial di negara-negara ASEAN untuk ...</t>
+          <t>Tim URC Burhan Satreskrim Polres Ende, Polda Nusa Tenggara Timur, menggagalkan dugaan perekrutan 21 calon pekerja ...</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679040/kemenhut-kolaborasi-perkuat-tata-kelola-perhutanan-sosial-di-asean</t>
+          <t>https://www.antaranews.com/berita/5678929/polda-ntt-gagalkan-dugaan-perekrutan-21-pekerja-migran-ilegal</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_1306.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/image_750x_6a6d44c0944c4.jpg</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4398,33 +4398,33 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, photo, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tambak modern udang vaname di kawasan industri Semarang bidik produksi 1,3 ton per siklus</t>
+          <t>Pakar: Harga minyak dunia turun jadi kesempatan menata aturan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:47:21 +0700</t>
+          <t>Tue, 04 Aug 2026 11:49:32 +0700</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pekerja menunjukkan udang vaname hasil budidaya Loka Perbenihan dan Budi Daya Ikan (PBI) Tugu Dinas Kelautan dan ...</t>
+          <t>Peneliti sekaligus dosen Fakultas Ekonomi dan Bisnis Universitas Padjadjaran Yayan Satyakti menilai turunnya harga ...</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5679037/tambak-modern-udang-vaname-di-kawasan-industri-semarang-bidik-produksi-13-ton-per-siklus</t>
+          <t>https://www.antaranews.com/berita/5678851/pakar-harga-minyak-dunia-turun-jadi-kesempatan-menata-aturan</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/panen-udang-vaname-budidaya-pemprov-jateng-040826-aaa-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4436,33 +4436,33 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BBPMP Jateng siapkan sekolah transisi bagi siswa SNT Banyumas</t>
+          <t>Wuling sediakan "test drive" mobil-mobil terbaru di GIIAS 2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:45:59 +0700</t>
+          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Balai Besar Penjaminan Mutu Pendidikan (BBPMP) Provinsi Jawa Tengah menyiapkan sekolah transisi bagi siswa Sekolah ...</t>
+          <t>Pabrikan otomotif asal China Wuling Motors menyediakan aneka mobil keluaran terbaru mereka untuk diuji coba ...</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679036/bbpmp-jateng-siapkan-sekolah-transisi-bagi-siswa-snt-banyumas</t>
+          <t>https://otomotif.antaranews.com/berita/5678837/wuling-sediakan-test-drive-mobil-mobil-terbaru-di-giias-2026</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001091712.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pada-area-test-drive-Wuling-menyediakan-beragam-lini-kendaraan-sehingga-pengunjung-dapat-merasakan-secara-langsung-performa-kenyamanan-serta-teknologi-yang-dihadirkan.jpeg</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4474,33 +4474,33 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Penjualan mobil naik, Menkeu yakin daya beli domestik tetap terjaga</t>
+          <t>Kementan siapkan Juknis penyerapan telur bagi SPPG Rp26.500/kg</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:45:23 +0700</t>
+          <t>Tue, 04 Aug 2026 11:26:36 +0700</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan pertumbuhan penjualan mobil menjadi salah satu indikator yang ...</t>
+          <t>Kementerian Pertanian (Kementan) menyiapkan petunjuk teknis (Juknis) penyerapan telur oleh seluruh Satuan Pelayanan ...</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679033/penjualan-mobil-naik-menkeu-yakin-daya-beli-domestik-tetap-terjaga</t>
+          <t>https://www.antaranews.com/berita/5678831/kementan-siapkan-juknis-penyerapan-telur-bagi-sppg-rp26500-kg</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.13.50.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/4FB30E01-205C-4253-9C88-5373F761A9FB.jpeg</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4512,33 +4512,33 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Pedagang Taman Puring tagih janji Pemprov revitalisasi pascakebakaran</t>
+          <t>Ekonom proyeksikan pangsa NEV capai 31,7 persen penjualan mobil 2026</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:42:39 +0700</t>
+          <t>Tue, 04 Aug 2026 11:22:55 +0700</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Koordinator pedagang di Taman Puring, Jakarta Selatan, menagih janji Pemerintah Provinsi DKI untuk segera ...</t>
+          <t>Ekonom PT Bank Danamon Indonesia Tbk memproyeksikan pangsa kendaraan energi baru (new energy vehicle/NEV) mencapai 31,7 ...</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679032/pedagang-taman-puring-tagih-janji-pemprov-revitalisasi-pascakebakaran</t>
+          <t>https://www.antaranews.com/berita/5678821/ekonom-proyeksikan-pangsa-nev-capai-317-persen-penjualan-mobil-2026</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001011610.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penjualan-kendaraan-di-semester-1-2026-meningkat-2831868.jpg</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4550,33 +4550,33 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tim Preventive Strike Polda Metro harus utamakan pencegahan gangguan kamtibmas</t>
+          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:40:28 +0700</t>
+          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ketua Dewan Nasional SETARA Institute, Hendardi mengingatkan tim Preventive Strike yang dibentuk Polda Metro Jaya harus ...</t>
+          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679029/tim-preventive-strike-polda-metro-harus-utamakan-pencegahan-gangguan-kamtibmas</t>
+          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/05/12/Petisi-Untuk-Perdamaian-Indonesia-011116-agr-02.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4593,28 +4593,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Samsung larang aplikasi TV yang mengekspos koneksi internet pengguna</t>
+          <t>Kejati NTB tangani tiga kasus dugaan korupsi terkait bank daerah</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:40:22 +0700</t>
+          <t>Tue, 04 Aug 2026 14:27:33 +0700</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Samsung menyatakan bahwa perusahaan melarang aplikasi-aplikasi yang berpotensi mengekspos koneksi internet ...</t>
+          <t>Kejaksaan Tinggi Nusa Tenggara Barat menangani tiga kasus dugaan korupsi yang berkaitan dengan penggunaan anggaran ...</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679025/samsung-larang-aplikasi-tv-yang-mengekspos-koneksi-internet-pengguna</t>
+          <t>https://www.antaranews.com/berita/5679099/kejati-ntb-tangani-tiga-kasus-dugaan-korupsi-terkait-bank-daerah</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/495339513_23879065098420444_7610565358307725dcCC188_n.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/aspidsus-kejati-ntb-zulkifli-said-7.jpg</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -4626,33 +4626,33 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bappenas rumuskan arah respons dalam 4 kluster utama hadapi El-Nino</t>
+          <t>Komisi III DPR masih kaji usulan penggantian nama RUU Perampasan Aset</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:40:21 +0700</t>
+          <t>Tue, 04 Aug 2026 14:27:28 +0700</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Pemerintah merumuskan arah respons empat kluster pembangunan utama dalam bentuk policy brief untuk menghadapi dan ...</t>
+          <t>Komisi III DPR RI masih mengkaji usulan penggantian nama terkait Rancangan Undang-Undang (RUU) tentang Perampasan ...</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679024/bappenas-rumuskan-arah-respons-dalam-4-kluster-utama-hadapi-el-nino</t>
+          <t>https://www.antaranews.com/berita/5679097/komisi-iii-dpr-masih-kaji-usulan-penggantian-nama-ruu-perampasan-aset</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-12.43.09.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/raker-komisi-iii-dpr-dengan-kpk-dan-bnn-2807117.jpg</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -4669,28 +4669,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mendag sebut perjanjian dagang pacu minat investasi</t>
+          <t>Kemenhub siapkan tujuh pola pikir konsep RUU Sistranas</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:38:49 +0700</t>
+          <t>Tue, 04 Aug 2026 14:27:24 +0700</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Menteri Perdagangan (Mendag) Budi Santoso menyampaikan semakin banyaknya perjanjian perdagangan yang dimiliki ...</t>
+          <t>Kementerian Perhubungan (Kemenhub) menyiapkan tujuh pola pikir dalam konsep Rancangan Undang-Undang Sistem Transportasi ...</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679017/mendag-sebut-perjanjian-dagang-pacu-minat-investasi</t>
+          <t>https://www.antaranews.com/berita/5679095/kemenhub-siapkan-tujuh-pola-pikir-konsep-ruu-sistranas</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Mendag.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/79D2CE48-CBEE-4E0E-9C88-371998B3F051.jpeg</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -4707,28 +4707,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BMKG: Waspada gelombang setinggi 6 meter di perairan selatan Bali</t>
+          <t>BSKDN minta pemda jadikan IPKD instrumen perbaikan tata kelola</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:36:42 +0700</t>
+          <t>Tue, 04 Aug 2026 14:23:48 +0700</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Balai Besar Meteorologi Klimatologi dan Geofisika (BBMKG) Wilayah III Denpasar memprakirakan ketinggian gelombang laut ...</t>
+          <t>Kepala Badan Strategi Kebijakan Dalam Negeri (BSKDN) Kementerian Dalam Negeri Yusharto Huntoyungo meminta pemerintah ...</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679015/bmkg-waspada-gelombang-setinggi-6-meter-di-perairan-selatan-bali</t>
+          <t>https://www.antaranews.com/berita/5679092/bskdn-minta-pemda-jadikan-ipkd-instrumen-perbaikan-tata-kelola</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_142653.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000579090.jpg</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -4740,33 +4740,33 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-finansial, terkini</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Pemkot Palu paparkan implementasi kota inklusif bagi disabilitas</t>
+          <t>Ekonom: Pasokan pangan membaik jaga inflasi tetap terkendali</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:35:28 +0700</t>
+          <t>Tue, 04 Aug 2026 14:23:45 +0700</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Pemerintah Kota (Pemkot) Palu, Sulawesi Tengah (Sulteng) memaparkan sejumlah kebijakan yang sudah dilakukan pemerintah ...</t>
+          <t>Ekonom PT Bank Danamon Indonesia Tbk menilai inflasi pada Juli 2026 tetap terkendali seiring membaiknya pasokan pangan ...</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679012/pemkot-palu-paparkan-implementasi-kota-inklusif-bagi-disabilitas</t>
+          <t>https://www.antaranews.com/berita/5679091/ekonom-pasokan-pangan-membaik-jaga-inflasi-tetap-terkendali</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-20.58.47.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/inflasi-juli-2026-jawa-barat-2833080.jpg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -4783,28 +4783,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Polda Metro Jaya panen 82 kg pakcoy untuk bahan baku MBG</t>
+          <t>BPJS Kesehatan: Syarat JKN untuk daftar SIM dorong keaktifan peserta</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:34:09 +0700</t>
+          <t>Tue, 04 Aug 2026 14:23:34 +0700</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Polda Metro Jaya kembali memanen 82 kilogram sayur pakcoy pada Selasa untuk didistribusikan langsung sebagai ...</t>
+          <t>Direktur Kepesertaan BPJS Kesehatan RI Akmal Budi Yulianto menyatakan persyaratan Jaminan Kesehatan Nasional (JKN) ...</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679011/polda-metro-jaya-panen-82-kg-pakcoy-untuk-bahan-baku-mbg</t>
+          <t>https://www.antaranews.com/berita/5679087/bpjs-kesehatan-syarat-jkn-untuk-daftar-sim-dorong-keaktifan-peserta</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/e5362e67-38db-4936-a5fa-c050f3c6eec9.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/20260804_111650.jpg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -4816,33 +4816,33 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>73 santri dan pengasuh ponpes lolos beasiswa Pemprov Jateng</t>
+          <t>Mendag yakin perdagangan bulanan surplus lagi usai harga minyak turun</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:33:28 +0700</t>
+          <t>Tue, 04 Aug 2026 14:23:25 +0700</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sebanyak 73 santri dan pengasuh pondok pesantren berhasil lolos dalam proses seleksi Beasiswa Santri dan Pengasuh ...</t>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso meyakini neraca perdagangan Indonesia kembali mencatatkan surplus secara ...</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679007/73-santri-dan-pengasuh-ponpes-lolos-beasiswa-pemprov-jateng</t>
+          <t>https://www.antaranews.com/berita/5679084/mendag-yakin-perdagangan-bulanan-surplus-lagi-usai-harga-minyak-turun</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002077974.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Mendag_edit_241553389416784.jpg</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -4854,33 +4854,33 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cegah banjir-longsor susulan, BNPB perbaiki tebing sungai di Sipange</t>
+          <t>Kemenko IPK: Kebijakan zero ODOL diharapkan bisa diterapkan awal 2027</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:30:48 +0700</t>
+          <t>Tue, 04 Aug 2026 14:19:33 +0700</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Badan Nasional Penanggulangan Bencana (BNPB) memperbaiki sekaligus memperkuat struktur tebing Sungai Sigala-gala di ...</t>
+          <t>Kementerian Koordinator Bidang Infrastruktur dan Pembangunan Kewilayahan (Kemenko IPK) mengungkapkan kebijakan zero ...</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679003/cegah-banjir-longsor-susulan-bnpb-perbaiki-tebing-sungai-di-sipange</t>
+          <t>https://www.antaranews.com/berita/5679083/kemenko-ipk-kebijakan-zero-odol-diharapkan-bisa-diterapkan-awal-2027</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/IMG_20251207_094949.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1033.jpg</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -4897,28 +4897,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Program Taruna Bhakti dimulai di Sekolah Rakyat Gumas</t>
+          <t>Dilanda cuaca panas, nakes Lhokseumawe bagikan masker untuk cegah ISPA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:29:40 +0700</t>
+          <t>Tue, 04 Aug 2026 14:18:17 +0700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Program Taruna Bhakti 2026 resmi berjalan di Sekolah Rakyat Terintegrasi 54 Kabupaten Gunung Mas (Gumas), Kalimantan ...</t>
+          <t>ANTARA - Dilanda cuaca panas hingga 35 derajat celcius, tim nakes dari Puskesmas Mon Gedong, Kecamatan Banda Sakti, ...</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679000/program-taruna-bhakti-dimulai-di-sekolah-rakyat-gumas</t>
+          <t>https://www.antaranews.com/video/5679057/dilanda-cuaca-panas-nakes-lhokseumawe-bagikan-masker-untuk-cegah-ispa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Gumas-Sekolah-Rakyat-di-gunung-mas-Kabupaten-Gunung-Mas-Kalimantan-Tengah-gumas-kalteng.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DILANDA-CUACA-PANAS-NAKES-LHOKSEUMAWE-BAGIKAN-MASKER-UNTUK-CEGAH-ISPA.jpg</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -4935,28 +4935,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BNPT sebut ormas agama mitra pemerintah perkuat ketahanan radikalisme</t>
+          <t>Anggota DPR minta polisi bongkar sindikat intimidasi korban curanmor</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:27:11 +0700</t>
+          <t>Tue, 04 Aug 2026 14:18:08 +0700</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Badan Nasional Penanggulangan Terorisme (BNPT) menyatakan organisasi kemasyarakatan keagamaan memiliki posisi strategis ...</t>
+          <t>Anggota Komisi III DPR RI Abdullah meminta aparat kepolisian untuk mengusut sekelompok orang diduga sindikat yang ...</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678997/bnpt-sebut-ormas-agama-mitra-pemerintah-perkuat-ketahanan-radikalisme</t>
+          <t>https://www.antaranews.com/berita/5679079/anggota-dpr-minta-polisi-bongkarsindikat-intimidasi-korban-curanmor</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469936.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/20/IMG-20251208-WA0044.jpg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -4968,33 +4968,33 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Jakpus percepat penyelesaian aset fasos hasil kewajiban pengembang</t>
+          <t>MIND ID setor pajak dan dividen senilai Rp32,82 triliun</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:26:16 +0700</t>
+          <t>Tue, 04 Aug 2026 14:16:56 +0700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pemerintah Kota Jakarta Pusat mempercepat penyelesaian administrasi aset berupa fasilitas sosial dan fasilitas ...</t>
+          <t>Holding Industri Pertambangan Indonesia MIND ID membayarkan kewajiban pajak kepada pemerintah serta dividen senilai ...</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678995/jakpus-percepat-penyelesaian-aset-fasos-hasil-kewajiban-pengembang</t>
+          <t>https://www.antaranews.com/berita/5679077/mind-id-setor-pajak-dan-dividen-senilai-rp3282-triliun</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Tamasya-Trotoar-Kita-271218-aaa-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/27/IMG_20260627_084103.jpg</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5011,28 +5011,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dinkes Tanjungpinang: Program CKG anak sekolah sasar 49.343 siswa</t>
+          <t>Qualcomm rilis varian baru Snapdragon 8 Elite Gen 5 V untuk "gaming"</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:20:20 +0700</t>
+          <t>Tue, 04 Aug 2026 14:16:32 +0700</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan, Pengendalian Penduduk, dan Keluarga Berencana (Dinkes PPKB) Kota Tanjungpinang, Kepulauan Riau (Kepri) ...</t>
+          <t>Qualcomm memperkenalkan varian baru dari chipset unggulan Snapdragon 8 Elite Gen 5 V-series yang berfokus ...</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678991/dinkes-tanjungpinang-program-ckg-anak-sekolah-sasar-49343-siswa</t>
+          <t>https://www.antaranews.com/berita/5679075/qualcomm-rilis-varian-baru-snapdragon-8-elite-gen-5-v-untuk-gaming</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_892E3D72-14C7-4D65-8D8A-54508D212D10.png</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Redmi-K100-Pro-chip-1068x1424.jpg</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5044,33 +5044,33 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>photo, terkini</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Pertamina Hulu Indonesia catat produksi migas di atas target</t>
+          <t>Ratusan siswa sekolah gratis di Semarang terima paket perlengkapan sekolah, bantu ringankan beban orang tua</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:19:27 +0700</t>
+          <t>Tue, 04 Aug 2026 14:15:18 +0700</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PT Pertamina Hulu Indonesia (PHI), bagian Subholding Upstream PT Pertamina (Persero), yang mengelola aset hulu migas di ...</t>
+          <t>Siswa menunjukkan tas berisi paket perlengkapan sekolah di Sekolah Gratis Kuncup Melati, Kauman, Semarang, Jawa Tengah, ...</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678988/pertamina-hulu-indonesia-catat-produksi-migas-di-atas-target</t>
+          <t>https://www.antaranews.com/foto/5679073/ratusan-siswa-sekolah-gratis-di-semarang-terima-paket-perlengkapan-sekolah-bantu-ringankan-beban-orang-tua</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260515_154910.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pembagian-seragam-alat-tulis-sd-kuncup-melati-040826-aaa-4.jpg</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5082,33 +5082,33 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Trump desak perusahaan minyak AS segera turunkan harga ke konsumen</t>
+          <t>BMKG: Penyesuaian pola tanam penting cegah gagal panen saat El Nino</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:18:22 +0700</t>
+          <t>Tue, 04 Aug 2026 14:06:51 +0700</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Presiden Amerika Serikat Donald Trump mendesak perusahaan-perusahaan minyak di negaranya untuk segera menurunkan harga ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menekankan pentingnya penyesuaian pola tanam di wilayah terdampak ...</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678984/trump-desak-perusahaan-minyak-as-segera-turunkan-harga-ke-konsumen</t>
+          <t>https://www.antaranews.com/berita/5679069/bmkg-penyesuaian-pola-tanam-penting-cegah-gagal-panen-saat-el-nino</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_ab5d296d556bf61eed768b8ca4900658.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/upaya-petani-beradaptasi-menghadapi-musim-kemarau-2830336.jpg</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5120,33 +5120,33 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>photo, terkini</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Gubernur Kepri pastikan program strategis nasional berjalan baik</t>
+          <t>Target besar 2029, TPST Bantargebang pasang geomembran sebagai kunci transformasi pengelolaan sampah</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:14:01 +0700</t>
+          <t>Tue, 04 Aug 2026 14:00:03 +0700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Gubernur Kepulauan Riau Ansar Ahmad memastikan pelaksanaan berbagai program nasional di daerahnya berjalan baik hingga ...</t>
+          <t>Petugas memasang patok pada geomembran sebagai media pelindung untuk menutup tumpukan sampah di Tempat Pengolahan ...</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678983/gubernur-kepri-pastikan-program-strategis-nasional-berjalan-baik</t>
+          <t>https://www.antaranews.com/foto/5679067/target-besar-2029-tpst-bantargebang-pasang-geomembran-sebagai-kunci-transformasi-pengelolaan-sampah</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_1BD7B733-6D15-464A-B72C-E9015EF50D0A.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Dinas-DLH-DKI-pasang-Geomembrane-di-TPST-Bantargebang-040826-ryl-5.jpg</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5163,28 +5163,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
+          <t>Kemenkes ajak sekolah perkuat perlindungan kesehatan anak lewat BIAS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:11:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:59:06 +0700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, ...</t>
+          <t>Kementerian Kesehatan (Kemenkes) mengajak seluruh kementerian dan lembaga terkait serta satuan pendidikan untuk ...</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
+          <t>https://www.antaranews.com/berita/5679065/kemenkes-ajak-sekolah-perkuat-perlindungan-kesehatan-anak-lewat-bias</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/07/bulan-imunisasi-anak-sekolah-15082025-bal-10.jpg</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5201,28 +5201,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>BNPT dan LAN sepakat tangkal pola baru terorisme di ruang digital</t>
+          <t>KAI Perkuat Keamanan Data Pelanggan, Terapkan ISO 27001 dan Bentuk Tim Respons Siber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:09:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:57:28 +0700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Badan Nasional Penanggulangan Terorisme (BNPT) bersama Lembaga Administrasi Negara (LAN) sepakat untuk menangkal pola ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat keamanan dan kerahasiaan data pelanggan seiring semakin luasnya ...</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678979/bnpt-dan-lan-sepakat-tangkal-pola-baru-terorisme-di-ruang-digital</t>
+          <t>https://www.antaranews.com/berita/5679063/kai-perkuat-keamanan-data-pelanggan-terapkan-iso-27001-dan-bentuk-tim-respons-siber</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469877.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/face-recognition.jpg</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5234,33 +5234,33 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Bocoran kamera Galaxy S27 Pro dan Ultra terungkap, ini perbedaannya</t>
+          <t>Kementerian ESDM: Teknologi hemat energi dukung target penurunan emisi</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:07:58 +0700</t>
+          <t>Tue, 04 Aug 2026 13:56:13 +0700</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bocoran spesifikasi kamera Galaxy S27 Pro dan Galaxy S27 Ultra mencuat setelah dokumen yang dibagikan Samsung kepada ...</t>
+          <t>Direktur Konservasi Energi Direktorat Jenderal Energi Baru, Terbarukan, dan Konservasi Energi (EBTKE) Kementerian ...</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678976/bocoran-kamera-galaxy-s27-pro-dan-ultra-terungkap-ini-perbedaannya</t>
+          <t>https://www.antaranews.com/berita/5679060/kementerian-esdm-teknologi-hemat-energi-dukung-target-penurunan-emisi</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/26/WhatsApp-Image-2026-02-26-at-16.18.01.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Proyek-SETI-EBTKE.jpeg</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5272,33 +5272,33 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Taruna AAL bekali siswa Sekolah Rakyat 32 Natuna pendidikan karakter</t>
+          <t>Kemenhub: Trans Sumatra Railway hadirkan transportasi terintegrasi</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:07:51 +0700</t>
+          <t>Tue, 04 Aug 2026 13:55:35 +0700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Taruna Akademi Angkatan Laut (AAL) membekali siswa Sekolah Rakyat (SR) Terintegrasi 32 Natuna, Provinsi Kepulauan Riau, ...</t>
+          <t>Kementerian Perhubungan (Kemenhub) mengatakan pengembangan Trans Sumatra Railway atau jalur kereta Trans Sumatra dapat ...</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678973/taruna-aal-bekali-siswa-sekolah-rakyat-32-natuna-pendidikan-karakter</t>
+          <t>https://www.antaranews.com/berita/5679053/kemenhub-trans-sumatra-railway-hadirkan-transportasi-terintegrasi</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000833131.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/0E2BC257-2126-4A9E-BCED-562A035F164A.jpeg</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5315,28 +5315,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Transjakarta beri alasan turunkan seorang penumpang di Kampung Melayu</t>
+          <t>Kemendagri minta pemdes libatkan kelompok rentan dalam pembangunan</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:07:38 +0700</t>
+          <t>Tue, 04 Aug 2026 13:55:16 +0700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>PT Transportasi Jakarta menyampaikan tindakan petugas menurunkan seorang penumpang dari bus di Halte Kampung Melayu, ...</t>
+          <t>Kementerian Dalam Negeri (Kemendagri) meminta pemerintah desa melibatkan kelompok rentan dalam perencanaan pembangunan ...</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678969/transjakarta-beri-alasan-turunkan-seorang-penumpang-di-kampung-melayu</t>
+          <t>https://www.antaranews.com/berita/5679049/kemendagri-minta-pemdes-libatkan-kelompok-rentan-dalam-pembangunan</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/jumlah-penumpang-angkutan-umum-di-jakarta-meningkat-2816319.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG-20260804-WA0011.jpg</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5353,28 +5353,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sopir truk korban KMP Mutiara Sentosa asal Tulungagung dimakamkan</t>
+          <t>Angkutan Perkebunan KAI Naik 18 Persen menjadi 374.098 Ton, Perkuat Rantai Pasok Sawit Nasional</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:05:38 +0700</t>
+          <t>Tue, 04 Aug 2026 13:52:09 +0700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Jenazah Sari Sukoco (39), salah satu korban meninggal dunia dalam kebakaran KMP Mutiara Sentosa 2 di perairan Madura, ...</t>
+          <t>PT Kereta Api Indonesia (Persero) melayani 374.098 ton angkutan perkebunan sepanjang 1 Januari–31 Juli 2026. ...</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678967/sopir-truk-korban-kmp-mutiara-sentosa-asal-tulungagung-dimakamkan</t>
+          <t>https://www.antaranews.com/berita/5679045/angkutan-perkebunan-kai-naik-18-persen-menjadi-374098-ton-perkuat-rantai-pasok-sawit-nasional</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/454482.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.18.37.jpeg</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5386,33 +5386,33 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
+          <t>KSP: RUU Sistranas jadi perekat sistem transportasi massal nasional</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:03:10 +0700</t>
+          <t>Tue, 04 Aug 2026 13:48:52 +0700</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi ...</t>
+          <t>Kantor Staf Presiden (KSP) mengungkapkan Rancangan Undang-Undang Sistem Transportasi Nasional (RUU Sistranas) menjadi ...</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
+          <t>https://www.antaranews.com/berita/5679041/ksp-ruu-sistranas-jadi-perekat-sistem-transportasi-massal-nasional</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1032.jpg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5429,28 +5429,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BNPB: 150 warga mengungsi akibat tanggul jebol picu banjir di Tapteng</t>
+          <t>Kemenhut kolaborasi perkuat tata kelola perhutanan sosial di ASEAN</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:59:51 +0700</t>
+          <t>Tue, 04 Aug 2026 13:47:42 +0700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Badan Nasional Penanggulangan Bencana (BNPB) mencatat sebanyak 150 warga di Kabupaten Tapanuli Tengah (Tapteng), ...</t>
+          <t>Kementerian Kehutanan (Kemenhut) RI mendukung penguatan tata kelola perhutanan sosial di negara-negara ASEAN untuk ...</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678961/bnpb-150-warga-mengungsi-akibat-tanggul-jebol-picu-banjir-di-tapteng</t>
+          <t>https://www.antaranews.com/berita/5679040/kemenhut-kolaborasi-perkuat-tata-kelola-perhutanan-sosial-di-asean</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/05/21/81e7716a-5d0a-474c-a05f-b4b702088781.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_1306.jpg</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5462,33 +5462,33 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, photo, terkini</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pemkab Karo imbau masyarakat patuhi zona aman Gunung Sinabung</t>
+          <t>Tambak modern udang vaname di kawasan industri Semarang bidik produksi 1,3 ton per siklus</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:59:44 +0700</t>
+          <t>Tue, 04 Aug 2026 13:47:21 +0700</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pemerintah Kabupaten (Pemkab) Karo mengimbau masyarakat mematuhi zona aman menyusul peningkatan status aktivitas ...</t>
+          <t>Pekerja menunjukkan udang vaname hasil budidaya Loka Perbenihan dan Budi Daya Ikan (PBI) Tugu Dinas Kelautan dan ...</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678957/pemkab-karo-imbau-masyarakat-patuhi-zona-aman-gunung-sinabung</t>
+          <t>https://www.antaranews.com/foto/5679037/tambak-modern-udang-vaname-di-kawasan-industri-semarang-bidik-produksi-13-ton-per-siklus</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000497965.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/panen-udang-vaname-budidaya-pemprov-jateng-040826-aaa-2.jpg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5505,28 +5505,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DKPP pastikan cadangan beras Kab. Serang aman hingga setahun ke depan</t>
+          <t>BBPMP Jateng siapkan sekolah transisi bagi siswa SNT Banyumas</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:58:52 +0700</t>
+          <t>Tue, 04 Aug 2026 13:45:59 +0700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Ketahanan Pangan dan Pertanian (DKPP) Kabupaten Serang, Selasa (4/8), memastikan cadangan beras ...</t>
+          <t>Balai Besar Penjaminan Mutu Pendidikan (BBPMP) Provinsi Jawa Tengah menyiapkan sekolah transisi bagi siswa Sekolah ...</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678939/dkpp-pastikan-cadangan-beras-kab-serang-aman-hingga-setahun-ke-depan</t>
+          <t>https://www.antaranews.com/berita/5679036/bbpmp-jateng-siapkan-sekolah-transisi-bagi-siswa-snt-banyumas</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DKPP-PASTIKAN-CADANGAN-BERAS-KAB.SERANG-AMAN-HINGGA-SETAHUN-KE-DEPAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001091712.jpg</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5538,33 +5538,33 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini, top-news</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Puan dorong penguatan keamanan transportasi laut pascakecelakaan kapal</t>
+          <t>Penjualan mobil naik, Menkeu yakin daya beli domestik tetap terjaga</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:58:46 +0700</t>
+          <t>Tue, 04 Aug 2026 13:45:23 +0700</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ketua DPR RI Puan Maharani mendorong penguatan keamanan dan keselamatan transportasi laut menyusul sejumlah kecelakaan ...</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan pertumbuhan penjualan mobil menjadi salah satu indikator yang ...</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678953/puan-dorong-penguatan-keamanan-transportasi-laut-pascakecelakaan-kapal</t>
+          <t>https://www.antaranews.com/berita/5679033/penjualan-mobil-naik-menkeu-yakin-daya-beli-domestik-tetap-terjaga</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/07/Tangkapan-Layar-2026-07-07-pukul-18.21.50.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.13.50.jpeg</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5581,28 +5581,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Maroon 5 dijadwalkan tampil di Jakarta pada Februari 2027</t>
+          <t>Pedagang Taman Puring tagih janji Pemprov revitalisasi pascakebakaran</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:57:20 +0700</t>
+          <t>Tue, 04 Aug 2026 13:42:39 +0700</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Grup musik pop-rock Maroon 5 dijadwalkan tampil di Jakarta pada 5 Februari 2027 dalam rangkaian tur pertunjukannya ...</t>
+          <t>Koordinator pedagang di Taman Puring, Jakarta Selatan, menagih janji Pemerintah Provinsi DKI untuk segera ...</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678949/maroon-5-dijadwalkan-tampil-di-jakarta-pada-februari-2027</t>
+          <t>https://www.antaranews.com/berita/5679032/pedagang-taman-puring-tagih-janji-pemprov-revitalisasi-pascakebakaran</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/02/02/Konser-Maroon5-Di-Jakarta-010225-IES-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001011610.jpg</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5614,33 +5614,33 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LPEM FEB UI perkirakan ekonomi RI tumbuh 4,8 persen di kuartal II 2026</t>
+          <t>Tim Preventive Strike Polda Metro harus utamakan pencegahan gangguan kamtibmas</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:57:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:28 +0700</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lembaga Penyelidikan Ekonomi dan Masyarakat Fakultas Ekonomi dan Bisnis Universitas Indonesia (LPEM FEB UI) ...</t>
+          <t>Ketua Dewan Nasional SETARA Institute, Hendardi mengingatkan tim Preventive Strike yang dibentuk Polda Metro Jaya harus ...</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678945/lpem-feb-ui-perkirakan-ekonomi-ri-tumbuh-48-persen-di-kuartal-ii-2026</t>
+          <t>https://www.antaranews.com/berita/5679029/tim-preventive-strike-polda-metro-harus-utamakan-pencegahan-gangguan-kamtibmas</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2022/05/17/Screenshot_20220517-151559_YouTube.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/12/Petisi-Untuk-Perdamaian-Indonesia-011116-agr-02.jpg</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -5657,28 +5657,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Polda Metro Jaya selidiki dugaan ekploitasi anak dalam promosi vape</t>
+          <t>Samsung larang aplikasi TV yang mengekspos koneksi internet pengguna</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:56:55 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:22 +0700</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Direktorat Perlindungan Perempuan dan Anak Pemberantasan Perdagangan Orang (PPA PPO) Polda Metro Jaya menyelidiki ...</t>
+          <t>Samsung menyatakan bahwa perusahaan melarang aplikasi-aplikasi yang berpotensi mengekspos koneksi internet ...</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678944/polda-metro-jaya-selidiki-dugaan-ekploitasi-anak-dalam-promosi-vape</t>
+          <t>https://www.antaranews.com/berita/5679025/samsung-larang-aplikasi-tv-yang-mengekspos-koneksi-internet-pengguna</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4026.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/495339513_23879065098420444_7610565358307725dcCC188_n.jpg</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -5695,28 +5695,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Saat rantai pasok menjadi benteng inflasi</t>
+          <t>Bappenas rumuskan arah respons dalam 4 kluster utama hadapi El-Nino</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:56:38 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:21 +0700</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Di tengah ancaman El Nino dan tantangan logistik negara kepulauan, inflasi Indonesia pada Juli 2026 menunjukkan bahwa ...</t>
+          <t>Pemerintah merumuskan arah respons empat kluster pembangunan utama dalam bentuk policy brief untuk menghadapi dan ...</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678943/saat-rantai-pasok-menjadi-benteng-inflasi</t>
+          <t>https://www.antaranews.com/berita/5679024/bappenas-rumuskan-arah-respons-dalam-4-kluster-utama-hadapi-el-nino</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/12/05/1000001928.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-12.43.09.jpeg</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -5728,33 +5728,33 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Diskominfo: Waspada ada 12 hoaks terkait Papua pada Januari-Juli 2026</t>
+          <t>Mendag sebut perjanjian dagang pacu minat investasi</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:55:52 +0700</t>
+          <t>Tue, 04 Aug 2026 13:38:49 +0700</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dinas Komunikasi dan Informatika (Diskominfo) Provinsi Papua mencatat sebanyak 12 hoaks yang berkaitan dengan Papua ...</t>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso menyampaikan semakin banyaknya perjanjian perdagangan yang dimiliki ...</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678940/diskominfo-waspada-ada-12-hoaks-terkait-papua-pada-januari-juli-2026</t>
+          <t>https://www.antaranews.com/berita/5679017/mendag-sebut-perjanjian-dagang-pacu-minat-investasi</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/1002059446.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Mendag.jpg</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -5766,33 +5766,33 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BMKG: Juli 2026 menjadi Juli terkering sejak 1991</t>
+          <t>BMKG: Waspada gelombang setinggi 6 meter di perairan selatan Bali</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:55:25 +0700</t>
+          <t>Tue, 04 Aug 2026 13:36:42 +0700</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyatakan Juli 2026 menjadi bulan Juli terkering di Indonesia ...</t>
+          <t>Balai Besar Meteorologi Klimatologi dan Geofisika (BBMKG) Wilayah III Denpasar memprakirakan ketinggian gelombang laut ...</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678936/bmkg-juli-2026-menjadi-juli-terkering-sejak-1991</t>
+          <t>https://www.antaranews.com/berita/5679015/bmkg-waspada-gelombang-setinggi-6-meter-di-perairan-selatan-bali</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Prediksi-kemarau-di-Jawa-Barat-160726-adb-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_142653.jpg</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -5809,28 +5809,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NTB ubah paradigma cagar budaya jadi penggerak ekonomi</t>
+          <t>Pemkot Palu paparkan implementasi kota inklusif bagi disabilitas</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:52:11 +0700</t>
+          <t>Tue, 04 Aug 2026 13:35:28 +0700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Gubernur Nusa Tenggara Barat (NTB) Lalu Muhamad Iqbal mengatakan paradigma cagar budaya perlu diubah agar warisan ...</t>
+          <t>Pemerintah Kota (Pemkot) Palu, Sulawesi Tengah (Sulteng) memaparkan sejumlah kebijakan yang sudah dilakukan pemerintah ...</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678935/ntb-ubah-paradigma-cagar-budaya-jadi-penggerak-ekonomi</t>
+          <t>https://www.antaranews.com/berita/5679012/pemkot-palu-paparkan-implementasi-kota-inklusif-bagi-disabilitas</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001433707.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-20.58.47.jpeg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -5847,28 +5847,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>RSUD Dompu tambah lima dokter spesialis perkuat layanan kesehatan</t>
+          <t>Polda Metro Jaya panen 82 kg pakcoy untuk bahan baku MBG</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:48:05 +0700</t>
+          <t>Tue, 04 Aug 2026 13:34:09 +0700</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rumah Sakit Umum Daerah (RSUD) Kabupaten Dompu, Nusa Tenggara Barat, menambah lima dokter spesialis untuk memperkuat ...</t>
+          <t>Polda Metro Jaya kembali memanen 82 kilogram sayur pakcoy pada Selasa untuk didistribusikan langsung sebagai ...</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678932/rsud-dompu-tambah-lima-dokter-spesialis-perkuat-layanan-kesehatan</t>
+          <t>https://www.antaranews.com/berita/5679011/polda-metro-jaya-panen-82-kg-pakcoy-untuk-bahan-baku-mbg</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001778561.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/e5362e67-38db-4936-a5fa-c050f3c6eec9.jpeg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -5885,28 +5885,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Polda NTT gagalkan dugaan perekrutan 21 pekerja migran ilegal</t>
+          <t>73 santri dan pengasuh ponpes lolos beasiswa Pemprov Jateng</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:47:34 +0700</t>
+          <t>Tue, 04 Aug 2026 13:33:28 +0700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Tim URC Burhan Satreskrim Polres Ende, Polda Nusa Tenggara Timur, menggagalkan dugaan perekrutan 21 calon pekerja ...</t>
+          <t>Sebanyak 73 santri dan pengasuh pondok pesantren berhasil lolos dalam proses seleksi Beasiswa Santri dan Pengasuh ...</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678929/polda-ntt-gagalkan-dugaan-perekrutan-21-pekerja-migran-ilegal</t>
+          <t>https://www.antaranews.com/berita/5679007/73-santri-dan-pengasuh-ponpes-lolos-beasiswa-pemprov-jateng</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/image_750x_6a6d44c0944c4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002077974.jpg</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -5918,33 +5918,33 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ada 2 bibit siklon tropis, BMKG: Waspada ombak setinggi 4 meter di RI</t>
+          <t>Cegah banjir-longsor susulan, BNPB perbaiki tebing sungai di Sipange</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:09:44 +0700</t>
+          <t>Tue, 04 Aug 2026 13:30:48 +0700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi kemunculan dua bibit siklon tropis sekaligus di wilayah ...</t>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) memperbaiki sekaligus memperkuat struktur tebing Sungai Sigala-gala di ...</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678879/ada-2-bibit-siklon-tropis-bmkg-waspada-ombak-setinggi-4-meter-di-ri</t>
+          <t>https://www.antaranews.com/berita/5679003/cegah-banjir-longsor-susulan-bnpb-perbaiki-tebing-sungai-di-sipange</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20250609_135328.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/IMG_20251207_094949.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -5956,33 +5956,33 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Korban tewas gempa Venezuela terus bertambah jadi 6.100 orang</t>
+          <t>Program Taruna Bhakti dimulai di Sekolah Rakyat Gumas</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:00:56 +0700</t>
+          <t>Tue, 04 Aug 2026 13:29:40 +0700</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Jumlah korban tewas akibat gempa kembar dahsyat yang mengguncang Venezuela pada 24 Juni 2026, terus bertambah ...</t>
+          <t>Program Taruna Bhakti 2026 resmi berjalan di Sekolah Rakyat Terintegrasi 54 Kabupaten Gunung Mas (Gumas), Kalimantan ...</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678865/korban-tewas-gempa-venezuela-terus-bertambah-jadi-6100-orang</t>
+          <t>https://www.antaranews.com/berita/5679000/program-taruna-bhakti-dimulai-di-sekolah-rakyat-gumas</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_d4a34a165f13a0667255577d3cfac46f.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Gumas-Sekolah-Rakyat-di-gunung-mas-Kabupaten-Gunung-Mas-Kalimantan-Tengah-gumas-kalteng.jpg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -5994,33 +5994,33 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BPKH salurkan Rp2,06 triliun nilai manfaat ke 5,7 juta calon haji</t>
+          <t>BNPT sebut ormas agama mitra pemerintah perkuat ketahanan radikalisme</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:47:58 +0700</t>
+          <t>Tue, 04 Aug 2026 13:27:11 +0700</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Badan Pengelola Keuangan Haji (BPKH) menyalurkan Nilai Manfaat Tahap I Tahun 2026 lebih dari Rp2,06 triliun kepada ...</t>
+          <t>Badan Nasional Penanggulangan Terorisme (BNPT) menyatakan organisasi kemasyarakatan keagamaan memiliki posisi strategis ...</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678849/bpkh-salurkan-rp206-triliun-nilai-manfaat-ke-57-juta-calon-haji</t>
+          <t>https://www.antaranews.com/berita/5678997/bnpt-sebut-ormas-agama-mitra-pemerintah-perkuat-ketahanan-radikalisme</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176506_1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469936.jpg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6032,33 +6032,33 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Aldila jadi petenis Indonesia yang pertama juarai DC Open</t>
+          <t>Jakpus percepat penyelesaian aset fasos hasil kewajiban pengembang</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
+          <t>Tue, 04 Aug 2026 13:26:16 +0700</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Petenis Indonesia Aldila Sutjiadi mencatatkan sejarah setelah menjuarai nomor ganda putri turnamen Mubadala DC Open ...</t>
+          <t>Pemerintah Kota Jakarta Pusat mempercepat penyelesaian administrasi aset berupa fasilitas sosial dan fasilitas ...</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678836/aldila-jadi-petenis-indonesia-yang-pertama-juarai-dc-open</t>
+          <t>https://www.antaranews.com/berita/5678995/jakpus-percepat-penyelesaian-aset-fasos-hasil-kewajiban-pengembang</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4155-copy.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Tamasya-Trotoar-Kita-271218-aaa-1.jpg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6070,33 +6070,33 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Indonesia raih 15 medali dari Kejuaraan MMAAsia</t>
+          <t>Dinkes Tanjungpinang: Program CKG anak sekolah sasar 49.343 siswa</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:16:36 +0700</t>
+          <t>Tue, 04 Aug 2026 13:20:20 +0700</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Tim mixed martial arts (MMA) amatir Indonesia meraih 15 medali dan menempati peringkat keempat pada GAMMA Asian ...</t>
+          <t>Dinas Kesehatan, Pengendalian Penduduk, dan Keluarga Berencana (Dinkes PPKB) Kota Tanjungpinang, Kepulauan Riau (Kepri) ...</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678689/indonesia-raih-15-medali-dari-kejuaraan-mmaasia</t>
+          <t>https://www.antaranews.com/berita/5678991/dinkes-tanjungpinang-program-ckg-anak-sekolah-sasar-49343-siswa</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Delvi-Novia_Medal.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_892E3D72-14C7-4D65-8D8A-54508D212D10.png</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6108,33 +6108,33 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Kontingen Indonesia di Asian Games 2026</t>
+          <t>Pertamina Hulu Indonesia catat produksi migas di atas target</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
+          <t>Tue, 04 Aug 2026 13:19:27 +0700</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
+          <t>PT Pertamina Hulu Indonesia (PHI), bagian Subholding Upstream PT Pertamina (Persero), yang mengelola aset hulu migas di ...</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
+          <t>https://www.antaranews.com/berita/5678988/pertamina-hulu-indonesia-catat-produksi-migas-di-atas-target</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260515_154910.jpg</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6146,33 +6146,33 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
+          <t>Trump desak perusahaan minyak AS segera turunkan harga ke konsumen</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
+          <t>Tue, 04 Aug 2026 13:18:22 +0700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
+          <t>Presiden Amerika Serikat Donald Trump mendesak perusahaan-perusahaan minyak di negaranya untuk segera menurunkan harga ...</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
+          <t>https://www.antaranews.com/berita/5678984/trump-desak-perusahaan-minyak-as-segera-turunkan-harga-ke-konsumen</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_ab5d296d556bf61eed768b8ca4900658.jpg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6184,33 +6184,33 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+          <t>Gubernur Kepri pastikan program strategis nasional berjalan baik</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+          <t>Tue, 04 Aug 2026 13:14:01 +0700</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+          <t>Gubernur Kepulauan Riau Ansar Ahmad memastikan pelaksanaan berbagai program nasional di daerahnya berjalan baik hingga ...</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+          <t>https://www.antaranews.com/berita/5678983/gubernur-kepri-pastikan-program-strategis-nasional-berjalan-baik</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_1BD7B733-6D15-464A-B72C-E9015EF50D0A.jpeg</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6222,33 +6222,33 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BI siapkan Rp20 miliar ekspedisi rupiah berdaulat 2026 di 3T Papua</t>
+          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:24:47 +0700</t>
+          <t>Tue, 04 Aug 2026 13:11:01 +0700</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kantor Perwakilan Bank Indonesia (BI) Provinsi Papua menyiapkan uang layak edar senilai Rp20 miliar dalam pelaksanaan ...</t>
+          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, ...</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678896/bi-siapkan-rp20-miliar-ekspedisi-rupiah-berdaulat-2026-di-3t-papua</t>
+          <t>https://www.antaranews.com/video/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002062154.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6260,33 +6260,33 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Panda Bond dan sinyal kepercayaan investasi global</t>
+          <t>BNPT dan LAN sepakat tangkal pola baru terorisme di ruang digital</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:26:35 +0700</t>
+          <t>Tue, 04 Aug 2026 13:09:01 +0700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Di tengah ketidakpastian ekonomi global yang semakin kompleks, pemerintah Indonesia perlu memastikan bahwa ...</t>
+          <t>Badan Nasional Penanggulangan Terorisme (BNPT) bersama Lembaga Administrasi Negara (LAN) sepakat untuk menangkal pola ...</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678827/panda-bond-dan-sinyal-kepercayaan-investasi-global</t>
+          <t>https://www.antaranews.com/berita/5678979/bnpt-dan-lan-sepakat-tangkal-pola-baru-terorisme-di-ruang-digital</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/permintaan-pembelian-obligasi-global-capai-46-miliar-dolar-as-2806089.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469877.jpg</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6298,33 +6298,33 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Rupiah Selasa melemah dipicu kenaikan harga minyak global</t>
+          <t>Bocoran kamera Galaxy S27 Pro dan Ultra terungkap, ini perbedaannya</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:15:57 +0700</t>
+          <t>Tue, 04 Aug 2026 13:07:58 +0700</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Selasa pagi bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per dolar AS ...</t>
+          <t>Bocoran spesifikasi kamera Galaxy S27 Pro dan Galaxy S27 Ultra mencuat setelah dokumen yang dibagikan Samsung kepada ...</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678808/rupiah-selasa-melemah-dipicu-kenaikan-harga-minyak-global</t>
+          <t>https://www.antaranews.com/berita/5678976/bocoran-kamera-galaxy-s27-pro-dan-ultra-terungkap-ini-perbedaannya</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/nilai-tukar-rupiah-melemah-44-poin-2821215.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/26/WhatsApp-Image-2026-02-26-at-16.18.01.jpeg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6336,33 +6336,33 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DJPb catat pembelanjaan di 75 KDKMP Sultra capai 1.055 kali transaksi</t>
+          <t>Taruna AAL bekali siswa Sekolah Rakyat 32 Natuna pendidikan karakter</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:00:21 +0700</t>
+          <t>Tue, 04 Aug 2026 13:07:51 +0700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Kantor Wilayah (Kanwil) Direktorat Jenderal Perbendaharaan (DJPb) Provinsi Sulawesi Tenggara (Sultra), mencatat ...</t>
+          <t>Taruna Akademi Angkatan Laut (AAL) membekali siswa Sekolah Rakyat (SR) Terintegrasi 32 Natuna, Provinsi Kepulauan Riau, ...</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678732/djpb-catat-pembelanjaan-di-75-kdkmp-sultra-capai-1055-kali-transaksi</t>
+          <t>https://www.antaranews.com/berita/5678973/taruna-aal-bekali-siswa-sekolah-rakyat-32-natuna-pendidikan-karakter</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/2798be53-c5ca-4be6-bcf8-a2e9eb6c7488.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000833131.jpg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6374,33 +6374,33 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Rupiah pada Selasa pagi melemah jadi Rp18.029 per dolar AS</t>
+          <t>Transjakarta beri alasan turunkan seorang penumpang di Kampung Melayu</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:16:27 +0700</t>
+          <t>Tue, 04 Aug 2026 13:07:38 +0700</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah terhadap dolar AS pada Selasa pagi, bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per ...</t>
+          <t>PT Transportasi Jakarta menyampaikan tindakan petugas menurunkan seorang penumpang dari bus di Halte Kampung Melayu, ...</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678685/rupiah-pada-selasa-pagi-melemah-jadi-rp18029-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5678969/transjakarta-beri-alasan-turunkan-seorang-penumpang-di-kampung-melayu</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/jumlah-penumpang-angkutan-umum-di-jakarta-meningkat-2816319.jpg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6412,33 +6412,33 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CORE: Penilaian kredit alternatif dapat perluas pembiayaan UMKM</t>
+          <t>Sopir truk korban KMP Mutiara Sentosa asal Tulungagung dimakamkan</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:58:42 +0700</t>
+          <t>Tue, 04 Aug 2026 13:05:38 +0700</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai pemanfaatan penilaian kredit ...</t>
+          <t>Jenazah Sari Sukoco (39), salah satu korban meninggal dunia dalam kebakaran KMP Mutiara Sentosa 2 di perairan Madura, ...</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678651/core-penilaian-kredit-alternatif-dapat-perluas-pembiayaan-umkm</t>
+          <t>https://www.antaranews.com/berita/5678967/sopir-truk-korban-kmp-mutiara-sentosa-asal-tulungagung-dimakamkan</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/realisasi-penyaluran-kur-umkm-2832719.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/454482.jpg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6450,33 +6450,33 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Airbus A380-800 Emirates akan mendarat perdana di Bandara Soetta</t>
+          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:47:25 +0700</t>
+          <t>Tue, 04 Aug 2026 13:03:10 +0700</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Pesawat jenis Airbus A380-800 milik maskapai Emirates yang melayani penerbangan EK358 rute Dubai (DXB)–Jakarta ...</t>
+          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi ...</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678928/airbus-a380-800-emirates-akan-mendarat-perdana-di-bandara-soetta</t>
+          <t>https://www.antaranews.com/video/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/06/02/A380-2_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -6488,33 +6488,33 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Pemerintah targetkan pembangunan 35.872 unit KDKMP rampung di Agustus</t>
+          <t>Ada 2 bibit siklon tropis, BMKG: Waspada ombak setinggi 4 meter di RI</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:41:37 +0700</t>
+          <t>Tue, 04 Aug 2026 12:09:44 +0700</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Pemerintah menargetkan pembangunan gedung koperasi desa dan kelurahan merah putih (KDKMP) rampung sebanyak 35.872 ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi kemunculan dua bibit siklon tropis sekaligus di wilayah ...</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678915/pemerintah-targetkan-pembangunan-35872-unit-kdkmp-rampung-di-agustus</t>
+          <t>https://www.antaranews.com/berita/5678879/ada-2-bibit-siklon-tropis-bmkg-waspada-ombak-setinggi-4-meter-di-ri</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002905262.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20250609_135328.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6526,33 +6526,33 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, photo</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Kementan usulkan telur ayam masuk skema cadangan pangan pemerintah</t>
+          <t>Korban tewas gempa Venezuela terus bertambah jadi 6.100 orang</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:30:53 +0700</t>
+          <t>Tue, 04 Aug 2026 12:00:56 +0700</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Pekerja memberikan pakan ayam di salah satu peternakan di Cihampelas, Kabupaten Bandung Barat, Jawa Barat, Selasa ...</t>
+          <t>Jumlah korban tewas akibat gempa kembar dahsyat yang mengguncang Venezuela pada 24 Juni 2026, terus bertambah ...</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678903/kementan-usulkan-telur-ayam-masuk-skema-cadangan-pangan-pemerintah</t>
+          <t>https://www.antaranews.com/berita/5678865/korban-tewas-gempa-venezuela-terus-bertambah-jadi-6100-orang</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Kementan-Usulkan-Telur-Ayam-Masuk-Skema-CPP-040826-DAN-07.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_d4a34a165f13a0667255577d3cfac46f.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -6564,33 +6564,33 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Honda Super-One 2026 dijual di Australia, segini harganya</t>
+          <t>BPKH salurkan Rp2,06 triliun nilai manfaat ke 5,7 juta calon haji</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:29:17 +0700</t>
+          <t>Tue, 04 Aug 2026 11:47:58 +0700</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Honda Super-One debut perdana di Gaikindo Indonesia International Auto Show (GIIAS) 2026, Indonesia, harganya masih ...</t>
+          <t>Badan Pengelola Keuangan Haji (BPKH) menyalurkan Nilai Manfaat Tahap I Tahun 2026 lebih dari Rp2,06 triliun kepada ...</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678901/honda-super-one-2026-dijual-di-australia-segini-harganya</t>
+          <t>https://www.antaranews.com/berita/5678849/bpkh-salurkan-rp206-triliun-nilai-manfaat-ke-57-juta-calon-haji</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG_1401.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176506_1.jpg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -6602,33 +6602,33 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Kemenekraf perkuat KPT Ekraf jadi penggerak hilirisasi talenta kreatif</t>
+          <t>Aldila jadi petenis Indonesia yang pertama juarai DC Open</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:59:18 +0700</t>
+          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Kementerian Ekonomi Kreatif/Badan Ekonomi Kreatif (Ekraf) memperkuat peran Konsorsium Perguruan Tinggi (KPT) Ekraf ...</t>
+          <t>Petenis Indonesia Aldila Sutjiadi mencatatkan sejarah setelah menjuarai nomor ganda putri turnamen Mubadala DC Open ...</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678861/kemenekraf-perkuat-kpt-ekraf-jadi-penggerak-hilirisasi-talenta-kreatif</t>
+          <t>https://www.antaranews.com/berita/5678836/aldila-jadi-petenis-indonesia-yang-pertama-juarai-dc-open</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000453579.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4155-copy.jpg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -6640,33 +6640,33 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Pakar: Harga minyak dunia turun jadi kesempatan menata aturan</t>
+          <t>Indonesia raih 15 medali dari Kejuaraan MMAAsia</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:49:32 +0700</t>
+          <t>Tue, 04 Aug 2026 09:16:36 +0700</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Peneliti sekaligus dosen Fakultas Ekonomi dan Bisnis Universitas Padjadjaran Yayan Satyakti menilai turunnya harga ...</t>
+          <t>Tim mixed martial arts (MMA) amatir Indonesia meraih 15 medali dan menempati peringkat keempat pada GAMMA Asian ...</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678851/pakar-harga-minyak-dunia-turun-jadi-kesempatan-menata-aturan</t>
+          <t>https://www.antaranews.com/berita/5678689/indonesia-raih-15-medali-dari-kejuaraan-mmaasia</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penurunan-harga-bbm-jenis-pertamax-2831783.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Delvi-Novia_Medal.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -6678,33 +6678,33 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Wuling sediakan "test drive" mobil-mobil terbaru di GIIAS 2026</t>
+          <t>Kontingen Indonesia di Asian Games 2026</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
+          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Pabrikan otomotif asal China Wuling Motors menyediakan aneka mobil keluaran terbaru mereka untuk diuji coba ...</t>
+          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678837/wuling-sediakan-test-drive-mobil-mobil-terbaru-di-giias-2026</t>
+          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pada-area-test-drive-Wuling-menyediakan-beragam-lini-kendaraan-sehingga-pengunjung-dapat-merasakan-secara-langsung-performa-kenyamanan-serta-teknologi-yang-dihadirkan.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -6716,33 +6716,33 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Kementan siapkan Juknis penyerapan telur bagi SPPG Rp26.500/kg</t>
+          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:26:36 +0700</t>
+          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Kementerian Pertanian (Kementan) menyiapkan petunjuk teknis (Juknis) penyerapan telur oleh seluruh Satuan Pelayanan ...</t>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678831/kementan-siapkan-juknis-penyerapan-telur-bagi-sppg-rp26500-kg</t>
+          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/4FB30E01-205C-4253-9C88-5373F761A9FB.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -6754,33 +6754,33 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>top-news</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ekonom proyeksikan pangsa NEV capai 31,7 persen penjualan mobil 2026</t>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:22:55 +0700</t>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Ekonom PT Bank Danamon Indonesia Tbk memproyeksikan pangsa kendaraan energi baru (new energy vehicle/NEV) mencapai 31,7 ...</t>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678821/ekonom-proyeksikan-pangsa-nev-capai-317-persen-penjualan-mobil-2026</t>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/penjualan-kendaraan-di-semester-1-2026-meningkat-2831868.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -6792,33 +6792,33 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>IHSG menguat ditopang kinerja keuangan emiten periode kuartal II</t>
+          <t>LPEM FEB UI perkirakan ekonomi RI tumbuh 4,8 persen di kuartal II 2026</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:12:17 +0700</t>
+          <t>Tue, 04 Aug 2026 12:57:01 +0700</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa bergerak menguat ditopang oleh laporan ...</t>
+          <t>Lembaga Penyelidikan Ekonomi dan Masyarakat Fakultas Ekonomi dan Bisnis Universitas Indonesia (LPEM FEB UI) ...</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678748/ihsg-menguat-ditopang-kinerja-keuangan-emiten-periode-kuartal-ii</t>
+          <t>https://www.antaranews.com/berita/5678945/lpem-feb-ui-perkirakan-ekonomi-ri-tumbuh-48-persen-di-kuartal-ii-2026</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/06/30/BEI-catatkan-14-perusahaan-baru-pada-2025-260625-fzn-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/05/17/Screenshot_20220517-151559_YouTube.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -6830,33 +6830,33 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IHSG Selasa dibuka menguat 20,28 poin ke posisi 6.254</t>
+          <t>BI siapkan Rp20 miliar ekspedisi rupiah berdaulat 2026 di 3T Papua</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:06:02 +0700</t>
+          <t>Tue, 04 Aug 2026 12:24:47 +0700</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa pagi, dibuka menguat 20,28 poin atau 0,33 ...</t>
+          <t>Kantor Perwakilan Bank Indonesia (BI) Provinsi Papua menyiapkan uang layak edar senilai Rp20 miliar dalam pelaksanaan ...</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678675/ihsg-selasa-dibuka-menguat-2028-poin-ke-posisi-6254</t>
+          <t>https://www.antaranews.com/berita/5678896/bi-siapkan-rp20-miliar-ekspedisi-rupiah-berdaulat-2026-di-3t-papua</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/Pembukaan-IHSG-usai-libur-Lebaran.jpg250326-Ada-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002062154.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -6868,33 +6868,33 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>252 siswa SMAN 28 Bandung belajar di Kompleks Sport Jabar, gedung sekolah baru rampung Desember 2026</t>
+          <t>Panda Bond dan sinyal kepercayaan investasi global</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:12:31 +0700</t>
+          <t>Tue, 04 Aug 2026 11:26:35 +0700</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Siswa kelas X SMAN 28 Bandung mengikuti kegiatan belajar mengajar di ruang kelas Gedung Laga Satria Sport Jabar Arcamanik, Bandung, Jawa Barat, Selasa (4/8/2026). Sebanyak 252 siswa angkatan pertama SMAN 28 Bandung untuk sementara mengikuti kegiatan belajar mengajar di kompleks Sport Jabar Arcamanik karena gedung sekolah masih dalam tahap pembangunan dan ditargetkan selesai pada Desember 2026. ANTARA FOTO/Novrian Arbi/agr</t>
+          <t>Di tengah ketidakpastian ekonomi global yang semakin kompleks, pemerintah Indonesia perlu memastikan bahwa ...</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678884/252-siswa-sman-28-bandung-belajar-di-kompleks-sport-jabar-gedung-sekolah-baru-rampung-desember-2026</t>
+          <t>https://www.antaranews.com/berita/5678827/panda-bond-dan-sinyal-kepercayaan-investasi-global</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Siswa-SMAN-28-Bandung-belajar-di-gedung-sementara-040826-NA-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/permintaan-pembelian-obligasi-global-capai-46-miliar-dolar-as-2806089.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -6906,33 +6906,33 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Kementerian Keuangan catat realisasi Belanja Pemerintah Pusat (BPP) capai Rp1.298,6 triliun atau tumbuh 29,4 persen</t>
+          <t>Rupiah Selasa melemah dipicu kenaikan harga minyak global</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:05:28 +0700</t>
+          <t>Tue, 04 Aug 2026 11:15:57 +0700</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Siswa berjalan membawa paket Makan Bergizi Gratis (MBG) di SDN Pejaten Barat 01, Pasar Minggu, Jakarta, Selasa (4/8/2026). Kementerian Keuangan mencatat realisasi Belanja Pemerintah Pusat (BPP) mencapai Rp1.298,6 triliun atau tumbuh 29,4 persen secara tahunan, yang antara lain didorong pelaksanaan program Makan Bergizi Gratis (MBG), penyaluran bantuan sosial, pembangunan infrastruktur, pembayaran tunjangan hari raya (THR) dan gaji ke-13, manfaat pensiun, subsidi dan kompensasi bahan bakar minyak (BBM) dan listrik. ANTARA FOTO/Angga Budhiyanto/agr</t>
+          <t>Nilai tukar rupiah pada Selasa pagi bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per dolar AS ...</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678877/kementerian-keuangan-catat-realisasi-belanja-pemerintah-pusat-bpp-capai-rp12986-triliun-atau-tumbuh-294-persen</t>
+          <t>https://www.antaranews.com/berita/5678808/rupiah-selasa-melemah-dipicu-kenaikan-harga-minyak-global</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Realisasi-Belanja-Pemerintah-Pusat-04082026-ab-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/nilai-tukar-rupiah-melemah-44-poin-2821215.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -6944,33 +6944,33 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>BPS proyeksikan produksi beras nasional capai 28,71 Juta ton hingga September 2026, stok dipastikan tetap aman</t>
+          <t>DJPb catat pembelanjaan di 75 KDKMP Sultra capai 1.055 kali transaksi</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:19:05 +0700</t>
+          <t>Tue, 04 Aug 2026 10:00:21 +0700</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pekerja menata karung berisi cadangan beras pemerintah di gudang Perum Bulog Cabang Meulaboh, Aceh Barat, Aceh, Selasa (4/8/2026). Badan Pusat Statistik (BPS) memproyeksi produksi beras nasional untuk konsumsi pangan sepanjang Januari - September 2026 mencapai 28,71 juta ton atau meningkat 0,01 persen dibandingkan periode yang sama tahun sebelumnya. ANTARA FOTO/Syifa Yulinnas/agr</t>
+          <t>Kantor Wilayah (Kanwil) Direktorat Jenderal Perbendaharaan (DJPb) Provinsi Sulawesi Tenggara (Sultra), mencatat ...</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678815/bps-proyeksikan-produksi-beras-nasional-capai-2871-juta-ton-hingga-september-2026-stok-dipastikan-tetap-aman</t>
+          <t>https://www.antaranews.com/berita/5678732/djpb-catat-pembelanjaan-di-75-kdkmp-sultra-capai-1055-kali-transaksi</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Prediksi-produksi-beras-nasional-040826-Syf-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/2798be53-c5ca-4be6-bcf8-a2e9eb6c7488.jpeg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -6982,33 +6982,33 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+          <t>Rupiah pada Selasa pagi melemah jadi Rp18.029 per dolar AS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+          <t>Tue, 04 Aug 2026 09:16:27 +0700</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, Pemulutan Barat, Ogan Ilir (OI), Sumatera Selatan, Senin (3/8/2026). Petugas dibantu warga masih berupaya memadamkan kebakaran lahan di daerah tersebut. ANTARA FOTO/Nova Wahyudi/agr</t>
+          <t>Nilai tukar rupiah terhadap dolar AS pada Selasa pagi, bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per ...</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+          <t>https://www.antaranews.com/berita/5678685/rupiah-pada-selasa-pagi-melemah-jadi-rp18029-per-dolar-as</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -7020,33 +7020,33 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-finansial</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
+          <t>CORE: Penilaian kredit alternatif dapat perluas pembiayaan UMKM</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 07:58:42 +0700</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, kota Ambon, Maluku, Selasa (4/8). Kegiatan digitalisasi bansos ini diwajibkan untuk seluruh Apartur Sipil Negara di lingkup Pemkot Ambon. (Alfian Sanusi/Denno Ramdha Asmara/Winanto)</t>
+          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai pemanfaatan penilaian kredit ...</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
+          <t>https://www.antaranews.com/berita/5678651/core-penilaian-kredit-alternatif-dapat-perluas-pembiayaan-umkm</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/realisasi-penyaluran-kur-umkm-2832719.jpg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -7058,33 +7058,33 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DKPP pastikan cadangan beras Kab. Serang aman hingga setahun ke depan</t>
+          <t>Saat rantai pasok menjadi benteng inflasi</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:56:38 +0700</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Ketahanan Pangan dan Pertanian (DKPP) Kabupaten Serang, Selasa (4/8), memastikan cadangan beras Kabupaten Serang aman hingga satu tahun ke depan. Kepala Bidang Ketahanan Pangan DKPP Kabupaten Serang, Endra Nuryana, mengatakan, hingga per Agustus 2026, Kabupaten Serang tercatat masih memiliki sebanyak 334 ton beras cadangan, yang saat ini masih tersimpan di gudang Bulog Cabang Serang. (Susmiatun Hayati/Denno Ramdha Asmara/Winanto)</t>
+          <t>Di tengah ancaman El Nino dan tantangan logistik negara kepulauan, inflasi Indonesia pada Juli 2026 menunjukkan bahwa ...</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678939/dkpp-pastikan-cadangan-beras-kab-serang-aman-hingga-setahun-ke-depan</t>
+          <t>https://www.antaranews.com/berita/5678943/saat-rantai-pasok-menjadi-benteng-inflasi</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DKPP-PASTIKAN-CADANGAN-BERAS-KAB.SERANG-AMAN-HINGGA-SETAHUN-KE-DEPAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/12/05/1000001928.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -7096,33 +7096,33 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
+          <t>BMKG: Juli 2026 menjadi Juli terkering sejak 1991</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:55:25 +0700</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi Rupiah Berdaulat (ERB) 2026  yang digelar di lima pulau  yang masuk dalam wilayah Terdepan, Terluar dan Terpencil (3T) di wilayah Papua, di Dermaga Satrol Kodaeral X Jayapura, Selasa (4/8). Kepala Perwakilan Bank Indonesia Provinsi Papua, Warsono, mengatakan pelepasan tim ERB mencakup kegiatan edukasi Cinta, Bangga, dan Paham (CBP) Rupiah bahwa kehadiran rupiah hingga ke pulau-pulau terluar merupakan bagian dari upaya menjaga kedaulatan ekonomi nasional. (Laksa Mahendra/Denno Ramdha Asmara/Winanto)</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyatakan Juli 2026 menjadi bulan Juli terkering di Indonesia ...</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
+          <t>https://www.antaranews.com/berita/5678936/bmkg-juli-2026-menjadi-juli-terkering-sejak-1991</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Prediksi-kemarau-di-Jawa-Barat-160726-adb-7.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -7134,33 +7134,33 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
+          <t>Airbus A380-800 Emirates akan mendarat perdana di Bandara Soetta</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:47:25 +0700</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi melalui penerapan sistem verifikasi berbasis Quick Response (QR) berlapis. Wali Kota Palu Harianto Rasyid pada Senin (3/8), mengatakan, bahwa QR tersebut menjadi verifikasi tambahan guna melengkapi sistem QR Subsidi tepat milik Pertamina, sehingga setiap kendaraan yang nantinya memperoleh solar bersubsidi wajib lebih dahulu terdaftar pada Pemerintah Kota Palu. (Farah Khadija/M. Izfaldi/Denno Ramdha Asmara/Winanto)</t>
+          <t>Pesawat jenis Airbus A380-800 milik maskapai Emirates yang melayani penerbangan EK358 rute Dubai (DXB)–Jakarta ...</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
+          <t>https://www.antaranews.com/berita/5678928/airbus-a380-800-emirates-akan-mendarat-perdana-di-bandara-soetta</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/06/02/A380-2_1.jpeg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -7172,33 +7172,33 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+          <t>Pemerintah targetkan pembangunan 35.872 unit KDKMP rampung di Agustus</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:41:37 +0700</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+          <t>Pemerintah menargetkan pembangunan gedung koperasi desa dan kelurahan merah putih (KDKMP) rampung sebanyak 35.872 ...</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+          <t>https://www.antaranews.com/berita/5678915/pemerintah-targetkan-pembangunan-35872-unit-kdkmp-rampung-di-agustus</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002905262.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -7210,33 +7210,33 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, photo</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Kementan usulkan telur ayam masuk skema cadangan pangan pemerintah</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:30:53 +0700</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+          <t>Pekerja memberikan pakan ayam di salah satu peternakan di Cihampelas, Kabupaten Bandung Barat, Jawa Barat, Selasa ...</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/foto/5678903/kementan-usulkan-telur-ayam-masuk-skema-cadangan-pangan-pemerintah</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Kementan-Usulkan-Telur-Ayam-Masuk-Skema-CPP-040826-DAN-07.jpg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -7248,33 +7248,33 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>Honda Super-One 2026 dijual di Australia, segini harganya</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:29:17 +0700</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+          <t>Honda Super-One debut perdana di Gaikindo Indonesia International Auto Show (GIIAS) 2026, Indonesia, harganya masih ...</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://otomotif.antaranews.com/berita/5678901/honda-super-one-2026-dijual-di-australia-segini-harganya</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG_1401.jpg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -7286,33 +7286,33 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Kemenekraf perkuat KPT Ekraf jadi penggerak hilirisasi talenta kreatif</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 11:59:18 +0700</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Kementerian Ekonomi Kreatif/Badan Ekonomi Kreatif (Ekraf) memperkuat peran Konsorsium Perguruan Tinggi (KPT) Ekraf ...</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5678861/kemenekraf-perkuat-kpt-ekraf-jadi-penggerak-hilirisasi-talenta-kreatif</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000453579.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -7324,33 +7324,33 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>IHSG menguat ditopang kinerja keuangan emiten periode kuartal II</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 10:12:17 +0700</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa bergerak menguat ditopang oleh laporan ...</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5678748/ihsg-menguat-ditopang-kinerja-keuangan-emiten-periode-kuartal-ii</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/30/BEI-catatkan-14-perusahaan-baru-pada-2025-260625-fzn-3.jpg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -7362,33 +7362,33 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bursa</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>IHSG Selasa dibuka menguat 20,28 poin ke posisi 6.254</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 09:06:02 +0700</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa pagi, dibuka menguat 20,28 poin atau 0,33 ...</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5678675/ihsg-selasa-dibuka-menguat-2028-poin-ke-posisi-6254</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/Pembukaan-IHSG-usai-libur-Lebaran.jpg250326-Ada-3.jpg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -7400,33 +7400,33 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>252 siswa SMAN 28 Bandung belajar di Kompleks Sport Jabar, gedung sekolah baru rampung Desember 2026</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:12:31 +0700</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+          <t>Siswa kelas X SMAN 28 Bandung mengikuti kegiatan belajar mengajar di ruang kelas Gedung Laga Satria Sport Jabar Arcamanik, Bandung, Jawa Barat, Selasa (4/8/2026). Sebanyak 252 siswa angkatan pertama SMAN 28 Bandung untuk sementara mengikuti kegiatan belajar mengajar di kompleks Sport Jabar Arcamanik karena gedung sekolah masih dalam tahap pembangunan dan ditargetkan selesai pada Desember 2026. ANTARA FOTO/Novrian Arbi/agr</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/foto/5678884/252-siswa-sman-28-bandung-belajar-di-kompleks-sport-jabar-gedung-sekolah-baru-rampung-desember-2026</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Siswa-SMAN-28-Bandung-belajar-di-gedung-sementara-040826-NA-6.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -7438,1493 +7438,2025 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Kementerian Keuangan catat realisasi Belanja Pemerintah Pusat (BPP) capai Rp1.298,6 triliun atau tumbuh 29,4 persen</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
+          <t>Tue, 04 Aug 2026 12:05:28 +0700</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
+          <t>Siswa berjalan membawa paket Makan Bergizi Gratis (MBG) di SDN Pejaten Barat 01, Pasar Minggu, Jakarta, Selasa (4/8/2026). Kementerian Keuangan mencatat realisasi Belanja Pemerintah Pusat (BPP) mencapai Rp1.298,6 triliun atau tumbuh 29,4 persen secara tahunan, yang antara lain didorong pelaksanaan program Makan Bergizi Gratis (MBG), penyaluran bantuan sosial, pembangunan infrastruktur, pembayaran tunjangan hari raya (THR) dan gaji ke-13, manfaat pensiun, subsidi dan kompensasi bahan bakar minyak (BBM) dan listrik. ANTARA FOTO/Angga Budhiyanto/agr</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678877/kementerian-keuangan-catat-realisasi-belanja-pemerintah-pusat-bpp-capai-rp12986-triliun-atau-tumbuh-294-persen</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Realisasi-Belanja-Pemerintah-Pusat-04082026-ab-6.jpg</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>BPS proyeksikan produksi beras nasional capai 28,71 Juta ton hingga September 2026, stok dipastikan tetap aman</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Pekerja menata karung berisi cadangan beras pemerintah di gudang Perum Bulog Cabang Meulaboh, Aceh Barat, Aceh, Selasa (4/8/2026). Badan Pusat Statistik (BPS) memproyeksi produksi beras nasional untuk konsumsi pangan sepanjang Januari - September 2026 mencapai 28,71 juta ton atau meningkat 0,01 persen dibandingkan periode yang sama tahun sebelumnya. ANTARA FOTO/Syifa Yulinnas/agr</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678815/bps-proyeksikan-produksi-beras-nasional-capai-2871-juta-ton-hingga-september-2026-stok-dipastikan-tetap-aman</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Prediksi-produksi-beras-nasional-040826-Syf-3.jpg</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, Pemulutan Barat, Ogan Ilir (OI), Sumatera Selatan, Senin (3/8/2026). Petugas dibantu warga masih berupaya memadamkan kebakaran lahan di daerah tersebut. ANTARA FOTO/Nova Wahyudi/agr</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Dilanda cuaca panas, nakes Lhokseumawe bagikan masker untuk cegah ISPA</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>ANTARA - Dilanda cuaca panas hingga 35 derajat celcius, tim nakes dari Puskesmas Mon Gedong, Kecamatan Banda Sakti, Kota Lhokseumawe, Aceh, membagikan masker bagi pengendara di Simpang Empat Masjid Islamic Center, sebagai salah satu upaya pencegahan penyakit Infeksi Saluran Pernapasan Akut (ISPA), Selasa (4/8). (Try Vanny S/Denno Ramdha Asmara/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679057/dilanda-cuaca-panas-nakes-lhokseumawe-bagikan-masker-untuk-cegah-ispa</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DILANDA-CUACA-PANAS-NAKES-LHOKSEUMAWE-BAGIKAN-MASKER-UNTUK-CEGAH-ISPA.jpg</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, kota Ambon, Maluku, Selasa (4/8). Kegiatan digitalisasi bansos ini diwajibkan untuk seluruh Apartur Sipil Negara di lingkup Pemkot Ambon. (Alfian Sanusi/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>DKPP pastikan cadangan beras Kab. Serang aman hingga setahun ke depan</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Ketahanan Pangan dan Pertanian (DKPP) Kabupaten Serang, Selasa (4/8), memastikan cadangan beras Kabupaten Serang aman hingga satu tahun ke depan. Kepala Bidang Ketahanan Pangan DKPP Kabupaten Serang, Endra Nuryana, mengatakan, hingga per Agustus 2026, Kabupaten Serang tercatat masih memiliki sebanyak 334 ton beras cadangan, yang saat ini masih tersimpan di gudang Bulog Cabang Serang. (Susmiatun Hayati/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678939/dkpp-pastikan-cadangan-beras-kab-serang-aman-hingga-setahun-ke-depan</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DKPP-PASTIKAN-CADANGAN-BERAS-KAB.SERANG-AMAN-HINGGA-SETAHUN-KE-DEPAN.jpg</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi Rupiah Berdaulat (ERB) 2026  yang digelar di lima pulau  yang masuk dalam wilayah Terdepan, Terluar dan Terpencil (3T) di wilayah Papua, di Dermaga Satrol Kodaeral X Jayapura, Selasa (4/8). Kepala Perwakilan Bank Indonesia Provinsi Papua, Warsono, mengatakan pelepasan tim ERB mencakup kegiatan edukasi Cinta, Bangga, dan Paham (CBP) Rupiah bahwa kehadiran rupiah hingga ke pulau-pulau terluar merupakan bagian dari upaya menjaga kedaulatan ekonomi nasional. (Laksa Mahendra/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi melalui penerapan sistem verifikasi berbasis Quick Response (QR) berlapis. Wali Kota Palu Harianto Rasyid pada Senin (3/8), mengatakan, bahwa QR tersebut menjadi verifikasi tambahan guna melengkapi sistem QR Subsidi tepat milik Pertamina, sehingga setiap kendaraan yang nantinya memperoleh solar bersubsidi wajib lebih dahulu terdaftar pada Pemerintah Kota Palu. (Farah Khadija/M. Izfaldi/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
 (Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G212" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr">
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
         <is>
           <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
+      <c r="G213" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
         <is>
           <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
 (Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B215" t="inlineStr">
         <is>
           <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
         <is>
           <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr">
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="G216" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr">
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
 (Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F217" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G217" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G218" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr">
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
         <is>
           <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
 (Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G219" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr">
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G220" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G221" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
         <is>
           <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F222" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G222" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
         <is>
           <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G223" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
         <is>
           <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F224" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G224" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F225" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G225" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr">
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
         <is>
           <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G226" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr">
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
         <is>
           <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (AFP/Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F227" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="G227" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G228" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="G229" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
         <is>
           <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="G230" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B231" t="inlineStr">
         <is>
           <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="F231" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G231" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B232" t="inlineStr">
         <is>
           <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
 (Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G232" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B233" t="inlineStr">
         <is>
           <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
         <is>
           <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="G233" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B234" t="inlineStr">
         <is>
           <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr">
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G234" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr">
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G235" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B236" t="inlineStr">
         <is>
           <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr">
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F236" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G236" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr">
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="F237" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G237" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr">
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
         <is>
           <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F238" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G238" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B239" t="inlineStr">
         <is>
           <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
         <is>
           <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F239" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G239" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F240" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G240" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr">
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
         <is>
           <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F241" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G241" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr">
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
         <is>
           <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
 (XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F243" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G243" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr">
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
         <is>
           <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F244" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="G244" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr">
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
         <is>
           <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
+      <c r="F245" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G245" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="F246" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G246" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
         <is>
           <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F247" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G247" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr">
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
         <is>
           <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F248" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G248" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Paus Leo XIV prihatin atas situasi krisis migran di Ceuta</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:10:01 +0700</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>ANTARA - Paus Leo XIV  menyampaikan keprihatinan atas situasi krisis migran di Enklave, Spanyol, Ceuta.  Saat memimpin doa angelus di Vatikan, Minggu (2/8), Paus berdoa agar terdapat solusi yang membawa perdamaian dan keadilan atas kondisi tersebut. (ANADOLU/Ludmila Yusufin Diah Nastiti/Agha Yuninda Maulana/Winanto)</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677384/paus-leo-xiv-prihatin-atas-situasi-krisis-migran-di-ceuta</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PAUS-LEO-XIV-PRIHATIN-ATAS-SITUASI-KRISIS.jpg</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr">
+      <c r="H248" t="inlineStr">
         <is>
           <t>antara</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H234"/>
+  <autoFilter ref="A1:H248"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_antara_2026-08-04.xlsx
+++ b/data/berita_antara_2026-08-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$358</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H248"/>
+  <dimension ref="A1:H358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -4740,33 +4740,33 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ekonomi-finansial, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ekonom: Pasokan pangan membaik jaga inflasi tetap terkendali</t>
+          <t>BPJS Kesehatan: Syarat JKN untuk daftar SIM dorong keaktifan peserta</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:23:45 +0700</t>
+          <t>Tue, 04 Aug 2026 14:23:34 +0700</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ekonom PT Bank Danamon Indonesia Tbk menilai inflasi pada Juli 2026 tetap terkendali seiring membaiknya pasokan pangan ...</t>
+          <t>Direktur Kepesertaan BPJS Kesehatan RI Akmal Budi Yulianto menyatakan persyaratan Jaminan Kesehatan Nasional (JKN) ...</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679091/ekonom-pasokan-pangan-membaik-jaga-inflasi-tetap-terkendali</t>
+          <t>https://www.antaranews.com/berita/5679087/bpjs-kesehatan-syarat-jkn-untuk-daftar-sim-dorong-keaktifan-peserta</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/inflasi-juli-2026-jawa-barat-2833080.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/20260804_111650.jpg</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -4778,33 +4778,33 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BPJS Kesehatan: Syarat JKN untuk daftar SIM dorong keaktifan peserta</t>
+          <t>Mendag yakin perdagangan bulanan surplus lagi usai harga minyak turun</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:23:34 +0700</t>
+          <t>Tue, 04 Aug 2026 14:23:25 +0700</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Direktur Kepesertaan BPJS Kesehatan RI Akmal Budi Yulianto menyatakan persyaratan Jaminan Kesehatan Nasional (JKN) ...</t>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso meyakini neraca perdagangan Indonesia kembali mencatatkan surplus secara ...</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679087/bpjs-kesehatan-syarat-jkn-untuk-daftar-sim-dorong-keaktifan-peserta</t>
+          <t>https://www.antaranews.com/berita/5679084/mendag-yakin-perdagangan-bulanan-surplus-lagi-usai-harga-minyak-turun</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/20260804_111650.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Mendag_edit_241553389416784.jpg</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -4821,28 +4821,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mendag yakin perdagangan bulanan surplus lagi usai harga minyak turun</t>
+          <t>Kemenko IPK: Kebijakan zero ODOL diharapkan bisa diterapkan awal 2027</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:23:25 +0700</t>
+          <t>Tue, 04 Aug 2026 14:19:33 +0700</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Menteri Perdagangan (Mendag) Budi Santoso meyakini neraca perdagangan Indonesia kembali mencatatkan surplus secara ...</t>
+          <t>Kementerian Koordinator Bidang Infrastruktur dan Pembangunan Kewilayahan (Kemenko IPK) mengungkapkan kebijakan zero ...</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679084/mendag-yakin-perdagangan-bulanan-surplus-lagi-usai-harga-minyak-turun</t>
+          <t>https://www.antaranews.com/berita/5679083/kemenko-ipk-kebijakan-zero-odol-diharapkan-bisa-diterapkan-awal-2027</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Mendag_edit_241553389416784.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1033.jpg</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -4854,33 +4854,33 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kemenko IPK: Kebijakan zero ODOL diharapkan bisa diterapkan awal 2027</t>
+          <t>Dilanda cuaca panas, nakes Lhokseumawe bagikan masker untuk cegah ISPA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:19:33 +0700</t>
+          <t>Tue, 04 Aug 2026 14:18:17 +0700</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kementerian Koordinator Bidang Infrastruktur dan Pembangunan Kewilayahan (Kemenko IPK) mengungkapkan kebijakan zero ...</t>
+          <t>ANTARA - Dilanda cuaca panas hingga 35 derajat celcius, tim nakes dari Puskesmas Mon Gedong, Kecamatan Banda Sakti, ...</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679083/kemenko-ipk-kebijakan-zero-odol-diharapkan-bisa-diterapkan-awal-2027</t>
+          <t>https://www.antaranews.com/video/5679057/dilanda-cuaca-panas-nakes-lhokseumawe-bagikan-masker-untuk-cegah-ispa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1033.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DILANDA-CUACA-PANAS-NAKES-LHOKSEUMAWE-BAGIKAN-MASKER-UNTUK-CEGAH-ISPA.jpg</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -4897,28 +4897,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dilanda cuaca panas, nakes Lhokseumawe bagikan masker untuk cegah ISPA</t>
+          <t>Anggota DPR minta polisi bongkar sindikat intimidasi korban curanmor</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:18:17 +0700</t>
+          <t>Tue, 04 Aug 2026 14:18:08 +0700</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ANTARA - Dilanda cuaca panas hingga 35 derajat celcius, tim nakes dari Puskesmas Mon Gedong, Kecamatan Banda Sakti, ...</t>
+          <t>Anggota Komisi III DPR RI Abdullah meminta aparat kepolisian untuk mengusut sekelompok orang diduga sindikat yang ...</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5679057/dilanda-cuaca-panas-nakes-lhokseumawe-bagikan-masker-untuk-cegah-ispa</t>
+          <t>https://www.antaranews.com/berita/5679079/anggota-dpr-minta-polisi-bongkarsindikat-intimidasi-korban-curanmor</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/DILANDA-CUACA-PANAS-NAKES-LHOKSEUMAWE-BAGIKAN-MASKER-UNTUK-CEGAH-ISPA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/20/IMG-20251208-WA0044.jpg</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -4930,33 +4930,33 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Anggota DPR minta polisi bongkar sindikat intimidasi korban curanmor</t>
+          <t>MIND ID setor pajak dan dividen senilai Rp32,82 triliun</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:18:08 +0700</t>
+          <t>Tue, 04 Aug 2026 14:16:56 +0700</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Anggota Komisi III DPR RI Abdullah meminta aparat kepolisian untuk mengusut sekelompok orang diduga sindikat yang ...</t>
+          <t>Holding Industri Pertambangan Indonesia MIND ID membayarkan kewajiban pajak kepada pemerintah serta dividen senilai ...</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679079/anggota-dpr-minta-polisi-bongkarsindikat-intimidasi-korban-curanmor</t>
+          <t>https://www.antaranews.com/berita/5679077/mind-id-setor-pajak-dan-dividen-senilai-rp3282-triliun</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/01/20/IMG-20251208-WA0044.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/27/IMG_20260627_084103.jpg</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -4968,33 +4968,33 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MIND ID setor pajak dan dividen senilai Rp32,82 triliun</t>
+          <t>Qualcomm rilis varian baru Snapdragon 8 Elite Gen 5 V untuk "gaming"</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:16:56 +0700</t>
+          <t>Tue, 04 Aug 2026 14:16:32 +0700</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Holding Industri Pertambangan Indonesia MIND ID membayarkan kewajiban pajak kepada pemerintah serta dividen senilai ...</t>
+          <t>Qualcomm memperkenalkan varian baru dari chipset unggulan Snapdragon 8 Elite Gen 5 V-series yang berfokus ...</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679077/mind-id-setor-pajak-dan-dividen-senilai-rp3282-triliun</t>
+          <t>https://www.antaranews.com/berita/5679075/qualcomm-rilis-varian-baru-snapdragon-8-elite-gen-5-v-untuk-gaming</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/27/IMG_20260627_084103.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Redmi-K100-Pro-chip-1068x1424.jpg</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5006,33 +5006,33 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Qualcomm rilis varian baru Snapdragon 8 Elite Gen 5 V untuk "gaming"</t>
+          <t>BMKG: Penyesuaian pola tanam penting cegah gagal panen saat El Nino</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:16:32 +0700</t>
+          <t>Tue, 04 Aug 2026 14:06:51 +0700</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Qualcomm memperkenalkan varian baru dari chipset unggulan Snapdragon 8 Elite Gen 5 V-series yang berfokus ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menekankan pentingnya penyesuaian pola tanam di wilayah terdampak ...</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679075/qualcomm-rilis-varian-baru-snapdragon-8-elite-gen-5-v-untuk-gaming</t>
+          <t>https://www.antaranews.com/berita/5679069/bmkg-penyesuaian-pola-tanam-penting-cegah-gagal-panen-saat-el-nino</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Redmi-K100-Pro-chip-1068x1424.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/upaya-petani-beradaptasi-menghadapi-musim-kemarau-2830336.jpg</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5044,33 +5044,33 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ratusan siswa sekolah gratis di Semarang terima paket perlengkapan sekolah, bantu ringankan beban orang tua</t>
+          <t>Kemenkes ajak sekolah perkuat perlindungan kesehatan anak lewat BIAS</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:15:18 +0700</t>
+          <t>Tue, 04 Aug 2026 13:59:06 +0700</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Siswa menunjukkan tas berisi paket perlengkapan sekolah di Sekolah Gratis Kuncup Melati, Kauman, Semarang, Jawa Tengah, ...</t>
+          <t>Kementerian Kesehatan (Kemenkes) mengajak seluruh kementerian dan lembaga terkait serta satuan pendidikan untuk ...</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5679073/ratusan-siswa-sekolah-gratis-di-semarang-terima-paket-perlengkapan-sekolah-bantu-ringankan-beban-orang-tua</t>
+          <t>https://www.antaranews.com/berita/5679065/kemenkes-ajak-sekolah-perkuat-perlindungan-kesehatan-anak-lewat-bias</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/pembagian-seragam-alat-tulis-sd-kuncup-melati-040826-aaa-4.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/07/bulan-imunisasi-anak-sekolah-15082025-bal-10.jpg</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5082,33 +5082,33 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>BMKG: Penyesuaian pola tanam penting cegah gagal panen saat El Nino</t>
+          <t>KAI Perkuat Keamanan Data Pelanggan, Terapkan ISO 27001 dan Bentuk Tim Respons Siber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:06:51 +0700</t>
+          <t>Tue, 04 Aug 2026 13:57:28 +0700</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menekankan pentingnya penyesuaian pola tanam di wilayah terdampak ...</t>
+          <t>PT Kereta Api Indonesia (Persero) terus memperkuat keamanan dan kerahasiaan data pelanggan seiring semakin luasnya ...</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679069/bmkg-penyesuaian-pola-tanam-penting-cegah-gagal-panen-saat-el-nino</t>
+          <t>https://www.antaranews.com/berita/5679063/kai-perkuat-keamanan-data-pelanggan-terapkan-iso-27001-dan-bentuk-tim-respons-siber</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/upaya-petani-beradaptasi-menghadapi-musim-kemarau-2830336.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/face-recognition.jpg</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5120,33 +5120,33 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>photo, terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Target besar 2029, TPST Bantargebang pasang geomembran sebagai kunci transformasi pengelolaan sampah</t>
+          <t>Kementerian ESDM: Teknologi hemat energi dukung target penurunan emisi</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:00:03 +0700</t>
+          <t>Tue, 04 Aug 2026 13:56:13 +0700</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Petugas memasang patok pada geomembran sebagai media pelindung untuk menutup tumpukan sampah di Tempat Pengolahan ...</t>
+          <t>Direktur Konservasi Energi Direktorat Jenderal Energi Baru, Terbarukan, dan Konservasi Energi (EBTKE) Kementerian ...</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5679067/target-besar-2029-tpst-bantargebang-pasang-geomembran-sebagai-kunci-transformasi-pengelolaan-sampah</t>
+          <t>https://www.antaranews.com/berita/5679060/kementerian-esdm-teknologi-hemat-energi-dukung-target-penurunan-emisi</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Dinas-DLH-DKI-pasang-Geomembrane-di-TPST-Bantargebang-040826-ryl-5.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Proyek-SETI-EBTKE.jpeg</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5158,33 +5158,33 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kemenkes ajak sekolah perkuat perlindungan kesehatan anak lewat BIAS</t>
+          <t>Kemenhub: Trans Sumatra Railway hadirkan transportasi terintegrasi</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:59:06 +0700</t>
+          <t>Tue, 04 Aug 2026 13:55:35 +0700</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kementerian Kesehatan (Kemenkes) mengajak seluruh kementerian dan lembaga terkait serta satuan pendidikan untuk ...</t>
+          <t>Kementerian Perhubungan (Kemenhub) mengatakan pengembangan Trans Sumatra Railway atau jalur kereta Trans Sumatra dapat ...</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679065/kemenkes-ajak-sekolah-perkuat-perlindungan-kesehatan-anak-lewat-bias</t>
+          <t>https://www.antaranews.com/berita/5679053/kemenhub-trans-sumatra-railway-hadirkan-transportasi-terintegrasi</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/07/bulan-imunisasi-anak-sekolah-15082025-bal-10.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/0E2BC257-2126-4A9E-BCED-562A035F164A.jpeg</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5201,28 +5201,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>KAI Perkuat Keamanan Data Pelanggan, Terapkan ISO 27001 dan Bentuk Tim Respons Siber</t>
+          <t>Kemendagri minta pemdes libatkan kelompok rentan dalam pembangunan</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:57:28 +0700</t>
+          <t>Tue, 04 Aug 2026 13:55:16 +0700</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) terus memperkuat keamanan dan kerahasiaan data pelanggan seiring semakin luasnya ...</t>
+          <t>Kementerian Dalam Negeri (Kemendagri) meminta pemerintah desa melibatkan kelompok rentan dalam perencanaan pembangunan ...</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679063/kai-perkuat-keamanan-data-pelanggan-terapkan-iso-27001-dan-bentuk-tim-respons-siber</t>
+          <t>https://www.antaranews.com/berita/5679049/kemendagri-minta-pemdes-libatkan-kelompok-rentan-dalam-pembangunan</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/face-recognition.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG-20260804-WA0011.jpg</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5234,33 +5234,33 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kementerian ESDM: Teknologi hemat energi dukung target penurunan emisi</t>
+          <t>Angkutan Perkebunan KAI Naik 18 Persen menjadi 374.098 Ton, Perkuat Rantai Pasok Sawit Nasional</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:56:13 +0700</t>
+          <t>Tue, 04 Aug 2026 13:52:09 +0700</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Direktur Konservasi Energi Direktorat Jenderal Energi Baru, Terbarukan, dan Konservasi Energi (EBTKE) Kementerian ...</t>
+          <t>PT Kereta Api Indonesia (Persero) melayani 374.098 ton angkutan perkebunan sepanjang 1 Januari–31 Juli 2026. ...</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679060/kementerian-esdm-teknologi-hemat-energi-dukung-target-penurunan-emisi</t>
+          <t>https://www.antaranews.com/berita/5679045/angkutan-perkebunan-kai-naik-18-persen-menjadi-374098-ton-perkuat-rantai-pasok-sawit-nasional</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Proyek-SETI-EBTKE.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.18.37.jpeg</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5277,28 +5277,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Kemenhub: Trans Sumatra Railway hadirkan transportasi terintegrasi</t>
+          <t>KSP: RUU Sistranas jadi perekat sistem transportasi massal nasional</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:55:35 +0700</t>
+          <t>Tue, 04 Aug 2026 13:48:52 +0700</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kementerian Perhubungan (Kemenhub) mengatakan pengembangan Trans Sumatra Railway atau jalur kereta Trans Sumatra dapat ...</t>
+          <t>Kantor Staf Presiden (KSP) mengungkapkan Rancangan Undang-Undang Sistem Transportasi Nasional (RUU Sistranas) menjadi ...</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679053/kemenhub-trans-sumatra-railway-hadirkan-transportasi-terintegrasi</t>
+          <t>https://www.antaranews.com/berita/5679041/ksp-ruu-sistranas-jadi-perekat-sistem-transportasi-massal-nasional</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/0E2BC257-2126-4A9E-BCED-562A035F164A.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1032.jpg</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5315,28 +5315,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Kemendagri minta pemdes libatkan kelompok rentan dalam pembangunan</t>
+          <t>Kemenhut kolaborasi perkuat tata kelola perhutanan sosial di ASEAN</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:55:16 +0700</t>
+          <t>Tue, 04 Aug 2026 13:47:42 +0700</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kementerian Dalam Negeri (Kemendagri) meminta pemerintah desa melibatkan kelompok rentan dalam perencanaan pembangunan ...</t>
+          <t>Kementerian Kehutanan (Kemenhut) RI mendukung penguatan tata kelola perhutanan sosial di negara-negara ASEAN untuk ...</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679049/kemendagri-minta-pemdes-libatkan-kelompok-rentan-dalam-pembangunan</t>
+          <t>https://www.antaranews.com/berita/5679040/kemenhut-kolaborasi-perkuat-tata-kelola-perhutanan-sosial-di-asean</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG-20260804-WA0011.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_1306.jpg</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5353,28 +5353,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Angkutan Perkebunan KAI Naik 18 Persen menjadi 374.098 Ton, Perkuat Rantai Pasok Sawit Nasional</t>
+          <t>BBPMP Jateng siapkan sekolah transisi bagi siswa SNT Banyumas</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:52:09 +0700</t>
+          <t>Tue, 04 Aug 2026 13:45:59 +0700</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PT Kereta Api Indonesia (Persero) melayani 374.098 ton angkutan perkebunan sepanjang 1 Januari–31 Juli 2026. ...</t>
+          <t>Balai Besar Penjaminan Mutu Pendidikan (BBPMP) Provinsi Jawa Tengah menyiapkan sekolah transisi bagi siswa Sekolah ...</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679045/angkutan-perkebunan-kai-naik-18-persen-menjadi-374098-ton-perkuat-rantai-pasok-sawit-nasional</t>
+          <t>https://www.antaranews.com/berita/5679036/bbpmp-jateng-siapkan-sekolah-transisi-bagi-siswa-snt-banyumas</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.18.37.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001091712.jpg</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5386,33 +5386,33 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>KSP: RUU Sistranas jadi perekat sistem transportasi massal nasional</t>
+          <t>Pedagang Taman Puring tagih janji Pemprov revitalisasi pascakebakaran</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:48:52 +0700</t>
+          <t>Tue, 04 Aug 2026 13:42:39 +0700</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Kantor Staf Presiden (KSP) mengungkapkan Rancangan Undang-Undang Sistem Transportasi Nasional (RUU Sistranas) menjadi ...</t>
+          <t>Koordinator pedagang di Taman Puring, Jakarta Selatan, menagih janji Pemerintah Provinsi DKI untuk segera ...</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679041/ksp-ruu-sistranas-jadi-perekat-sistem-transportasi-massal-nasional</t>
+          <t>https://www.antaranews.com/berita/5679032/pedagang-taman-puring-tagih-janji-pemprov-revitalisasi-pascakebakaran</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1032.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001011610.jpg</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5429,28 +5429,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Kemenhut kolaborasi perkuat tata kelola perhutanan sosial di ASEAN</t>
+          <t>Tim Preventive Strike Polda Metro harus utamakan pencegahan gangguan kamtibmas</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:47:42 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:28 +0700</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kementerian Kehutanan (Kemenhut) RI mendukung penguatan tata kelola perhutanan sosial di negara-negara ASEAN untuk ...</t>
+          <t>Ketua Dewan Nasional SETARA Institute, Hendardi mengingatkan tim Preventive Strike yang dibentuk Polda Metro Jaya harus ...</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679040/kemenhut-kolaborasi-perkuat-tata-kelola-perhutanan-sosial-di-asean</t>
+          <t>https://www.antaranews.com/berita/5679029/tim-preventive-strike-polda-metro-harus-utamakan-pencegahan-gangguan-kamtibmas</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_1306.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/05/12/Petisi-Untuk-Perdamaian-Indonesia-011116-agr-02.jpg</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5462,33 +5462,33 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, photo, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tambak modern udang vaname di kawasan industri Semarang bidik produksi 1,3 ton per siklus</t>
+          <t>Samsung larang aplikasi TV yang mengekspos koneksi internet pengguna</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:47:21 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:22 +0700</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pekerja menunjukkan udang vaname hasil budidaya Loka Perbenihan dan Budi Daya Ikan (PBI) Tugu Dinas Kelautan dan ...</t>
+          <t>Samsung menyatakan bahwa perusahaan melarang aplikasi-aplikasi yang berpotensi mengekspos koneksi internet ...</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5679037/tambak-modern-udang-vaname-di-kawasan-industri-semarang-bidik-produksi-13-ton-per-siklus</t>
+          <t>https://www.antaranews.com/berita/5679025/samsung-larang-aplikasi-tv-yang-mengekspos-koneksi-internet-pengguna</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/panen-udang-vaname-budidaya-pemprov-jateng-040826-aaa-2.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/495339513_23879065098420444_7610565358307725dcCC188_n.jpg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -5500,33 +5500,33 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BBPMP Jateng siapkan sekolah transisi bagi siswa SNT Banyumas</t>
+          <t>Bappenas rumuskan arah respons dalam 4 kluster utama hadapi El-Nino</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:45:59 +0700</t>
+          <t>Tue, 04 Aug 2026 13:40:21 +0700</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Balai Besar Penjaminan Mutu Pendidikan (BBPMP) Provinsi Jawa Tengah menyiapkan sekolah transisi bagi siswa Sekolah ...</t>
+          <t>Pemerintah merumuskan arah respons empat kluster pembangunan utama dalam bentuk policy brief untuk menghadapi dan ...</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679036/bbpmp-jateng-siapkan-sekolah-transisi-bagi-siswa-snt-banyumas</t>
+          <t>https://www.antaranews.com/berita/5679024/bappenas-rumuskan-arah-respons-dalam-4-kluster-utama-hadapi-el-nino</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001091712.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-12.43.09.jpeg</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -5538,33 +5538,33 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini, top-news</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Penjualan mobil naik, Menkeu yakin daya beli domestik tetap terjaga</t>
+          <t>Mendag sebut perjanjian dagang pacu minat investasi</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:45:23 +0700</t>
+          <t>Tue, 04 Aug 2026 13:38:49 +0700</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan pertumbuhan penjualan mobil menjadi salah satu indikator yang ...</t>
+          <t>Menteri Perdagangan (Mendag) Budi Santoso menyampaikan semakin banyaknya perjanjian perdagangan yang dimiliki ...</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679033/penjualan-mobil-naik-menkeu-yakin-daya-beli-domestik-tetap-terjaga</t>
+          <t>https://www.antaranews.com/berita/5679017/mendag-sebut-perjanjian-dagang-pacu-minat-investasi</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.13.50.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Mendag.jpg</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5581,28 +5581,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Pedagang Taman Puring tagih janji Pemprov revitalisasi pascakebakaran</t>
+          <t>BMKG: Waspada gelombang setinggi 6 meter di perairan selatan Bali</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:42:39 +0700</t>
+          <t>Tue, 04 Aug 2026 13:36:42 +0700</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Koordinator pedagang di Taman Puring, Jakarta Selatan, menagih janji Pemerintah Provinsi DKI untuk segera ...</t>
+          <t>Balai Besar Meteorologi Klimatologi dan Geofisika (BBMKG) Wilayah III Denpasar memprakirakan ketinggian gelombang laut ...</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679032/pedagang-taman-puring-tagih-janji-pemprov-revitalisasi-pascakebakaran</t>
+          <t>https://www.antaranews.com/berita/5679015/bmkg-waspada-gelombang-setinggi-6-meter-di-perairan-selatan-bali</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1001011610.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_142653.jpg</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5619,28 +5619,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Tim Preventive Strike Polda Metro harus utamakan pencegahan gangguan kamtibmas</t>
+          <t>Pemkot Palu paparkan implementasi kota inklusif bagi disabilitas</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:40:28 +0700</t>
+          <t>Tue, 04 Aug 2026 13:35:28 +0700</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ketua Dewan Nasional SETARA Institute, Hendardi mengingatkan tim Preventive Strike yang dibentuk Polda Metro Jaya harus ...</t>
+          <t>Pemerintah Kota (Pemkot) Palu, Sulawesi Tengah (Sulteng) memaparkan sejumlah kebijakan yang sudah dilakukan pemerintah ...</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679029/tim-preventive-strike-polda-metro-harus-utamakan-pencegahan-gangguan-kamtibmas</t>
+          <t>https://www.antaranews.com/berita/5679012/pemkot-palu-paparkan-implementasi-kota-inklusif-bagi-disabilitas</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/05/12/Petisi-Untuk-Perdamaian-Indonesia-011116-agr-02.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-20.58.47.jpeg</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -5657,28 +5657,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Samsung larang aplikasi TV yang mengekspos koneksi internet pengguna</t>
+          <t>Polda Metro Jaya panen 82 kg pakcoy untuk bahan baku MBG</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:40:22 +0700</t>
+          <t>Tue, 04 Aug 2026 13:34:09 +0700</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Samsung menyatakan bahwa perusahaan melarang aplikasi-aplikasi yang berpotensi mengekspos koneksi internet ...</t>
+          <t>Polda Metro Jaya kembali memanen 82 kilogram sayur pakcoy pada Selasa untuk didistribusikan langsung sebagai ...</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679025/samsung-larang-aplikasi-tv-yang-mengekspos-koneksi-internet-pengguna</t>
+          <t>https://www.antaranews.com/berita/5679011/polda-metro-jaya-panen-82-kg-pakcoy-untuk-bahan-baku-mbg</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/495339513_23879065098420444_7610565358307725dcCC188_n.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/e5362e67-38db-4936-a5fa-c050f3c6eec9.jpeg</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -5690,33 +5690,33 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Bappenas rumuskan arah respons dalam 4 kluster utama hadapi El-Nino</t>
+          <t>73 santri dan pengasuh ponpes lolos beasiswa Pemprov Jateng</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:40:21 +0700</t>
+          <t>Tue, 04 Aug 2026 13:33:28 +0700</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Pemerintah merumuskan arah respons empat kluster pembangunan utama dalam bentuk policy brief untuk menghadapi dan ...</t>
+          <t>Sebanyak 73 santri dan pengasuh pondok pesantren berhasil lolos dalam proses seleksi Beasiswa Santri dan Pengasuh ...</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679024/bappenas-rumuskan-arah-respons-dalam-4-kluster-utama-hadapi-el-nino</t>
+          <t>https://www.antaranews.com/berita/5679007/73-santri-dan-pengasuh-ponpes-lolos-beasiswa-pemprov-jateng</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-12.43.09.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002077974.jpg</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -5728,33 +5728,33 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Mendag sebut perjanjian dagang pacu minat investasi</t>
+          <t>Cegah banjir-longsor susulan, BNPB perbaiki tebing sungai di Sipange</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:38:49 +0700</t>
+          <t>Tue, 04 Aug 2026 13:30:48 +0700</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Menteri Perdagangan (Mendag) Budi Santoso menyampaikan semakin banyaknya perjanjian perdagangan yang dimiliki ...</t>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) memperbaiki sekaligus memperkuat struktur tebing Sungai Sigala-gala di ...</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679017/mendag-sebut-perjanjian-dagang-pacu-minat-investasi</t>
+          <t>https://www.antaranews.com/berita/5679003/cegah-banjir-longsor-susulan-bnpb-perbaiki-tebing-sungai-di-sipange</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Mendag.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/IMG_20251207_094949.jpg</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -5771,28 +5771,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BMKG: Waspada gelombang setinggi 6 meter di perairan selatan Bali</t>
+          <t>Program Taruna Bhakti dimulai di Sekolah Rakyat Gumas</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:36:42 +0700</t>
+          <t>Tue, 04 Aug 2026 13:29:40 +0700</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Balai Besar Meteorologi Klimatologi dan Geofisika (BBMKG) Wilayah III Denpasar memprakirakan ketinggian gelombang laut ...</t>
+          <t>Program Taruna Bhakti 2026 resmi berjalan di Sekolah Rakyat Terintegrasi 54 Kabupaten Gunung Mas (Gumas), Kalimantan ...</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679015/bmkg-waspada-gelombang-setinggi-6-meter-di-perairan-selatan-bali</t>
+          <t>https://www.antaranews.com/berita/5679000/program-taruna-bhakti-dimulai-di-sekolah-rakyat-gumas</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_142653.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Gumas-Sekolah-Rakyat-di-gunung-mas-Kabupaten-Gunung-Mas-Kalimantan-Tengah-gumas-kalteng.jpg</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -5809,28 +5809,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Pemkot Palu paparkan implementasi kota inklusif bagi disabilitas</t>
+          <t>BNPT sebut ormas agama mitra pemerintah perkuat ketahanan radikalisme</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:35:28 +0700</t>
+          <t>Tue, 04 Aug 2026 13:27:11 +0700</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Pemerintah Kota (Pemkot) Palu, Sulawesi Tengah (Sulteng) memaparkan sejumlah kebijakan yang sudah dilakukan pemerintah ...</t>
+          <t>Badan Nasional Penanggulangan Terorisme (BNPT) menyatakan organisasi kemasyarakatan keagamaan memiliki posisi strategis ...</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679012/pemkot-palu-paparkan-implementasi-kota-inklusif-bagi-disabilitas</t>
+          <t>https://www.antaranews.com/berita/5678997/bnpt-sebut-ormas-agama-mitra-pemerintah-perkuat-ketahanan-radikalisme</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-20.58.47.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469936.jpg</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -5847,28 +5847,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Polda Metro Jaya panen 82 kg pakcoy untuk bahan baku MBG</t>
+          <t>Jakpus percepat penyelesaian aset fasos hasil kewajiban pengembang</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:34:09 +0700</t>
+          <t>Tue, 04 Aug 2026 13:26:16 +0700</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Polda Metro Jaya kembali memanen 82 kilogram sayur pakcoy pada Selasa untuk didistribusikan langsung sebagai ...</t>
+          <t>Pemerintah Kota Jakarta Pusat mempercepat penyelesaian administrasi aset berupa fasilitas sosial dan fasilitas ...</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679011/polda-metro-jaya-panen-82-kg-pakcoy-untuk-bahan-baku-mbg</t>
+          <t>https://www.antaranews.com/berita/5678995/jakpus-percepat-penyelesaian-aset-fasos-hasil-kewajiban-pengembang</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/e5362e67-38db-4936-a5fa-c050f3c6eec9.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Tamasya-Trotoar-Kita-271218-aaa-1.jpg</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -5885,28 +5885,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>73 santri dan pengasuh ponpes lolos beasiswa Pemprov Jateng</t>
+          <t>Dinkes Tanjungpinang: Program CKG anak sekolah sasar 49.343 siswa</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:33:28 +0700</t>
+          <t>Tue, 04 Aug 2026 13:20:20 +0700</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sebanyak 73 santri dan pengasuh pondok pesantren berhasil lolos dalam proses seleksi Beasiswa Santri dan Pengasuh ...</t>
+          <t>Dinas Kesehatan, Pengendalian Penduduk, dan Keluarga Berencana (Dinkes PPKB) Kota Tanjungpinang, Kepulauan Riau (Kepri) ...</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679007/73-santri-dan-pengasuh-ponpes-lolos-beasiswa-pemprov-jateng</t>
+          <t>https://www.antaranews.com/berita/5678991/dinkes-tanjungpinang-program-ckg-anak-sekolah-sasar-49343-siswa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002077974.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_892E3D72-14C7-4D65-8D8A-54508D212D10.png</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -5918,33 +5918,33 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Cegah banjir-longsor susulan, BNPB perbaiki tebing sungai di Sipange</t>
+          <t>Pertamina Hulu Indonesia catat produksi migas di atas target</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:30:48 +0700</t>
+          <t>Tue, 04 Aug 2026 13:19:27 +0700</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Badan Nasional Penanggulangan Bencana (BNPB) memperbaiki sekaligus memperkuat struktur tebing Sungai Sigala-gala di ...</t>
+          <t>PT Pertamina Hulu Indonesia (PHI), bagian Subholding Upstream PT Pertamina (Persero), yang mengelola aset hulu migas di ...</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679003/cegah-banjir-longsor-susulan-bnpb-perbaiki-tebing-sungai-di-sipange</t>
+          <t>https://www.antaranews.com/berita/5678988/pertamina-hulu-indonesia-catat-produksi-migas-di-atas-target</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/IMG_20251207_094949.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260515_154910.jpg</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -5961,28 +5961,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Program Taruna Bhakti dimulai di Sekolah Rakyat Gumas</t>
+          <t>Trump desak perusahaan minyak AS segera turunkan harga ke konsumen</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:29:40 +0700</t>
+          <t>Tue, 04 Aug 2026 13:18:22 +0700</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Program Taruna Bhakti 2026 resmi berjalan di Sekolah Rakyat Terintegrasi 54 Kabupaten Gunung Mas (Gumas), Kalimantan ...</t>
+          <t>Presiden Amerika Serikat Donald Trump mendesak perusahaan-perusahaan minyak di negaranya untuk segera menurunkan harga ...</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679000/program-taruna-bhakti-dimulai-di-sekolah-rakyat-gumas</t>
+          <t>https://www.antaranews.com/berita/5678984/trump-desak-perusahaan-minyak-as-segera-turunkan-harga-ke-konsumen</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Gumas-Sekolah-Rakyat-di-gunung-mas-Kabupaten-Gunung-Mas-Kalimantan-Tengah-gumas-kalteng.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_ab5d296d556bf61eed768b8ca4900658.jpg</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -5999,28 +5999,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BNPT sebut ormas agama mitra pemerintah perkuat ketahanan radikalisme</t>
+          <t>Gubernur Kepri pastikan program strategis nasional berjalan baik</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:27:11 +0700</t>
+          <t>Tue, 04 Aug 2026 13:14:01 +0700</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Badan Nasional Penanggulangan Terorisme (BNPT) menyatakan organisasi kemasyarakatan keagamaan memiliki posisi strategis ...</t>
+          <t>Gubernur Kepulauan Riau Ansar Ahmad memastikan pelaksanaan berbagai program nasional di daerahnya berjalan baik hingga ...</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678997/bnpt-sebut-ormas-agama-mitra-pemerintah-perkuat-ketahanan-radikalisme</t>
+          <t>https://www.antaranews.com/berita/5678983/gubernur-kepri-pastikan-program-strategis-nasional-berjalan-baik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469936.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_1BD7B733-6D15-464A-B72C-E9015EF50D0A.jpeg</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6037,28 +6037,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Jakpus percepat penyelesaian aset fasos hasil kewajiban pengembang</t>
+          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:26:16 +0700</t>
+          <t>Tue, 04 Aug 2026 13:11:01 +0700</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Pemerintah Kota Jakarta Pusat mempercepat penyelesaian administrasi aset berupa fasilitas sosial dan fasilitas ...</t>
+          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, ...</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678995/jakpus-percepat-penyelesaian-aset-fasos-hasil-kewajiban-pengembang</t>
+          <t>https://www.antaranews.com/video/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/Tamasya-Trotoar-Kita-271218-aaa-1.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6075,28 +6075,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dinkes Tanjungpinang: Program CKG anak sekolah sasar 49.343 siswa</t>
+          <t>BNPT dan LAN sepakat tangkal pola baru terorisme di ruang digital</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:20:20 +0700</t>
+          <t>Tue, 04 Aug 2026 13:09:01 +0700</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Dinas Kesehatan, Pengendalian Penduduk, dan Keluarga Berencana (Dinkes PPKB) Kota Tanjungpinang, Kepulauan Riau (Kepri) ...</t>
+          <t>Badan Nasional Penanggulangan Terorisme (BNPT) bersama Lembaga Administrasi Negara (LAN) sepakat untuk menangkal pola ...</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678991/dinkes-tanjungpinang-program-ckg-anak-sekolah-sasar-49343-siswa</t>
+          <t>https://www.antaranews.com/berita/5678979/bnpt-dan-lan-sepakat-tangkal-pola-baru-terorisme-di-ruang-digital</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_892E3D72-14C7-4D65-8D8A-54508D212D10.png</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469877.jpg</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6108,33 +6108,33 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, terkini</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Pertamina Hulu Indonesia catat produksi migas di atas target</t>
+          <t>Bocoran kamera Galaxy S27 Pro dan Ultra terungkap, ini perbedaannya</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:19:27 +0700</t>
+          <t>Tue, 04 Aug 2026 13:07:58 +0700</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>PT Pertamina Hulu Indonesia (PHI), bagian Subholding Upstream PT Pertamina (Persero), yang mengelola aset hulu migas di ...</t>
+          <t>Bocoran spesifikasi kamera Galaxy S27 Pro dan Galaxy S27 Ultra mencuat setelah dokumen yang dibagikan Samsung kepada ...</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678988/pertamina-hulu-indonesia-catat-produksi-migas-di-atas-target</t>
+          <t>https://www.antaranews.com/berita/5678976/bocoran-kamera-galaxy-s27-pro-dan-ultra-terungkap-ini-perbedaannya</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260515_154910.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/26/WhatsApp-Image-2026-02-26-at-16.18.01.jpeg</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6151,28 +6151,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Trump desak perusahaan minyak AS segera turunkan harga ke konsumen</t>
+          <t>Taruna AAL bekali siswa Sekolah Rakyat 32 Natuna pendidikan karakter</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:18:22 +0700</t>
+          <t>Tue, 04 Aug 2026 13:07:51 +0700</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Presiden Amerika Serikat Donald Trump mendesak perusahaan-perusahaan minyak di negaranya untuk segera menurunkan harga ...</t>
+          <t>Taruna Akademi Angkatan Laut (AAL) membekali siswa Sekolah Rakyat (SR) Terintegrasi 32 Natuna, Provinsi Kepulauan Riau, ...</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678984/trump-desak-perusahaan-minyak-as-segera-turunkan-harga-ke-konsumen</t>
+          <t>https://www.antaranews.com/berita/5678973/taruna-aal-bekali-siswa-sekolah-rakyat-32-natuna-pendidikan-karakter</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_ab5d296d556bf61eed768b8ca4900658.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000833131.jpg</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6189,28 +6189,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Gubernur Kepri pastikan program strategis nasional berjalan baik</t>
+          <t>Transjakarta beri alasan turunkan seorang penumpang di Kampung Melayu</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:14:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:07:38 +0700</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Gubernur Kepulauan Riau Ansar Ahmad memastikan pelaksanaan berbagai program nasional di daerahnya berjalan baik hingga ...</t>
+          <t>PT Transportasi Jakarta menyampaikan tindakan petugas menurunkan seorang penumpang dari bus di Halte Kampung Melayu, ...</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678983/gubernur-kepri-pastikan-program-strategis-nasional-berjalan-baik</t>
+          <t>https://www.antaranews.com/berita/5678969/transjakarta-beri-alasan-turunkan-seorang-penumpang-di-kampung-melayu</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Facebook_creation_1BD7B733-6D15-464A-B72C-E9015EF50D0A.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/jumlah-penumpang-angkutan-umum-di-jakarta-meningkat-2816319.jpg</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6227,28 +6227,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
+          <t>Sopir truk korban KMP Mutiara Sentosa asal Tulungagung dimakamkan</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:11:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:05:38 +0700</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, ...</t>
+          <t>Jenazah Sari Sukoco (39), salah satu korban meninggal dunia dalam kebakaran KMP Mutiara Sentosa 2 di perairan Madura, ...</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
+          <t>https://www.antaranews.com/berita/5678967/sopir-truk-korban-kmp-mutiara-sentosa-asal-tulungagung-dimakamkan</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/454482.jpg</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6265,28 +6265,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>BNPT dan LAN sepakat tangkal pola baru terorisme di ruang digital</t>
+          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:09:01 +0700</t>
+          <t>Tue, 04 Aug 2026 13:03:10 +0700</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Badan Nasional Penanggulangan Terorisme (BNPT) bersama Lembaga Administrasi Negara (LAN) sepakat untuk menangkal pola ...</t>
+          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi ...</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678979/bnpt-dan-lan-sepakat-tangkal-pola-baru-terorisme-di-ruang-digital</t>
+          <t>https://www.antaranews.com/video/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000469877.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6298,33 +6298,33 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Bocoran kamera Galaxy S27 Pro dan Ultra terungkap, ini perbedaannya</t>
+          <t>Saat rantai pasok menjadi benteng inflasi</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:07:58 +0700</t>
+          <t>Tue, 04 Aug 2026 12:56:38 +0700</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Bocoran spesifikasi kamera Galaxy S27 Pro dan Galaxy S27 Ultra mencuat setelah dokumen yang dibagikan Samsung kepada ...</t>
+          <t>Di tengah ancaman El Nino dan tantangan logistik negara kepulauan, inflasi Indonesia pada Juli 2026 menunjukkan bahwa ...</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678976/bocoran-kamera-galaxy-s27-pro-dan-ultra-terungkap-ini-perbedaannya</t>
+          <t>https://www.antaranews.com/berita/5678943/saat-rantai-pasok-menjadi-benteng-inflasi</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/02/26/WhatsApp-Image-2026-02-26-at-16.18.01.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/12/05/1000001928.jpg</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6336,33 +6336,33 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Taruna AAL bekali siswa Sekolah Rakyat 32 Natuna pendidikan karakter</t>
+          <t>BMKG: Juli 2026 menjadi Juli terkering sejak 1991</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:07:51 +0700</t>
+          <t>Tue, 04 Aug 2026 12:55:25 +0700</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Taruna Akademi Angkatan Laut (AAL) membekali siswa Sekolah Rakyat (SR) Terintegrasi 32 Natuna, Provinsi Kepulauan Riau, ...</t>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyatakan Juli 2026 menjadi bulan Juli terkering di Indonesia ...</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678973/taruna-aal-bekali-siswa-sekolah-rakyat-32-natuna-pendidikan-karakter</t>
+          <t>https://www.antaranews.com/berita/5678936/bmkg-juli-2026-menjadi-juli-terkering-sejak-1991</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000833131.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Prediksi-kemarau-di-Jawa-Barat-160726-adb-7.jpg</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6374,33 +6374,33 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Transjakarta beri alasan turunkan seorang penumpang di Kampung Melayu</t>
+          <t>Airbus A380-800 Emirates akan mendarat perdana di Bandara Soetta</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:07:38 +0700</t>
+          <t>Tue, 04 Aug 2026 12:47:25 +0700</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PT Transportasi Jakarta menyampaikan tindakan petugas menurunkan seorang penumpang dari bus di Halte Kampung Melayu, ...</t>
+          <t>Pesawat jenis Airbus A380-800 milik maskapai Emirates yang melayani penerbangan EK358 rute Dubai (DXB)–Jakarta ...</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678969/transjakarta-beri-alasan-turunkan-seorang-penumpang-di-kampung-melayu</t>
+          <t>https://www.antaranews.com/berita/5678928/airbus-a380-800-emirates-akan-mendarat-perdana-di-bandara-soetta</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/03/jumlah-penumpang-angkutan-umum-di-jakarta-meningkat-2816319.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/06/02/A380-2_1.jpeg</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -6412,33 +6412,33 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Sopir truk korban KMP Mutiara Sentosa asal Tulungagung dimakamkan</t>
+          <t>Pemerintah targetkan pembangunan 35.872 unit KDKMP rampung di Agustus</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:05:38 +0700</t>
+          <t>Tue, 04 Aug 2026 12:41:37 +0700</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Jenazah Sari Sukoco (39), salah satu korban meninggal dunia dalam kebakaran KMP Mutiara Sentosa 2 di perairan Madura, ...</t>
+          <t>Pemerintah menargetkan pembangunan gedung koperasi desa dan kelurahan merah putih (KDKMP) rampung sebanyak 35.872 ...</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678967/sopir-truk-korban-kmp-mutiara-sentosa-asal-tulungagung-dimakamkan</t>
+          <t>https://www.antaranews.com/berita/5678915/pemerintah-targetkan-pembangunan-35872-unit-kdkmp-rampung-di-agustus</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/454482.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002905262.jpg</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6450,33 +6450,33 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>terkini</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
+          <t>Honda Super-One 2026 dijual di Australia, segini harganya</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:03:10 +0700</t>
+          <t>Tue, 04 Aug 2026 12:29:17 +0700</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi ...</t>
+          <t>Honda Super-One debut perdana di Gaikindo Indonesia International Auto Show (GIIAS) 2026, Indonesia, harganya masih ...</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/video/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
+          <t>https://otomotif.antaranews.com/berita/5678901/honda-super-one-2026-dijual-di-australia-segini-harganya</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG_1401.jpg</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -6488,33 +6488,33 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>ekonomi-bisnis</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ada 2 bibit siklon tropis, BMKG: Waspada ombak setinggi 4 meter di RI</t>
+          <t>Kemenekraf perkuat KPT Ekraf jadi penggerak hilirisasi talenta kreatif</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:09:44 +0700</t>
+          <t>Tue, 04 Aug 2026 11:59:18 +0700</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi kemunculan dua bibit siklon tropis sekaligus di wilayah ...</t>
+          <t>Kementerian Ekonomi Kreatif/Badan Ekonomi Kreatif (Ekraf) memperkuat peran Konsorsium Perguruan Tinggi (KPT) Ekraf ...</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678879/ada-2-bibit-siklon-tropis-bmkg-waspada-ombak-setinggi-4-meter-di-ri</t>
+          <t>https://www.antaranews.com/berita/5678861/kemenekraf-perkuat-kpt-ekraf-jadi-penggerak-hilirisasi-talenta-kreatif</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20250609_135328.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000453579.jpg</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6526,33 +6526,33 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Korban tewas gempa Venezuela terus bertambah jadi 6.100 orang</t>
+          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:00:56 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Jumlah korban tewas akibat gempa kembar dahsyat yang mengguncang Venezuela pada 24 Juni 2026, terus bertambah ...</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678865/korban-tewas-gempa-venezuela-terus-bertambah-jadi-6100-orang</t>
+          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_d4a34a165f13a0667255577d3cfac46f.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -6564,33 +6564,33 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BPKH salurkan Rp2,06 triliun nilai manfaat ke 5,7 juta calon haji</t>
+          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:47:58 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Badan Pengelola Keuangan Haji (BPKH) menyalurkan Nilai Manfaat Tahap I Tahun 2026 lebih dari Rp2,06 triliun kepada ...</t>
+          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678849/bpkh-salurkan-rp206-triliun-nilai-manfaat-ke-57-juta-calon-haji</t>
+          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176506_1.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMKAB-TEMANGGUNG-GANDENG-KEMITRAAN-KACANG-PANJANG-DENGAN-PERUSAHAN.jpg</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -6602,33 +6602,33 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Aldila jadi petenis Indonesia yang pertama juarai DC Open</t>
+          <t>Dinkes Lhokseumawe uji kualitas air Sekolah Rakyat</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Petenis Indonesia Aldila Sutjiadi mencatatkan sejarah setelah menjuarai nomor ganda putri turnamen Mubadala DC Open ...</t>
+          <t>ANTARA - Dinas Kesehatan (Dinkes) Kota Lhokseumawe melakukan uji kualitas air baku dan air minum di Sekolah Rakyat, Desa Jeulikat, Kecamatan Blang Mangat, Senin (3/8). Pemeriksaan dilakukan untuk memastikan air yang digunakan ratusan siswa memenuhi standar kesehatan sebelum dikonsumsi. (Try Vanny S/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678836/aldila-jadi-petenis-indonesia-yang-pertama-juarai-dc-open</t>
+          <t>https://www.antaranews.com/berita/5677740/dinkes-lhokseumawe-uji-kualitas-air-sekolah-rakyat</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4155-copy.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_DINKES-LHOKSEUMAWE-UJI-KUALITAS-AIR-SEKOLAH-RAKYAT.jpg</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -6640,33 +6640,33 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Indonesia raih 15 medali dari Kejuaraan MMAAsia</t>
+          <t>HPAI Jember tanam pohon untuk mitigasi longsor dan banjir</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:16:36 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Tim mixed martial arts (MMA) amatir Indonesia meraih 15 medali dan menempati peringkat keempat pada GAMMA Asian ...</t>
+          <t>ANTARA - Himpunan Pegiat Adiwiyata Indonesia (HPAI) Kabupaten Jember menanam belasan bibit pohon beringin dan 20 bibit pohon karet kebo di kawasan Air Terjun Tancak, lereng selatan Pegunungan Hyang Argopuro, Kecamatan Panti, Senin (3/8). Penanaman dilakukan untuk mendukung konservasi kawasan, menjaga sumber air, serta mengurangi risiko longsor dan banjir bandang. (Hamka Agung Balya/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678689/indonesia-raih-15-medali-dari-kejuaraan-mmaasia</t>
+          <t>https://www.antaranews.com/berita/5677707/hpai-jember-tanam-pohon-untuk-mitigasi-longsor-dan-banjir</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Delvi-Novia_Medal.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/HPAI-JEMBER-TANAM-POHON-UNTUK-MITIGASI-LONGSOR-DAN-BANJIR.jpg</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -6678,33 +6678,33 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Kontingen Indonesia di Asian Games 2026</t>
+          <t>75 gerai Koperasi Merah Putih di Sulawesi Tenggara telah beroperasi</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
+          <t>ANTARA - Sebanyak 75 gerai Koperasi Desa Kelurahan Merah Putih (KDKMP) di Provinsi Sulawesi Tenggara telah mulai beroperasi pada Juli 2026. Kantor Wilayah Direktorat Jenderal Perbendaharaan Provinsi Sulawesi Tenggara (Kanwil DJPb Sultra) menyebut sepanjang 2026, KDKMP di Sultra mencatatkan 1.055 transaksi dengan nilai Rp25,22 juta dengan transaksi didominasi komoditas kebutuhan pokok dan energi bersubsidi, antara lain beras medium SPHP, MinyaKita, gula, dan elpiji 3 kilogram. (Saharudin/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
+          <t>https://www.antaranews.com/berita/5677680/75-gerai-koperasi-merah-putih-di-sulawesi-tenggara-telah-beroperasi</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_75-GERAI-KOPERASI-MERAH-PUTIH-DI-SULAWESI-TENGGARA-TELAH-BEROPERASI.jpg</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -6716,33 +6716,33 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
+          <t>Pimpinan MPR RI bertemu Presiden sampaikan undangan Sidang Tahunan</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
+          <t>ANTARA - Jajaran pimpinan MPR RI menyambangi Istana Kepresidenan Jakarta pada Senin (3/8). Ketua MPR RI Ahmad Muzani menyebut kunjungan itu salah satunya untuk menyampaikan undangan Sidang Tahunan MPR RI pada 14 Agustus 2026. (Aria Cindyara/Irfansyah Naufal Nasution/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
+          <t>https://www.antaranews.com/berita/5677637/pimpinan-mpr-ri-bertemu-presiden-sampaikan-undangan-sidang-tahunan</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PIMPINAN-MPR-RI-BERTEMU-PRESIDEN-SAMPAIKAN-UNDANGAN-SIDANG-TAHUNAN.jpg</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -6754,33 +6754,33 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>top-news</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+          <t>Menkomdigi kukuhkan komisioner KI Pusat, perkuat keterbukaan informasi</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengambil sumpah jabatan dan mengukuhkan tujuh anggota Komisi Informasi Pusat (KIP) Periode 2026–2030 di Kantor Kementerian Komdigi Jakarta, Senin (3/8).  Komisioner KI Pusat Periode 2026–2030 akan melanjutkan tugas dan fungsi komisioner sebelumnya, yakni penyelesaian sengketa informasi publik secara adil, menetapkan kebijakan teknis di bidang keterbukaan informasi, dan memperkuat implementasi UU Nomor 14 Tahun 2008 tentang Keterbukaan Informasi Publik. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+          <t>https://www.antaranews.com/berita/5677604/menkomdigi-kukuhkan-komisioner-ki-pusat-perkuat-keterbukaan-informasi</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-KUKUHKAN-KOMISIONER-KI-PUSAT-PERKUAT-KETERBUKAAN-INFORMASI.jpg</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -6792,33 +6792,34 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LPEM FEB UI perkirakan ekonomi RI tumbuh 4,8 persen di kuartal II 2026</t>
+          <t>Partai Buruh Brasil calonkan Lula da Silva untuk masa jabatan keempat</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:57:01 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Lembaga Penyelidikan Ekonomi dan Masyarakat Fakultas Ekonomi dan Bisnis Universitas Indonesia (LPEM FEB UI) ...</t>
+          <t>ANTARA - Partai Buruh di Brasil pada Minggu (2/8) waktu setempat, resmi mencalonkan petahana Luiz Inacio Lula da Silva sebagai kandidat dalam pemilihan presiden mendatang untuk masa jabatan keempat. Pada konvensi nasional partai di Sao Paulo, para delegasi secara resmi menyetujui pasangan Lula dengan Wakil Presiden petahana Geraldo Alckmin dari Partai Sosialis Brasil.
+(XINHUA /Winanto/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678945/lpem-feb-ui-perkirakan-ekonomi-ri-tumbuh-48-persen-di-kuartal-ii-2026</t>
+          <t>https://www.antaranews.com/berita/5677541/partai-buruh-brasil-calonkan-lula-da-silva-untuk-masa-jabatan-keempat</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2022/05/17/Screenshot_20220517-151559_YouTube.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-154005.jpg</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -6830,33 +6831,33 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BI siapkan Rp20 miliar ekspedisi rupiah berdaulat 2026 di 3T Papua</t>
+          <t>Kesbangpol Pontianak antisipasi konflik sosial akibat karhutla</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:24:47 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Kantor Perwakilan Bank Indonesia (BI) Provinsi Papua menyiapkan uang layak edar senilai Rp20 miliar dalam pelaksanaan ...</t>
+          <t>ANTARA - Badan Kesatuan Bangsa dan Politik (Kesbangpol) Kota Pontianak mengidentifikasi potensi gangguan keamanan dan konflik sosial akibat kebakaran hutan dan lahan (karhutla), Senin (3/8). Langkah yang dilakukan meliputi koordinasi lintas sektor, pemantauan situasi, hingga mediasi untuk menjaga kondusivitas selama penanganan karhutla. (Indra Budi Santoso/Rizky Bagus Dhermawan/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678896/bi-siapkan-rp20-miliar-ekspedisi-rupiah-berdaulat-2026-di-3t-papua</t>
+          <t>https://www.antaranews.com/berita/5677519/kesbangpol-pontianak-antisipasi-konflik-sosial-akibat-karhutla</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002062154.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/KESBANGPOL-PONTIANAK-ANTISIPASI-KONFLIK-SOSIAL-AKIBAT-KARHUTLA.jpg</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -6868,33 +6869,33 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Panda Bond dan sinyal kepercayaan investasi global</t>
+          <t>PSEL Serang Raya jadi solusi pengelolaan sampah tiga daerah</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:26:35 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Di tengah ketidakpastian ekonomi global yang semakin kompleks, pemerintah Indonesia perlu memastikan bahwa ...</t>
+          <t>ANTARA - Fasilitas Pengolahan Sampah menjadi Energi Listrik (PSEL) Serang Raya akan dibangun di TPSA Cilowong, Kota Serang, untuk melayani pengelolaan sampah Kabupaten Serang, Kota Serang, dan Kota Cilegon. Fasilitas berkapasitas 1.161 ton sampah per hari itu diharapkan mampu mengurangi beban tempat pemrosesan akhir sekaligus mengubah sampah menjadi energi listrik. (Susmiatun Hayati/Agha Yuninda Maulana/Arsy Fitriady)</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678827/panda-bond-dan-sinyal-kepercayaan-investasi-global</t>
+          <t>https://www.antaranews.com/berita/5677492/psel-serang-raya-jadi-solusi-pengelolaan-sampah-tiga-daerah</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/permintaan-pembelian-obligasi-global-capai-46-miliar-dolar-as-2806089.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_PSEL-SERANG-RAYA-JADI-SOLUSI-PENGELOLAAN-SAMPAH.jpg</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -6906,33 +6907,33 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Rupiah Selasa melemah dipicu kenaikan harga minyak global</t>
+          <t>Pemkot Ambon salurkan air bersih gratis jika kekeringan terjadi</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:15:57 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah pada Selasa pagi bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per dolar AS ...</t>
+          <t>ANTARA - Pemerintah Kota Ambon, Maluku, menyiapkan langkah antisipasi untuk menjamin ketersediaan air bersih bagi masyarakat dalam menghadapi potensi musim kemarau panjang akibat fenomena El Nino. Wali kota Ambon Bodewin Wattimena, Senin (3/8), mengatakan, pemerintah melakukan pemetaan wilayah yang rawan lalu mendistribusikan air bersih ke wilayah terdampak kekeringan. (Alfian Sanusi/Rizky Bagus Dhermawan/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678808/rupiah-selasa-melemah-dipicu-kenaikan-harga-minyak-global</t>
+          <t>https://www.antaranews.com/berita/5677489/pemkot-ambon-salurkan-air-bersih-gratis-jika-kekeringan-terjadi</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/nilai-tukar-rupiah-melemah-44-poin-2821215.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-03-151844.jpg</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -6944,33 +6945,33 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DJPb catat pembelanjaan di 75 KDKMP Sultra capai 1.055 kali transaksi</t>
+          <t>Razia balap liar, Polres Temanggung sita 106 motor</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:00:21 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Kantor Wilayah (Kanwil) Direktorat Jenderal Perbendaharaan (DJPb) Provinsi Sulawesi Tenggara (Sultra), mencatat ...</t>
+          <t>ANTARA - Kepolisian Resor (Polres) Temanggung, Jawa Tengah menyita 106 sepeda motor dalam razia balap liar yang digelar Minggu malam (2/8). Kegiatan razia tersebut digelar sebagai bagian  upaya kepolisian dalam menekan aksi balap liar  di Temanggung.(Firman Eko Handy/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678732/djpb-catat-pembelanjaan-di-75-kdkmp-sultra-capai-1055-kali-transaksi</t>
+          <t>https://www.antaranews.com/berita/5677488/razia-balap-liar-polres-temanggung-sita-106-motor</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/2798be53-c5ca-4be6-bcf8-a2e9eb6c7488.jpeg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_RAZIA-BALAP-LIAR-POLRES-TEMANGGUNG-SITA-106-MOTOR.jpg</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -6982,33 +6983,33 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Rupiah pada Selasa pagi melemah jadi Rp18.029 per dolar AS</t>
+          <t>Ditjenpas Kaltim gelar CKG bagi 12 ribu warga binaan</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:16:27 +0700</t>
+          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Nilai tukar rupiah terhadap dolar AS pada Selasa pagi, bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per ...</t>
+          <t>ANTARA - Program Cek Kesehatan Gratis (CKG) menyasar warga binaan di Lembaga Pemasyarakatan (Lapas) dan Rumah Tahanan (Rutan) di Kalimantan Timur. CKG untuk 12 ribu warga binaan bertujuan mengantisipasi penyebaran risiko penyakit menular di lapas. (Hanifan Ma'ruf/Agha Yuninda Maulana/Rijalul Vikry)</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678685/rupiah-pada-selasa-pagi-melemah-jadi-rp18029-per-dolar-as</t>
+          <t>https://www.antaranews.com/berita/5677480/ditjenpas-kaltim-gelar-ckg-bagi-12-ribu-warga-binaan</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AYM_DITJENPAS-KALTIM-GELAR-CKG.jpg</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -7020,33 +7021,33 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ekonomi-finansial</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CORE: Penilaian kredit alternatif dapat perluas pembiayaan UMKM</t>
+          <t>Banjarbaru perkuat pencegahan karhutla lewat status siaga darurat</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 07:58:42 +0700</t>
+          <t>Tue, 04 Aug 2026 17:31:24 +0700</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai pemanfaatan penilaian kredit ...</t>
+          <t>Pemerintah Kota Banjarbaru, Kalimantan Selatan, memperkuat langkah pencegahan kebakaran hutan dan lahan (karhutla) ...</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678651/core-penilaian-kredit-alternatif-dapat-perluas-pembiayaan-umkm</t>
+          <t>https://www.antaranews.com/berita/5679512/banjarbaru-perkuat-pencegahan-karhutla-lewat-status-siaga-darurat</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/realisasi-penyaluran-kur-umkm-2832719.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_181801.jpg</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -7058,33 +7059,33 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Saat rantai pasok menjadi benteng inflasi</t>
+          <t>Jaksa Agung berhentikan sementara status jaksa Febrie Adriansyah</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:56:38 +0700</t>
+          <t>Tue, 04 Aug 2026 17:28:52 +0700</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Di tengah ancaman El Nino dan tantangan logistik negara kepulauan, inflasi Indonesia pada Juli 2026 menunjukkan bahwa ...</t>
+          <t>Jaksa Agung RI ST Burhanuddin memberhentikan sementara status jaksa dari mantan Jaksa Agung Muda Bidang Tindak Pidana ...</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678943/saat-rantai-pasok-menjadi-benteng-inflasi</t>
+          <t>https://www.antaranews.com/berita/5679508/jaksa-agung-berhentikan-sementara-status-jaksa-febrie-adriansyah</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2024/12/05/1000001928.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000087161.jpg</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -7096,33 +7097,33 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>BMKG: Juli 2026 menjadi Juli terkering sejak 1991</t>
+          <t>Ekonom: Stimulus KBLBB perlu dibarengi produktivitas industri</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:55:25 +0700</t>
+          <t>Tue, 04 Aug 2026 17:27:43 +0700</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) menyatakan Juli 2026 menjadi bulan Juli terkering di Indonesia ...</t>
+          <t>Ekonom Universitas Jember (Unej) Adhitya Wardhono menilai kebijakan paket stimulus baru untuk memperkuat ekosistem ...</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678936/bmkg-juli-2026-menjadi-juli-terkering-sejak-1991</t>
+          <t>https://www.antaranews.com/berita/5679507/ekonom-stimulus-kblbb-perlu-dibarengi-produktivitas-industri</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Prediksi-kemarau-di-Jawa-Barat-160726-adb-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/28/1298232.jpg</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -7134,33 +7135,33 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Airbus A380-800 Emirates akan mendarat perdana di Bandara Soetta</t>
+          <t>LPSK akan hitung nilai restitusi korban TPPO di Libya</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:47:25 +0700</t>
+          <t>Tue, 04 Aug 2026 17:27:03 +0700</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Pesawat jenis Airbus A380-800 milik maskapai Emirates yang melayani penerbangan EK358 rute Dubai (DXB)–Jakarta ...</t>
+          <t>Lembaga Perlindungan Saksi dan Korban (LPSK) akan melakukan penghitungan besaran nilai restitusi yang akan didapatkan ...</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678928/airbus-a380-800-emirates-akan-mendarat-perdana-di-bandara-soetta</t>
+          <t>https://www.antaranews.com/berita/5679503/lpsk-akan-hitung-nilai-restitusi-korban-tppo-di-libya</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2023/06/02/A380-2_1.jpeg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-15.06.23_1.jpeg</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -7172,33 +7173,33 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Pemerintah targetkan pembangunan 35.872 unit KDKMP rampung di Agustus</t>
+          <t>Menko Airlangga tegaskan ekonomi RI kuat hadapi gejolak global</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:41:37 +0700</t>
+          <t>Tue, 04 Aug 2026 17:26:37 +0700</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Pemerintah menargetkan pembangunan gedung koperasi desa dan kelurahan merah putih (KDKMP) rampung sebanyak 35.872 ...</t>
+          <t>ANTARA - Pemerintah memastikan kondisi ekonomi Indonesia masih berada pada jalur yang kuat, meski dihadapkan pada ...</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678915/pemerintah-targetkan-pembangunan-35872-unit-kdkmp-rampung-di-agustus</t>
+          <t>https://www.antaranews.com/video/5679481/menko-airlangga-tegaskan-ekonomi-ri-kuat-hadapi-gejolak-global</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002905262.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_MENKO-AIRLANGGA-TEGASKAN-EKONOMI-RI-KUAT-HADAPI-GEJOLAK-GLOBAL.jpg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -7210,33 +7211,33 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis, photo</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Kementan usulkan telur ayam masuk skema cadangan pangan pemerintah</t>
+          <t>BPS: Harga beras medium dan premium masih naik</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:30:53 +0700</t>
+          <t>Tue, 04 Aug 2026 17:24:40 +0700</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Pekerja memberikan pakan ayam di salah satu peternakan di Cihampelas, Kabupaten Bandung Barat, Jawa Barat, Selasa ...</t>
+          <t>Badan Pusat Statistik (BPS) mencatat harga beras medium maupun premium masih mengalami kenaikan hingga pekan kelima ...</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678903/kementan-usulkan-telur-ayam-masuk-skema-cadangan-pangan-pemerintah</t>
+          <t>https://www.antaranews.com/berita/5679501/bps-harga-beras-medium-dan-premium-masih-naik</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Kementan-Usulkan-Telur-Ayam-Masuk-Skema-CPP-040826-DAN-07.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/18/IMG20251105193658_BURST001_COVER.jpg</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -7248,33 +7249,33 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Honda Super-One 2026 dijual di Australia, segini harganya</t>
+          <t>Kemenkes: CKG jawab isu kesehatan modern tingkatkan harapan hidup</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:29:17 +0700</t>
+          <t>Tue, 04 Aug 2026 17:24:24 +0700</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Honda Super-One debut perdana di Gaikindo Indonesia International Auto Show (GIIAS) 2026, Indonesia, harganya masih ...</t>
+          <t>Kementerian Kesehatan menyatakan Cek Kesehatan Gratis (CKG) menjadi salah satu jawaban tantangan kesehatan yang ...</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://otomotif.antaranews.com/berita/5678901/honda-super-one-2026-dijual-di-australia-segini-harganya</t>
+          <t>https://www.antaranews.com/berita/5679499/kemenkes-ckg-jawab-isu-kesehatan-modern-tingkatkan-harapan-hidup</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/IMG_1401.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-17.11.15.jpeg</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -7286,33 +7287,33 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ekonomi-bisnis</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Kemenekraf perkuat KPT Ekraf jadi penggerak hilirisasi talenta kreatif</t>
+          <t>Kemenkum Babel harmonisasi lima Ranperkada Bangka Tengah</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:59:18 +0700</t>
+          <t>Tue, 04 Aug 2026 17:21:18 +0700</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Kementerian Ekonomi Kreatif/Badan Ekonomi Kreatif (Ekraf) memperkuat peran Konsorsium Perguruan Tinggi (KPT) Ekraf ...</t>
+          <t>Kantor Wilayah Kementerian Hukum Kepulauan Bangka Belitung mengharmonisasikan dan memantapkan konsepsi lima Rancangan ...</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678861/kemenekraf-perkuat-kpt-ekraf-jadi-penggerak-hilirisasi-talenta-kreatif</t>
+          <t>https://www.antaranews.com/berita/5679496/kemenkum-babel-harmonisasi-lima-ranperkada-bangka-tengah</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000453579.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/kemenkum-har.jpg</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -7324,33 +7325,34 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>IHSG menguat ditopang kinerja keuangan emiten periode kuartal II</t>
+          <t>Indonesia target gondol satu medali emas Asian Games 2026</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:12:17 +0700</t>
+          <t>Tue, 04 Aug 2026 17:16:31 +0700</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa bergerak menguat ditopang oleh laporan ...</t>
+          <t>Tim bulu tangkis Indonesia ditargetkan menggondol satu medali emas Asian Games Aichi-Nagoya 2026.
+“Sesuai ...</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678748/ihsg-menguat-ditopang-kinerja-keuangan-emiten-periode-kuartal-ii</t>
+          <t>https://www.antaranews.com/berita/5679495/indonesia-target-gondol-satu-medali-emas-asian-games-2026</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2025/06/30/BEI-catatkan-14-perusahaan-baru-pada-2025-260625-fzn-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG-20260804-WA0035.jpg</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -7362,33 +7364,33 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ekonomi-bursa</t>
+          <t>ekonomi-finansial, terkini</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IHSG Selasa dibuka menguat 20,28 poin ke posisi 6.254</t>
+          <t>Rupiah melemah dipicu defisit neraca perdagangan Indonesia</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:06:02 +0700</t>
+          <t>Tue, 04 Aug 2026 17:15:39 +0700</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa pagi, dibuka menguat 20,28 poin atau 0,33 ...</t>
+          <t>Nilai tukar rupiah terhadap dolar AS pada penutupan perdagangan Selasa, bergerak melemah 30 poin atau 0,17 persen ...</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678675/ihsg-selasa-dibuka-menguat-2028-poin-ke-posisi-6254</t>
+          <t>https://www.antaranews.com/berita/5679493/rupiah-melemah-dipicu-defisit-neraca-perdagangan-indonesia</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/Pembukaan-IHSG-usai-libur-Lebaran.jpg250326-Ada-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/23/1000680361.jpg</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -7400,33 +7402,33 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>252 siswa SMAN 28 Bandung belajar di Kompleks Sport Jabar, gedung sekolah baru rampung Desember 2026</t>
+          <t>Pemprov DKI hadirkan "LapakMain Corner" di RPTRA Tunas Muda Jaksel</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:12:31 +0700</t>
+          <t>Tue, 04 Aug 2026 17:15:26 +0700</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Siswa kelas X SMAN 28 Bandung mengikuti kegiatan belajar mengajar di ruang kelas Gedung Laga Satria Sport Jabar Arcamanik, Bandung, Jawa Barat, Selasa (4/8/2026). Sebanyak 252 siswa angkatan pertama SMAN 28 Bandung untuk sementara mengikuti kegiatan belajar mengajar di kompleks Sport Jabar Arcamanik karena gedung sekolah masih dalam tahap pembangunan dan ditargetkan selesai pada Desember 2026. ANTARA FOTO/Novrian Arbi/agr</t>
+          <t>Pemerintah Provinsi DKI Jakarta bekerja sama dengan Kementerian Komunikasi dan Digital dan swasta menghadirkan ruang ...</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678884/252-siswa-sman-28-bandung-belajar-di-kompleks-sport-jabar-gedung-sekolah-baru-rampung-desember-2026</t>
+          <t>https://www.antaranews.com/berita/5679489/pemprov-dki-hadirkan-lapakmain-corner-di-rptra-tunas-muda-jaksel</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Siswa-SMAN-28-Bandung-belajar-di-gedung-sementara-040826-NA-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000314377.jpg</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -7438,33 +7440,33 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Kementerian Keuangan catat realisasi Belanja Pemerintah Pusat (BPP) capai Rp1.298,6 triliun atau tumbuh 29,4 persen</t>
+          <t>Wamenhub serahkan santunan ke keluarga korban KMP Mutiara Sentosa II</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 12:05:28 +0700</t>
+          <t>Tue, 04 Aug 2026 17:14:28 +0700</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Siswa berjalan membawa paket Makan Bergizi Gratis (MBG) di SDN Pejaten Barat 01, Pasar Minggu, Jakarta, Selasa (4/8/2026). Kementerian Keuangan mencatat realisasi Belanja Pemerintah Pusat (BPP) mencapai Rp1.298,6 triliun atau tumbuh 29,4 persen secara tahunan, yang antara lain didorong pelaksanaan program Makan Bergizi Gratis (MBG), penyaluran bantuan sosial, pembangunan infrastruktur, pembayaran tunjangan hari raya (THR) dan gaji ke-13, manfaat pensiun, subsidi dan kompensasi bahan bakar minyak (BBM) dan listrik. ANTARA FOTO/Angga Budhiyanto/agr</t>
+          <t>Wakil Menteri Perhubungan (Wamenhub) Suntana menyerahkan santunan kepada keluarga korban meninggal akibat ...</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678877/kementerian-keuangan-catat-realisasi-belanja-pemerintah-pusat-bpp-capai-rp12986-triliun-atau-tumbuh-294-persen</t>
+          <t>https://www.antaranews.com/berita/5679485/wamenhub-serahkan-santunan-ke-keluarga-korban-kmp-mutiara-sentosa-ii</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Realisasi-Belanja-Pemerintah-Pusat-04082026-ab-6.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1323295.jpg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -7476,33 +7478,33 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BPS proyeksikan produksi beras nasional capai 28,71 Juta ton hingga September 2026, stok dipastikan tetap aman</t>
+          <t>FHI 2026 perkuat akses pasar industri hospitality Indonesia</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:19:05 +0700</t>
+          <t>Tue, 04 Aug 2026 17:12:21 +0700</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pekerja menata karung berisi cadangan beras pemerintah di gudang Perum Bulog Cabang Meulaboh, Aceh Barat, Aceh, Selasa (4/8/2026). Badan Pusat Statistik (BPS) memproyeksi produksi beras nasional untuk konsumsi pangan sepanjang Januari - September 2026 mencapai 28,71 juta ton atau meningkat 0,01 persen dibandingkan periode yang sama tahun sebelumnya. ANTARA FOTO/Syifa Yulinnas/agr</t>
+          <t>Food &amp; Hospitality Indonesia (FHI) 2026 memperkuat peluang bisnis sekaligus meningkatkan daya saing industri ...</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678815/bps-proyeksikan-produksi-beras-nasional-capai-2871-juta-ton-hingga-september-2026-stok-dipastikan-tetap-aman</t>
+          <t>https://www.antaranews.com/berita/5679479/fhi-2026-perkuat-akses-pasar-industri-hospitality-indonesia</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Prediksi-produksi-beras-nasional-040826-Syf-3.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_162615.jpg</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -7514,33 +7516,33 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>photo</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+          <t>Kadin yakini RI dan Thailand berpeluang unggul dalam ketahanan pangan</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+          <t>Tue, 04 Aug 2026 17:11:05 +0700</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, Pemulutan Barat, Ogan Ilir (OI), Sumatera Selatan, Senin (3/8/2026). Petugas dibantu warga masih berupaya memadamkan kebakaran lahan di daerah tersebut. ANTARA FOTO/Nova Wahyudi/agr</t>
+          <t>Kamar Dagang dan Industri (Kadin) meyakini Indonesia dan Thailand memiliki peluang besar untuk maju bersama secara ...</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+          <t>https://www.antaranews.com/berita/5679475/kadin-yakini-ri-dan-thailand-berpeluang-unggul-dalam-ketahanan-pangan</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-16.24.18_edit_249465416700473.jpg</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -7552,33 +7554,33 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Dilanda cuaca panas, nakes Lhokseumawe bagikan masker untuk cegah ISPA</t>
+          <t>Bocoran spesifikasi Huawei Mate 90 Pro Max terungkap jelang peluncuran</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 17:10:47 +0700</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>ANTARA - Dilanda cuaca panas hingga 35 derajat celcius, tim nakes dari Puskesmas Mon Gedong, Kecamatan Banda Sakti, Kota Lhokseumawe, Aceh, membagikan masker bagi pengendara di Simpang Empat Masjid Islamic Center, sebagai salah satu upaya pencegahan penyakit Infeksi Saluran Pernapasan Akut (ISPA), Selasa (4/8). (Try Vanny S/Denno Ramdha Asmara/Roy Rosa Bachtiar)</t>
+          <t>Bocoran spesifikasi utama Huawei Mate 90 Pro Max terungkap menjelang peluncurannya yang diperkirakan berlangsung pada ...</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5679057/dilanda-cuaca-panas-nakes-lhokseumawe-bagikan-masker-untuk-cegah-ispa</t>
+          <t>https://www.antaranews.com/berita/5679472/bocoran-spesifikasi-huawei-mate-90-pro-max-terungkap-jelang-peluncuran</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DILANDA-CUACA-PANAS-NAKES-LHOKSEUMAWE-BAGIKAN-MASKER-UNTUK-CEGAH-ISPA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000141030.jpg</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -7590,33 +7592,33 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
+          <t>Prabowo antar kepulangan PM Thailand Anutin dari Lanud Halim</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 17:07:04 +0700</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, kota Ambon, Maluku, Selasa (4/8). Kegiatan digitalisasi bansos ini diwajibkan untuk seluruh Apartur Sipil Negara di lingkup Pemkot Ambon. (Alfian Sanusi/Denno Ramdha Asmara/Winanto)</t>
+          <t>Presiden Prabowo Subianto mengantar kepulangan Perdana Menteri Thailand Anutin Charnvirakul di Pangkalan Udara TNI AU ...</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
+          <t>https://www.antaranews.com/berita/5679468/prabowo-antar-kepulangan-pm-thailand-anutin-dari-lanud-halim</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000034560.jpg</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -7628,33 +7630,33 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DKPP pastikan cadangan beras Kab. Serang aman hingga setahun ke depan</t>
+          <t>Pengamat nilai perpindahan konsumen ke Pertalite perlu perhatian</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 17:05:28 +0700</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>ANTARA - Dinas Ketahanan Pangan dan Pertanian (DKPP) Kabupaten Serang, Selasa (4/8), memastikan cadangan beras Kabupaten Serang aman hingga satu tahun ke depan. Kepala Bidang Ketahanan Pangan DKPP Kabupaten Serang, Endra Nuryana, mengatakan, hingga per Agustus 2026, Kabupaten Serang tercatat masih memiliki sebanyak 334 ton beras cadangan, yang saat ini masih tersimpan di gudang Bulog Cabang Serang. (Susmiatun Hayati/Denno Ramdha Asmara/Winanto)</t>
+          <t>Pengamat ekonomi energi Universitas Gadjah Mada (UGM) Fahmy Radhi menilai perpindahan konsumen Pertamax ke Pertalite ...</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678939/dkpp-pastikan-cadangan-beras-kab-serang-aman-hingga-setahun-ke-depan</t>
+          <t>https://www.antaranews.com/berita/5679464/pengamat-nilai-perpindahan-konsumen-ke-pertalite-perlu-perhatian</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DKPP-PASTIKAN-CADANGAN-BERAS-KAB.SERANG-AMAN-HINGGA-SETAHUN-KE-DEPAN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/11/02/antarafoto-harga-bbm-non-subsidi-turun-021123-arf-2.jpg</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -7666,33 +7668,33 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
+          <t>KAI Jakarta beri diskon tiket hingga 30 persen pada awal bulan ini</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 17:04:38 +0700</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi Rupiah Berdaulat (ERB) 2026  yang digelar di lima pulau  yang masuk dalam wilayah Terdepan, Terluar dan Terpencil (3T) di wilayah Papua, di Dermaga Satrol Kodaeral X Jayapura, Selasa (4/8). Kepala Perwakilan Bank Indonesia Provinsi Papua, Warsono, mengatakan pelepasan tim ERB mencakup kegiatan edukasi Cinta, Bangga, dan Paham (CBP) Rupiah bahwa kehadiran rupiah hingga ke pulau-pulau terluar merupakan bagian dari upaya menjaga kedaulatan ekonomi nasional. (Laksa Mahendra/Denno Ramdha Asmara/Winanto)</t>
+          <t>PT Kereta Api Indonesia (Persero Daerah Operasi 1 Jakarta memberikan diskon tarif tiket kereta api untuk berbagai ...</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
+          <t>https://www.antaranews.com/berita/5679461/kai-jakarta-beri-diskon-tiket-hingga-30-persen-pada-awal-bulan-ini</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000314331.jpg</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -7704,33 +7706,33 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
+          <t>Purbaya tawarkan insentif agar Toyota relokasi produksi ke RI</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 17:00:07 +0700</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi melalui penerapan sistem verifikasi berbasis Quick Response (QR) berlapis. Wali Kota Palu Harianto Rasyid pada Senin (3/8), mengatakan, bahwa QR tersebut menjadi verifikasi tambahan guna melengkapi sistem QR Subsidi tepat milik Pertamina, sehingga setiap kendaraan yang nantinya memperoleh solar bersubsidi wajib lebih dahulu terdaftar pada Pemerintah Kota Palu. (Farah Khadija/M. Izfaldi/Denno Ramdha Asmara/Winanto)</t>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa menawarkan pemberian insentif agar perusahaan otomotif Toyota merelokasi pusat ...</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
+          <t>https://www.antaranews.com/berita/5679456/purbaya-tawarkan-insentif-agar-toyota-relokasi-produksi-ke-ri</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.13.51.jpeg</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -7742,33 +7744,33 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>photo, terkini</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+          <t>Menhan Sjafrie terima kunjungan Menhan Thailand</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 17:00:03 +0700</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+          <t>Menteri Pertahanan Sjafrie Sjamsoeddin (kedua kanan) dan Menteri Pertahanan Thailand Adul Boonthumjaroen (kanan) ...</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+          <t>https://www.antaranews.com/foto/5679453/menhan-sjafrie-terima-kunjungan-menhan-thailand</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Menhan-Sjafrie-terima-kunjungan-Menhan-Thailand-040826-MRH-5.jpg</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -7780,33 +7782,33 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+          <t>Seribu hari pertama kehidupan tentukan kualitas tumbuh kembang anak</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 16:59:22 +0700</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+          <t>Ikatan Dokter Anak Indonesia (IDAI) mengingatkan bahwa 1.000 hari pertama kehidupan anak merupakan masa yang menentukan ...</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+          <t>https://www.antaranews.com/berita/5679445/seribu-hari-pertama-kehidupan-tentukan-kualitas-tumbuh-kembang-anak</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/06/14/Pengukuran-Intervensi-Serentak-Pencegahan-Stunting-140624-yn-3.jpg</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -7818,33 +7820,33 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+          <t>Pelantikan DHD 45, Gubernur Sumut tekankan semangat juang pahlawan</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 16:59:12 +0700</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+          <t>ANTARA - Dewan Harian Daerah (DHD) Badan Pembudayaan Kejuangan 45 Sumatera Utara resmi dilantik dan disaksikan langsung ...</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+          <t>https://www.antaranews.com/video/5679368/pelantikan-dhd-45-gubernur-sumut-tekankan-semangat-juang-pahlawan</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_PELANTIKAN-DHD-45-GUBERNUR-SUMUT-TEKANKAN-SEMANGAT-JUANG-PAHLAWAN.jpg</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -7856,33 +7858,33 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>ekonomi-bisnis, terkini</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+          <t>Menko Pangan minta asosiasi dan kepala desa luruskan hoaks soal Kopdes</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 16:58:49 +0700</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Menteri Koordinator (Menko) Bidang Pangan Zulkifli Hasan meminta kepada sejumlah asosiasi desa dan kepala desa ikut ...</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+          <t>https://www.antaranews.com/berita/5679441/menko-pangan-minta-asosiasi-dan-kepala-desa-luruskan-hoaks-soal-kopdes</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002906202.jpg</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -7894,33 +7896,33 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+          <t>Kesalahan menyusui yang kerap dilakukan ibu saat payudara bengkak</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 16:57:53 +0700</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+          <t>Seringkali ketika payudara bengkak para ibu yang sedang memasuki fase menyusui memaksakan diri untuk kerap memompa ASI ...</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+          <t>https://www.antaranews.com/berita/5679437/kesalahan-menyusui-yang-kerap-dilakukan-ibu-saat-payudara-bengkak</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Pexels.jpg</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -7932,33 +7934,33 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+          <t>Munjirin minta aset SDA bekas TPS liar di Kramat Jati dimanfaatkan</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 16:57:33 +0700</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+          <t>Wali Kota Jakarta Timur Munjirin meminta Dinas Sumber Daya Air (SDA) DKI Jakarta untuk memanfaatkan lahan yang ...</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+          <t>https://www.antaranews.com/berita/5679436/munjirin-minta-aset-sda-bekas-tps-liar-di-kramat-jati-dimanfaatkan</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/InShot_20260804_162347988.jpg</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -7970,33 +7972,33 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>terkini</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+          <t>Komisi III: Tak benar ada surat presiden soal penggantian Kapolri</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 16:53:36 +0700</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+          <t>Ketua Komisi III DPR RI Habiburokhman membantah isu adanya surat presiden (surpres) soal penggantian Kepala Kepolisian ...</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+          <t>https://www.antaranews.com/berita/5679432/komisi-iii-tak-benar-ada-surat-presiden-soal-penggantian-kapolri</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/1001272341.jpg</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -8008,1455 +8010,5275 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>lifestyle, terkini</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+          <t>Kenapa nyamuk lebih banyak saat musim kemarau? Ini penyebabnya</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
+          <t>Tue, 04 Aug 2026 16:51:54 +0700</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
+          <t>Jumlah nyamuk yang meningkat saat musim kemarau kerap dirasakan masyarakat, terutama ketika cuaca panas dan kering ...</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679429/kenapa-nyamuk-lebih-banyak-saat-musim-kemarau-ini-penyebabnya</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/10/DBD.jpg</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>KPK ajak publik pantau sidang Yaqut dkk yang dimulai Selasa depan</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:51:15 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) RI mengajak kalangan publik untuk memantau persidangan mantan Menteri Agama Yaqut ...</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679427/kpk-ajak-publik-pantau-sidang-yaqut-dkk-yang-dimulai-selasa-depan</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/pemeriksaan-tersangka-yaqut-cholil-qoumas-2821379.jpg</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Sulteng dan UEA perkuat komitmen investasi empat sektor</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:50:58 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Sulawesi Tengah (Sulteng) dan Kedutaan Besar Uni Emirat Arab (UEA) untuk Indonesia, memperkuat ...</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679423/sulteng-dan-uea-perkuat-komitmen-investasiempat-sektor</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/DUBES-UEA-dan-Gubernur-Sulteng.jpeg</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Rektor: Arah kebijakan strategis USU fokus pada lima pilar utama</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:49:45 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Universitas Sumatera Utara (USU) telah menetapkan arah kebijakan strategis periode 2026–2031 yang berfokus pada ...</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679421/rektor-arah-kebijakan-strategis-usu-fokus-pada-lima-pilar-utama</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000498283.jpg</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Polisi: Masih ada 41 PMI di Libya yang belum pulang ke Indonesia</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:49:36 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Direktorat Reserse Kriminal Umum (Ditreskrimum) Polda Metro Jaya menyatakan masih ada 41 Pekerja Migran Indonesia ...</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679419/polisi-masih-ada-41-pmi-di-libya-yang-belum-pulang-ke-indonesia</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-15.06.24_1.jpeg</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PM Thailand dorong pendekatan bertahap ASEAN untuk krisis Myanmar</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:47:12 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Perdana Menteri (PM) Thailand Anutin Charnvirakul mengatakan pihaknya mendorong pendekatan kembali secara bertahap ...</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679415/pm-thailand-dorong-pendekatan-bertahap-asean-untuk-krisis-myanmar</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/kunjungan-pm-thailand-ke-sekretariat-asean-2833969.jpg</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Waketum MUI Marsudi Syuhud siap maju calon Ketum PBNU</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:46:45 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Tokoh senior Nahdlatul Ulama (NU) yang juga Wakil Ketua Umum Majelis Ulama Indonesia (MUI) KH Marsudi Syuhud menyatakan ...</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679411/waketum-mui-marsudi-syuhud-siap-maju-calon-ketum-pbnu</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176588.jpg</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Iran batal serang Ukraina usai terima "permintaan maaf" Kiev</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:45:12 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Iran sudah bersiap melancarkan serangan ke tiga titik di Ukraina, sebagai balasan atas dugaan serangan Kiev terhadap ...</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679407/iran-batal-serang-ukraina-usai-terima-permintaan-maaf-kiev</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/26/lau-kaspia.jpg</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa, terkini</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>IHSG ditutup menguat seiring sentimen positif domestik dan global</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:45:11 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa sore ditutup menguat dipicu oleh sentimen ...</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679403/ihsg-ditutup-menguat-seiring-sentimen-positif-domestik-dan-global</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/pergerakan-indeks-harga-saham-gabungan-270726-dr-02.jpg</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Mendag targetkan neraca dagang pada Juli 2026 kembali surplus</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:43:03 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Perdagangan Budi Santoso menargetkan neraca perdagangan Indonesia akan kembali mencetak surplus pada ...</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5679321/mendag-targetkan-neraca-dagang-pada-juli-2026-kembali-surplus</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-04-160042.jpg</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Prabowo perintahkan Menteri ESDM atasi pemadaman listrik di Kalimantan</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:42:46 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memerintahkan Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia untuk segera ...</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679401/prabowo-perintahkan-menteri-esdm-atasi-pemadaman-listrik-di-kalimantan</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000034553.jpg</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Prabowo perintahkan harga BBM subsidi tidak dinaikkan</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:40:44 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memerintahkan agar harga bahan bakar minyak (BBM) bersubsidi tidak dinaikkan di tengah ...</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679397/prabowo-perintahkan-harga-bbm-subsidi-tidak-dinaikkan</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000034556.jpg</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Pemprov DKI ajak pria tingkatkan wawasan tentang kesehatan reproduksi</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:40:25 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Dinas Pemberdayaan, Perlindungan Anak, dan Pengendalian Penduduk (PPAPP) DKI Jakarta mengajak para pria di ibu kota ...</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679396/pemprov-dki-ajak-pria-tingkatkan-wawasan-tentang-kesehatan-reproduksi</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000314326.jpg</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Bulog siap distribusi bantuan beras ke 33,2 juta KPM mulai 17 Agustus</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:38:47 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Perum Bulog menyatakan kesiapannya menyalurkan bantuan pangan beras kepada 33,2 juta keluarga penerima manfaat (KPM) ...</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679395/bulog-siap-distribusi-bantuan-beras-ke-332-juta-kpm-mulai-17-agustus</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/C686D451-0C0D-4DEB-8561-A9D4BC06D3EF.jpeg</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial, terkini</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Krom Bank perkuat kerja sama pembiayaan dengan Pandai Gadai</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:37:21 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>PT Krom Bank Indonesia Tbk (Kode emiten: BBSI), memperkuat kemitraan pembiayaannya dengan memberikan fasilitas kredit ...</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679393/krom-bank-perkuat-kerja-sama-pembiayaan-dengan-pandai-gadai</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-2.14.24-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis, terkini</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>BPS catat harga bawang putih naik di 248 daerah</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:36:45 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) mencatat harga bawang putih mengalami kenaikan di 248 kabupaten/kota atau sekitar 68,89 ...</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679392/bps-catat-harga-bawang-putih-naik-di-248-daerah</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_3691.jpeg</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Iran: Negosiasi dengan Oman fokus pada rute sementara di Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:36:43 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>ANTARA - Negosiasi antara Iran dan Oman berfokus pada pencapaian kesepakatan tentang penetapan rute "sementara" untuk ...</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5679379/iran-negosiasi-dengan-oman-fokus-pada-rute-sementara-di-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-04-162550.jpg</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Kemenkes minta orang tua laporkan jika temukan KIPI pada anak</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:36:24 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan (Kemenkes) meminta orang tua atau wali murid untuk segera melaporkan dan memeriksakan anak jika ...</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679389/kemenkes-minta-orang-tua-laporkan-jika-temukan-kipi-pada-anak</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/bulan-imunisasi-anak-sekolah-di-ternate-2832636.jpg</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>IDAI: Stunting bisa dideteksi dini lewat kurva pertumbuhan</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:34:14 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Ikatan Dokter Anak Indonesia (IDAI) mengingatkan bahwa risiko stunting dapat dideteksi lebih dini melalui pemantauan ...</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679385/idai-stunting-bisa-dideteksi-dini-lewat-kurva-pertumbuhan</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/07/215441.jpg</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Advokat usul RUU Perampasan Aset atur pemulihan korban salah sita</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:34:10 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Ketua Umum Persatuan Advokat Indonesia (Peradin) Firman Wijaya mengusulkan Rancangan Undang-Undang (RUU) Perampasan ...</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679383/advokat-usul-ruu-perampasan-aset-atur-pemulihan-korban-salah-sita</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Firman-Wijaya.jpeg</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>lifestyle, terkini</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>10 Cara move on setelah putus cinta yang sehat dan efektif</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:33:16 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Putus cinta sering kali menjadi pengalaman emosional yang tidak mudah dilalui. Rasa sedih, kecewa, marah, hingga ...</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679381/10-cara-move-on-setelah-putus-cinta-yang-sehat-dan-efektif</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2014/06/20140624patah_hati.jpg</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Indonesia kirim 14 perenang ke Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:30:52 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Pengurus Besar Akuatik Indonesia mengumumkan 14 perenang untuk membela Merah Putih pada Asian Games Aichi-Nagoya 2026 ...</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679377/indonesia-kirim-14-perenang-ke-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/02/22/IMG_20240221_104316.jpg</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>terkini</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Pemkot Jaktim perkuat sinergitas dengan media untuk kemajuan wilayah</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:30:07 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Jakarta Timur (Pemkot Jaktim) memperkuat sinergitas dengan media massa untuk kemajuan wilayah ...</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679376/pemkot-jaktim-perkuat-sinergitas-dengan-media-untuk-kemajuan-wilayah</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/InShot_20260804_160020248.jpg</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ekonomi, ekonomi-bisnis, otomotif, terkini</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Tiket GIIAS 2026: Daftar Harga dan cara belinya</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:29:46 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Pameran GAIKINDO Indonesia International Auto Show (GIIAS) 2026 resmi digelar sejak 30 Juli hingga 9 Agustus 2026. ...</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5679373/tiket-giias-2026-daftar-harga-dan-cara-belinya</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/WhatsApp-Image-2026-07-30-at-21.31.47.jpeg</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Tiga korban TPPO di Libya alami eksploitasi ekonomi</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:17:19 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Ketiga korban Tindak Pidana Perdagangan Orang (TPPO) berinisial NAR (21), SS (45), dan NKR (39) mengalami ...</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679340/tiga-korban-tppo-di-libya-alami-eksploitasi-ekonomi</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-15.06.24.jpeg</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>PM Thailand: ASEAN kini di persimpangan jalan hadapi tantangan global</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:11:35 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Perdana Menteri (PM) Thailand Anutin Charnvirakul mengatakan ASEAN kini berada di persimpangan jalan, dimana pilihan ...</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679317/pm-thailand-asean-kini-di-persimpangan-jalan-hadapi-tantangan-global</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/tempImageWJRC1F.jpg</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Penjualan mobil naik, Menkeu yakin daya beli domestik tetap terjaga</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:45:23 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa mengatakan pertumbuhan penjualan mobil menjadi salah satu indikator yang ...</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679033/penjualan-mobil-naik-menkeu-yakin-daya-beli-domestik-tetap-terjaga</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-13.13.50.jpg</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Ada 2 bibit siklon tropis, BMKG: Waspada ombak setinggi 4 meter di RI</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:09:44 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) mendeteksi kemunculan dua bibit siklon tropis sekaligus di wilayah ...</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678879/ada-2-bibit-siklon-tropis-bmkg-waspada-ombak-setinggi-4-meter-di-ri</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20250609_135328.jpg</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Korban tewas gempa Venezuela terus bertambah jadi 6.100 orang</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:00:56 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Jumlah korban tewas akibat gempa kembar dahsyat yang mengguncang Venezuela pada 24 Juni 2026, terus bertambah ...</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678865/korban-tewas-gempa-venezuela-terus-bertambah-jadi-6100-orang</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_d4a34a165f13a0667255577d3cfac46f.jpg</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>BPKH salurkan Rp2,06 triliun nilai manfaat ke 5,7 juta calon haji</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:47:58 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Keuangan Haji (BPKH) menyalurkan Nilai Manfaat Tahap I Tahun 2026 lebih dari Rp2,06 triliun kepada ...</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678849/bpkh-salurkan-rp206-triliun-nilai-manfaat-ke-57-juta-calon-haji</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000176506_1.jpg</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Aldila jadi petenis Indonesia yang pertama juarai DC Open</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:39:37 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Petenis Indonesia Aldila Sutjiadi mencatatkan sejarah setelah menjuarai nomor ganda putri turnamen Mubadala DC Open ...</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678836/aldila-jadi-petenis-indonesia-yang-pertama-juarai-dc-open</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4155-copy.jpg</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Indonesia raih 15 medali dari Kejuaraan MMAAsia</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:16:36 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Tim mixed martial arts (MMA) amatir Indonesia meraih 15 medali dan menempati peringkat keempat pada GAMMA Asian ...</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678689/indonesia-raih-15-medali-dari-kejuaraan-mmaasia</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/Delvi-Novia_Medal.jpg</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Kontingen Indonesia di Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Indonesia mengirimkan 432 atlet terbaik untuk berlaga di Asian Games 2026 pada 19 September-4 Oktober di Aichi dan ...</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://asiangames.antaranews.com/infografik/5677857/kontingen-indonesia-di-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/20260803-Kontingen-Indonesia-di-Asian-Games-2026.jpg</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Rizky Ridho abaikan kritik negatif untuk jaga fokus kontra Singapura</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:45:38 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Kapten tim nasional sepak bola Indonesia Rizky Ridho memilih mengabaikan kritik negatif terkait penampilannya saat ...</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678603/rizky-ridho-abaikan-kritik-negatif-untuk-jaga-fokus-kontra-singapura</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833529.jpg</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>top-news</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Bahlil ungkap strategi insentif NMC pacu mobil listrik berbasis nikel</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 01:34:36 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menyampaikan pemberian insentif nickel-manganese-cobalt ...</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678583/bahlil-ungkap-strategi-insentif-nmc-pacu-mobil-listrik-berbasis-nikel</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/03/22/antarafoto-pertumbuhan-penjualan-kendaraan-listrik-22032023-adw.jpg</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>OJK luncurkan 12.969 rekening "Simpel" perluas akses keuangan pelajar</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:07:32 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) Sulawesi Tenggara (Sultra) bersama pemerintah kabupaten dan PT BPR Bahteramas Konawe ...</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679311/ojk-luncurkan-12969-rekening-simpel-perluas-akses-keuangan-pelajar</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_1266.jpeg</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand gelar forum bisnis tingkatkan kerja sama ekonomi</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:41:45 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>ANTARA - Kamar Dagang dan Industri (Kadin) Indonesia menggelar Indonesia-Thailand Bisnis Forum di Jakarta pada Selasa ...</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5679221/indonesia-thailand-gelar-forum-bisnis-tingkatkan-kerja-sama-ekonomi</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-THAILAND-GELAR-FORUM-BISNIS-TINGKATKAN-KERJA-SAMA-EKONOMI.jpg</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Bappenas: Presiden minta soal iklim tIdak ganggu stabilitas nasional</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:47:39 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Menteri Perencanaan Pembangunan Nasional (PPN)/Kepala Badan Perencanaan Pembangunan Nasional (Bappenas) Rachmat Pambudy ...</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679137/bappenas-presiden-minta-soal-iklim-tidak-ganggu-stabilitas-nasional</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-14.11.29.jpeg</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Ekonom: Pasokan pangan membaik jaga inflasi tetap terkendali</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:23:45 +0700</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Ekonom PT Bank Danamon Indonesia Tbk menilai inflasi pada Juli 2026 tetap terkendali seiring membaiknya pasokan pangan ...</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679091/ekonom-pasokan-pangan-membaik-jaga-inflasi-tetap-terkendali</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/inflasi-juli-2026-jawa-barat-2833080.jpg</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>LPEM FEB UI perkirakan ekonomi RI tumbuh 4,8 persen di kuartal II 2026</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:57:01 +0700</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Lembaga Penyelidikan Ekonomi dan Masyarakat Fakultas Ekonomi dan Bisnis Universitas Indonesia (LPEM FEB UI) ...</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678945/lpem-feb-ui-perkirakan-ekonomi-ri-tumbuh-48-persen-di-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/05/17/Screenshot_20220517-151559_YouTube.jpg</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>BI siapkan Rp20 miliar ekspedisi rupiah berdaulat 2026 di 3T Papua</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:24:47 +0700</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Kantor Perwakilan Bank Indonesia (BI) Provinsi Papua menyiapkan uang layak edar senilai Rp20 miliar dalam pelaksanaan ...</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678896/bi-siapkan-rp20-miliar-ekspedisi-rupiah-berdaulat-2026-di-3t-papua</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1002062154.jpg</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Panda Bond dan sinyal kepercayaan investasi global</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:26:35 +0700</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Di tengah ketidakpastian ekonomi global yang semakin kompleks, pemerintah Indonesia perlu memastikan bahwa ...</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678827/panda-bond-dan-sinyal-kepercayaan-investasi-global</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/15/permintaan-pembelian-obligasi-global-capai-46-miliar-dolar-as-2806089.jpg</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Rupiah Selasa melemah dipicu kenaikan harga minyak global</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:15:57 +0700</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah pada Selasa pagi bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per dolar AS ...</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678808/rupiah-selasa-melemah-dipicu-kenaikan-harga-minyak-global</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/13/nilai-tukar-rupiah-melemah-44-poin-2821215.jpg</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>DJPb catat pembelanjaan di 75 KDKMP Sultra capai 1.055 kali transaksi</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:00:21 +0700</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Kantor Wilayah (Kanwil) Direktorat Jenderal Perbendaharaan (DJPb) Provinsi Sulawesi Tenggara (Sultra), mencatat ...</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678732/djpb-catat-pembelanjaan-di-75-kdkmp-sultra-capai-1055-kali-transaksi</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/2798be53-c5ca-4be6-bcf8-a2e9eb6c7488.jpeg</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Rupiah pada Selasa pagi melemah jadi Rp18.029 per dolar AS</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:16:27 +0700</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah terhadap dolar AS pada Selasa pagi, bergerak melemah 32 poin atau 0,18 persen menjadi Rp18.029 per ...</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678685/rupiah-pada-selasa-pagi-melemah-jadi-rp18029-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/nilai-tukar-rupiah-melemah-2828879.jpg</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ekonomi-finansial</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CORE: Penilaian kredit alternatif dapat perluas pembiayaan UMKM</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:58:42 +0700</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Direktur Eksekutif Center of Reform on Economics (CORE) Indonesia Mohammad Faisal menilai pemanfaatan penilaian kredit ...</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678651/core-penilaian-kredit-alternatif-dapat-perluas-pembiayaan-umkm</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/realisasi-penyaluran-kur-umkm-2832719.jpg</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Gubernur Sherly: Kolaborasi dengan KKP untuk tingkatkan kesejahteraan</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:13:11 +0700</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Gubernur Maluku Utara (Malut) Sherly Tjoanda mengatakan bahwa kolaborasi antara Pemerintah Provinsi (Pemprov) ...</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679332/gubernur-sherly-kolaborasi-dengan-kkp-untuk-tingkatkan-kesejahteraan</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_20260804_160238.jpg</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>PHR menjaga produksi migas di tengah tantangan sumur tua</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:08:40 +0700</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>PT Pertamina Hulu Rokan (PHR) Regional 1 menjaga produksi minyak dan gas bumi (migas) di tengah tantangan lapangan ...</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679312/phr-menjaga-produksi-migas-di-tengah-tantangan-sumur-tua</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-03-at-19.15.22.jpeg</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>PGE pacu potensi pemanfaatan panas bumi untuk "green data center"</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:06:57 +0700</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>PT Pertamina Geothermal Energy (PGE) siap mengakselerasi potensi pemanfaatan energi panas bumi (geothermal) dalam ...</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679309/pge-pacu-potensi-pemanfaatan-panas-bumi-untuk-green-data-center</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_0376.jpeg</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>PGE membidik pilot project hidrogen hijau Ulubelu beroperasi November</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:05:34 +0700</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>PT Pertamina Geothermal Energy (PGE) menargetkan proyek percontohan (pilot project) hidrogen hijau (green hydrogen) di ...</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679299/pge-membidik-pilot-project-hidrogen-hijau-ulubelu-beroperasi-november</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_0372.jpeg</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>PNM perluas akses pembiayaan hingga wilayah 3T</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:03:01 +0700</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>PT Permodalan Nasional Madani/PNM (Persero) memperluas akses pembiayaan hingga ke wilayah terdepan, terluar, ...</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679287/pnm-perluas-akses-pembiayaan-hingga-wilayah-3t</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/26/IMG_20260626_171233.jpg</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>BSI bangun ekosistem UMKM nasional bersama Danantara</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:02:20 +0700</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>PT Bank Syariah Indonesia (Persero) Tbk (BSI) bersama Danantara Indonesia mempercepat penguatan ekonomi kerakyatan ...</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679276/bsi-bangun-ekosistem-umkm-nasional-bersama-danantara</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-1.31.09-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Kemenhub siapkan konsep RUU Sistranas integrasikan transportasi RI</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:54:23 +0700</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan (Kemenhub) menyiapkan konsep Rancangan Undang-Undang Sistem Transportasi Nasional (RUU ...</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679255/kemenhub-siapkan-konsep-ruu-sistranas-integrasikan-transportasi-ri</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/3A66ACDB-E0FA-479B-AF79-9B7E49AAB4DF.jpeg</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Kepala Bappenas sebut gradasi El Nino miliki pengaruh luar biasa besar</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Menteri Perencanaan Pembangunan Nasional (PPN)/Kepala Badan Perencanaan Pembangunan Nasional (Bappenas) Rachmat Pambudy ...</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679197/kepala-bappenas-sebut-gradasi-el-nino-miliki-pengaruh-luar-biasa-besar</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/WhatsApp-Image-2026-08-04-at-15.00.36.jpeg</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>ekonomi-bisnis</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Bandara Soetta tambah 4 maskapai dalam layanan jamaah umroh</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:17:20 +0700</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>PT Angkasa Pura Indonesia (Persero) atau InJourney Airports melalui Kantor Cabang Bandar Udara Internasional ...</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679196/bandara-soetta-tambah-4-maskapai-dalam-layanan-jamaah-umroh</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000313178.jpg</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>IHSG menguat ditopang kinerja keuangan emiten periode kuartal II</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:12:17 +0700</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa bergerak menguat ditopang oleh laporan ...</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678748/ihsg-menguat-ditopang-kinerja-keuangan-emiten-periode-kuartal-ii</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/06/30/BEI-catatkan-14-perusahaan-baru-pada-2025-260625-fzn-3.jpg</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>ekonomi-bursa</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>IHSG Selasa dibuka menguat 20,28 poin ke posisi 6.254</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 09:06:02 +0700</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Selasa pagi, dibuka menguat 20,28 poin atau 0,33 ...</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678675/ihsg-selasa-dibuka-menguat-2028-poin-ke-posisi-6254</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/Pembukaan-IHSG-usai-libur-Lebaran.jpg250326-Ada-3.jpg</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>10 Kesalahan yang sebaiknya Anda hindari setelah putus cinta</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:04:43 +0700</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Putus cinta merupakan pengalaman emosional yang bisa dirasakan siapa saja. Berakhirnya sebuah hubungan sering kali ...</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679292/10-kesalahan-yang-sebaiknya-anda-hindari-setelah-putus-cinta</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/02/03/patah.jpg</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Tanda-tanda Anda belum benar-benar move on dari mantan</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:54:35 +0700</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Putus cinta bukan hanya mengakhiri sebuah hubungan, tetapi juga memulai proses penyesuaian emosional yang tidak selalu ...</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679256/tanda-tanda-anda-belum-benar-benar-move-on-dari-mantan</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/09/shutterstock_362866388.jpg</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Urus KTP Elektronik kini lebih mudah, Pemprov Jateng buka layanan jemput bola gratis untuk warga</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:29:32 +0700</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Petugas Disdukcapil merekam iris mata warga untuk pembuatan KTP elektronik saat layanan jemput bola administrasi kependudukan di Rumah Rakyat Jateng, Semarang, Jawa Tengah, Selasa (4/8/2026). Pemerintah Provinsi Jawa Tengah menggelar layanan gratis perekaman data KTP elektronik secara jemput bola di kantor tersebut untuk mendekatkan akses layanan dan mempermudah masyarakat mengurus dokumen kependudukan, seperti KTP lintas domisili, sekaligus menjadi pusat aspirasi yang cepat, mudah, dan transparan. ANTARA FOTO/Makna Zaezar/agr</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5679100/urus-ktp-elektronik-kini-lebih-mudah-pemprov-jateng-buka-layanan-jemput-bola-gratis-untuk-warga</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Layanan-Jemput-Bola-Administrasi-Kependudukan-Di-Jateng-040826-mz-1.jpg</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Ratusan siswa sekolah gratis di Semarang terima paket perlengkapan sekolah, bantu ringankan beban orang tua</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:15:18 +0700</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Siswa menunjukkan tas berisi paket perlengkapan sekolah di Sekolah Gratis Kuncup Melati, Kauman, Semarang, Jawa Tengah, Selasa (4/8/2026). Sebanyak 180 siswa jenjang TK hingga SMP menerima paket perlengkapan sekolah berupa tas, buku, alat tulis, sepatu, seragam, dan topi dari sumbangan berbagai donatur untuk menunjang kegiatan belajar mengajar serta meringankan beban kebutuhan pendidikan keluarga kurang mampu. ANTARA FOTO/Aprillio Akbar/agr</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5679073/ratusan-siswa-sekolah-gratis-di-semarang-terima-paket-perlengkapan-sekolah-bantu-ringankan-beban-orang-tua</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/pembagian-seragam-alat-tulis-sd-kuncup-melati-040826-aaa-4.jpg</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Target besar 2029, TPST Bantargebang pasang geomembran sebagai kunci transformasi pengelolaan sampah</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 14:00:03 +0700</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Petugas memasang patok pada geomembran sebagai media pelindung untuk menutup tumpukan sampah di Tempat Pengolahan Sampah Terpadu (TPST) Bantargebang, Kota Bekasi, Jawa Barat, Selasa (4/8/2026). Dinas Lingkungan Hidup DKI Jakarta melalui Unit Pengelolaan Sampah Terpadu (UPST) Bantargebang memasang geomembran sebagai bagian dari transformasi pengelolaan sampah guna menghentikan praktik open dumping secara total pada 2029. ANTARA FOTO/Darryl Ramadhan/agr</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5679067/target-besar-2029-tpst-bantargebang-pasang-geomembran-sebagai-kunci-transformasi-pengelolaan-sampah</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Dinas-DLH-DKI-pasang-Geomembrane-di-TPST-Bantargebang-040826-ryl-5.jpg</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Tambak modern udang vaname di kawasan industri Semarang bidik produksi 1,3 ton per siklus</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:47:21 +0700</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Pekerja menunjukkan udang vaname hasil budidaya Loka Perbenihan dan Budi Daya Ikan (PBI) Tugu Dinas Kelautan dan Perikanan Jawa Tengah saat panen di Kawasan Industri Wijayakusuma (KIW), Semarang, Jawa Tengah, Selasa (4/8/2026). Pemerintah Provinsi Jawa Tengah membudidayakan udang vaname di tambak seluas 1.561 meter persegi dengan teknologi sistem tertutup (closed system) yang menghemat penggunaan air sehingga tetap optimal di kawasan industri, dengan target produksi 1,3 ton udang vaname per siklus budidaya selama sekitar 82 hari sebagai upaya meningkatkan produktivitas perikanan budidaya sekaligus menjadi model revitalisasi tambak modern di kawasan Pantura. ANTARA FOTO/Aprillio Akbar/agr</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5679037/tambak-modern-udang-vaname-di-kawasan-industri-semarang-bidik-produksi-13-ton-per-siklus</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/panen-udang-vaname-budidaya-pemprov-jateng-040826-aaa-2.jpg</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Kementan usulkan telur ayam masuk skema cadangan pangan pemerintah</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:30:53 +0700</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Pekerja memberikan pakan ayam di salah satu peternakan di Cihampelas, Kabupaten Bandung Barat, Jawa Barat, Selasa (4/8/2026). Kementerian Pertanian mengusulkan telur ayam sebagai komoditas dalam skema Cadangan Pangan Pemerintah (CPP) guna memperkuat stabilisasi harga di tingkat produsen sekaligus melindungi keberlangsungan usaha peternak rakyat. ANTARA FOTO/Abdan Syakura/agr</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678903/kementan-usulkan-telur-ayam-masuk-skema-cadangan-pangan-pemerintah</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Kementan-Usulkan-Telur-Ayam-Masuk-Skema-CPP-040826-DAN-07.jpg</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>252 siswa SMAN 28 Bandung belajar di Kompleks Sport Jabar, gedung sekolah baru rampung Desember 2026</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:12:31 +0700</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Siswa kelas X SMAN 28 Bandung mengikuti kegiatan belajar mengajar di ruang kelas Gedung Laga Satria Sport Jabar Arcamanik, Bandung, Jawa Barat, Selasa (4/8/2026). Sebanyak 252 siswa angkatan pertama SMAN 28 Bandung untuk sementara mengikuti kegiatan belajar mengajar di kompleks Sport Jabar Arcamanik karena gedung sekolah masih dalam tahap pembangunan dan ditargetkan selesai pada Desember 2026. ANTARA FOTO/Novrian Arbi/agr</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678884/252-siswa-sman-28-bandung-belajar-di-kompleks-sport-jabar-gedung-sekolah-baru-rampung-desember-2026</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Siswa-SMAN-28-Bandung-belajar-di-gedung-sementara-040826-NA-6.jpg</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan catat realisasi Belanja Pemerintah Pusat (BPP) capai Rp1.298,6 triliun atau tumbuh 29,4 persen</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 12:05:28 +0700</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Siswa berjalan membawa paket Makan Bergizi Gratis (MBG) di SDN Pejaten Barat 01, Pasar Minggu, Jakarta, Selasa (4/8/2026). Kementerian Keuangan mencatat realisasi Belanja Pemerintah Pusat (BPP) mencapai Rp1.298,6 triliun atau tumbuh 29,4 persen secara tahunan, yang antara lain didorong pelaksanaan program Makan Bergizi Gratis (MBG), penyaluran bantuan sosial, pembangunan infrastruktur, pembayaran tunjangan hari raya (THR) dan gaji ke-13, manfaat pensiun, subsidi dan kompensasi bahan bakar minyak (BBM) dan listrik. ANTARA FOTO/Angga Budhiyanto/agr</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678877/kementerian-keuangan-catat-realisasi-belanja-pemerintah-pusat-bpp-capai-rp12986-triliun-atau-tumbuh-294-persen</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Realisasi-Belanja-Pemerintah-Pusat-04082026-ab-6.jpg</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>BPS proyeksikan produksi beras nasional capai 28,71 Juta ton hingga September 2026, stok dipastikan tetap aman</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 11:19:05 +0700</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Pekerja menata karung berisi cadangan beras pemerintah di gudang Perum Bulog Cabang Meulaboh, Aceh Barat, Aceh, Selasa (4/8/2026). Badan Pusat Statistik (BPS) memproyeksi produksi beras nasional untuk konsumsi pangan sepanjang Januari - September 2026 mencapai 28,71 juta ton atau meningkat 0,01 persen dibandingkan periode yang sama tahun sebelumnya. ANTARA FOTO/Syifa Yulinnas/agr</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678815/bps-proyeksikan-produksi-beras-nasional-capai-2871-juta-ton-hingga-september-2026-stok-dipastikan-tetap-aman</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Prediksi-produksi-beras-nasional-040826-Syf-3.jpg</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Begini kondisi terkini kebakaran lahan menjelang malam di Arisan Jaya Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 06:24:55 +0700</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Petugas dari Manggala Agni Daops Sumatera XIV-Banyuasin berusaha memadamkan kebakaran lahan di Desa Arisan Jaya, Pemulutan Barat, Ogan Ilir (OI), Sumatera Selatan, Senin (3/8/2026). Petugas dibantu warga masih berupaya memadamkan kebakaran lahan di daerah tersebut. ANTARA FOTO/Nova Wahyudi/agr</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5678617/begini-kondisi-terkini-kebakaran-lahan-menjelang-malam-di-arisan-jaya-ogan-ilir</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/255x170/2026/08/04/Pemadaman-kebakaran-lahan-di-Arisan-Jaya-030826-Lmo-7.jpg</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Menko Airlangga tegaskan ekonomi RI kuat hadapi gejolak global</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah memastikan kondisi ekonomi Indonesia masih berada pada jalur yang kuat, meski dihadapkan pada gejolak ekonomi global. Kepastian tersebut disampaikan Menteri Koordinator Bidang Perekonomian Airlangga Hartarto di Makassar, Sulsel, Selasa (4/8). Menurutnya fundamental ekonomi nasional masih terjaga yang tercermin dari laju inflasi yang menurun,hingga proyeksi pertumbuhan ekonomi yang tetap berada di atas 5 persen.(Shintia Aryanti Krisna/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679481/menko-airlangga-tegaskan-ekonomi-ri-kuat-hadapi-gejolak-global</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKO-AIRLANGGA-TEGASKAN-EKONOMI-RI-KUAT-HADAPI-GEJOLAK-GLOBAL.jpg</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Iran: Negosiasi dengan Oman fokus pada rute sementara di Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>ANTARA - Negosiasi antara Iran dan Oman berfokus pada pencapaian kesepakatan tentang penetapan rute "sementara" untuk memastikan pelayaran yang aman di Selat Hormuz. Hal tersebut disampaikan Juru bicara Kementerian Luar Negeri Iran, Esmaeil Baghaei, pada  Senin (3/8). (XINHUA/Ludmila Yusufin Diah Nastiti/Rizky Bagus Dhermawan/Winanto)</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679379/iran-negosiasi-dengan-oman-fokus-pada-rute-sementara-di-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-04-162550.jpg</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Pelantikan DHD 45, Gubernur Sumut tekankan semangat juang pahlawan</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>ANTARA - Dewan Harian Daerah (DHD) Badan Pembudayaan Kejuangan 45 Sumatera Utara resmi dilantik dan disaksikan langsung oleh Gubernur Sumatera Utara Bobby Nasution di Kantor Gubernur Sumut, Selasa, (4/8). Bobby menyebutkan tujuan dilantiknya DHD 45 Sumut ini untuk meneruskan semangat juang para pahlawan terdahulu agar tetap diterapkan hingga saat ini.
+(M. Valery Maulidzar S/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679368/pelantikan-dhd-45-gubernur-sumut-tekankan-semangat-juang-pahlawan</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PELANTIKAN-DHD-45-GUBERNUR-SUMUT-TEKANKAN-SEMANGAT-JUANG-PAHLAWAN.jpg</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Kabut tebal hentikan lalu lintas maritim di Selat Bosporus Turki</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>ANTARA - Lalu lintas maritim di Selat Bosporus Istanbul, Turki, dihentikan pada Senin (2/8) karena kabut tebal.Kabut tebal juga mengganggu layanan feri antara sisi Eropa dan Asia Istanbul, dengan feri penumpang dan kendaraan yang dihentikan hingga pemberitahuan lebih lanjut. (XINHUA/Ludmila Yusufin Diah Nastiti/Rizky Bagus Dhermawan/Winanto)</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679345/kabut-tebal-hentikan-lalu-lintas-maritim-di-selat-bosporus-turki</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-04-161506.jpg</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Mendag targetkan neraca dagang pada Juli 2026 kembali surplus</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Perdagangan Budi Santoso menargetkan neraca perdagangan Indonesia akan kembali mencetak surplus pada Juli 2026. Mendag di Jakarta pada Selasa (4/8) menyebut hal itu diproyeksikan seiring mulai stabilnya harga minyak dunia. (Sanya Dinda Susanti/Pradanna Putra Tampi/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679321/mendag-targetkan-neraca-dagang-pada-juli-2026-kembali-surplus</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-04-160042.jpg</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Menko Zulhas bantah isu Kopdes penyebab tutupnya warung kelontong</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Koordinator Bidang Pangan, Zulkifli Hasan, membantah isu yang menyebut kehadiran Koperasi Desa/Kelurahan Merah Putih akan menyebabkan penutupan warung kelontong. Zulhas menegaskan Koperasi Merah Putih merupakan infrastruktur pemerintah yang dibentuk untuk memperkuat penyaluran berbagai subsidi dan bantuan kepada masyarakat. (Shintia Aryanti Krisna/Dudy Yanuwardhana/Winanto)</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679253/menko-zulhas-bantah-isu-kopdes-penyebab-tutupnya-warung-kelontong</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/MENKO-ZULHAS-BANTAH-ISU-KOPDES.jpg</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Pemkot Yogyakarta berikan vaksin HPV perdana pada anak laki-laki</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>ANTARA -Dinas Kesehatan Kota Yogyakarta memperluas sasaran program Vaksinasi Human Papillomavirus (HPV) yang tidak hanya diperuntukan bagi anak perempuan, namun juga menyasar anak laki-laki usia 11 tahun. Pemberian vaksin HPV tersebut dilakukan perdana di Sekolah Dasar Intis School Kotagede pada Selasa (4/8).(Imam Prasetyo Nugroho/Rizky Bagus Dhermawan/Ludmila Yusufin Diah Nastiti)</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679247/pemkot-yogyakarta-berikan-vaksin-hpv-perdana-pada-anak-laki-laki</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/Screenshot-2026-08-04-154404.jpg</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Pemerintah targetkan perdagangan RI-Thailand tembus 20 miliar dolar AS</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Perdagangan Budi Santoso usai menghadiri Indonesia-Thailand Business Forum, di Jakarta, Selasa (4/8), menyatakan, pemerintah menargetkan nilai perdagangan Indonesia dan Thailand meningkat menjadi lebih dari 20 miliar dolar AS dari posisi saat ini sebesar 17,7 miliar dolar AS. Target tersebut akan diupayakan melalui peningkatan pertemuan bilateral untuk mengurangi hambatan perdagangan dan memperluas akses pasar kedua negara. (Sanya Dinda Susanti/Pradanna Putra Tampi/Andi Bagasela/Winanto)</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679237/pemerintah-targetkan-perdagangan-ri-thailand-tembus-20-miliar-dolar-as</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PEMERINTAH-TARGETKAN-PERDAGANGAN-RI-THAILAND-TEMBUS-20-MILIAR-DOLAR-AS.jpg</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Pemkab Banjarnegara fasilitasi warga deteksi dini kesehatan mata</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kabupaten Banjarnegara, Jawa Tengah, bersama Yayasan Satu Karsa Karya (YSKK) meluncurkan program penguatan sistem dan pelayanan kesehatan mata yang efektif dan inklusif. Kegiatan ini  merupakan upaya untuk mencegah gangguan penglihatan dan katarak dengan penanganan terintegrasi dari tingkat pelayanan primer hingga sekunder melalui penjaringan keluhan pada berbagai kelembagaan yang dekat dengan masyarakat. (Addin Alfath Amajida/Dudy Yanuwardhana/Winanto)</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679229/pemkab-banjarnegara-fasilitasi-warga-deteksi-dini-kesehatan-mata</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKAB-BANJARNEGARA-FASILITASI-WARGA.jpg</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand gelar forum bisnis tingkatkan kerja sama ekonomi</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>ANTARA - Kamar Dagang dan Industri (Kadin) Indonesia menggelar Indonesia-Thailand Bisnis Forum di Jakarta pada Selasa (4/8), yang dihadiri Perdana Menteri (PM) Thailand Anutin Charnvirakul. Dalam kesempatan tersebut ditandatangani sejumlah perjanjian kerja sama di bidang perekonomian. (Sanya Dinda Susanti/Pradanna Putra Tampi/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679221/indonesia-thailand-gelar-forum-bisnis-tingkatkan-kerja-sama-ekonomi</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-THAILAND-GELAR-FORUM-BISNIS-TINGKATKAN-KERJA-SAMA-EKONOMI.jpg</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Dilanda cuaca panas, nakes Lhokseumawe bagikan masker untuk cegah ISPA</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>ANTARA - Dilanda cuaca panas hingga 35 derajat celcius, tim nakes dari Puskesmas Mon Gedong, Kecamatan Banda Sakti, Kota Lhokseumawe, Aceh, membagikan masker bagi pengendara di Simpang Empat Masjid Islamic Center, sebagai salah satu upaya pencegahan penyakit Infeksi Saluran Pernapasan Akut (ISPA), Selasa (4/8). (Try Vanny S/Denno Ramdha Asmara/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679057/dilanda-cuaca-panas-nakes-lhokseumawe-bagikan-masker-untuk-cegah-ispa</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DILANDA-CUACA-PANAS-NAKES-LHOKSEUMAWE-BAGIKAN-MASKER-UNTUK-CEGAH-ISPA.jpg</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Pelatihan warga binaan Lapas Kupang hasilkan barang bernilai ekonomi</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>ANTARA - Lembaga Pemasyarakatan Kelas IIA Kupang, Nusa Tenggara Timur, pada Senin (3/8), terus mengoptimalkan pembinaan kemandirian warga binaan melalui berbagai program pemberdayaan, mulai dari pelatihan keterampilan, pendidikan, hingga ketahanan pangan. Program ini diharapkan menjadi bekal bagi warga binaan setelah bebas sekaligus meningkatkan nilai ekonomi hasil karya mereka. (Farah Khadija/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5679020/pelatihan-warga-binaan-lapas-kupang-hasilkan-barang-bernilai-ekonomi</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PELATIHAN-WARGA-BINAAN-LAPAS-KUPANG-HASILKAN-BARANG-BERNILAI-EKONOMI.jpg</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Pemkot Ambon wajibkan ASN registrasi digitalisasi Bansos</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota (Pemkot) Ambon melakukan registrasi digitalisasi Bantuan Sosial (Bansos) di Pattimura Park, kota Ambon, Maluku, Selasa (4/8). Kegiatan digitalisasi bansos ini diwajibkan untuk seluruh Apartur Sipil Negara di lingkup Pemkot Ambon. (Alfian Sanusi/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678964/pemkot-ambon-wajibkan-asn-registrasi-digitalisasi-bansos</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-AMBON-WAJIBKAN-ASN-REGISTRASI-DIGITALISASI-BANSOS.jpg</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>DKPP pastikan cadangan beras Kab. Serang aman hingga setahun ke depan</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>ANTARA - Dinas Ketahanan Pangan dan Pertanian (DKPP) Kabupaten Serang, Selasa (4/8), memastikan cadangan beras Kabupaten Serang aman hingga satu tahun ke depan. Kepala Bidang Ketahanan Pangan DKPP Kabupaten Serang, Endra Nuryana, mengatakan, hingga per Agustus 2026, Kabupaten Serang tercatat masih memiliki sebanyak 334 ton beras cadangan, yang saat ini masih tersimpan di gudang Bulog Cabang Serang. (Susmiatun Hayati/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678939/dkpp-pastikan-cadangan-beras-kab-serang-aman-hingga-setahun-ke-depan</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DKPP-PASTIKAN-CADANGAN-BERAS-KAB.SERANG-AMAN-HINGGA-SETAHUN-KE-DEPAN.jpg</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>BI Papua siapkan Rp 20 miliar dalam ekspedisi rupiah berdaulat 2026</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>ANTARA - Kantor Perwakilan Bank Indonesia Provinsi Papua  menyiapkan Rp20 miliar dalam pelaksanaan Ekspedisi Rupiah Berdaulat (ERB) 2026  yang digelar di lima pulau  yang masuk dalam wilayah Terdepan, Terluar dan Terpencil (3T) di wilayah Papua, di Dermaga Satrol Kodaeral X Jayapura, Selasa (4/8). Kepala Perwakilan Bank Indonesia Provinsi Papua, Warsono, mengatakan pelepasan tim ERB mencakup kegiatan edukasi Cinta, Bangga, dan Paham (CBP) Rupiah bahwa kehadiran rupiah hingga ke pulau-pulau terluar merupakan bagian dari upaya menjaga kedaulatan ekonomi nasional. (Laksa Mahendra/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678925/bi-papua-siapkan-rp-20-miliar-dalam-ekspedisi-rupiah-berdaulat-2026</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BI-SIAPKAN-RP20-MILIAR-EKSPEDISI-RUPIAH-BERDAULAT-2026-DI-3T-PAPUA.jpg</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Pemkot Palu siapkan skema QR berlapis untuk pembelian solar subsidi</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Kota Palu menyiapkan regulasi baru penyaluran bahan bakar minyak (BBM) jenis solar bersubsidi melalui penerapan sistem verifikasi berbasis Quick Response (QR) berlapis. Wali Kota Palu Harianto Rasyid pada Senin (3/8), mengatakan, bahwa QR tersebut menjadi verifikasi tambahan guna melengkapi sistem QR Subsidi tepat milik Pertamina, sehingga setiap kendaraan yang nantinya memperoleh solar bersubsidi wajib lebih dahulu terdaftar pada Pemerintah Kota Palu. (Farah Khadija/M. Izfaldi/Denno Ramdha Asmara/Winanto)</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678833/pemkot-palu-siapkan-skema-qr-berlapis-untuk-pembelian-solar-subsidi</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PEMKOT-PALU-SIAPKAN-SKEMA-QR-BERLAPIS-UNTUK-PEMBELIAN-SOLAR-SUBSIDI.jpg</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Aku Jeje rayakan indahnya jatuh hati di lagu Ceritanya Jatuh Cinta</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>ANTARA - Penyanyi Aku Jeje mempersembahkan lagu baru “Ceritanya Jatuh Cinta” yang dirilis pada Juli ini. Hadir dengan aransemen segar, Aku Jeje ternyata sempat mengalami kebuntuan dalam membuat “Ceritanya Jatuh Cinta”. Lalu bagaimana Aku Jeje akhirnya dapat meliris lagu yang dapat membuat pendengarnya jatuh cinta? Inilah cerita Aku Jeje kepada ANTARA! (Setyanka Harviana Putri/Ibnu Zaki, Syamsul Rizal/Satrio Giri Marwanto/Yogi Rachman)</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678793/aku-jeje-rayakan-indahnya-jatuh-hati-di-lagu-ceritanya-jatuh-cinta</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/WAWANCARA-AKU-JEJE.jpg</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Dibungkam Vietnam 0-3, Skuad Garuda kejar kemenangan dari Singapura</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>ANTARA - Tim Nasional Indonesia harus menelan kekalahan atas Vietnam dengan skor 0-3, pada pertandingan grup A piala AFF 2026 atau ASEAN Championship di stadion Pakansari, Kabupaten Bogor, Jawa Barat (3/8). Pelatih Timnas Indonesia, John Herdman, saat jumpa pers usai laga tersebut menyebut, meski kalah, saat ini anak asuhnya tengah berfokus untuk memenangkan pertandingan lanjutan melawan Singapura. (Ryan Rahman/Rayyan/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678599/dibungkam-vietnam-0-3-skuad-garuda-kejar-kemenangan-dari-singapura</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/DIBUNGKAM-VIETNAM-0-3-SKUAD-GARUDA-KEJAR-KEMENANGAN-DARI-SINGAPURA.jpg</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Perjuangan dan semangat pengabdian di balik derap langkah Paskibraka</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>ANTARA - Derap langkah puluhan peserta pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) menyimpan kisah semangat perjuangan dan pantang menyerah dari putra putri terbaik bangsa. Dari latar belakang suku, budaya, dan ekonomi yang berbeda, mereka menyatukan langkah, membulatkan tekad, demi memberikan yang terbaik untuk Indonesia. Satu diantaranya adalah siswi dari Sekolah Rakyat Terintegrasi 22 Polewali Mandar, Sulawesi Barat. (Cahya Sari/Ibnu Zaki/Rayyan/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678591/perjuangan-dan-semangat-pengabdian-di-balik-derap-langkah-paskibraka</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PERJUANGAN-DAN-SEMANGAT-PENGABDIAN-DI-BALIK-DERAP-LANGKAH-PASKIBRAKA.jpg</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo terima tanda kehormatan militer Thailand</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menerima tanda kehormatan militer dari Kerajaan Thailand berupa Medali Special Warfare Command, Royal Thai Army. Tanda Kehormatan tersebut disampaikan oleh PM Anutin Charnvirakul dalam kunjungan resmi ke Istana Merdeka Jakarta, pada Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Fahrul Marwansyah/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678581/presiden-prabowo-terima-tanda-kehormatan-militer-thailand</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-TANDA-KEHORMATAN-MILITER-THAILAND.jpg</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Satgas Cartenz evakuasi korban penyerangan yang tewaskan lima pekerja</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>ANTARA - Satgas Penegakan Hukum Operasi Damai Cartenz 2026 bersama Polres Tolikara dan Polsek Ilu mengevakuasi seluruh korban penyerangan terhadap pekerja proyek jalan di Kali Kabur, Distrik Kanggime, Kabupaten Tolikara, Papua Pegunungan. Kasatgas Humas Operasi Damai Cartenz 2026 Kombes Pol Yusuf Sutejo, di Jayapura, Senin (3/8), menjelaskan lima pekerja tewas, sedangkan lima pekerja lainnya berhasil dievakuasi dalam kondisi selamat. (Laksa Mahendra/Fahrul Marwansyah/Arsy Fitriady)</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678563/satgas-cartenz-evakuasi-korban-penyerangan-yang-tewaskan-lima-pekerja</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/SATGAS-CARTENZ-EVAKUASI-KORBAN-PENYERANGAN-YANG-TEWASKAN-LIMA-PEKERJA.jpg</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR bahas Pokok-Pokok Haluan Negara dengan Presiden</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>ANTARA - Ketua MPR RI Ahmad Muzani menyebut kunjungan jajaran pimpinan MPR ke Istana Kepresidenan Jakarta pada Senin (3/8) salah satunya untuk membahas Pokok-Pokok Haluan Negara. Hal itu disampaikan Muzani saat memberikan keterangan usai pertemuan dengan Presiden. (Aria Cindyara/Irfansyah Naufal Nasution/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678553/pimpinan-mpr-bahas-pokok-pokok-haluan-negara-dengan-presiden</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/PIMPINAN-MPR-BAHAS-POKOK-POKOK-HALUAN-NEGARA-DENGAN-PRESIDEN.jpg</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Bakom: WFH ASN diperpanjang untuk wujudkan birokrasi lebih modern</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Komunikasi Pemerintah (Bakom) RI Muhammad Qodari menyebut perpanjangan kebijakan Work From Home (WFH) bagi aparatur sipil negara (ASN) selama satu hari dalam sepekan hingga akhir September 2026 bertujuan mewujudkan birokrasi yang lebih modern, adaptif, dan efisien. Pemerintah juga memastikan pelayanan publik tetap berjalan optimal selama kebijakan tersebut diterapkan. (Setyanka Harviana Putri/Pradanna Putra Tampi/Rayyan/I Gusti Agung Ayu N)</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678536/bakom-wfh-asn-diperpanjang-untuk-wujudkan-birokrasi-lebih-modern</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/BAKOM-WFH-ASN-DIPERPANJANG-UNTUK-WUJUDKAN-BIROKRASI-LEBIH-MODERN.jpg</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Indonesia-Thailand sepakati penguatan kerja sama lintas bidang</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia dan Thailand sepakat memperkuat kemitraan strategis di berbagai sektor, mulai dari keamanan, ekonomi, ketahanan pangan, energi, hingga isu-isu regional. Kesepakatan tersebut dibahas dalam pertemuan Presiden Prabowo Subianto dengan Perdana Menteri Thailand Anutin Charnvirakul dalam kunjungan resmi di Jakarta, Senin (3/8). (Aria Cindyara/Irfansyah Naufal Nasution/Soni Namura/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678533/indonesia-thailand-sepakati-penguatan-kerja-sama-lintas-bidang</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/INDONESIA-THAILAND-SEPAKATI-PENGUATAN-KERJA-SAMA-LINTAS-BIDANG.jpg</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>BGN naikkan status keracunan MBG jadi kejadian fatal</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono melalui video keterangan yang diterima Antara pada Senin (3/8) mengatakan, BGN meningkatkan status keracunan Makan Bergizi Gratis (MBG) menjadi kejadian fatal. Sudaryono juga menjelaskan, pihaknya telah menangguhkan SPPG dan mencopot kepala dapur yang melayani siswa keracunan di Semarang, Jawa Tengah, dan menginvestigasi penyebab kejadian tersebut. (Ryan Rahman/Andi Bagasela/Roy Rosa Bachtiar)</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5678493/bgn-naikkan-status-keracunan-mbg-jadi-kejadian-fatal</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BGN-NAIKKAN-STATUS-KERACUNAN-MBG-JADI-KEJADIAN-FATAL.jpg</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Basarnas jemput 66 korban KM Mutiara Sentosa II dari Masalembu</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
           <t>ANTARA - Badan Pencarian dan Pertolongan Nasional (Basarnas) mengerahkan satu unit kapal untuk menjemput 66 korban kebakaran KM Mutiara Sentosa II yang berada di Pulau Masalembu, Kabupaten Sumenep, Jawa Timur. Para korban selanjutnya akan dievakuasi menuju Pelabuhan Tanjung Perak Surabaya untuk mendapatkan penanganan lebih lanjut.
 (Hanif Nasrullah/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F304" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678472/basarnas-jemput-66-korban-km-mutiara-sentosa-ii-dari-masalembu</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G304" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BASARNAS-JEMPUT-66-KORBAN-KM-MUTIARA-SENTOSA-II-DARI-MASALEMBU.jpg</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>Presiden Prabowo terima kunjungan PM Thailand di Istana Merdeka</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr">
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menerima kunjungan resmi Perdana Menteri Thailand Anutin Charnvirakul di Istana Merdeka, Jakarta, Senin (3/8). Pertemuan membahas penguatan kerja sama bilateral dan berbagai isu strategis kedua negara. (Aria Cindyara/Irfansyah Naufal Nasution/Satrio Giri Marwanto/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F305" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678461/presiden-prabowo-terima-kunjungan-pm-thailand-di-istana-merdeka</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="G305" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PRESIDEN-PRABOWO-TERIMA-KUNJUNGAN-PM-THAILAND-DI-ISTANA-MERDEKA.jpg</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>Banjir kepung 15 titik di Kota Padang akibat cuaca ekstrem</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
         <is>
           <t>ANTARA - Hujan lebat disertai angin kencang memicu bencana di Kabupaten Agam, Kota Pariaman, dan Kota Padang, Sumatera Barat, Senin (3/8). Kota Padang menjadi wilayah terdampak paling parah dengan banjir di 15 titik. BPBD Sumatera Barat bersama lintas instansi melakukan penanganan darurat dan evakuasi warga. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F306" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678396/banjir-kepung-15-titik-di-kota-padang-akibat-cuaca-ekstrem</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G306" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BANJIR-KEPUNG-15-TITIK-DI-KOTA-PADANG-AKIBAT-CUACA-EKSTREM.jpg</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B307" t="inlineStr">
         <is>
           <t>Kongres PSSI sepakati pemilihan pengurus mundur ke Juli 2027</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
         <is>
           <t>ANTARA - Kongres Biasa PSSI 2026 menyepakati perubahan jadwal Kongres Pemilihan Pengurus PSSI 2027 dari semula Mei menjadi Juli 2027. Ketua Umum PSSI Erick Thohir mengatakan penyesuaian jadwal dilakukan untuk menyesuaikan pelaksanaan pemilihan Asosiasi Provinsi (Asprov) PSSI serta agenda kompetisi nasional.
 (Irfan Hardiansah/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="F307" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678395/kongres-pssi-sepakati-pemilihan-pengurus-mundur-ke-juli-2027</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="G307" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KONGRES-PSSI-SEPAKATI-PEMILIHAN-PENGURUS-MUNDUR-KE-JULI-2027.jpg</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B308" t="inlineStr">
         <is>
           <t>Cadangan devisa RI jadi 145 M dolar AS, BI sebut masih di level aman</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
         <is>
           <t>ANTARA - Bank Indonesia (BI) mengungkapkan cadangan devisa pada akhir Juli 2026 berada di posisi 145 miliar dolar AS. Meski menurun dari sebelumnya yang berjumlah 156 dolar AS, BI pun menyatakan posisi tersebut masih di level aman. (Setyanka Harviana Putri/Pradanna Putra Tampi/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F308" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678347/cadangan-devisa-ri-jadi-145-m-dolar-as-bi-sebut-masih-di-level-aman</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="G308" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_CADANGAN-DEVISA-RI-JADI-145-M-DOLAR-AS-BI-SEBUT-MASIH-DI-LEVEL-AMAN.jpg</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B309" t="inlineStr">
         <is>
           <t>Erick ungkap strategi sebelum kembali ke bursa calon Ketum PSSI 2027</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
         <is>
           <t>ANTARA - Ketua Umum Persatuan Sepak Bola Seluruh Indonesia (PSSI) Erick Thohir tidak menutup kemungkinan untuk kembali mencalonkan diri sebagai Ketua Umum PSSI pada pemilihan Ketua Umum PSSI yang berlangsung pada 2027 mendatang. Hal ini disampaikan Erick, usai acara Kongres Biasa PSSI 2026, yang berlangsung di Jakarta, pada Senin (3/8). (Irfan Hardiansah/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="F309" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678327/erick-ungkap-strategi-sebelum-kembali-ke-bursa-calon-ketum-pssi-2027</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G309" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/ERICK-UNGKAP-STRATEGI-SEBELUM-KEMBALI-KE-BURSA-CALON-KETUM-PSSI-2027.jpg</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>Industri kreatif tunjukkan tren positif, musik dan film mendominasi</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa pertumbuhan ekosistem industri kreatif menunjukkan tren positif. Menurutnya, pangsa pasar film Indonesia mencapai sekitar 67 persen, dan 80 persen masyarakat Indonesia lebih banyak mendengarkan musik karya musisi Tanah Air.
 (Cahya Sari/Ibnu Zaki/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F310" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678325/industri-kreatif-tunjukkan-tren-positif-musik-dan-film-mendominasi</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G310" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDUSTRI-KREATIF-TUNJUKKAN-TREN-POSITIF-MUSIK-DAN-FILM-MENDOMINASI.jpg</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B311" t="inlineStr">
         <is>
           <t>Pemprov NTB benahi tarif hingga infrastruktur Mandalika jelang MotoGP</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
         <is>
           <t>ANTARA - Pemerintah Provinsi Nusa Tenggara Barat benahi sejumlah aspek yang menjadi sorotan pada ajang MotoGP seri Indonesia di Sirkuit Mandalika pada 9 - 11 Oktober mendatang. Mulai dari persoalan tarif akomodasi hingga transportasi, serta perbaikan infrastruktur yang akan menunjang kenyamanan wisatawan penonton, dengan target 140 ribu orang. (Kusnandar/Chairul Fajri/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="F311" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678319/pemprov-ntb-benahi-tarif-hingga-infrastruktur-mandalika-jelang-motogp</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="G311" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PEMPROV-NTB-BENAHI-TARIF-HINGGA-INFRASTRUKTUR-MANDALIKA-JELANG-MOTOGP.jpg</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>Purbaya: Stabilitas sistem keuangan Indonesia tetap terjaga</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr">
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
         <is>
           <t>ANTARA - Komite Stabilitas Sistem Keuangan (KSSK) memastikan stabilitas sistem keuangan Indonesia tetap terjaga pada triwulan II 2026 meski dihadapkan pada meningkatnya risiko global akibat eskalasi konflik geopolitik dan gejolak pasar keuangan internasional.
 (Setyanka Harviana Putri/Pradanna Putra Tampi/Chairul Fajri/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F312" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678257/purbaya-stabilitas-sistem-keuangan-indonesia-tetap-terjaga</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G312" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PURBAYA-STABILITAS-SISTEM-KEUANGAN-INDONESIA-TETAP-TERJAGA.jpg</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B313" t="inlineStr">
         <is>
           <t>Indonesia punya 2.723 warisan budaya, Menbud: jaga untuk wisata budaya</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr">
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Kebudayaan, Fadli Zon, Senin (3/8), menekankan pengembangan wisata budaya di setiap daerah bahkan hingga ke tingkat desa maupun kelurahan. Indonesia memiliki 2.723 warisan budaya tak benda yang tercatat secara nasional, 16 di antaranya telah diakui oleh UNESCO. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F313" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678243/indonesia-punya-2723-warisan-budaya-menbud-jaga-untuk-wisata-budaya</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G313" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INDONESIA-PUNYA-2.723-WARISAN-BUDAYA-MENBUD-JAGA-UNTUK-WISATA-BUDAYA.jpg</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>Trump umumkan negosiasi dengan Iran dimulai pada Senin</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr">
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Amerika Serkat Donald Trump pada hari Minggu (2/8) mengatakan bahwa negosiasi dengan Iran akan dimulai Senin sore. Trump menyebut Arab Saudi, Uni Emirat Arab (UEA) dan Qatar telah meminta Amerika Serikat untuk membatalkan serangan yang direncanakan. (XINHUA/Winanto/Chairul Fajri/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F314" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678223/trump-umumkan-negosiasi-dengan-iran-dimulai-pada-senin</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G314" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/TRUMP-UMUMKAN-NEGOSIASI-DENGAN-IRAN-DIMULAI-PADA-SENIN.jpg</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>Polda Banten apel siaga waspada bencana dan karhutla di musim kemarau</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr">
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
         <is>
           <t>ANTARA - Polda Banten bersama sejumlah instansi terkait, Senin (3/8), menggelar apel gabungan dalam rangka kesiapsiagaan tanggap darurat bencana dan kebakaran hutan dan lahan (karhutla) di Lapangan Apel Polda Banten, Serang. Apel ini menjadi langkah memperkuat sinergi lintas instansi dalam mengantisipasi potensi bencana dan karhutla selama masa kemarau. (Susmiatun Hayati/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="F315" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678213/polda-banten-apel-siaga-waspada-bencana-dan-karhutla-di-musim-kemarau</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G315" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_POLDA-BANTEN-APEL-SIAGA-WASPADA-BENCANA-DAN-KARHUTLA-DI-MUSIM-KEMARAU.jpg</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>OJK catat penyaluran kredit perbankan capai Rp9.080,9 triliun</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr">
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
         <is>
           <t>ANTARA - Otoritas Jasa Keuangan (OJK) mengungkapkan pertumbuhan kredit perbankan pada Juni 2026 tumbuh hingga 12,67% year-on-year (yoy). Di Jakarta, Senin (3/8), OJK pun memaparkan faktor yang mendukung pertumbuhan tersebut. (Setyanka Harviana Putri/Pradanna Putra Tampi/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F316" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678208/ojk-catat-penyaluran-kredit-perbankan-capai-rp90809-triliun</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G316" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_15_15_01.Still474.jpg</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>Lawan stunting dan isu iklim lewat program Cadiak Pandai</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
         <is>
           <t>ANTARA - Pertamina Patra Niaga bersama Perkumpulan Keluarga Berencana Indonesia (PKBI) Sumatera Barat meluncurkan program "Cadiak Pandai Goes to School" di Kabupaten Padang Pariaman, Senin (3/8). Program ini membekali pelajar dengan edukasi gizi, kesehatan reproduksi, dan kepedulian lingkungan sebagai upaya mendukung percepatan penurunan stunting. (Fandi Yogari Saputra/Andi Bagasela/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F317" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678187/lawan-stunting-dan-isu-iklim-lewat-program-cadiak-pandai</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G317" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_LAWAN-STUNTING-DAN-ISU-IKLIM-LEWAT-PROGRAM-CADIAK-PANDAI.jpg</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>Ketum PSSI utarakan pesan Presiden agar timnas tampil di Piala Dunia</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
         <is>
           <t>ANTARA - Presiden Prabowo Subianto menyampaikan, Tim Nasional (Timnas) Indonesia sangat dekat untuk bisa tampil di Pialaa Dunia 2026, jika tidak gugur pada babak kualifikasi putaran keempat di Arab Saudi, pada Oktober tahun lalu. Hal ini disampaikan Prabowo dalam pidatonya, pada pembukaan Kongres Biasa PSSI 2026, di Jakarta, pada Senin (3/8), yang dibacakan Ketua Umum PSSI sekaligus Menteri Pemuda dan Olahraga (Menpora) Erick Thohir. (Irfan Hardiansah/Soni Namura/Roy Rosa Bachtiar)</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F318" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678179/ketum-pssi-utarakan-pesan-presiden-agar-timnas-tampil-di-piala-dunia</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G318" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/KETUM-PSSI-UTARAKAN-PESAN-PRESIDEN-AGAR-TIMNAS-TAMPIL-DI-PIALA-DUNIA.jpg</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>PMI dan Pemkot Semarang salurkan air bersih ke Jabungan</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr">
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
         <is>
           <t>ANTARA - Palang Merah Indonesia (PMI) Kota Semarang bersama Pemerintah Kota Semarang menyalurkan bantuan air bersih bagi warga Kelurahan Jabungan, Kecamatan Banyumanik, Senin (3/8). Bantuan diberikan untuk memenuhi kebutuhan warga yang terdampak krisis air bersih akibat musim kemarau. (Fx. Suryo Wicaksono/Chairul Fajri/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F319" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678175/pmi-dan-pemkot-semarang-salurkan-air-bersih-ke-jabungan</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G319" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PMI-DAN-PEMKOT-SEMARANG-SALURKAN-AIR-BERSIH-KE-JABUNGAN.jpg</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>Pendaki Nirmal Purja dan tim tewas di longsoran salju di Broad Peak</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr">
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
         <is>
           <t>ANTARA - Pendaki gunung, Nirmal Purja, meninggal saat mendaki salah satu gunung tertinggi ke-12 di dunia Broad Peak di Pakistan utara, Kamis (30/7). Dilansir dari AFP, tim penyelamat menemukan jenazah Nirmal Purja, pada Minggu (2/8), setelah longsoran salju menewaskannya bersama sembilan anggota timnya. (AFP/Ludmila Yusufin Diah Nastiti/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F320" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678112/pendaki-nirmal-purja-dan-tim-tewas-di-longsoran-salju-di-broad-peak</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G320" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/PENDAKI-NIRMAL-PURJA-DAN-TIM-TEWAS-DI-LONGSORAN-SALJU-DI-BROAD-PEAK.jpg</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>Menbud buka pembinaan Gita Bahana Nusantara 2026</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
         <is>
           <t>ANTARA - Sebanyak 183 peserta Gita Bahana Nusantara (GBN) mulai menjalani pembinaan intensif dalam rangka menyemarakkan HUT ke-81 RI di Istana Merdeka, Jakarta. Menteri Kebudayaan Fadli Zon, Senin (3/8), menyebut bahwa GBN bukan sekadar kemampuan vokal dan musik, melainkan wujud persatuan Indonesia yang beragam. (Cahya Sari/Ibnu Zaki/Andi Bagasela/Rijalul Vikry)</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F321" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678104/menbud-buka-pembinaan-gita-bahana-nusantara-2026</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G321" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENBUD-BUKA-PEMBINAAN-GITA-BAHANA-NUSANTARA-2026.jpg</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>Capai 78 persen, Sensus Ekonomi NTB 2026 dominan pada sektor pertanian</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr">
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) mencatat progres pendataan Sensus Ekonomi (SE) tahun 2026 di Provinsi Nusa Tenggara Barat mencapai 78 persen. Dengan capaian tertinggi diperoleh dari Kabupaten Dompu pada progres 92 persen, dan terendah dari Kota Mataram dengan progres 67 persen. (Kusnandar/Chairul Fajri/Winanto)</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F322" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678087/capai-78-persen-sensus-ekonomi-ntb-2026-dominan-pada-sektor-pertanian</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="G322" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/CAPAI-78-PERSEN-SENSUS-EKONOMI-NTB-2026-DOMINAN-PADA-SEKTOR-PERTANIAN.jpg</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>Kodaeral IV gagalkan penyelundupan timah 1.6 ton senilai Rp1,3 miliar</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr">
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
         <is>
           <t>ANTARA - Komando Daerah Angkatan Laut (Kodaeral) IV menggagalkan upaya penyelundupan pasir timah sebanyak 42 karung seberat 1,6 ton, yang akan diselundupkan ke Malaysia dari wilayah Pekajang, Kabupaten Lingga, Kepulauan Riau. Dari penindakan itu nilai ekonomis yang berhasil diamankan ditaksir mencapai Rp 1,3 M, dan satu orang diamankan bersama barang bukti berupa satu senapan angin predator air gun, satu pistol airsoft gun jenis magnum jericho 941, dua ponsel serta satu buah KTP. (Angiela Chantiequ/Arif Prada/Winanto)</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
+      <c r="F323" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678084/kodaeral-iv-gagalkan-penyelundupan-timah-16-ton-senilai-rp13-miliar</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G323" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/Sequence-13.13_16_51_23.Still474.jpg</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B324" t="inlineStr">
         <is>
           <t>BPIP: Pelatihan Paskibraka bentuk calon pemimpin berkarakter Pancasila</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pembinaan Ideologi Pancasila (BPIP) menyatakan pemusatan pelatihan Pasukan Pengibar Bendera Pusaka (Paskibraka) nasional tidak hanya menjadi persiapan pengibaran bendera pada HUT ke-81 Kemerdekaan RI, tetapi juga bagian dari pembentukan calon pemimpin bangsa yang berkarakter Pancasila. Sebanyak 76 peserta dari 38 provinsi saat ini menjalani pelatihan di Depok, Jawa Barat. (Cahya Sari/Ibnu Zaki/Soni Namura/Arsy Fitriady)</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="F324" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678076/bpip-pelatihan-paskibraka-bentuk-calon-pemimpin-berkarakter-pancasila</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G324" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/BPIP-PELATIHAN-PASKIBRAKA-BENTUK-CALON-PEMIMPIN-BERKARAKTER-PANCASILA_1.jpg</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t>BPS Bali catat peningkatan hunian hotel berbintang selama Juni 2026</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Bali mencatat tingkat penghunian kamar (TPK) hotel berbintang meningkat hingga 3,71 persen dibanding periode bulan Mei 2026. Sementara untuk meningkatkan kunjungan wisatawan mancanegara, Dinas Pariwisata Provinsi Bali mempromosikan wisata kesehatan atau wellness tourism. 
 (Rita Laura/Andi Bagasela/I Gusti Agung Ayu N)</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F325" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678064/bps-bali-catat-peningkatan-hunian-hotel-berbintang-selama-juni-2026</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G325" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_BPS-BALI-CATAT-PENINGKATAN-HUNIAN-HOTEL-BERBINTANG-SELAMA-JUNI-2026.jpg</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>Program Taruna Bakti Kepolisian latih siswa Sekolah Rakyat Lhokseumawe</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr">
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
         <is>
           <t>ANTARA - Ratusan siswa dari Sekolah Rakyat Lhokseumawe, Aceh, memperoleh edukasi kemandirian oleh Taruna Akademi Kepolisian untuk mengubah prilaku, Senin (3/8). Kegiatan ini merupakan salah satu dari program Taruna Bakti, yang diinstruksikan langsung oleh Presiden RI Prabowo Subianto ke seluruh Sekolah Rakyat di Indonesia. (Try Vanny S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F326" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5678013/program-taruna-bakti-kepolisian-latih-siswa-sekolah-rakyat-lhokseumawe</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G326" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_PROGRAM-TARUNA-BAKTI-KEPOLISIAN-LATIH-SISWA-SEKOLAH-RAKYAT-LHOKSEUMAWE.jpg</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>Menkomdigi minta masyarakat waspadai lonjakan hoaks jelang HUT RI</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
         <is>
           <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengingatkan masyarakat untuk mewaspadai meningkatnya penyebaran hoaks menjelang peringatan Hari Ulang Tahun (HUT) ke-81 Republik Indonesia. Saat ditemui di Jakarta pada Senin (3/8), Menkomdigi  juga menegaskan tidak pernah melarang media melakukan peliputan, selama sesuai kaidah jurnalistik dan Undang-Undang Pers.(Sanya Dinda Susanti/Andi Bagasela/Ludmila Yusufin Diah Nastiti)</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F327" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677959/menkomdigi-minta-masyarakat-waspadai-lonjakan-hoaks-jelang-hut-ri</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G327" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_MENKOMDIGI-MINTA-MASYARAKAT-WASPADAI-LONJAKAN-HOAKS-JELANG-HUT-RI.jpg</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>Inflasi di Sumut sebesar 4,20 persen, emas menjadi penyumbang utama</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr">
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 17:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
         <is>
           <t>ANTARA - Badan Pusat Statistik (BPS) Provinsi Sumatera Utara mencatat pada Juli 2026 Sumatera Utara mengalami inflasi 4,20 persen. Komoditas penyumbang inflasi pada bulan Juli 2026 yakni, emas perhiasan, cabai merah, cabai rawit, tomat dan bensin. (M. Valery Maulidzar S/Andi Bagasela/Winanto)</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F328" t="inlineStr">
         <is>
           <t>https://www.antaranews.com/berita/5677867/inflasi-di-sumut-sebesar-420-persenemas-menjadi-penyumbang-utama</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G328" t="inlineStr">
         <is>
           <t>https://img.antaranews.com/video/preview/2026/08/small/AB_INFLASI-DI-SUMUT-SEBESAR-4-20-PERSEN-EMAS-MENJADI-PENYUMBANG-UTAMA.jpg</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Komdigi tegur YouTube soal pelibatan anak dalam promosi rokok elektrik</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>ANTARA - Menteri Komunikasi dan Digital Meutya Hafid mengatakan telah melayangkan surat teguran pertama kepada YouTube yang memuat konten siaran langsung atau live streaming seorang pemengaruh yang menampilkan promosi produk rokok elektrik atau vape dengan melibatkan anak-anak. Menteri Komdigi Meutya Hafid, di Jakarta, Senin (3/8), mengatakan dalam tiga hari ke depan Komdigi juga akan memanggil pihak YouTube untuk meminta keterangan. (Sanya Dinda Susanti/Andi Bagasela/Rijalul Vikry)</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677812/komdigi-tegur-youtube-soal-pelibatan-anak-dalam-promosi-rokok-elektrik</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>https://img.antaranews.com/video/preview/2026/08/small/AB_KOMDIGI-TEGUR-YOUTUBE-SOAL-PELIBATAN-ANAK-DALAM-PROMOSI-ROKOK-ELEKTRIK.jpg</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>antara</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Pemkab Temanggung gandeng kemitraan kacang panjang dengan perusahaan</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Tue, 04 Aug 2026 14:25:01 +0700</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>ANTARA - Dinas Penanaman Modal dan Pelayanan Terpadu Satu Pintu (DPMPTSP) Kabupaten Temanggung, Jawa Tengah, menjajaki peluang kemitraan budidaya kacang panjang dengan pihak perusahaan. Langkah ini dilakukan sebagai upaya memperluas akses pasar, sekaligus meningkatkan kesejahteraan petani melalui kepastian harga dan penyerapan hasil panen. (Firman Eko Handy/Andi Bagasela/Winanto)</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>https://www.antaranews.com/berita/5677779/pemkab-temanggung-gandeng-kemitraan-kacang-panjang-dengan-perusahaan</t>
-        </is>
-      </c>
-    